--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-12 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-13 06:54</t>
         </is>
       </c>
     </row>
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-12) 상위: 반도체  점수 56.0점</t>
+          <t>⚡ 최신(2026-09-13) 상위: 반도체  점수 48.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-12) 상위: 삼성전자  점수 24.0점</t>
+          <t>⚡ 최신(2026-09-13) 상위: 인공지능  점수 18.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-12) 상위: 바이오  점수 21.0점</t>
+          <t>⚡ 최신(2026-09-13) 상위: 삼성전자  점수 15.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -967,14 +967,14 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -982,15 +982,15 @@
       <c r="G15" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="18" t="n">
-        <v>-3.53</v>
-      </c>
-      <c r="I15" s="19" t="n">
-        <v>1.57</v>
+      <c r="H15" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v/>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1025,27 +1025,25 @@
       <c r="G16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="15" t="n">
+      <c r="H16" s="18" t="n">
+        <v>-3.53</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J16" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="n">
         <v/>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,14 +1051,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1068,25 +1066,27 @@
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <v>3.43</v>
+      <c r="H17" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v/>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="n">
-        <v/>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K17" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1109,27 +1109,25 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="15" t="n">
+      <c r="H18" s="19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="J18" s="17" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="n">
         <v/>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J18" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1137,14 +1135,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1152,27 +1150,25 @@
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="15" t="n">
+      <c r="H19" s="18" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="J19" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K19" s="17" t="n">
         <v/>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J19" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1180,14 +1176,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1195,25 +1191,27 @@
       <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v/>
+      <c r="H20" s="19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>14</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="n">
-        <v/>
+          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1221,7 +1219,7 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
@@ -1244,17 +1242,19 @@
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K21" s="17" t="n">
-        <v/>
+          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K21" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B22" s="20" t="n">
@@ -1285,19 +1285,19 @@
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +782% / 중요공시 6건</t>
+          <t>네이버 검색 당일 +1153% / 중요공시 6건</t>
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B23" s="20" t="n">
@@ -1305,42 +1305,40 @@
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D23" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E23" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F23" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="22" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="I23" s="22" t="n">
-        <v>18.04</v>
+      <c r="H23" s="24" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="I23" s="24" t="n">
+        <v>-4.14</v>
       </c>
       <c r="J23" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K23" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K23" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B24" s="20" t="n">
@@ -1348,7 +1346,7 @@
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D24" s="20" t="n">
@@ -1364,14 +1362,14 @@
         <v>0</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>-2.03</v>
-      </c>
-      <c r="I24" s="24" t="n">
-        <v>-4.14</v>
+        <v>-5.34</v>
+      </c>
+      <c r="I24" s="22" t="n">
+        <v>6.45</v>
       </c>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K24" s="23" t="n">
@@ -1381,7 +1379,7 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B25" s="20" t="n">
@@ -1389,40 +1387,42 @@
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="D25" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E25" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F25" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>-5.34</v>
+        <v>-3.61</v>
       </c>
       <c r="I25" s="22" t="n">
-        <v>6.45</v>
+        <v>7.65</v>
       </c>
       <c r="J25" s="23" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K25" s="23" t="n">
-        <v/>
+          <t>중요공시 5건 / 중요공시 7일 +400%</t>
+        </is>
+      </c>
+      <c r="K25" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B26" s="20" t="n">
@@ -1430,30 +1430,30 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>루멘스</t>
         </is>
       </c>
       <c r="D26" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E26" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F26" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" s="24" t="n">
-        <v>-3.61</v>
-      </c>
-      <c r="I26" s="22" t="n">
-        <v>7.65</v>
+        <v>0</v>
+      </c>
+      <c r="H26" s="22" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I26" s="24" t="n">
+        <v>-5.58</v>
       </c>
       <c r="J26" s="23" t="inlineStr">
         <is>
-          <t>중요공시 5건 / 중요공시 7일 +400%</t>
+          <t>중요공시 5건 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K26" s="23" t="inlineStr">
@@ -1465,7 +1465,7 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B27" s="20" t="n">
@@ -1473,30 +1473,30 @@
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>루멘스</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="D27" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E27" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F27" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="22" t="n">
-        <v>0.39</v>
+        <v>3</v>
+      </c>
+      <c r="H27" s="24" t="n">
+        <v>-11.52</v>
       </c>
       <c r="I27" s="24" t="n">
-        <v>-5.58</v>
+        <v>-7.67</v>
       </c>
       <c r="J27" s="23" t="inlineStr">
         <is>
-          <t>중요공시 5건 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 3건 / 중요공시 7일 +50%</t>
         </is>
       </c>
       <c r="K27" s="23" t="inlineStr">
@@ -1508,7 +1508,7 @@
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B28" s="20" t="n">
@@ -1516,42 +1516,40 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="D28" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E28" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F28" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H28" s="24" t="n">
-        <v>-11.52</v>
-      </c>
-      <c r="I28" s="24" t="n">
-        <v>-7.67</v>
+        <v>0</v>
+      </c>
+      <c r="H28" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I28" s="20" t="n">
+        <v/>
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 7일 +50%</t>
-        </is>
-      </c>
-      <c r="K28" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B29" s="20" t="n">
@@ -1559,7 +1557,7 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>비에이치</t>
         </is>
       </c>
       <c r="D29" s="20" t="n">
@@ -1575,24 +1573,26 @@
         <v>0</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>-4.66</v>
+        <v>-1.25</v>
       </c>
       <c r="I29" s="24" t="n">
-        <v>-7.1</v>
+        <v>-12.95</v>
       </c>
       <c r="J29" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K29" s="23" t="n">
-        <v/>
+          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K29" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
@@ -1615,27 +1615,27 @@
       <c r="G30" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="24" t="n">
-        <v>-2.21</v>
+      <c r="H30" s="22" t="n">
+        <v>0.71</v>
       </c>
       <c r="I30" s="22" t="n">
-        <v>10.02</v>
+        <v>18.04</v>
       </c>
       <c r="J30" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>중요공시 2건 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K30" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1643,14 +1643,14 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>코스나인</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F31" s="20" t="n">
         <v>0</v>
@@ -1658,27 +1658,25 @@
       <c r="G31" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="24" t="n">
-        <v>-23.08</v>
-      </c>
-      <c r="I31" s="24" t="n">
-        <v>-97.92</v>
+      <c r="H31" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I31" s="20" t="n">
+        <v/>
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +750% / 중요공시 2건</t>
-        </is>
-      </c>
-      <c r="K31" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K31" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1686,7 +1684,7 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>코다코</t>
+          <t>코스나인</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
@@ -1701,27 +1699,27 @@
       <c r="G32" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="22" t="n">
-        <v>10.24</v>
+      <c r="H32" s="24" t="n">
+        <v>-23.08</v>
       </c>
       <c r="I32" s="24" t="n">
-        <v>-99.45</v>
+        <v>-97.92</v>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +646% / 중요공시 2건</t>
+          <t>네이버 검색 당일 +1174% / 중요공시 2건</t>
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1729,7 +1727,7 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>헝셩그룹</t>
+          <t>코다코</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
@@ -1745,26 +1743,26 @@
         <v>0</v>
       </c>
       <c r="H33" s="22" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="I33" s="22" t="n">
-        <v>5.94</v>
+        <v>10.24</v>
+      </c>
+      <c r="I33" s="24" t="n">
+        <v>-99.45</v>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +994% / 중요공시 2건</t>
         </is>
       </c>
       <c r="K33" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1772,42 +1770,42 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="I34" s="24" t="n">
-        <v>-5.26</v>
+        <v>-3.22</v>
+      </c>
+      <c r="I34" s="22" t="n">
+        <v>8.83</v>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+          <t>네이버 검색 당일 +122% / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K34" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1815,7 +1813,7 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>샘표</t>
+          <t>수성웹툰</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
@@ -1830,27 +1828,27 @@
       <c r="G35" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="22" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="I35" s="22" t="n">
-        <v>33.72</v>
+      <c r="H35" s="24" t="n">
+        <v>-25.47</v>
+      </c>
+      <c r="I35" s="24" t="n">
+        <v>-49.62</v>
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +121% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K35" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1858,7 +1856,7 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>아티스트스튜디오</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
@@ -1874,26 +1872,24 @@
         <v>0</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>-13.9</v>
-      </c>
-      <c r="I36" s="24" t="n">
-        <v>-8.789999999999999</v>
+        <v>-1.21</v>
+      </c>
+      <c r="I36" s="22" t="n">
+        <v>8.93</v>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1901,7 +1897,7 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
@@ -1917,10 +1913,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="22" t="n">
-        <v>2.24</v>
+        <v>1.19</v>
       </c>
       <c r="I37" s="22" t="n">
-        <v>14</v>
+        <v>11.23</v>
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
@@ -1936,7 +1932,7 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1944,7 +1940,7 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>바이오비쥬</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
@@ -1959,27 +1955,27 @@
       <c r="G38" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="22" t="n">
-        <v>7.28</v>
+      <c r="H38" s="24" t="n">
+        <v>-4</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>5.46</v>
+        <v>8.76</v>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K38" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1987,7 +1983,7 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>넥써쓰</t>
+          <t>헝셩그룹</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
@@ -2003,10 +1999,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>2.08</v>
+        <v>14.63</v>
       </c>
       <c r="I39" s="22" t="n">
-        <v>5.99</v>
+        <v>5.94</v>
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
@@ -2022,7 +2018,7 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2030,40 +2026,42 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F40" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="22" t="n">
-        <v>6.24</v>
+        <v>3</v>
+      </c>
+      <c r="H40" s="24" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="I40" s="24" t="n">
+        <v>-8.58</v>
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K40" s="23" t="n">
-        <v/>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2071,384 +2069,378 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H41" s="24" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="I41" s="24" t="n">
+        <v>-5.26</v>
+      </c>
+      <c r="J41" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K41" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>샘표</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="22" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="I42" s="22" t="n">
+        <v>33.72</v>
+      </c>
+      <c r="J42" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K42" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>아티스트스튜디오</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="24" t="n">
+        <v>-13.9</v>
+      </c>
+      <c r="I43" s="24" t="n">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="J43" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K43" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="n">
+        <v>31</v>
+      </c>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>바이오비쥬</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="22" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="I44" s="22" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="J44" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K44" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>넥써쓰</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I45" s="22" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="J45" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K45" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>로봇</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I46" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J46" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K46" s="23" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>로보티즈</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="22" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="J47" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K47" s="23" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="C48" s="21" t="inlineStr">
+        <is>
           <t>전기차</t>
         </is>
       </c>
-      <c r="D41" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="20" t="n">
+      <c r="D48" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="20" t="n">
         <v/>
       </c>
-      <c r="I41" s="20" t="n">
+      <c r="I48" s="20" t="n">
         <v/>
       </c>
-      <c r="J41" s="23" t="inlineStr">
+      <c r="J48" s="23" t="inlineStr">
         <is>
           <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
-      <c r="K41" s="23" t="n">
+      <c r="K48" s="23" t="n">
         <v/>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B42" s="25" t="n">
-        <v>29</v>
-      </c>
-      <c r="C42" s="26" t="inlineStr">
-        <is>
-          <t>삼미금속</t>
-        </is>
-      </c>
-      <c r="D42" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E42" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F42" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="27" t="n">
-        <v>-2.69</v>
-      </c>
-      <c r="I42" s="28" t="n">
-        <v>47.19</v>
-      </c>
-      <c r="J42" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +888%</t>
-        </is>
-      </c>
-      <c r="K42" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B43" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="C43" s="26" t="inlineStr">
-        <is>
-          <t>액스비스</t>
-        </is>
-      </c>
-      <c r="D43" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E43" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F43" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="28" t="n">
-        <v>11.97</v>
-      </c>
-      <c r="I43" s="28" t="n">
-        <v>57.45</v>
-      </c>
-      <c r="J43" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +449%</t>
-        </is>
-      </c>
-      <c r="K43" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B44" s="25" t="n">
-        <v>31</v>
-      </c>
-      <c r="C44" s="26" t="inlineStr">
-        <is>
-          <t>카프로</t>
-        </is>
-      </c>
-      <c r="D44" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E44" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F44" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="27" t="n">
-        <v>-16.67</v>
-      </c>
-      <c r="I44" s="27" t="n">
-        <v>-96.72</v>
-      </c>
-      <c r="J44" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +404%</t>
-        </is>
-      </c>
-      <c r="K44" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B45" s="25" t="n">
-        <v>32</v>
-      </c>
-      <c r="C45" s="26" t="inlineStr">
-        <is>
-          <t>엔에이치스팩34호</t>
-        </is>
-      </c>
-      <c r="D45" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E45" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="27" t="n">
-        <v>-6.94</v>
-      </c>
-      <c r="I45" s="27" t="n">
-        <v>-6.94</v>
-      </c>
-      <c r="J45" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +398%</t>
-        </is>
-      </c>
-      <c r="K45" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B46" s="25" t="n">
-        <v>33</v>
-      </c>
-      <c r="C46" s="26" t="inlineStr">
-        <is>
-          <t>샘표식품</t>
-        </is>
-      </c>
-      <c r="D46" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="27" t="n">
-        <v>-14.76</v>
-      </c>
-      <c r="I46" s="28" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="J46" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +342%</t>
-        </is>
-      </c>
-      <c r="K46" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B47" s="25" t="n">
-        <v>34</v>
-      </c>
-      <c r="C47" s="26" t="inlineStr">
-        <is>
-          <t>서전기전</t>
-        </is>
-      </c>
-      <c r="D47" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E47" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F47" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="27" t="n">
-        <v>-3.51</v>
-      </c>
-      <c r="I47" s="28" t="n">
-        <v>24.43</v>
-      </c>
-      <c r="J47" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +330%</t>
-        </is>
-      </c>
-      <c r="K47" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B48" s="25" t="n">
-        <v>35</v>
-      </c>
-      <c r="C48" s="26" t="inlineStr">
-        <is>
-          <t>머큐리</t>
-        </is>
-      </c>
-      <c r="D48" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F48" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="27" t="n">
-        <v>-4.43</v>
-      </c>
-      <c r="I48" s="28" t="n">
-        <v>39.71</v>
-      </c>
-      <c r="J48" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +279%</t>
-        </is>
-      </c>
-      <c r="K48" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B49" s="25" t="n">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="n">
         <v>36</v>
       </c>
-      <c r="C49" s="26" t="inlineStr">
-        <is>
-          <t>오르비텍</t>
-        </is>
-      </c>
-      <c r="D49" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E49" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F49" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="27" t="n">
-        <v>-3.34</v>
-      </c>
-      <c r="I49" s="28" t="n">
-        <v>40.35</v>
-      </c>
-      <c r="J49" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +243%</t>
-        </is>
-      </c>
-      <c r="K49" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="C49" s="21" t="inlineStr">
+        <is>
+          <t>혜인</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I49" s="24" t="n">
+        <v>-11.27</v>
+      </c>
+      <c r="J49" s="23" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K49" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2456,7 +2448,7 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>한빛레이저</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -2471,15 +2463,15 @@
       <c r="G50" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="28" t="n">
-        <v>2.83</v>
+      <c r="H50" s="27" t="n">
+        <v>-2.69</v>
       </c>
       <c r="I50" s="28" t="n">
-        <v>36.01</v>
+        <v>47.19</v>
       </c>
       <c r="J50" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +216%</t>
+          <t>네이버 검색 당일 +1054%</t>
         </is>
       </c>
       <c r="K50" s="29" t="inlineStr">
@@ -2491,7 +2483,7 @@
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2499,7 +2491,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>액스비스</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2514,15 +2506,15 @@
       <c r="G51" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="27" t="n">
-        <v>-1.4</v>
+      <c r="H51" s="28" t="n">
+        <v>11.97</v>
       </c>
       <c r="I51" s="28" t="n">
-        <v>42.54</v>
+        <v>57.45</v>
       </c>
       <c r="J51" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +157%</t>
+          <t>네이버 검색 당일 +735%</t>
         </is>
       </c>
       <c r="K51" s="29" t="inlineStr">
@@ -2534,7 +2526,7 @@
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2542,7 +2534,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>에스투더블유</t>
+          <t>샘표식품</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2557,15 +2549,15 @@
       <c r="G52" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="28" t="n">
-        <v>26.38</v>
+      <c r="H52" s="27" t="n">
+        <v>-14.76</v>
       </c>
       <c r="I52" s="28" t="n">
-        <v>52.78</v>
+        <v>10.78</v>
       </c>
       <c r="J52" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +143%</t>
+          <t>네이버 검색 당일 +663%</t>
         </is>
       </c>
       <c r="K52" s="29" t="inlineStr">
@@ -2577,7 +2569,7 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2585,7 +2577,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>스트라드비젼</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2601,14 +2593,14 @@
         <v>0</v>
       </c>
       <c r="H53" s="27" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="I53" s="28" t="n">
-        <v>35.05</v>
+        <v>-6.94</v>
+      </c>
+      <c r="I53" s="27" t="n">
+        <v>-6.94</v>
       </c>
       <c r="J53" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +111%</t>
+          <t>네이버 검색 당일 +486%</t>
         </is>
       </c>
       <c r="K53" s="29" t="inlineStr">
@@ -2620,7 +2612,7 @@
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2628,7 +2620,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>카프로</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2644,26 +2636,26 @@
         <v>0</v>
       </c>
       <c r="H54" s="27" t="n">
-        <v>-1.47</v>
+        <v>-16.67</v>
       </c>
       <c r="I54" s="27" t="n">
-        <v>-68.62</v>
+        <v>-96.72</v>
       </c>
       <c r="J54" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +74% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +470%</t>
         </is>
       </c>
       <c r="K54" s="29" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2671,7 +2663,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>수성웹툰</t>
+          <t>에스투더블유</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2686,27 +2678,27 @@
       <c r="G55" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="27" t="n">
-        <v>-25.47</v>
-      </c>
-      <c r="I55" s="27" t="n">
-        <v>-49.62</v>
+      <c r="H55" s="28" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="I55" s="28" t="n">
+        <v>52.78</v>
       </c>
       <c r="J55" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +68% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +403%</t>
         </is>
       </c>
       <c r="K55" s="29" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2714,7 +2706,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>서전기전</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2729,15 +2721,15 @@
       <c r="G56" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="28" t="n">
-        <v>29.94</v>
+      <c r="H56" s="27" t="n">
+        <v>-3.51</v>
       </c>
       <c r="I56" s="28" t="n">
-        <v>40.51</v>
+        <v>24.43</v>
       </c>
       <c r="J56" s="29" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급</t>
+          <t>네이버 검색 당일 +398%</t>
         </is>
       </c>
       <c r="K56" s="29" t="inlineStr">
@@ -2749,7 +2741,7 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2757,7 +2749,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>머큐리</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2772,25 +2764,27 @@
       <c r="G57" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="28" t="n">
-        <v>1</v>
+      <c r="H57" s="27" t="n">
+        <v>-4.43</v>
       </c>
       <c r="I57" s="28" t="n">
-        <v>14.65</v>
+        <v>39.71</v>
       </c>
       <c r="J57" s="29" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K57" s="29" t="n">
-        <v/>
+          <t>네이버 검색 당일 +359%</t>
+        </is>
+      </c>
+      <c r="K57" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2798,7 +2792,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>오르비텍</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2813,27 +2807,27 @@
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="28" t="n">
-        <v>1.19</v>
+      <c r="H58" s="27" t="n">
+        <v>-3.34</v>
       </c>
       <c r="I58" s="28" t="n">
-        <v>11.23</v>
+        <v>40.35</v>
       </c>
       <c r="J58" s="29" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +296%</t>
         </is>
       </c>
       <c r="K58" s="29" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2841,7 +2835,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>한빛레이저</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2856,25 +2850,27 @@
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="27" t="n">
-        <v>-1.21</v>
+      <c r="H59" s="28" t="n">
+        <v>2.83</v>
       </c>
       <c r="I59" s="28" t="n">
-        <v>8.93</v>
+        <v>36.01</v>
       </c>
       <c r="J59" s="29" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K59" s="29" t="n">
-        <v/>
+          <t>네이버 검색 당일 +273%</t>
+        </is>
+      </c>
+      <c r="K59" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2882,7 +2878,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2898,24 +2894,26 @@
         <v>0</v>
       </c>
       <c r="H60" s="27" t="n">
-        <v>-4.78</v>
+        <v>-1.4</v>
       </c>
       <c r="I60" s="28" t="n">
-        <v>0.89</v>
+        <v>42.54</v>
       </c>
       <c r="J60" s="29" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K60" s="29" t="n">
-        <v/>
+          <t>네이버 검색 당일 +204%</t>
+        </is>
+      </c>
+      <c r="K60" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2923,7 +2921,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>엠젠솔루션</t>
+          <t>원익피앤이</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2938,27 +2936,27 @@
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="27" t="n">
-        <v>-8.75</v>
+      <c r="H61" s="28" t="n">
+        <v>6.62</v>
       </c>
       <c r="I61" s="28" t="n">
-        <v>15.63</v>
+        <v>41</v>
       </c>
       <c r="J61" s="29" t="inlineStr">
         <is>
-          <t>중요공시 5건</t>
+          <t>네이버 검색 당일 +200%</t>
         </is>
       </c>
       <c r="K61" s="29" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2966,7 +2964,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>모아데이타</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2981,27 +2979,27 @@
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="27" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="I62" s="27" t="n">
-        <v>-7.79</v>
+      <c r="H62" s="28" t="n">
+        <v>29.94</v>
+      </c>
+      <c r="I62" s="28" t="n">
+        <v>40.51</v>
       </c>
       <c r="J62" s="29" t="inlineStr">
         <is>
-          <t>중요공시 4건</t>
+          <t>네이버 검색 당일 +198%</t>
         </is>
       </c>
       <c r="K62" s="29" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3009,35 +3007,35 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>CG인바이츠</t>
+          <t>케이에스피</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E63" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F63" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="27" t="n">
-        <v>-4.7</v>
+      <c r="H63" s="28" t="n">
+        <v>6.57</v>
       </c>
       <c r="I63" s="28" t="n">
-        <v>7.32</v>
+        <v>29.35</v>
       </c>
       <c r="J63" s="29" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>네이버 검색 당일 +183%</t>
         </is>
       </c>
       <c r="K63" s="29" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
@@ -3134,22 +3132,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3158,37 +3156,33 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H4" s="27" t="n">
-        <v>-3.53</v>
-      </c>
-      <c r="I4" s="28" t="n">
-        <v>1.57</v>
-      </c>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H4" s="25" t="n"/>
+      <c r="I4" s="25" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
@@ -3200,22 +3194,22 @@
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H5" s="25" t="n"/>
@@ -3224,135 +3218,147 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H6" s="28" t="n">
-        <v>2.6</v>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>-3.53</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>3.43</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H7" s="25" t="n"/>
-      <c r="I7" s="25" t="n"/>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I7" s="28" t="n">
+        <v>3.43</v>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H8" s="25" t="n"/>
-      <c r="I8" s="25" t="n"/>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="I8" s="27" t="n">
+        <v>-7.1</v>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H9" s="25" t="n"/>
-      <c r="I9" s="25" t="n"/>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I9" s="28" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
@@ -3369,12 +3375,12 @@
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H10" s="25" t="n"/>
@@ -3383,7 +3389,7 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
@@ -3400,25 +3406,25 @@
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H11" s="27" t="n">
-        <v>-4.66</v>
-      </c>
-      <c r="I11" s="27" t="n">
-        <v>-7.1</v>
+        <v>-5.34</v>
+      </c>
+      <c r="I11" s="28" t="n">
+        <v>6.45</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
@@ -3435,25 +3441,25 @@
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H12" s="27" t="n">
-        <v>-5.34</v>
+        <v>-3.61</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>6.45</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -3470,25 +3476,25 @@
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H13" s="27" t="n">
-        <v>-3.61</v>
-      </c>
-      <c r="I13" s="28" t="n">
-        <v>7.65</v>
+        <v>-2.03</v>
+      </c>
+      <c r="I13" s="27" t="n">
+        <v>-4.14</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -3505,25 +3511,25 @@
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H14" s="28" t="n">
-        <v>0.71</v>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="I14" s="28" t="n">
-        <v>18.04</v>
+        <v>185.01</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>루멘스</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -3540,25 +3546,25 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H15" s="27" t="n">
-        <v>-2.03</v>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H15" s="28" t="n">
+        <v>0.39</v>
       </c>
       <c r="I15" s="27" t="n">
-        <v>-4.14</v>
+        <v>-5.58</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -3575,25 +3581,21 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="28" t="n">
-        <v>185.01</v>
-      </c>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>루멘스</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -3610,25 +3612,25 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H17" s="28" t="n">
-        <v>0.39</v>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>-11.52</v>
       </c>
       <c r="I17" s="27" t="n">
-        <v>-5.58</v>
+        <v>-7.67</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>비에이치</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -3645,25 +3647,25 @@
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H18" s="27" t="n">
-        <v>-11.52</v>
+        <v>-1.25</v>
       </c>
       <c r="I18" s="27" t="n">
-        <v>-7.67</v>
+        <v>-12.95</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -3680,60 +3682,56 @@
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H19" s="27" t="n">
-        <v>-2.21</v>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H19" s="28" t="n">
+        <v>0.71</v>
       </c>
       <c r="I19" s="28" t="n">
-        <v>10.02</v>
+        <v>18.04</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>넥써쓰</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H20" s="28" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="I20" s="28" t="n">
-        <v>5.99</v>
-      </c>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H20" s="25" t="n"/>
+      <c r="I20" s="25" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -3750,25 +3748,25 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H21" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="28" t="n">
-        <v>6.24</v>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H21" s="27" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="I21" s="27" t="n">
+        <v>-8.58</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>바이오비쥬</t>
+          <t>넥써쓰</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
@@ -3785,25 +3783,25 @@
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H22" s="28" t="n">
-        <v>7.28</v>
+        <v>2.08</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>5.46</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -3820,25 +3818,25 @@
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H23" s="28" t="n">
-        <v>2.24</v>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H23" s="27" t="n">
+        <v>-4</v>
       </c>
       <c r="I23" s="28" t="n">
-        <v>14</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>샘표</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -3855,25 +3853,25 @@
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H24" s="28" t="n">
-        <v>3.23</v>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H24" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="I24" s="28" t="n">
-        <v>33.72</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
@@ -3890,25 +3888,21 @@
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H25" s="27" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="I25" s="27" t="n">
-        <v>-5.26</v>
-      </c>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H25" s="25" t="n"/>
+      <c r="I25" s="25" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>아티스트스튜디오</t>
+          <t>바이오비쥬</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
@@ -3925,25 +3919,25 @@
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H26" s="27" t="n">
-        <v>-13.9</v>
-      </c>
-      <c r="I26" s="27" t="n">
-        <v>-8.789999999999999</v>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H26" s="28" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="I26" s="28" t="n">
+        <v>5.46</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
@@ -3960,21 +3954,25 @@
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H27" s="25" t="n"/>
-      <c r="I27" s="25" t="n"/>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H27" s="28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I27" s="28" t="n">
+        <v>11.23</v>
+      </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>코다코</t>
+          <t>샘표</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
@@ -3991,25 +3989,25 @@
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H28" s="28" t="n">
-        <v>10.24</v>
-      </c>
-      <c r="I28" s="27" t="n">
-        <v>-99.45</v>
+        <v>3.23</v>
+      </c>
+      <c r="I28" s="28" t="n">
+        <v>33.72</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>코스나인</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
@@ -4026,25 +4024,25 @@
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H29" s="27" t="n">
-        <v>-23.08</v>
+        <v>-1.44</v>
       </c>
       <c r="I29" s="27" t="n">
-        <v>-97.92</v>
+        <v>-5.26</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>헝셩그룹</t>
+          <t>수성웹툰</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
@@ -4061,305 +4059,301 @@
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H30" s="28" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="I30" s="28" t="n">
-        <v>5.94</v>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H30" s="27" t="n">
+        <v>-25.47</v>
+      </c>
+      <c r="I30" s="27" t="n">
+        <v>-49.62</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>CG인바이츠</t>
+          <t>아티스트스튜디오</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H31" s="27" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="I31" s="28" t="n">
-        <v>7.32</v>
+        <v>-13.9</v>
+      </c>
+      <c r="I31" s="27" t="n">
+        <v>-8.789999999999999</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H32" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="28" t="n">
-        <v>14.65</v>
-      </c>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H32" s="25" t="n"/>
+      <c r="I32" s="25" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>머큐리</t>
+          <t>코다코</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H33" s="27" t="n">
-        <v>-4.43</v>
-      </c>
-      <c r="I33" s="28" t="n">
-        <v>39.71</v>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H33" s="28" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="I33" s="27" t="n">
+        <v>-99.45</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>모아데이타</t>
+          <t>코스나인</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H34" s="27" t="n">
-        <v>-3.4</v>
+        <v>-23.08</v>
       </c>
       <c r="I34" s="27" t="n">
-        <v>-7.79</v>
+        <v>-97.92</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H35" s="27" t="n">
-        <v>-1.4</v>
+        <v>-3.22</v>
       </c>
       <c r="I35" s="28" t="n">
-        <v>42.54</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>헝셩그룹</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H36" s="27" t="n">
-        <v>-2.69</v>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H36" s="28" t="n">
+        <v>14.63</v>
       </c>
       <c r="I36" s="28" t="n">
-        <v>47.19</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>혜인</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H37" s="28" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="I37" s="28" t="n">
-        <v>11.23</v>
+        <v>3.85</v>
+      </c>
+      <c r="I37" s="27" t="n">
+        <v>-11.27</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D38" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H38" s="27" t="n">
-        <v>-4.78</v>
+        <v>-1.21</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>0.89</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>샘표식품</t>
+          <t>머큐리</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4376,25 +4370,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H39" s="27" t="n">
-        <v>-14.76</v>
+        <v>-4.43</v>
       </c>
       <c r="I39" s="28" t="n">
-        <v>10.78</v>
+        <v>39.71</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>서전기전</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4411,25 +4405,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H40" s="27" t="n">
-        <v>-3.51</v>
+        <v>-1.4</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>24.43</v>
+        <v>42.54</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>수성웹툰</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4446,25 +4440,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H41" s="27" t="n">
-        <v>-25.47</v>
-      </c>
-      <c r="I41" s="27" t="n">
-        <v>-49.62</v>
+        <v>-2.69</v>
+      </c>
+      <c r="I41" s="28" t="n">
+        <v>47.19</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>스트라드비젼</t>
+          <t>샘표식품</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4481,25 +4475,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H42" s="27" t="n">
-        <v>-0.39</v>
+        <v>-14.76</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>35.05</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>액스비스</t>
+          <t>서전기전</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4516,25 +4510,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H43" s="28" t="n">
-        <v>11.97</v>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H43" s="27" t="n">
+        <v>-3.51</v>
       </c>
       <c r="I43" s="28" t="n">
-        <v>57.45</v>
+        <v>24.43</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>에스투더블유</t>
+          <t>액스비스</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4551,25 +4545,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H44" s="28" t="n">
-        <v>26.38</v>
+        <v>11.97</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>52.78</v>
+        <v>57.45</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>에스투더블유</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4586,25 +4580,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H45" s="28" t="n">
-        <v>29.94</v>
+        <v>26.38</v>
       </c>
       <c r="I45" s="28" t="n">
-        <v>40.51</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4621,25 +4615,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H46" s="27" t="n">
-        <v>-6.94</v>
-      </c>
-      <c r="I46" s="27" t="n">
-        <v>-6.94</v>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H46" s="28" t="n">
+        <v>29.94</v>
+      </c>
+      <c r="I46" s="28" t="n">
+        <v>40.51</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>엠젠솔루션</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4656,19 +4650,19 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H47" s="27" t="n">
-        <v>-8.75</v>
-      </c>
-      <c r="I47" s="28" t="n">
-        <v>15.63</v>
+        <v>-6.94</v>
+      </c>
+      <c r="I47" s="27" t="n">
+        <v>-6.94</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -4691,12 +4685,12 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H48" s="27" t="n">
@@ -4709,7 +4703,7 @@
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>원익피앤이</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4726,19 +4720,19 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H49" s="27" t="n">
-        <v>-1.47</v>
-      </c>
-      <c r="I49" s="27" t="n">
-        <v>-68.62</v>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H49" s="28" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="I49" s="28" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -4761,12 +4755,12 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H50" s="27" t="n">
@@ -4779,7 +4773,7 @@
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>한빛레이저</t>
+          <t>케이에스피</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4796,25 +4790,25 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H51" s="28" t="n">
-        <v>2.83</v>
+        <v>6.57</v>
       </c>
       <c r="I51" s="28" t="n">
-        <v>36.01</v>
+        <v>29.35</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>한빛레이저</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -4831,19 +4825,19 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="H52" s="27" t="n">
-        <v>-1.21</v>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H52" s="28" t="n">
+        <v>2.83</v>
       </c>
       <c r="I52" s="28" t="n">
-        <v>8.93</v>
+        <v>36.01</v>
       </c>
     </row>
   </sheetData>
@@ -4927,19 +4921,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4958,19 +4952,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4996,12 +4990,12 @@
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5013,26 +5007,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5044,26 +5038,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5075,26 +5069,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5106,65 +5100,69 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="F9" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="G9" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
           <t>인공지능</t>
         </is>
       </c>
-      <c r="B9" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="36" t="n">
-        <v>13</v>
-      </c>
-      <c r="D9" s="36" t="n">
-        <v>13</v>
-      </c>
-      <c r="E9" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="F9" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G9" s="37" t="inlineStr">
+      <c r="B10" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="D10" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="G10" s="37" t="inlineStr">
         <is>
           <t>⚡ 관심</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>이차전지</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="29" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G10" s="29" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
@@ -5191,7 +5189,7 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-13 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-14 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-13) 상위: 반도체  점수 48.0점</t>
+          <t>⚡ 최신(2026-09-14) 상위: 반도체  점수 52.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-13) 상위: 인공지능  점수 18.0점</t>
+          <t>⚡ 최신(2026-09-14) 상위: 인공지능  점수 21.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-13) 상위: 삼성전자  점수 15.0점</t>
+          <t>⚡ 최신(2026-09-14) 상위: 바이오  점수 18.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1025,25 +1025,27 @@
       <c r="G16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="18" t="n">
-        <v>-3.53</v>
-      </c>
-      <c r="I16" s="19" t="n">
-        <v>1.57</v>
+      <c r="H16" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v/>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="n">
-        <v/>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1051,14 +1053,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1066,27 +1068,25 @@
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="15" t="n">
+      <c r="H17" s="18" t="n">
+        <v>-3.53</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J17" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K17" s="17" t="n">
         <v/>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1109,25 +1109,27 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I18" s="19" t="n">
-        <v>3.43</v>
+      <c r="H18" s="18" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <v>-7.1</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="n">
-        <v/>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1135,14 +1137,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1150,15 +1152,15 @@
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="18" t="n">
-        <v>-4.66</v>
-      </c>
-      <c r="I19" s="18" t="n">
-        <v>-7.1</v>
+      <c r="H19" s="19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>3.43</v>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="n">
@@ -1168,7 +1170,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1176,14 +1178,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1191,27 +1193,27 @@
       <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="19" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="I20" s="19" t="n">
-        <v>14</v>
+      <c r="H20" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v/>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K20" s="17" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1223,10 +1225,10 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1242,7 +1244,7 @@
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
@@ -1252,134 +1254,136 @@
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="n">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>더코디</t>
-        </is>
-      </c>
-      <c r="D22" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E22" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F22" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="22" t="n">
-        <v>185.01</v>
-      </c>
-      <c r="J22" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +1153% / 중요공시 6건</t>
-        </is>
-      </c>
-      <c r="K22" s="23" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="18" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="I22" s="19" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J22" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="18" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <v>-5.26</v>
+      </c>
+      <c r="J23" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100% / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="inlineStr">
         <is>
           <t>네이버, 공시</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>대한항공</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E23" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F23" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="24" t="n">
-        <v>-2.03</v>
-      </c>
-      <c r="I23" s="24" t="n">
-        <v>-4.14</v>
-      </c>
-      <c r="J23" s="23" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K23" s="23" t="n">
-        <v/>
-      </c>
-    </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="n">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>SG</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E24" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F24" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="24" t="n">
-        <v>-5.34</v>
-      </c>
-      <c r="I24" s="22" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="J24" s="23" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K24" s="23" t="n">
-        <v/>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="J24" s="17" t="inlineStr">
+        <is>
+          <t>Google 급상승 검색어 등장 (US) / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B25" s="20" t="n">
@@ -1387,42 +1391,42 @@
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="D25" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E25" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F25" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="24" t="n">
-        <v>-3.61</v>
+        <v>0</v>
+      </c>
+      <c r="H25" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="I25" s="22" t="n">
-        <v>7.65</v>
+        <v>185.01</v>
       </c>
       <c r="J25" s="23" t="inlineStr">
         <is>
-          <t>중요공시 5건 / 중요공시 7일 +400%</t>
+          <t>네이버 검색 당일 +1211% / 중요공시 6건</t>
         </is>
       </c>
       <c r="K25" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B26" s="20" t="n">
@@ -1430,7 +1434,7 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>루멘스</t>
+          <t>에스투더블유</t>
         </is>
       </c>
       <c r="D26" s="20" t="n">
@@ -1446,26 +1450,26 @@
         <v>0</v>
       </c>
       <c r="H26" s="22" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I26" s="24" t="n">
-        <v>-5.58</v>
+        <v>26.38</v>
+      </c>
+      <c r="I26" s="22" t="n">
+        <v>52.78</v>
       </c>
       <c r="J26" s="23" t="inlineStr">
         <is>
-          <t>중요공시 5건 / 매일경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +451% / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K26" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B27" s="20" t="n">
@@ -1473,42 +1477,40 @@
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="D27" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E27" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F27" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H27" s="24" t="n">
-        <v>-11.52</v>
+        <v>-0.78</v>
       </c>
       <c r="I27" s="24" t="n">
-        <v>-7.67</v>
+        <v>-2.52</v>
       </c>
       <c r="J27" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 7일 +50%</t>
-        </is>
-      </c>
-      <c r="K27" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K27" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B28" s="20" t="n">
@@ -1516,7 +1518,7 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>루멘스</t>
         </is>
       </c>
       <c r="D28" s="20" t="n">
@@ -1531,25 +1533,27 @@
       <c r="G28" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I28" s="20" t="n">
-        <v/>
+      <c r="H28" s="22" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I28" s="24" t="n">
+        <v>-5.58</v>
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K28" s="23" t="n">
-        <v/>
+          <t>중요공시 5건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B29" s="20" t="n">
@@ -1557,7 +1561,7 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>비에이치</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D29" s="20" t="n">
@@ -1572,27 +1576,25 @@
       <c r="G29" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="24" t="n">
-        <v>-1.25</v>
+      <c r="H29" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="I29" s="24" t="n">
-        <v>-12.95</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J29" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K29" s="23" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K29" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1600,7 +1602,7 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
@@ -1615,27 +1617,25 @@
       <c r="G30" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="22" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="I30" s="22" t="n">
-        <v>18.04</v>
+      <c r="H30" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I30" s="20" t="n">
+        <v/>
       </c>
       <c r="J30" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1643,14 +1643,14 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>코스나인</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F31" s="20" t="n">
         <v>0</v>
@@ -1658,25 +1658,27 @@
       <c r="G31" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I31" s="20" t="n">
-        <v/>
+      <c r="H31" s="24" t="n">
+        <v>-23.08</v>
+      </c>
+      <c r="I31" s="24" t="n">
+        <v>-97.92</v>
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K31" s="23" t="n">
-        <v/>
+          <t>네이버 검색 당일 +1239% / 중요공시 2건</t>
+        </is>
+      </c>
+      <c r="K31" s="23" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1684,7 +1686,7 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>코스나인</t>
+          <t>코다코</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
@@ -1699,15 +1701,15 @@
       <c r="G32" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="24" t="n">
-        <v>-23.08</v>
+      <c r="H32" s="22" t="n">
+        <v>10.24</v>
       </c>
       <c r="I32" s="24" t="n">
-        <v>-97.92</v>
+        <v>-99.45</v>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1174% / 중요공시 2건</t>
+          <t>네이버 검색 당일 +1086% / 중요공시 2건</t>
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr">
@@ -1719,7 +1721,7 @@
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1727,7 +1729,7 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>코다코</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
@@ -1742,27 +1744,27 @@
       <c r="G33" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="22" t="n">
-        <v>10.24</v>
-      </c>
-      <c r="I33" s="24" t="n">
-        <v>-99.45</v>
+      <c r="H33" s="24" t="n">
+        <v>-3.22</v>
+      </c>
+      <c r="I33" s="22" t="n">
+        <v>8.83</v>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +994% / 중요공시 2건</t>
+          <t>네이버 검색 당일 +132% / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K33" s="23" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1770,7 +1772,7 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>한국석유</t>
+          <t>수성웹툰</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
@@ -1786,26 +1788,26 @@
         <v>0</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>-3.22</v>
-      </c>
-      <c r="I34" s="22" t="n">
-        <v>8.83</v>
+        <v>-25.47</v>
+      </c>
+      <c r="I34" s="24" t="n">
+        <v>-49.62</v>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +122% / 매일경제 기사 언급</t>
+          <t>네이버 검색 당일 +132% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K34" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1813,7 +1815,7 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>수성웹툰</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
@@ -1829,14 +1831,14 @@
         <v>0</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>-25.47</v>
+        <v>-1.47</v>
       </c>
       <c r="I35" s="24" t="n">
-        <v>-49.62</v>
+        <v>-68.62</v>
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +121% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +101% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K35" s="23" t="inlineStr">
@@ -1848,7 +1850,7 @@
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1856,40 +1858,42 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>에넥스</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="24" t="n">
-        <v>-1.21</v>
+        <v>3</v>
+      </c>
+      <c r="H36" s="22" t="n">
+        <v>10.85</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>8.93</v>
+        <v>14.32</v>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="n">
-        <v/>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1897,7 +1901,7 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
@@ -1912,27 +1916,27 @@
       <c r="G37" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="I37" s="22" t="n">
-        <v>11.23</v>
+      <c r="H37" s="24" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="I37" s="24" t="n">
+        <v>-2.21</v>
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 2건 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K37" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1940,7 +1944,7 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>아티스트스튜디오</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
@@ -1956,26 +1960,26 @@
         <v>0</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>-4</v>
-      </c>
-      <c r="I38" s="22" t="n">
-        <v>8.76</v>
+        <v>-13.9</v>
+      </c>
+      <c r="I38" s="24" t="n">
+        <v>-8.789999999999999</v>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급</t>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K38" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1983,7 +1987,7 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>헝셩그룹</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
@@ -1999,26 +2003,24 @@
         <v>0</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="I39" s="22" t="n">
-        <v>5.94</v>
+        <v>1.35</v>
+      </c>
+      <c r="I39" s="24" t="n">
+        <v>-2.95</v>
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K39" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K39" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2026,421 +2028,427 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F40" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>-2.19</v>
+        <v>-1.67</v>
       </c>
       <c r="I40" s="24" t="n">
-        <v>-8.58</v>
+        <v>-0.26</v>
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K40" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B41" s="20" t="n">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="n">
         <v>28</v>
       </c>
-      <c r="C41" s="21" t="inlineStr">
-        <is>
-          <t>셀트리온</t>
-        </is>
-      </c>
-      <c r="D41" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H41" s="24" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="I41" s="24" t="n">
-        <v>-5.26</v>
-      </c>
-      <c r="J41" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K41" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>삼미금속</t>
+        </is>
+      </c>
+      <c r="D41" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="27" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="I41" s="28" t="n">
+        <v>47.19</v>
+      </c>
+      <c r="J41" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +1091%</t>
+        </is>
+      </c>
+      <c r="K41" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="n">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="n">
         <v>29</v>
       </c>
-      <c r="C42" s="21" t="inlineStr">
-        <is>
-          <t>샘표</t>
-        </is>
-      </c>
-      <c r="D42" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E42" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F42" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="22" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="I42" s="22" t="n">
-        <v>33.72</v>
-      </c>
-      <c r="J42" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K42" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>액스비스</t>
+        </is>
+      </c>
+      <c r="D42" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="28" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="I42" s="28" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="J42" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +784%</t>
+        </is>
+      </c>
+      <c r="K42" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B43" s="20" t="n">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="C43" s="21" t="inlineStr">
-        <is>
-          <t>아티스트스튜디오</t>
-        </is>
-      </c>
-      <c r="D43" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E43" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F43" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="24" t="n">
-        <v>-13.9</v>
-      </c>
-      <c r="I43" s="24" t="n">
-        <v>-8.789999999999999</v>
-      </c>
-      <c r="J43" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K43" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>샘표식품</t>
+        </is>
+      </c>
+      <c r="D43" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="27" t="n">
+        <v>-14.76</v>
+      </c>
+      <c r="I43" s="28" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="J43" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +713%</t>
+        </is>
+      </c>
+      <c r="K43" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B44" s="20" t="n">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B44" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="C44" s="21" t="inlineStr">
-        <is>
-          <t>바이오비쥬</t>
-        </is>
-      </c>
-      <c r="D44" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E44" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F44" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="22" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="I44" s="22" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="J44" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K44" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>엔에이치스팩34호</t>
+        </is>
+      </c>
+      <c r="D44" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="27" t="n">
+        <v>-6.94</v>
+      </c>
+      <c r="I44" s="27" t="n">
+        <v>-6.94</v>
+      </c>
+      <c r="J44" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +496%</t>
+        </is>
+      </c>
+      <c r="K44" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="n">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B45" s="25" t="n">
         <v>32</v>
       </c>
-      <c r="C45" s="21" t="inlineStr">
-        <is>
-          <t>넥써쓰</t>
-        </is>
-      </c>
-      <c r="D45" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E45" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F45" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="I45" s="22" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="J45" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K45" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>카프로</t>
+        </is>
+      </c>
+      <c r="D45" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="27" t="n">
+        <v>-16.67</v>
+      </c>
+      <c r="I45" s="27" t="n">
+        <v>-96.72</v>
+      </c>
+      <c r="J45" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +487%</t>
+        </is>
+      </c>
+      <c r="K45" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B46" s="20" t="n">
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B46" s="25" t="n">
         <v>33</v>
       </c>
-      <c r="C46" s="21" t="inlineStr">
-        <is>
-          <t>로봇</t>
-        </is>
-      </c>
-      <c r="D46" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E46" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I46" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J46" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K46" s="23" t="n">
-        <v/>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>서전기전</t>
+        </is>
+      </c>
+      <c r="D46" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="27" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="I46" s="28" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="J46" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +410%</t>
+        </is>
+      </c>
+      <c r="K46" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B47" s="20" t="n">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B47" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="C47" s="21" t="inlineStr">
-        <is>
-          <t>로보티즈</t>
-        </is>
-      </c>
-      <c r="D47" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F47" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="22" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="J47" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K47" s="23" t="n">
-        <v/>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>머큐리</t>
+        </is>
+      </c>
+      <c r="D47" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="27" t="n">
+        <v>-4.43</v>
+      </c>
+      <c r="I47" s="28" t="n">
+        <v>39.71</v>
+      </c>
+      <c r="J47" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +380%</t>
+        </is>
+      </c>
+      <c r="K47" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B48" s="20" t="n">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B48" s="25" t="n">
         <v>35</v>
       </c>
-      <c r="C48" s="21" t="inlineStr">
-        <is>
-          <t>전기차</t>
-        </is>
-      </c>
-      <c r="D48" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E48" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F48" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I48" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J48" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K48" s="23" t="n">
-        <v/>
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>오르비텍</t>
+        </is>
+      </c>
+      <c r="D48" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="27" t="n">
+        <v>-3.34</v>
+      </c>
+      <c r="I48" s="28" t="n">
+        <v>40.35</v>
+      </c>
+      <c r="J48" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +307%</t>
+        </is>
+      </c>
+      <c r="K48" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="n">
+      <c r="A49" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B49" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="C49" s="21" t="inlineStr">
-        <is>
-          <t>혜인</t>
-        </is>
-      </c>
-      <c r="D49" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E49" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F49" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="I49" s="24" t="n">
-        <v>-11.27</v>
-      </c>
-      <c r="J49" s="23" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K49" s="23" t="n">
-        <v/>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>한빛레이저</t>
+        </is>
+      </c>
+      <c r="D49" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="28" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="I49" s="28" t="n">
+        <v>36.01</v>
+      </c>
+      <c r="J49" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +282%</t>
+        </is>
+      </c>
+      <c r="K49" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2448,7 +2456,7 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -2463,15 +2471,15 @@
       <c r="G50" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="27" t="n">
-        <v>-2.69</v>
+      <c r="H50" s="28" t="n">
+        <v>29.94</v>
       </c>
       <c r="I50" s="28" t="n">
-        <v>47.19</v>
+        <v>40.51</v>
       </c>
       <c r="J50" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1054%</t>
+          <t>네이버 검색 당일 +236%</t>
         </is>
       </c>
       <c r="K50" s="29" t="inlineStr">
@@ -2483,7 +2491,7 @@
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2491,7 +2499,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>액스비스</t>
+          <t>원익피앤이</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2507,14 +2515,14 @@
         <v>0</v>
       </c>
       <c r="H51" s="28" t="n">
-        <v>11.97</v>
+        <v>6.62</v>
       </c>
       <c r="I51" s="28" t="n">
-        <v>57.45</v>
+        <v>41</v>
       </c>
       <c r="J51" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +735%</t>
+          <t>네이버 검색 당일 +220%</t>
         </is>
       </c>
       <c r="K51" s="29" t="inlineStr">
@@ -2526,7 +2534,7 @@
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2534,7 +2542,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>샘표식품</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2550,14 +2558,14 @@
         <v>0</v>
       </c>
       <c r="H52" s="27" t="n">
-        <v>-14.76</v>
+        <v>-1.4</v>
       </c>
       <c r="I52" s="28" t="n">
-        <v>10.78</v>
+        <v>42.54</v>
       </c>
       <c r="J52" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +663%</t>
+          <t>네이버 검색 당일 +211%</t>
         </is>
       </c>
       <c r="K52" s="29" t="inlineStr">
@@ -2569,7 +2577,7 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2577,7 +2585,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>케이에스피</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2592,15 +2600,15 @@
       <c r="G53" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="27" t="n">
-        <v>-6.94</v>
-      </c>
-      <c r="I53" s="27" t="n">
-        <v>-6.94</v>
+      <c r="H53" s="28" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="I53" s="28" t="n">
+        <v>29.35</v>
       </c>
       <c r="J53" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +486%</t>
+          <t>네이버 검색 당일 +198%</t>
         </is>
       </c>
       <c r="K53" s="29" t="inlineStr">
@@ -2612,7 +2620,7 @@
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2620,7 +2628,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>카프로</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2635,15 +2643,15 @@
       <c r="G54" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="27" t="n">
-        <v>-16.67</v>
-      </c>
-      <c r="I54" s="27" t="n">
-        <v>-96.72</v>
+      <c r="H54" s="28" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="I54" s="28" t="n">
+        <v>31.03</v>
       </c>
       <c r="J54" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +470%</t>
+          <t>네이버 검색 당일 +193%</t>
         </is>
       </c>
       <c r="K54" s="29" t="inlineStr">
@@ -2655,7 +2663,7 @@
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2663,7 +2671,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>에스투더블유</t>
+          <t>피아이이</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2679,14 +2687,14 @@
         <v>0</v>
       </c>
       <c r="H55" s="28" t="n">
-        <v>26.38</v>
+        <v>7.61</v>
       </c>
       <c r="I55" s="28" t="n">
-        <v>52.78</v>
+        <v>37.84</v>
       </c>
       <c r="J55" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +403%</t>
+          <t>네이버 검색 당일 +178%</t>
         </is>
       </c>
       <c r="K55" s="29" t="inlineStr">
@@ -2698,7 +2706,7 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2706,7 +2714,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>서전기전</t>
+          <t>스트라드비젼</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2722,14 +2730,14 @@
         <v>0</v>
       </c>
       <c r="H56" s="27" t="n">
-        <v>-3.51</v>
+        <v>-0.39</v>
       </c>
       <c r="I56" s="28" t="n">
-        <v>24.43</v>
+        <v>35.05</v>
       </c>
       <c r="J56" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +398%</t>
+          <t>네이버 검색 당일 +168%</t>
         </is>
       </c>
       <c r="K56" s="29" t="inlineStr">
@@ -2741,7 +2749,7 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2749,7 +2757,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>머큐리</t>
+          <t>금강철강</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2764,15 +2772,15 @@
       <c r="G57" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="27" t="n">
-        <v>-4.43</v>
+      <c r="H57" s="28" t="n">
+        <v>2.34</v>
       </c>
       <c r="I57" s="28" t="n">
-        <v>39.71</v>
+        <v>30.51</v>
       </c>
       <c r="J57" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +359%</t>
+          <t>네이버 검색 당일 +165%</t>
         </is>
       </c>
       <c r="K57" s="29" t="inlineStr">
@@ -2784,7 +2792,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2792,7 +2800,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>오르비텍</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2807,15 +2815,15 @@
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="27" t="n">
-        <v>-3.34</v>
+      <c r="H58" s="28" t="n">
+        <v>7.31</v>
       </c>
       <c r="I58" s="28" t="n">
-        <v>40.35</v>
+        <v>48.55</v>
       </c>
       <c r="J58" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +296%</t>
+          <t>네이버 검색 당일 +161%</t>
         </is>
       </c>
       <c r="K58" s="29" t="inlineStr">
@@ -2827,7 +2835,7 @@
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2835,7 +2843,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>한빛레이저</t>
+          <t>우리넷</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2851,14 +2859,14 @@
         <v>0</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>2.83</v>
+        <v>3.49</v>
       </c>
       <c r="I59" s="28" t="n">
-        <v>36.01</v>
+        <v>15.6</v>
       </c>
       <c r="J59" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +273%</t>
+          <t>네이버 검색 당일 +158%</t>
         </is>
       </c>
       <c r="K59" s="29" t="inlineStr">
@@ -2870,7 +2878,7 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2878,7 +2886,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2893,15 +2901,15 @@
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="27" t="n">
-        <v>-1.4</v>
+      <c r="H60" s="28" t="n">
+        <v>29.98</v>
       </c>
       <c r="I60" s="28" t="n">
-        <v>42.54</v>
+        <v>34.01</v>
       </c>
       <c r="J60" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +204%</t>
+          <t>네이버 검색 당일 +140%</t>
         </is>
       </c>
       <c r="K60" s="29" t="inlineStr">
@@ -2913,7 +2921,7 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2921,7 +2929,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>원익피앤이</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2937,14 +2945,14 @@
         <v>0</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>6.62</v>
+        <v>23.29</v>
       </c>
       <c r="I61" s="28" t="n">
-        <v>41</v>
+        <v>29.38</v>
       </c>
       <c r="J61" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +200%</t>
+          <t>네이버 검색 당일 +124%</t>
         </is>
       </c>
       <c r="K61" s="29" t="inlineStr">
@@ -2956,7 +2964,7 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2964,7 +2972,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>넥스틸</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2980,14 +2988,14 @@
         <v>0</v>
       </c>
       <c r="H62" s="28" t="n">
-        <v>29.94</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I62" s="28" t="n">
-        <v>40.51</v>
+        <v>10.7</v>
       </c>
       <c r="J62" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +198%</t>
+          <t>네이버 검색 당일 +118%</t>
         </is>
       </c>
       <c r="K62" s="29" t="inlineStr">
@@ -2999,7 +3007,7 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3007,7 +3015,7 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>케이에스피</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
@@ -3022,15 +3030,15 @@
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="28" t="n">
-        <v>6.57</v>
+      <c r="H63" s="27" t="n">
+        <v>-3.77</v>
       </c>
       <c r="I63" s="28" t="n">
-        <v>29.35</v>
+        <v>32.17</v>
       </c>
       <c r="J63" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +183%</t>
+          <t>네이버 검색 당일 +115%</t>
         </is>
       </c>
       <c r="K63" s="29" t="inlineStr">
@@ -3132,22 +3140,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3163,22 +3171,22 @@
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H4" s="25" t="n"/>
@@ -3194,22 +3202,22 @@
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H5" s="25" t="n"/>
@@ -3218,142 +3226,138 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H6" s="27" t="n">
-        <v>-3.53</v>
-      </c>
-      <c r="I6" s="28" t="n">
-        <v>1.57</v>
+        <v>-4.66</v>
+      </c>
+      <c r="I6" s="27" t="n">
+        <v>-7.1</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H7" s="28" t="n">
-        <v>2.6</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>-3.53</v>
       </c>
       <c r="I7" s="28" t="n">
-        <v>3.43</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>-4.66</v>
-      </c>
-      <c r="I8" s="27" t="n">
-        <v>-7.1</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I8" s="28" t="n">
+        <v>3.43</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H9" s="28" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="I9" s="28" t="n">
-        <v>14</v>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H9" s="25" t="n"/>
+      <c r="I9" s="25" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
@@ -3365,22 +3369,22 @@
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H10" s="25" t="n"/>
@@ -3389,112 +3393,112 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H11" s="27" t="n">
-        <v>-5.34</v>
+        <v>-4.78</v>
       </c>
       <c r="I11" s="28" t="n">
-        <v>6.45</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H12" s="27" t="n">
-        <v>-3.61</v>
+        <v>-0.06</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>7.65</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H13" s="27" t="n">
-        <v>-2.03</v>
+        <v>-1.44</v>
       </c>
       <c r="I13" s="27" t="n">
-        <v>-4.14</v>
+        <v>-5.26</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -3511,25 +3515,25 @@
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H14" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="28" t="n">
-        <v>185.01</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H14" s="27" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="I14" s="27" t="n">
+        <v>-2.52</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>루멘스</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -3546,25 +3550,25 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H15" s="28" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I15" s="27" t="n">
-        <v>-5.58</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H15" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="28" t="n">
+        <v>185.01</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>루멘스</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -3581,21 +3585,25 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H16" s="25" t="n"/>
-      <c r="I16" s="25" t="n"/>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H16" s="28" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I16" s="27" t="n">
+        <v>-5.58</v>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -3612,25 +3620,25 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H17" s="27" t="n">
-        <v>-11.52</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H17" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="I17" s="27" t="n">
-        <v>-7.67</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>비에이치</t>
+          <t>에스투더블유</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -3647,25 +3655,25 @@
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H18" s="27" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="I18" s="27" t="n">
-        <v>-12.95</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H18" s="28" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="I18" s="28" t="n">
+        <v>52.78</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -3682,56 +3690,56 @@
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H19" s="28" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="I19" s="28" t="n">
-        <v>18.04</v>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H19" s="25" t="n"/>
+      <c r="I19" s="25" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H20" s="25" t="n"/>
-      <c r="I20" s="25" t="n"/>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H20" s="28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I20" s="27" t="n">
+        <v>-2.95</v>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -3748,25 +3756,25 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H21" s="27" t="n">
-        <v>-2.19</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I21" s="27" t="n">
-        <v>-8.58</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>넥써쓰</t>
+          <t>수성웹툰</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
@@ -3783,25 +3791,25 @@
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H22" s="28" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="I22" s="28" t="n">
-        <v>5.99</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H22" s="27" t="n">
+        <v>-25.47</v>
+      </c>
+      <c r="I22" s="27" t="n">
+        <v>-49.62</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>아티스트스튜디오</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -3818,25 +3826,25 @@
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H23" s="27" t="n">
-        <v>-4</v>
-      </c>
-      <c r="I23" s="28" t="n">
-        <v>8.76</v>
+        <v>-13.9</v>
+      </c>
+      <c r="I23" s="27" t="n">
+        <v>-8.789999999999999</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>에넥스</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -3853,25 +3861,25 @@
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H24" s="25" t="n">
-        <v>0</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H24" s="28" t="n">
+        <v>10.85</v>
       </c>
       <c r="I24" s="28" t="n">
-        <v>6.24</v>
+        <v>14.32</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
@@ -3888,21 +3896,25 @@
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H25" s="25" t="n"/>
-      <c r="I25" s="25" t="n"/>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H25" s="27" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="I25" s="27" t="n">
+        <v>-68.62</v>
+      </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>바이오비쥬</t>
+          <t>코다코</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
@@ -3919,25 +3931,25 @@
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H26" s="28" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="I26" s="28" t="n">
-        <v>5.46</v>
+        <v>10.24</v>
+      </c>
+      <c r="I26" s="27" t="n">
+        <v>-99.45</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>코스나인</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
@@ -3954,25 +3966,25 @@
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H27" s="28" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="I27" s="28" t="n">
-        <v>11.23</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H27" s="27" t="n">
+        <v>-23.08</v>
+      </c>
+      <c r="I27" s="27" t="n">
+        <v>-97.92</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>샘표</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
@@ -3989,25 +4001,25 @@
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H28" s="28" t="n">
-        <v>3.23</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H28" s="27" t="n">
+        <v>-3.22</v>
       </c>
       <c r="I28" s="28" t="n">
-        <v>33.72</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
@@ -4024,336 +4036,340 @@
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H29" s="27" t="n">
-        <v>-1.44</v>
+        <v>-1.67</v>
       </c>
       <c r="I29" s="27" t="n">
-        <v>-5.26</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>수성웹툰</t>
+          <t>금강철강</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H30" s="27" t="n">
-        <v>-25.47</v>
-      </c>
-      <c r="I30" s="27" t="n">
-        <v>-49.62</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H30" s="28" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I30" s="28" t="n">
+        <v>30.51</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>아티스트스튜디오</t>
+          <t>넥스틸</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H31" s="27" t="n">
-        <v>-13.9</v>
-      </c>
-      <c r="I31" s="27" t="n">
-        <v>-8.789999999999999</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H31" s="28" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I31" s="28" t="n">
+        <v>10.7</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H32" s="25" t="n"/>
-      <c r="I32" s="25" t="n"/>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H32" s="28" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="I32" s="28" t="n">
+        <v>29.38</v>
+      </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>코다코</t>
+          <t>머큐리</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E33" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H33" s="28" t="n">
-        <v>10.24</v>
-      </c>
-      <c r="I33" s="27" t="n">
-        <v>-99.45</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H33" s="27" t="n">
+        <v>-4.43</v>
+      </c>
+      <c r="I33" s="28" t="n">
+        <v>39.71</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>코스나인</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H34" s="27" t="n">
-        <v>-23.08</v>
-      </c>
-      <c r="I34" s="27" t="n">
-        <v>-97.92</v>
+        <v>-1.4</v>
+      </c>
+      <c r="I34" s="28" t="n">
+        <v>42.54</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>한국석유</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H35" s="27" t="n">
-        <v>-3.22</v>
+        <v>-2.69</v>
       </c>
       <c r="I35" s="28" t="n">
-        <v>8.83</v>
+        <v>47.19</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>헝셩그룹</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H36" s="28" t="n">
-        <v>14.63</v>
+        <v>29.8</v>
       </c>
       <c r="I36" s="28" t="n">
-        <v>5.94</v>
+        <v>31.03</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>혜인</t>
+          <t>샘표식품</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E37" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H37" s="28" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="I37" s="27" t="n">
-        <v>-11.27</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H37" s="27" t="n">
+        <v>-14.76</v>
+      </c>
+      <c r="I37" s="28" t="n">
+        <v>10.78</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>서전기전</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D38" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H38" s="27" t="n">
-        <v>-1.21</v>
+        <v>-3.51</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>8.93</v>
+        <v>24.43</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>머큐리</t>
+          <t>스트라드비젼</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4370,25 +4386,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H39" s="27" t="n">
-        <v>-4.43</v>
+        <v>-0.39</v>
       </c>
       <c r="I39" s="28" t="n">
-        <v>39.71</v>
+        <v>35.05</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4405,25 +4421,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H40" s="27" t="n">
-        <v>-1.4</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H40" s="28" t="n">
+        <v>29.98</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>42.54</v>
+        <v>34.01</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>액스비스</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4440,25 +4456,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H41" s="27" t="n">
-        <v>-2.69</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H41" s="28" t="n">
+        <v>11.97</v>
       </c>
       <c r="I41" s="28" t="n">
-        <v>47.19</v>
+        <v>57.45</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>샘표식품</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4475,25 +4491,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H42" s="27" t="n">
-        <v>-14.76</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H42" s="28" t="n">
+        <v>29.94</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>10.78</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>서전기전</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4510,25 +4526,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H43" s="27" t="n">
-        <v>-3.51</v>
-      </c>
-      <c r="I43" s="28" t="n">
-        <v>24.43</v>
+        <v>-6.94</v>
+      </c>
+      <c r="I43" s="27" t="n">
+        <v>-6.94</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>액스비스</t>
+          <t>오르비텍</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4545,25 +4561,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H44" s="28" t="n">
-        <v>11.97</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H44" s="27" t="n">
+        <v>-3.34</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>57.45</v>
+        <v>40.35</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>에스투더블유</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4580,25 +4596,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H45" s="28" t="n">
-        <v>26.38</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H45" s="27" t="n">
+        <v>-3.77</v>
       </c>
       <c r="I45" s="28" t="n">
-        <v>52.78</v>
+        <v>32.17</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>우리넷</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4615,25 +4631,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H46" s="28" t="n">
-        <v>29.94</v>
+        <v>3.49</v>
       </c>
       <c r="I46" s="28" t="n">
-        <v>40.51</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4650,25 +4666,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H47" s="27" t="n">
-        <v>-6.94</v>
-      </c>
-      <c r="I47" s="27" t="n">
-        <v>-6.94</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H47" s="28" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="I47" s="28" t="n">
+        <v>48.55</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>오르비텍</t>
+          <t>원익피앤이</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4685,25 +4701,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H48" s="27" t="n">
-        <v>-3.34</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H48" s="28" t="n">
+        <v>6.62</v>
       </c>
       <c r="I48" s="28" t="n">
-        <v>40.35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>원익피앤이</t>
+          <t>카프로</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4720,25 +4736,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H49" s="28" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="I49" s="28" t="n">
-        <v>41</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H49" s="27" t="n">
+        <v>-16.67</v>
+      </c>
+      <c r="I49" s="27" t="n">
+        <v>-96.72</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>카프로</t>
+          <t>케이에스피</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4755,25 +4771,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H50" s="27" t="n">
-        <v>-16.67</v>
-      </c>
-      <c r="I50" s="27" t="n">
-        <v>-96.72</v>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H50" s="28" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="I50" s="28" t="n">
+        <v>29.35</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>케이에스피</t>
+          <t>피아이이</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4790,19 +4806,19 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H51" s="28" t="n">
-        <v>6.57</v>
+        <v>7.61</v>
       </c>
       <c r="I51" s="28" t="n">
-        <v>29.35</v>
+        <v>37.84</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -4825,12 +4841,12 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H52" s="28" t="n">
@@ -4921,19 +4937,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4952,19 +4968,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4976,26 +4992,26 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B5" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5007,26 +5023,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5038,26 +5054,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5069,26 +5085,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5098,71 +5114,63 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="35" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="B9" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="D9" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="E9" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="F9" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G9" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>이차전지</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="29" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G9" s="29" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="35" t="inlineStr">
-        <is>
-          <t>인공지능</t>
-        </is>
-      </c>
-      <c r="B10" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="36" t="n">
-        <v>18</v>
-      </c>
-      <c r="D10" s="36" t="n">
-        <v>18</v>
-      </c>
-      <c r="E10" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="F10" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G10" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>AI반도체</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="29" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G10" s="29" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>이차전지</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
@@ -5189,7 +5197,7 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -258,13 +258,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-14 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-15 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-14) 상위: 반도체  점수 52.0점</t>
+          <t>⚡ 최신(2026-09-15) 상위: 반도체  점수 57.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-14) 상위: 인공지능  점수 21.0점</t>
+          <t>⚡ 최신(2026-09-15) 상위: 삼성전자  점수 19.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-14) 상위: 바이오  점수 18.0점</t>
+          <t>⚡ 최신(2026-09-15) 상위: 로봇  점수 18.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -967,14 +967,14 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -982,15 +982,15 @@
       <c r="G15" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v/>
+      <c r="H15" s="18" t="n">
+        <v>-4.24</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>-7.96</v>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
@@ -1033,19 +1033,17 @@
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,7 +1051,7 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
@@ -1069,24 +1067,26 @@
         <v>0</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>-3.53</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <v>1.57</v>
+        <v>-0.89</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>-10.44</v>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="n">
-        <v/>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K17" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1109,15 +1109,15 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="18" t="n">
-        <v>-4.66</v>
-      </c>
-      <c r="I18" s="18" t="n">
-        <v>-7.1</v>
+      <c r="H18" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v/>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
@@ -1129,7 +1129,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1153,14 +1153,14 @@
         <v>0</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>3.43</v>
+        <v>3.01</v>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="n">
@@ -1170,7 +1170,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1178,14 +1178,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K20" s="17" t="inlineStr">
@@ -1213,7 +1213,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>KS인더스트리</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="I21" s="19" t="n">
+        <v>48.4</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>중요공시 3건 / 중요공시 7일 +200% / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1264,14 +1264,14 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1280,24 +1280,26 @@
         <v>0</v>
       </c>
       <c r="H22" s="18" t="n">
-        <v>-4.78</v>
-      </c>
-      <c r="I22" s="19" t="n">
-        <v>0.89</v>
+        <v>-7.12</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>-5.61</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="n">
-        <v/>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1305,42 +1307,42 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
         <v>8</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H23" s="18" t="n">
-        <v>-1.44</v>
+        <v>-6.97</v>
       </c>
       <c r="I23" s="18" t="n">
-        <v>-5.26</v>
+        <v>-1.1</v>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 7일 +100% / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +200%</t>
         </is>
       </c>
       <c r="K23" s="17" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1348,7 +1350,7 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
@@ -1363,113 +1365,113 @@
       <c r="G24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="18" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="I24" s="19" t="n">
-        <v>9.42</v>
+      <c r="H24" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v/>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (US) / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="n">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>더코디</t>
-        </is>
-      </c>
-      <c r="D25" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E25" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="22" t="n">
-        <v>185.01</v>
-      </c>
-      <c r="J25" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +1211% / 중요공시 6건</t>
-        </is>
-      </c>
-      <c r="K25" s="23" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>우리로</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="18" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="I25" s="19" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +172% / 중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="inlineStr">
         <is>
           <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="n">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="C26" s="21" t="inlineStr">
-        <is>
-          <t>에스투더블유</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E26" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F26" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="22" t="n">
-        <v>26.38</v>
-      </c>
-      <c r="I26" s="22" t="n">
-        <v>52.78</v>
-      </c>
-      <c r="J26" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +451% / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K26" s="23" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>코나아이</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B27" s="20" t="n">
@@ -1477,7 +1479,7 @@
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D27" s="20" t="n">
@@ -1492,15 +1494,15 @@
       <c r="G27" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="24" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="I27" s="24" t="n">
-        <v>-2.52</v>
+      <c r="H27" s="22" t="n">
+        <v>-3.92</v>
+      </c>
+      <c r="I27" s="22" t="n">
+        <v>-6.49</v>
       </c>
       <c r="J27" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K27" s="23" t="n">
@@ -1510,7 +1512,7 @@
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B28" s="20" t="n">
@@ -1518,7 +1520,7 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>루멘스</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="D28" s="20" t="n">
@@ -1533,27 +1535,25 @@
       <c r="G28" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="22" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I28" s="24" t="n">
-        <v>-5.58</v>
+      <c r="H28" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I28" s="20" t="n">
+        <v/>
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>중요공시 5건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K28" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B29" s="20" t="n">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="D29" s="20" t="n">
@@ -1576,15 +1576,15 @@
       <c r="G29" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="24" t="n">
-        <v>-0.07000000000000001</v>
+      <c r="H29" s="22" t="n">
+        <v>-3.62</v>
+      </c>
+      <c r="I29" s="22" t="n">
+        <v>-5.16</v>
       </c>
       <c r="J29" s="23" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K29" s="23" t="n">
@@ -1594,7 +1594,7 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1602,40 +1602,42 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
         <v>5</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I30" s="20" t="n">
-        <v/>
+      <c r="H30" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" s="22" t="n">
+        <v>-5.65</v>
       </c>
       <c r="J30" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="n">
-        <v/>
+          <t>중요공시 5건 / 중요공시 3일 +67%</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1643,42 +1645,42 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>코스나인</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F31" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="24" t="n">
-        <v>-23.08</v>
-      </c>
-      <c r="I31" s="24" t="n">
-        <v>-97.92</v>
+        <v>3</v>
+      </c>
+      <c r="H31" s="22" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="I31" s="22" t="n">
+        <v>-4.37</v>
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1239% / 중요공시 2건</t>
+          <t>중요공시 2건 / 중요공시 7일 +100% / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K31" s="23" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1686,14 +1688,14 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>코다코</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F32" s="20" t="n">
         <v>0</v>
@@ -1702,26 +1704,26 @@
         <v>0</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>10.24</v>
-      </c>
-      <c r="I32" s="24" t="n">
-        <v>-99.45</v>
+        <v>-3.87</v>
+      </c>
+      <c r="I32" s="22" t="n">
+        <v>-8.92</v>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1086% / 중요공시 2건</t>
+          <t>Google 급상승 검색어 등장 (US)</t>
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1729,14 +1731,14 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>한국석유</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>0</v>
@@ -1744,27 +1746,25 @@
       <c r="G33" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="24" t="n">
-        <v>-3.22</v>
-      </c>
-      <c r="I33" s="22" t="n">
-        <v>8.83</v>
+      <c r="H33" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I33" s="20" t="n">
+        <v/>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +132% / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K33" s="23" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K33" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1772,14 +1772,14 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>수성웹툰</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>0</v>
@@ -1787,27 +1787,27 @@
       <c r="G34" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="24" t="n">
-        <v>-25.47</v>
-      </c>
-      <c r="I34" s="24" t="n">
-        <v>-49.62</v>
+      <c r="H34" s="22" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="I34" s="22" t="n">
+        <v>-8.93</v>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +132% / 중요공시 1건</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K34" s="23" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>코스나인</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
@@ -1830,15 +1830,15 @@
       <c r="G35" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="24" t="n">
-        <v>-1.47</v>
-      </c>
-      <c r="I35" s="24" t="n">
-        <v>-68.62</v>
+      <c r="H35" s="22" t="n">
+        <v>-30</v>
+      </c>
+      <c r="I35" s="22" t="n">
+        <v>-98.54000000000001</v>
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +101% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +1295% / 중요공시 2건</t>
         </is>
       </c>
       <c r="K35" s="23" t="inlineStr">
@@ -1850,7 +1850,7 @@
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1858,42 +1858,42 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>에넥스</t>
+          <t>코다코</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>10.85</v>
+        <v>-33.63</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>14.32</v>
+        <v>-99.64</v>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+          <t>네이버 검색 당일 +1164% / 중요공시 2건</t>
         </is>
       </c>
       <c r="K36" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>수성웹툰</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
@@ -1916,15 +1916,15 @@
       <c r="G37" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="24" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="I37" s="24" t="n">
-        <v>-2.21</v>
+      <c r="H37" s="22" t="n">
+        <v>-14.07</v>
+      </c>
+      <c r="I37" s="22" t="n">
+        <v>-66.67</v>
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 네이버뉴스 헤드라인 언급</t>
+          <t>네이버 검색 당일 +139% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K37" s="23" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>아티스트스튜디오</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
@@ -1959,27 +1959,27 @@
       <c r="G38" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="24" t="n">
-        <v>-13.9</v>
-      </c>
-      <c r="I38" s="24" t="n">
-        <v>-8.789999999999999</v>
+      <c r="H38" s="22" t="n">
+        <v>-26.12</v>
+      </c>
+      <c r="I38" s="22" t="n">
+        <v>-66.89</v>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +106% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K38" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
@@ -2002,25 +2002,27 @@
       <c r="G39" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="22" t="n">
-        <v>1.35</v>
+      <c r="H39" s="24" t="n">
+        <v>3.27</v>
       </c>
       <c r="I39" s="24" t="n">
-        <v>-2.95</v>
+        <v>3.27</v>
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K39" s="23" t="n">
-        <v/>
+          <t>중요공시 2건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K39" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2028,7 +2030,7 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>인피니트헬스케어</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
@@ -2044,153 +2046,151 @@
         <v>0</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>-1.67</v>
+        <v>30</v>
       </c>
       <c r="I40" s="24" t="n">
-        <v>-0.26</v>
+        <v>24.29</v>
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K40" s="23" t="n">
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>전기차</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="20" t="n">
         <v/>
       </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B41" s="25" t="n">
-        <v>28</v>
-      </c>
-      <c r="C41" s="26" t="inlineStr">
-        <is>
-          <t>삼미금속</t>
-        </is>
-      </c>
-      <c r="D41" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E41" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F41" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="27" t="n">
-        <v>-2.69</v>
-      </c>
-      <c r="I41" s="28" t="n">
-        <v>47.19</v>
-      </c>
-      <c r="J41" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +1091%</t>
-        </is>
-      </c>
-      <c r="K41" s="29" t="inlineStr">
+      <c r="I41" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J41" s="23" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K41" s="23" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B42" s="25" t="n">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="n">
         <v>29</v>
       </c>
-      <c r="C42" s="26" t="inlineStr">
-        <is>
-          <t>액스비스</t>
-        </is>
-      </c>
-      <c r="D42" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E42" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F42" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="28" t="n">
-        <v>11.97</v>
-      </c>
-      <c r="I42" s="28" t="n">
-        <v>57.45</v>
-      </c>
-      <c r="J42" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +784%</t>
-        </is>
-      </c>
-      <c r="K42" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>원전</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I42" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J42" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K42" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B43" s="25" t="n">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="C43" s="26" t="inlineStr">
-        <is>
-          <t>샘표식품</t>
-        </is>
-      </c>
-      <c r="D43" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E43" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F43" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="27" t="n">
-        <v>-14.76</v>
-      </c>
-      <c r="I43" s="28" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="J43" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +713%</t>
-        </is>
-      </c>
-      <c r="K43" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>아모레퍼시픽</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="24" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I43" s="24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="J43" s="23" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K43" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C44" s="26" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="D44" s="25" t="n">
@@ -2214,14 +2214,14 @@
         <v>0</v>
       </c>
       <c r="H44" s="27" t="n">
-        <v>-6.94</v>
-      </c>
-      <c r="I44" s="27" t="n">
-        <v>-6.94</v>
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="I44" s="28" t="n">
+        <v>10.59</v>
       </c>
       <c r="J44" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +496%</t>
+          <t>네이버 검색 당일 +1128%</t>
         </is>
       </c>
       <c r="K44" s="29" t="inlineStr">
@@ -2233,7 +2233,7 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C45" s="26" t="inlineStr">
         <is>
-          <t>카프로</t>
+          <t>액스비스</t>
         </is>
       </c>
       <c r="D45" s="25" t="n">
@@ -2257,14 +2257,14 @@
         <v>0</v>
       </c>
       <c r="H45" s="27" t="n">
-        <v>-16.67</v>
-      </c>
-      <c r="I45" s="27" t="n">
-        <v>-96.72</v>
+        <v>-3.59</v>
+      </c>
+      <c r="I45" s="28" t="n">
+        <v>47.72</v>
       </c>
       <c r="J45" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +487%</t>
+          <t>네이버 검색 당일 +831%</t>
         </is>
       </c>
       <c r="K45" s="29" t="inlineStr">
@@ -2276,7 +2276,7 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="C46" s="26" t="inlineStr">
         <is>
-          <t>서전기전</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D46" s="25" t="n">
@@ -2299,15 +2299,15 @@
       <c r="G46" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="27" t="n">
-        <v>-3.51</v>
-      </c>
-      <c r="I46" s="28" t="n">
-        <v>24.43</v>
+      <c r="H46" s="28" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I46" s="27" t="n">
+        <v>-6.8</v>
       </c>
       <c r="J46" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +410%</t>
+          <t>네이버 검색 당일 +503%</t>
         </is>
       </c>
       <c r="K46" s="29" t="inlineStr">
@@ -2319,7 +2319,7 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="C47" s="26" t="inlineStr">
         <is>
-          <t>머큐리</t>
+          <t>카프로</t>
         </is>
       </c>
       <c r="D47" s="25" t="n">
@@ -2343,14 +2343,14 @@
         <v>0</v>
       </c>
       <c r="H47" s="27" t="n">
-        <v>-4.43</v>
-      </c>
-      <c r="I47" s="28" t="n">
-        <v>39.71</v>
+        <v>-40.83</v>
+      </c>
+      <c r="I47" s="27" t="n">
+        <v>-98.06</v>
       </c>
       <c r="J47" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +380%</t>
+          <t>네이버 검색 당일 +500%</t>
         </is>
       </c>
       <c r="K47" s="29" t="inlineStr">
@@ -2362,7 +2362,7 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="C48" s="26" t="inlineStr">
         <is>
-          <t>오르비텍</t>
+          <t>에스투더블유</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
@@ -2385,15 +2385,15 @@
       <c r="G48" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="27" t="n">
-        <v>-3.34</v>
+      <c r="H48" s="28" t="n">
+        <v>7.95</v>
       </c>
       <c r="I48" s="28" t="n">
-        <v>40.35</v>
+        <v>66.98</v>
       </c>
       <c r="J48" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +307%</t>
+          <t>네이버 검색 당일 +490%</t>
         </is>
       </c>
       <c r="K48" s="29" t="inlineStr">
@@ -2405,7 +2405,7 @@
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>한빛레이저</t>
+          <t>머큐리</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
@@ -2429,14 +2429,14 @@
         <v>0</v>
       </c>
       <c r="H49" s="28" t="n">
-        <v>2.83</v>
+        <v>0.11</v>
       </c>
       <c r="I49" s="28" t="n">
-        <v>36.01</v>
+        <v>41.31</v>
       </c>
       <c r="J49" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +282%</t>
+          <t>네이버 검색 당일 +397%</t>
         </is>
       </c>
       <c r="K49" s="29" t="inlineStr">
@@ -2448,7 +2448,7 @@
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2472,14 +2472,14 @@
         <v>0</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>29.94</v>
+        <v>6.97</v>
       </c>
       <c r="I50" s="28" t="n">
-        <v>40.51</v>
+        <v>51.63</v>
       </c>
       <c r="J50" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +236%</t>
+          <t>네이버 검색 당일 +275%</t>
         </is>
       </c>
       <c r="K50" s="29" t="inlineStr">
@@ -2491,7 +2491,7 @@
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>원익피앤이</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2515,14 +2515,14 @@
         <v>0</v>
       </c>
       <c r="H51" s="28" t="n">
-        <v>6.62</v>
+        <v>29.95</v>
       </c>
       <c r="I51" s="28" t="n">
-        <v>41</v>
+        <v>70.48</v>
       </c>
       <c r="J51" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +220%</t>
+          <t>네이버 검색 당일 +246%</t>
         </is>
       </c>
       <c r="K51" s="29" t="inlineStr">
@@ -2534,7 +2534,7 @@
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>에스엠벡셀</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2558,14 +2558,14 @@
         <v>0</v>
       </c>
       <c r="H52" s="27" t="n">
-        <v>-1.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="I52" s="28" t="n">
-        <v>42.54</v>
+        <v>38.56</v>
       </c>
       <c r="J52" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +211%</t>
+          <t>네이버 검색 당일 +244%</t>
         </is>
       </c>
       <c r="K52" s="29" t="inlineStr">
@@ -2577,7 +2577,7 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>케이에스피</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2601,14 +2601,14 @@
         <v>0</v>
       </c>
       <c r="H53" s="28" t="n">
-        <v>6.57</v>
+        <v>12.53</v>
       </c>
       <c r="I53" s="28" t="n">
-        <v>29.35</v>
+        <v>55.54</v>
       </c>
       <c r="J53" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +198%</t>
+          <t>네이버 검색 당일 +218%</t>
         </is>
       </c>
       <c r="K53" s="29" t="inlineStr">
@@ -2620,7 +2620,7 @@
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>금강철강</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2644,14 +2644,14 @@
         <v>0</v>
       </c>
       <c r="H54" s="28" t="n">
-        <v>29.8</v>
+        <v>0.13</v>
       </c>
       <c r="I54" s="28" t="n">
-        <v>31.03</v>
+        <v>22.93</v>
       </c>
       <c r="J54" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +193%</t>
+          <t>네이버 검색 당일 +173%</t>
         </is>
       </c>
       <c r="K54" s="29" t="inlineStr">
@@ -2663,7 +2663,7 @@
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>피아이이</t>
+          <t>우리넷</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2687,14 +2687,14 @@
         <v>0</v>
       </c>
       <c r="H55" s="28" t="n">
-        <v>7.61</v>
+        <v>7.71</v>
       </c>
       <c r="I55" s="28" t="n">
-        <v>37.84</v>
+        <v>24.69</v>
       </c>
       <c r="J55" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +178%</t>
+          <t>네이버 검색 당일 +171%</t>
         </is>
       </c>
       <c r="K55" s="29" t="inlineStr">
@@ -2706,7 +2706,7 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>스트라드비젼</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2729,15 +2729,15 @@
       <c r="G56" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="27" t="n">
-        <v>-0.39</v>
+      <c r="H56" s="28" t="n">
+        <v>4.43</v>
       </c>
       <c r="I56" s="28" t="n">
-        <v>35.05</v>
+        <v>41.07</v>
       </c>
       <c r="J56" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +168%</t>
+          <t>네이버 검색 당일 +167%</t>
         </is>
       </c>
       <c r="K56" s="29" t="inlineStr">
@@ -2749,7 +2749,7 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>금강철강</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2773,14 +2773,14 @@
         <v>0</v>
       </c>
       <c r="H57" s="28" t="n">
-        <v>2.34</v>
+        <v>5.53</v>
       </c>
       <c r="I57" s="28" t="n">
-        <v>30.51</v>
+        <v>37.22</v>
       </c>
       <c r="J57" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +165%</t>
+          <t>네이버 검색 당일 +147%</t>
         </is>
       </c>
       <c r="K57" s="29" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>넥스틸</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2816,14 +2816,14 @@
         <v>0</v>
       </c>
       <c r="H58" s="28" t="n">
-        <v>7.31</v>
+        <v>1.53</v>
       </c>
       <c r="I58" s="28" t="n">
-        <v>48.55</v>
+        <v>10.27</v>
       </c>
       <c r="J58" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +161%</t>
+          <t>네이버 검색 당일 +131%</t>
         </is>
       </c>
       <c r="K58" s="29" t="inlineStr">
@@ -2835,7 +2835,7 @@
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>우리넷</t>
+          <t>메가터치</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2858,15 +2858,15 @@
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="28" t="n">
-        <v>3.49</v>
+      <c r="H59" s="27" t="n">
+        <v>-1.19</v>
       </c>
       <c r="I59" s="28" t="n">
-        <v>15.6</v>
+        <v>17.49</v>
       </c>
       <c r="J59" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +158%</t>
+          <t>네이버 검색 당일 +125%</t>
         </is>
       </c>
       <c r="K59" s="29" t="inlineStr">
@@ -2878,7 +2878,7 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2901,15 +2901,15 @@
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="28" t="n">
-        <v>29.98</v>
+      <c r="H60" s="27" t="n">
+        <v>-2.35</v>
       </c>
       <c r="I60" s="28" t="n">
-        <v>34.01</v>
+        <v>25.64</v>
       </c>
       <c r="J60" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +140%</t>
+          <t>네이버 검색 당일 +119%</t>
         </is>
       </c>
       <c r="K60" s="29" t="inlineStr">
@@ -2921,7 +2921,7 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2945,14 +2945,14 @@
         <v>0</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>23.29</v>
+        <v>30</v>
       </c>
       <c r="I61" s="28" t="n">
-        <v>29.38</v>
+        <v>38.4</v>
       </c>
       <c r="J61" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +124%</t>
+          <t>네이버 검색 당일 +117%</t>
         </is>
       </c>
       <c r="K61" s="29" t="inlineStr">
@@ -2964,7 +2964,7 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>넥스틸</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2988,14 +2988,14 @@
         <v>0</v>
       </c>
       <c r="H62" s="28" t="n">
-        <v>0.07000000000000001</v>
+        <v>4.38</v>
       </c>
       <c r="I62" s="28" t="n">
-        <v>10.7</v>
+        <v>35.8</v>
       </c>
       <c r="J62" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +118%</t>
+          <t>네이버 검색 당일 +115%</t>
         </is>
       </c>
       <c r="K62" s="29" t="inlineStr">
@@ -3007,7 +3007,7 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>모니터랩</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
@@ -3030,15 +3030,15 @@
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="27" t="n">
-        <v>-3.77</v>
+      <c r="H63" s="28" t="n">
+        <v>5.53</v>
       </c>
       <c r="I63" s="28" t="n">
-        <v>32.17</v>
+        <v>17.05</v>
       </c>
       <c r="J63" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +115%</t>
+          <t>네이버 검색 당일 +108%</t>
         </is>
       </c>
       <c r="K63" s="29" t="inlineStr">
@@ -3140,22 +3140,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3164,38 +3164,42 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H4" s="25" t="n"/>
-      <c r="I4" s="25" t="n"/>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H4" s="27" t="n">
+        <v>-4.24</v>
+      </c>
+      <c r="I4" s="27" t="n">
+        <v>-7.96</v>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
@@ -3212,12 +3216,12 @@
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H5" s="25" t="n"/>
@@ -3243,117 +3247,113 @@
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H6" s="27" t="n">
-        <v>-4.66</v>
+        <v>-0.89</v>
       </c>
       <c r="I6" s="27" t="n">
-        <v>-7.1</v>
+        <v>-10.44</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>-3.53</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>1.85</v>
       </c>
       <c r="I7" s="28" t="n">
-        <v>1.57</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H8" s="28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I8" s="28" t="n">
-        <v>3.43</v>
-      </c>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="25" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H9" s="25" t="n"/>
@@ -3362,73 +3362,77 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>KS인더스트리</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H10" s="25" t="n"/>
-      <c r="I10" s="25" t="n"/>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H10" s="28" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="I10" s="28" t="n">
+        <v>48.4</v>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H11" s="27" t="n">
-        <v>-4.78</v>
-      </c>
-      <c r="I11" s="28" t="n">
-        <v>0.89</v>
+        <v>-7.12</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>-5.61</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
@@ -3445,25 +3449,21 @@
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H12" s="27" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="I12" s="28" t="n">
-        <v>9.42</v>
-      </c>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H12" s="25" t="n"/>
+      <c r="I12" s="25" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -3480,95 +3480,95 @@
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H13" s="27" t="n">
-        <v>-1.44</v>
+        <v>-6.97</v>
       </c>
       <c r="I13" s="27" t="n">
-        <v>-5.26</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H14" s="27" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="I14" s="27" t="n">
-        <v>-2.52</v>
+        <v>-0.97</v>
+      </c>
+      <c r="I14" s="28" t="n">
+        <v>46.65</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H15" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="28" t="n">
-        <v>185.01</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H15" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" s="25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>루멘스</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -3585,25 +3585,25 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H16" s="28" t="n">
-        <v>0.39</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>-3.62</v>
       </c>
       <c r="I16" s="27" t="n">
-        <v>-5.58</v>
+        <v>-5.16</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -3620,25 +3620,21 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H17" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="27" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>에스투더블유</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -3655,25 +3651,25 @@
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H18" s="28" t="n">
-        <v>26.38</v>
-      </c>
-      <c r="I18" s="28" t="n">
-        <v>52.78</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>-3.92</v>
+      </c>
+      <c r="I18" s="27" t="n">
+        <v>-6.49</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -3690,161 +3686,161 @@
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H19" s="25" t="n"/>
-      <c r="I19" s="25" t="n"/>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H19" s="27" t="n">
+        <v>-3.87</v>
+      </c>
+      <c r="I19" s="27" t="n">
+        <v>-8.92</v>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H20" s="28" t="n">
-        <v>1.35</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>-2.31</v>
       </c>
       <c r="I20" s="27" t="n">
-        <v>-2.95</v>
+        <v>-8.93</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H21" s="27" t="n">
-        <v>-0.5600000000000001</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H21" s="28" t="n">
+        <v>2</v>
       </c>
       <c r="I21" s="27" t="n">
-        <v>-2.21</v>
+        <v>-5.65</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>수성웹툰</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H22" s="27" t="n">
-        <v>-25.47</v>
+        <v>-0.92</v>
       </c>
       <c r="I22" s="27" t="n">
-        <v>-49.62</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>아티스트스튜디오</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H23" s="27" t="n">
-        <v>-13.9</v>
-      </c>
-      <c r="I23" s="27" t="n">
-        <v>-8.789999999999999</v>
-      </c>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="25" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>에넥스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -3861,25 +3857,25 @@
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H24" s="28" t="n">
-        <v>10.85</v>
+        <v>3.27</v>
       </c>
       <c r="I24" s="28" t="n">
-        <v>14.32</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>수성웹툰</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
@@ -3896,25 +3892,25 @@
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H25" s="27" t="n">
-        <v>-1.47</v>
+        <v>-14.07</v>
       </c>
       <c r="I25" s="27" t="n">
-        <v>-68.62</v>
+        <v>-66.67</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>코다코</t>
+          <t>아모레퍼시픽</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
@@ -3931,25 +3927,25 @@
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H26" s="28" t="n">
-        <v>10.24</v>
-      </c>
-      <c r="I26" s="27" t="n">
-        <v>-99.45</v>
+        <v>2.78</v>
+      </c>
+      <c r="I26" s="28" t="n">
+        <v>2.56</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>코스나인</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
@@ -3966,25 +3962,21 @@
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H27" s="27" t="n">
-        <v>-23.08</v>
-      </c>
-      <c r="I27" s="27" t="n">
-        <v>-97.92</v>
-      </c>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H27" s="25" t="n"/>
+      <c r="I27" s="25" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>한국석유</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
@@ -4001,25 +3993,25 @@
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H28" s="27" t="n">
-        <v>-3.22</v>
-      </c>
-      <c r="I28" s="28" t="n">
-        <v>8.83</v>
+        <v>-26.12</v>
+      </c>
+      <c r="I28" s="27" t="n">
+        <v>-66.89</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>인피니트헬스케어</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
@@ -4036,130 +4028,126 @@
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H29" s="27" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="I29" s="27" t="n">
-        <v>-0.26</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H29" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="28" t="n">
+        <v>24.29</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>금강철강</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H30" s="28" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="I30" s="28" t="n">
-        <v>30.51</v>
-      </c>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="25" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>넥스틸</t>
+          <t>코다코</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H31" s="28" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I31" s="28" t="n">
-        <v>10.7</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H31" s="27" t="n">
+        <v>-33.63</v>
+      </c>
+      <c r="I31" s="27" t="n">
+        <v>-99.64</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>코스나인</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H32" s="28" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="I32" s="28" t="n">
-        <v>29.38</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H32" s="27" t="n">
+        <v>-30</v>
+      </c>
+      <c r="I32" s="27" t="n">
+        <v>-98.54000000000001</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>머큐리</t>
+          <t>금강철강</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
@@ -4176,25 +4164,25 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H33" s="27" t="n">
-        <v>-4.43</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H33" s="28" t="n">
+        <v>0.13</v>
       </c>
       <c r="I33" s="28" t="n">
-        <v>39.71</v>
+        <v>22.93</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>넥스틸</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
@@ -4211,25 +4199,25 @@
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H34" s="27" t="n">
-        <v>-1.4</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H34" s="28" t="n">
+        <v>1.53</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>42.54</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
@@ -4246,25 +4234,25 @@
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H35" s="27" t="n">
-        <v>-2.69</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H35" s="28" t="n">
+        <v>5.53</v>
       </c>
       <c r="I35" s="28" t="n">
-        <v>47.19</v>
+        <v>37.22</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>머큐리</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
@@ -4281,25 +4269,25 @@
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H36" s="28" t="n">
-        <v>29.8</v>
+        <v>0.11</v>
       </c>
       <c r="I36" s="28" t="n">
-        <v>31.03</v>
+        <v>41.31</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>샘표식품</t>
+          <t>메가터치</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
@@ -4316,25 +4304,25 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H37" s="27" t="n">
-        <v>-14.76</v>
+        <v>-1.19</v>
       </c>
       <c r="I37" s="28" t="n">
-        <v>10.78</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>서전기전</t>
+          <t>모니터랩</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4351,25 +4339,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H38" s="27" t="n">
-        <v>-3.51</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H38" s="28" t="n">
+        <v>5.53</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>24.43</v>
+        <v>17.05</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>스트라드비젼</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4386,25 +4374,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H39" s="27" t="n">
-        <v>-0.39</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H39" s="28" t="n">
+        <v>12.53</v>
       </c>
       <c r="I39" s="28" t="n">
-        <v>35.05</v>
+        <v>55.54</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4421,25 +4409,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H40" s="28" t="n">
-        <v>29.98</v>
+        <v>30</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>34.01</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>액스비스</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4456,25 +4444,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H41" s="28" t="n">
-        <v>11.97</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H41" s="27" t="n">
+        <v>-8.220000000000001</v>
       </c>
       <c r="I41" s="28" t="n">
-        <v>57.45</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4491,25 +4479,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H42" s="28" t="n">
-        <v>29.94</v>
+        <v>29.95</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>40.51</v>
+        <v>70.48</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4526,25 +4514,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H43" s="27" t="n">
-        <v>-6.94</v>
-      </c>
-      <c r="I43" s="27" t="n">
-        <v>-6.94</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H43" s="28" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="I43" s="28" t="n">
+        <v>41.07</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>오르비텍</t>
+          <t>액스비스</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4561,25 +4549,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H44" s="27" t="n">
-        <v>-3.34</v>
+        <v>-3.59</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>40.35</v>
+        <v>47.72</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>에스엠벡셀</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4596,25 +4584,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H45" s="27" t="n">
-        <v>-3.77</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="I45" s="28" t="n">
-        <v>32.17</v>
+        <v>38.56</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>우리넷</t>
+          <t>에스투더블유</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4631,25 +4619,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H46" s="28" t="n">
-        <v>3.49</v>
+        <v>7.95</v>
       </c>
       <c r="I46" s="28" t="n">
-        <v>15.6</v>
+        <v>66.98</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4666,25 +4654,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H47" s="28" t="n">
-        <v>7.31</v>
+        <v>6.97</v>
       </c>
       <c r="I47" s="28" t="n">
-        <v>48.55</v>
+        <v>51.63</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>원익피앤이</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4701,25 +4689,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H48" s="28" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="I48" s="28" t="n">
-        <v>41</v>
+        <v>0.16</v>
+      </c>
+      <c r="I48" s="27" t="n">
+        <v>-6.8</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>카프로</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4736,25 +4724,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H49" s="27" t="n">
-        <v>-16.67</v>
-      </c>
-      <c r="I49" s="27" t="n">
-        <v>-96.72</v>
+        <v>-2.35</v>
+      </c>
+      <c r="I49" s="28" t="n">
+        <v>25.64</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>케이에스피</t>
+          <t>우리넷</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4771,25 +4759,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H50" s="28" t="n">
-        <v>6.57</v>
+        <v>7.71</v>
       </c>
       <c r="I50" s="28" t="n">
-        <v>29.35</v>
+        <v>24.69</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>피아이이</t>
+          <t>카프로</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4806,25 +4794,25 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H51" s="28" t="n">
-        <v>7.61</v>
-      </c>
-      <c r="I51" s="28" t="n">
-        <v>37.84</v>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H51" s="27" t="n">
+        <v>-40.83</v>
+      </c>
+      <c r="I51" s="27" t="n">
+        <v>-98.06</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>한빛레이저</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -4841,19 +4829,19 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H52" s="28" t="n">
-        <v>2.83</v>
+        <v>4.38</v>
       </c>
       <c r="I52" s="28" t="n">
-        <v>36.01</v>
+        <v>35.8</v>
       </c>
     </row>
   </sheetData>
@@ -4937,19 +4925,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4968,19 +4956,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4992,26 +4980,26 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B5" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5023,26 +5011,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5054,26 +5042,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5085,119 +5073,131 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
+          <t>로봇</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="D8" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="E8" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="F8" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G8" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>조선</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="F9" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G9" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B10" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G10" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
           <t>인공지능</t>
         </is>
       </c>
-      <c r="B8" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="D8" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="E8" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="F8" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G8" s="37" t="inlineStr">
+      <c r="B11" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="F11" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G11" s="37" t="inlineStr">
         <is>
           <t>⚡ 관심</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
-        <is>
-          <t>이차전지</t>
-        </is>
-      </c>
-      <c r="B9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="29" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G9" s="29" t="inlineStr"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>AI반도체</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="29" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G10" s="29" t="inlineStr"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>전기차</t>
-        </is>
-      </c>
-      <c r="B11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="29" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G11" s="29" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
@@ -5224,7 +5224,7 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -5251,7 +5251,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5278,7 +5278,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5305,7 +5305,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5332,7 +5332,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5359,7 +5359,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5386,7 +5386,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -57,13 +57,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="002563EB"/>
+      <color rgb="00E53935"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00E53935"/>
+      <color rgb="002563EB"/>
       <sz val="10"/>
     </font>
     <font>
@@ -258,13 +258,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -276,11 +276,11 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-15 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-16 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-15) 상위: 반도체  점수 57.0점</t>
+          <t>⚡ 최신(2026-09-16) 상위: 반도체  점수 32.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-15) 상위: 삼성전자  점수 19.0점</t>
+          <t>⚡ 최신(2026-09-16) 상위: 바이오  점수 27.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-15) 상위: 로봇  점수 18.0점</t>
+          <t>⚡ 최신(2026-09-16) 상위: 제약  점수 18.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -967,14 +967,14 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -982,15 +982,15 @@
       <c r="G15" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="18" t="n">
-        <v>-4.24</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>-7.96</v>
+      <c r="H15" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v/>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
@@ -1033,17 +1033,19 @@
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="n">
-        <v/>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1051,14 +1053,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1066,15 +1068,15 @@
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="18" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>-10.44</v>
+      <c r="H17" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v/>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
@@ -1086,7 +1088,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1094,14 +1096,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1109,15 +1111,15 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v/>
+      <c r="H18" s="18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <v>-7.05</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
@@ -1129,7 +1131,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1137,14 +1139,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1152,15 +1154,15 @@
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="I19" s="19" t="n">
-        <v>3.01</v>
+      <c r="H19" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v/>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="n">
@@ -1170,7 +1172,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1178,14 +1180,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1193,27 +1195,25 @@
       <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="15" t="n">
+      <c r="H20" s="18" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="n">
         <v/>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1221,42 +1221,40 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>KS인더스트리</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
         <v>9</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>29.97</v>
+        <v>-6.43</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>48.4</v>
+        <v>-12.46</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 7일 +200% / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K21" s="17" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K21" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1264,14 +1262,14 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1279,27 +1277,25 @@
       <c r="G22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="18" t="n">
-        <v>-7.12</v>
-      </c>
-      <c r="I22" s="18" t="n">
-        <v>-5.61</v>
+      <c r="H22" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v/>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1307,42 +1303,42 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" s="18" t="n">
-        <v>-6.97</v>
-      </c>
-      <c r="I23" s="18" t="n">
-        <v>-1.1</v>
+        <v>0</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v/>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +200%</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K23" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1350,14 +1346,14 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" s="15" t="n">
         <v>0</v>
@@ -1365,27 +1361,25 @@
       <c r="G24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="15" t="n">
+      <c r="H24" s="18" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="J24" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="n">
         <v/>
-      </c>
-      <c r="I24" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J24" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1393,42 +1387,42 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>KS인더스트리</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>-0.97</v>
-      </c>
-      <c r="I25" s="19" t="n">
-        <v>46.65</v>
+        <v>8.460000000000001</v>
+      </c>
+      <c r="I25" s="18" t="n">
+        <v>63.37</v>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +172% / 중요공시 1건 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +200%</t>
         </is>
       </c>
       <c r="K25" s="17" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1436,251 +1430,251 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" s="18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +200%</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>대한항공</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>시지트로닉스</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="E26" s="15" t="n">
+      <c r="E28" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="F26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="19" t="n">
+      <c r="F28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="18" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="I28" s="18" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="J28" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>방산</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="I26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="17" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="C27" s="21" t="inlineStr">
-        <is>
-          <t>현대차</t>
-        </is>
-      </c>
-      <c r="D27" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E27" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="22" t="n">
-        <v>-3.92</v>
-      </c>
-      <c r="I27" s="22" t="n">
-        <v>-6.49</v>
-      </c>
-      <c r="J27" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K27" s="23" t="n">
+      <c r="E29" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="15" t="n">
         <v/>
       </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>방산</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E28" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="20" t="n">
+      <c r="I29" s="15" t="n">
         <v/>
       </c>
-      <c r="I28" s="20" t="n">
+      <c r="J29" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K29" s="17" t="n">
         <v/>
       </c>
-      <c r="J28" s="23" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K28" s="23" t="n">
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>카카오</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="18" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I30" s="19" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="J30" s="17" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K30" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>SK이노베이션</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="18" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="I31" s="18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J31" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K31" s="17" t="n">
         <v/>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="C29" s="21" t="inlineStr">
-        <is>
-          <t>고영</t>
-        </is>
-      </c>
-      <c r="D29" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E29" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="22" t="n">
-        <v>-3.62</v>
-      </c>
-      <c r="I29" s="22" t="n">
-        <v>-5.16</v>
-      </c>
-      <c r="J29" s="23" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K29" s="23" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="n">
-        <v>17</v>
-      </c>
-      <c r="C30" s="21" t="inlineStr">
-        <is>
-          <t>넥사다이내믹스</t>
-        </is>
-      </c>
-      <c r="D30" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="E30" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F30" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G30" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I30" s="22" t="n">
-        <v>-5.65</v>
-      </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 5건 / 중요공시 3일 +67%</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>삼성바이오로직스</t>
-        </is>
-      </c>
-      <c r="D31" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="E31" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="F31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H31" s="22" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="I31" s="22" t="n">
-        <v>-4.37</v>
-      </c>
-      <c r="J31" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100% / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K31" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1688,14 +1682,14 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>엠젠솔루션</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F32" s="20" t="n">
         <v>0</v>
@@ -1704,26 +1698,26 @@
         <v>0</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>-3.87</v>
+        <v>-14.46</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>-8.92</v>
+        <v>-15.82</v>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (US)</t>
+          <t>중요공시 6건 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1731,14 +1725,14 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>보령</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>0</v>
@@ -1746,25 +1740,27 @@
       <c r="G33" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I33" s="20" t="n">
-        <v/>
+      <c r="H33" s="22" t="n">
+        <v>-5.04</v>
+      </c>
+      <c r="I33" s="22" t="n">
+        <v>-0.8</v>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K33" s="23" t="n">
-        <v/>
+          <t>중요공시 4건 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K33" s="23" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1772,14 +1768,14 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>0</v>
@@ -1787,27 +1783,25 @@
       <c r="G34" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="22" t="n">
-        <v>-2.31</v>
-      </c>
-      <c r="I34" s="22" t="n">
-        <v>-8.93</v>
+      <c r="H34" s="24" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I34" s="24" t="n">
+        <v>3.96</v>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1815,14 +1809,14 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>코스나인</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F35" s="20" t="n">
         <v>0</v>
@@ -1830,27 +1824,27 @@
       <c r="G35" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="22" t="n">
-        <v>-30</v>
-      </c>
-      <c r="I35" s="22" t="n">
-        <v>-98.54000000000001</v>
+      <c r="H35" s="24" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="I35" s="24" t="n">
+        <v>58.66</v>
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1295% / 중요공시 2건</t>
+          <t>중요공시 2건 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K35" s="23" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1858,14 +1852,14 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>코다코</t>
+          <t>YTN</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>0</v>
@@ -1873,27 +1867,25 @@
       <c r="G36" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="22" t="n">
-        <v>-33.63</v>
-      </c>
-      <c r="I36" s="22" t="n">
-        <v>-99.64</v>
+      <c r="H36" s="24" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="I36" s="24" t="n">
+        <v>32.21</v>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1164% / 중요공시 2건</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1901,14 +1893,14 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>수성웹툰</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F37" s="20" t="n">
         <v>0</v>
@@ -1916,27 +1908,25 @@
       <c r="G37" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="22" t="n">
-        <v>-14.07</v>
+      <c r="H37" s="24" t="n">
+        <v>0.61</v>
       </c>
       <c r="I37" s="22" t="n">
-        <v>-66.67</v>
+        <v>-2.92</v>
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +139% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K37" s="23" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K37" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1944,7 +1934,7 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
@@ -1959,27 +1949,27 @@
       <c r="G38" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="22" t="n">
-        <v>-26.12</v>
-      </c>
-      <c r="I38" s="22" t="n">
-        <v>-66.89</v>
+      <c r="H38" s="24" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="I38" s="24" t="n">
+        <v>8.23</v>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +106% / 중요공시 1건</t>
+          <t>중요공시 2건 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K38" s="23" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1987,7 +1977,7 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
@@ -2003,10 +1993,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>3.27</v>
+        <v>11.85</v>
       </c>
       <c r="I39" s="24" t="n">
-        <v>3.27</v>
+        <v>5.38</v>
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
@@ -2022,7 +2012,7 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2030,30 +2020,30 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>인피니트헬스케어</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F40" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>30</v>
-      </c>
-      <c r="I40" s="24" t="n">
-        <v>24.29</v>
+        <v>0.5</v>
+      </c>
+      <c r="I40" s="22" t="n">
+        <v>-2.15</v>
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr">
@@ -2065,7 +2055,7 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2073,7 +2063,7 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>동아지질</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
@@ -2088,27 +2078,27 @@
       <c r="G41" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I41" s="20" t="n">
-        <v/>
+      <c r="H41" s="24" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="I41" s="24" t="n">
+        <v>6.79</v>
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K41" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -2116,7 +2106,7 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
@@ -2139,17 +2129,19 @@
       </c>
       <c r="J42" s="23" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K42" s="23" t="n">
-        <v/>
+          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K42" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B43" s="20" t="n">
@@ -2157,7 +2149,7 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="D43" s="20" t="n">
@@ -2173,14 +2165,14 @@
         <v>0</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="I43" s="24" t="n">
-        <v>2.56</v>
+        <v>0.35</v>
+      </c>
+      <c r="I43" s="22" t="n">
+        <v>-7.79</v>
       </c>
       <c r="J43" s="23" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K43" s="23" t="n">
@@ -2188,95 +2180,91 @@
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B44" s="25" t="n">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="n">
         <v>31</v>
       </c>
-      <c r="C44" s="26" t="inlineStr">
-        <is>
-          <t>삼미금속</t>
-        </is>
-      </c>
-      <c r="D44" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E44" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F44" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="27" t="n">
-        <v>-8.220000000000001</v>
-      </c>
-      <c r="I44" s="28" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="J44" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +1128%</t>
-        </is>
-      </c>
-      <c r="K44" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>철강</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I44" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J44" s="23" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K44" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B45" s="25" t="n">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="n">
         <v>32</v>
       </c>
-      <c r="C45" s="26" t="inlineStr">
-        <is>
-          <t>액스비스</t>
-        </is>
-      </c>
-      <c r="D45" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E45" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="27" t="n">
-        <v>-3.59</v>
-      </c>
-      <c r="I45" s="28" t="n">
-        <v>47.72</v>
-      </c>
-      <c r="J45" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +831%</t>
-        </is>
-      </c>
-      <c r="K45" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="24" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I45" s="22" t="n">
+        <v>-4.03</v>
+      </c>
+      <c r="J45" s="23" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K45" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -2284,7 +2272,7 @@
       </c>
       <c r="C46" s="26" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="D46" s="25" t="n">
@@ -2299,27 +2287,25 @@
       <c r="G46" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="28" t="n">
-        <v>0.16</v>
+      <c r="H46" s="27" t="n">
+        <v>20.46</v>
       </c>
       <c r="I46" s="27" t="n">
-        <v>-6.8</v>
-      </c>
-      <c r="J46" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +503%</t>
-        </is>
-      </c>
-      <c r="K46" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+        <v>30.51</v>
+      </c>
+      <c r="J46" s="28" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K46" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -2327,42 +2313,42 @@
       </c>
       <c r="C47" s="26" t="inlineStr">
         <is>
-          <t>카프로</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="D47" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E47" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F47" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G47" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="27" t="n">
-        <v>-40.83</v>
-      </c>
-      <c r="I47" s="27" t="n">
-        <v>-98.06</v>
-      </c>
-      <c r="J47" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +500%</t>
-        </is>
-      </c>
-      <c r="K47" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H47" s="29" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="I47" s="29" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="J47" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K47" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -2370,7 +2356,7 @@
       </c>
       <c r="C48" s="26" t="inlineStr">
         <is>
-          <t>에스투더블유</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
@@ -2385,27 +2371,25 @@
       <c r="G48" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="28" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="I48" s="28" t="n">
-        <v>66.98</v>
-      </c>
-      <c r="J48" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +490%</t>
-        </is>
-      </c>
-      <c r="K48" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="H48" s="27" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="I48" s="27" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="J48" s="28" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K48" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -2413,7 +2397,7 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>머큐리</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
@@ -2428,18 +2412,18 @@
       <c r="G49" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="28" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I49" s="28" t="n">
-        <v>41.31</v>
-      </c>
-      <c r="J49" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +397%</t>
-        </is>
-      </c>
-      <c r="K49" s="29" t="inlineStr">
+      <c r="H49" s="27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I49" s="29" t="n">
+        <v>-4.52</v>
+      </c>
+      <c r="J49" s="28" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K49" s="28" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -2448,7 +2432,7 @@
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2456,7 +2440,7 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>하이젠알앤엠</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -2471,27 +2455,25 @@
       <c r="G50" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="28" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="I50" s="28" t="n">
-        <v>51.63</v>
-      </c>
-      <c r="J50" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +275%</t>
-        </is>
-      </c>
-      <c r="K50" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="H50" s="27" t="n">
+        <v>27.11</v>
+      </c>
+      <c r="I50" s="27" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="J50" s="28" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K50" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2499,7 +2481,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2514,27 +2496,27 @@
       <c r="G51" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="28" t="n">
-        <v>29.95</v>
-      </c>
-      <c r="I51" s="28" t="n">
-        <v>70.48</v>
-      </c>
-      <c r="J51" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +246%</t>
-        </is>
-      </c>
-      <c r="K51" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H51" s="29" t="n">
+        <v>-9.18</v>
+      </c>
+      <c r="I51" s="27" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="J51" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 6건</t>
+        </is>
+      </c>
+      <c r="K51" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2542,7 +2524,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>에스엠벡셀</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2558,26 +2540,26 @@
         <v>0</v>
       </c>
       <c r="H52" s="27" t="n">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="I52" s="28" t="n">
-        <v>38.56</v>
-      </c>
-      <c r="J52" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +244%</t>
-        </is>
-      </c>
-      <c r="K52" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
+        <v>0.37</v>
+      </c>
+      <c r="I52" s="29" t="n">
+        <v>-17.9</v>
+      </c>
+      <c r="J52" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 6건</t>
+        </is>
+      </c>
+      <c r="K52" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2585,7 +2567,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>다보링크</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2600,27 +2582,27 @@
       <c r="G53" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="28" t="n">
-        <v>12.53</v>
-      </c>
-      <c r="I53" s="28" t="n">
-        <v>55.54</v>
-      </c>
-      <c r="J53" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +218%</t>
-        </is>
-      </c>
-      <c r="K53" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H53" s="27" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I53" s="29" t="n">
+        <v>-9.289999999999999</v>
+      </c>
+      <c r="J53" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K53" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2628,42 +2610,42 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>금강철강</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E54" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F54" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G54" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="28" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I54" s="28" t="n">
-        <v>22.93</v>
-      </c>
-      <c r="J54" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +173%</t>
-        </is>
-      </c>
-      <c r="K54" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H54" s="27" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="I54" s="29" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="J54" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K54" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2671,42 +2653,42 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>우리넷</t>
+          <t>비투엔</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E55" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G55" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="28" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="I55" s="28" t="n">
-        <v>24.69</v>
-      </c>
-      <c r="J55" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +171%</t>
-        </is>
-      </c>
-      <c r="K55" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H55" s="29" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="I55" s="29" t="n">
+        <v>-8.34</v>
+      </c>
+      <c r="J55" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K55" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2714,7 +2696,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>코윈로보틱스</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2729,27 +2711,25 @@
       <c r="G56" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="28" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="I56" s="28" t="n">
-        <v>41.07</v>
-      </c>
-      <c r="J56" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +167%</t>
-        </is>
-      </c>
-      <c r="K56" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="H56" s="27" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="I56" s="27" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="J56" s="28" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K56" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2757,7 +2737,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>원텍</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2772,18 +2752,18 @@
       <c r="G57" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="28" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="I57" s="28" t="n">
-        <v>37.22</v>
-      </c>
-      <c r="J57" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +147%</t>
-        </is>
-      </c>
-      <c r="K57" s="29" t="inlineStr">
+      <c r="H57" s="29" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="I57" s="27" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J57" s="28" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K57" s="28" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -2792,7 +2772,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2800,7 +2780,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>넥스틸</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2815,27 +2795,25 @@
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="I58" s="28" t="n">
-        <v>10.27</v>
-      </c>
-      <c r="J58" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +131%</t>
-        </is>
-      </c>
-      <c r="K58" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="H58" s="27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I58" s="27" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="J58" s="28" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K58" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2843,7 +2821,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>한컴</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2859,26 +2837,24 @@
         <v>0</v>
       </c>
       <c r="H59" s="27" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="I59" s="28" t="n">
-        <v>17.49</v>
-      </c>
-      <c r="J59" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +125%</t>
-        </is>
-      </c>
-      <c r="K59" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+        <v>1.22</v>
+      </c>
+      <c r="I59" s="27" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="J59" s="28" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K59" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2886,7 +2862,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2901,27 +2877,25 @@
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="27" t="n">
-        <v>-2.35</v>
-      </c>
-      <c r="I60" s="28" t="n">
-        <v>25.64</v>
-      </c>
-      <c r="J60" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +119%</t>
-        </is>
-      </c>
-      <c r="K60" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="H60" s="29" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="I60" s="29" t="n">
+        <v>-5.46</v>
+      </c>
+      <c r="J60" s="28" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K60" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2929,7 +2903,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2944,27 +2918,25 @@
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="28" t="n">
-        <v>30</v>
-      </c>
-      <c r="I61" s="28" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="J61" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +117%</t>
-        </is>
-      </c>
-      <c r="K61" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="H61" s="25" t="n">
+        <v/>
+      </c>
+      <c r="I61" s="25" t="n">
+        <v/>
+      </c>
+      <c r="J61" s="28" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K61" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2972,7 +2944,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2987,18 +2959,18 @@
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="28" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="I62" s="28" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="J62" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +115%</t>
-        </is>
-      </c>
-      <c r="K62" s="29" t="inlineStr">
+      <c r="H62" s="25" t="n">
+        <v/>
+      </c>
+      <c r="I62" s="25" t="n">
+        <v/>
+      </c>
+      <c r="J62" s="28" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K62" s="28" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -3007,7 +2979,7 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3015,14 +2987,14 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>모니터랩</t>
+          <t>위메이드맥스</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F63" s="25" t="n">
         <v>0</v>
@@ -3030,18 +3002,18 @@
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="28" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="I63" s="28" t="n">
-        <v>17.05</v>
-      </c>
-      <c r="J63" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +108%</t>
-        </is>
-      </c>
-      <c r="K63" s="29" t="inlineStr">
+      <c r="H63" s="29" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="I63" s="27" t="n">
+        <v>25.31</v>
+      </c>
+      <c r="J63" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +70%</t>
+        </is>
+      </c>
+      <c r="K63" s="28" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -3140,22 +3112,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3164,42 +3136,38 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H4" s="27" t="n">
-        <v>-4.24</v>
-      </c>
-      <c r="I4" s="27" t="n">
-        <v>-7.96</v>
-      </c>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H4" s="25" t="n"/>
+      <c r="I4" s="25" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
@@ -3216,12 +3184,12 @@
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H5" s="25" t="n"/>
@@ -3230,130 +3198,130 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="I6" s="27" t="n">
-        <v>-10.44</v>
-      </c>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H6" s="25" t="n"/>
+      <c r="I6" s="25" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H7" s="28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="I7" s="28" t="n">
-        <v>3.01</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I7" s="29" t="n">
+        <v>-7.05</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H8" s="25" t="n"/>
-      <c r="I8" s="25" t="n"/>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>-4.46</v>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H9" s="25" t="n"/>
@@ -3362,7 +3330,7 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>KS인더스트리</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
@@ -3379,82 +3347,82 @@
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H10" s="28" t="n">
-        <v>29.97</v>
-      </c>
-      <c r="I10" s="28" t="n">
-        <v>48.4</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H10" s="27" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="I10" s="29" t="n">
+        <v>-1.46</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H11" s="27" t="n">
-        <v>-7.12</v>
-      </c>
-      <c r="I11" s="27" t="n">
-        <v>-5.61</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H11" s="29" t="n">
+        <v>-6.43</v>
+      </c>
+      <c r="I11" s="29" t="n">
+        <v>-12.46</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H12" s="25" t="n"/>
@@ -3463,489 +3431,489 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H13" s="27" t="n">
-        <v>-6.97</v>
-      </c>
-      <c r="I13" s="27" t="n">
-        <v>-1.1</v>
-      </c>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H13" s="25" t="n"/>
+      <c r="I13" s="25" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>KS인더스트리</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H14" s="27" t="n">
-        <v>-0.97</v>
-      </c>
-      <c r="I14" s="28" t="n">
-        <v>46.65</v>
+        <v>8.460000000000001</v>
+      </c>
+      <c r="I14" s="27" t="n">
+        <v>63.37</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H15" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="I15" s="25" t="n">
-        <v>0</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H15" s="29" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="I15" s="29" t="n">
+        <v>-2.49</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H16" s="27" t="n">
-        <v>-3.62</v>
-      </c>
-      <c r="I16" s="27" t="n">
-        <v>-5.16</v>
+        <v>2.63</v>
+      </c>
+      <c r="I16" s="29" t="n">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H17" s="25" t="n"/>
-      <c r="I17" s="25" t="n"/>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="I17" s="27" t="n">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H18" s="27" t="n">
-        <v>-3.92</v>
-      </c>
-      <c r="I18" s="27" t="n">
-        <v>-6.49</v>
-      </c>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="25" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>시지트로닉스</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H19" s="27" t="n">
-        <v>-3.87</v>
+        <v>6.79</v>
       </c>
       <c r="I19" s="27" t="n">
-        <v>-8.92</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H20" s="27" t="n">
-        <v>-2.31</v>
-      </c>
-      <c r="I20" s="27" t="n">
-        <v>-8.93</v>
+        <v>0.43</v>
+      </c>
+      <c r="I20" s="29" t="n">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>보령</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H21" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" s="27" t="n">
-        <v>-5.65</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H21" s="29" t="n">
+        <v>-5.04</v>
+      </c>
+      <c r="I21" s="29" t="n">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H22" s="27" t="n">
-        <v>-0.92</v>
+        <v>3.77</v>
       </c>
       <c r="I22" s="27" t="n">
-        <v>-4.37</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>엠젠솔루션</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H23" s="25" t="n"/>
-      <c r="I23" s="25" t="n"/>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H23" s="29" t="n">
+        <v>-14.46</v>
+      </c>
+      <c r="I23" s="29" t="n">
+        <v>-15.82</v>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>YTN</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E24" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H24" s="28" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="I24" s="28" t="n">
-        <v>3.27</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H24" s="27" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="I24" s="27" t="n">
+        <v>32.21</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>수성웹툰</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H25" s="27" t="n">
-        <v>-14.07</v>
+        <v>34.11</v>
       </c>
       <c r="I25" s="27" t="n">
-        <v>-66.67</v>
+        <v>58.66</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H26" s="28" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="I26" s="28" t="n">
-        <v>2.56</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H26" s="27" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <v>-2.92</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
@@ -3962,21 +3930,25 @@
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H27" s="25" t="n"/>
-      <c r="I27" s="25" t="n"/>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H27" s="27" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I27" s="29" t="n">
+        <v>-7.79</v>
+      </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
@@ -3993,25 +3965,25 @@
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H28" s="27" t="n">
-        <v>-26.12</v>
+        <v>5.39</v>
       </c>
       <c r="I28" s="27" t="n">
-        <v>-66.89</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>인피니트헬스케어</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
@@ -4028,25 +4000,21 @@
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H29" s="28" t="n">
-        <v>30</v>
-      </c>
-      <c r="I29" s="28" t="n">
-        <v>24.29</v>
-      </c>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H29" s="25" t="n"/>
+      <c r="I29" s="25" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>동아지질</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
@@ -4063,21 +4031,25 @@
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H30" s="25" t="n"/>
-      <c r="I30" s="25" t="n"/>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H30" s="27" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="I30" s="27" t="n">
+        <v>6.79</v>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>코다코</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
@@ -4094,25 +4066,25 @@
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H31" s="27" t="n">
-        <v>-33.63</v>
+        <v>11.85</v>
       </c>
       <c r="I31" s="27" t="n">
-        <v>-99.64</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>코스나인</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
@@ -4129,95 +4101,91 @@
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H32" s="27" t="n">
-        <v>-30</v>
-      </c>
-      <c r="I32" s="27" t="n">
-        <v>-98.54000000000001</v>
+        <v>0.5</v>
+      </c>
+      <c r="I32" s="29" t="n">
+        <v>-2.15</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>금강철강</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H33" s="28" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I33" s="28" t="n">
-        <v>22.93</v>
-      </c>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H33" s="25" t="n"/>
+      <c r="I33" s="25" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>넥스틸</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H34" s="28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="I34" s="28" t="n">
-        <v>10.27</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H34" s="27" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I34" s="29" t="n">
+        <v>-4.03</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
@@ -4234,25 +4202,25 @@
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H35" s="28" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="I35" s="28" t="n">
-        <v>37.22</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H35" s="29" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="I35" s="29" t="n">
+        <v>-5.46</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>머큐리</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
@@ -4269,25 +4237,25 @@
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H36" s="28" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I36" s="28" t="n">
-        <v>41.31</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H36" s="27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I36" s="29" t="n">
+        <v>-4.52</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
@@ -4304,25 +4272,25 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H37" s="27" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="I37" s="28" t="n">
-        <v>17.49</v>
+        <v>0.37</v>
+      </c>
+      <c r="I37" s="29" t="n">
+        <v>-17.9</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>모니터랩</t>
+          <t>다보링크</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4339,25 +4307,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H38" s="28" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="I38" s="28" t="n">
-        <v>17.05</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H38" s="27" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I38" s="29" t="n">
+        <v>-9.289999999999999</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4374,25 +4342,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H39" s="28" t="n">
-        <v>12.53</v>
-      </c>
-      <c r="I39" s="28" t="n">
-        <v>55.54</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H39" s="29" t="n">
+        <v>-9.18</v>
+      </c>
+      <c r="I39" s="27" t="n">
+        <v>19.8</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>비투엔</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4409,25 +4377,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H40" s="28" t="n">
-        <v>30</v>
-      </c>
-      <c r="I40" s="28" t="n">
-        <v>38.4</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H40" s="29" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="I40" s="29" t="n">
+        <v>-8.34</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4444,25 +4412,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H41" s="27" t="n">
-        <v>-8.220000000000001</v>
-      </c>
-      <c r="I41" s="28" t="n">
-        <v>10.59</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H41" s="29" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="I41" s="29" t="n">
+        <v>-1.64</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4479,25 +4447,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H42" s="28" t="n">
-        <v>29.95</v>
-      </c>
-      <c r="I42" s="28" t="n">
-        <v>70.48</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H42" s="27" t="n">
+        <v>20.46</v>
+      </c>
+      <c r="I42" s="27" t="n">
+        <v>30.51</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4514,25 +4482,21 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H43" s="28" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="I43" s="28" t="n">
-        <v>41.07</v>
-      </c>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H43" s="25" t="n"/>
+      <c r="I43" s="25" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>액스비스</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4549,25 +4513,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H44" s="27" t="n">
-        <v>-3.59</v>
-      </c>
-      <c r="I44" s="28" t="n">
-        <v>47.72</v>
+        <v>3.87</v>
+      </c>
+      <c r="I44" s="29" t="n">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>에스엠벡셀</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4584,25 +4548,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H45" s="27" t="n">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="I45" s="28" t="n">
-        <v>38.56</v>
+        <v>2.62</v>
+      </c>
+      <c r="I45" s="27" t="n">
+        <v>5.17</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>에스투더블유</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4619,25 +4583,21 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H46" s="28" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="I46" s="28" t="n">
-        <v>66.98</v>
-      </c>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H46" s="25" t="n"/>
+      <c r="I46" s="25" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>원텍</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4654,25 +4614,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H47" s="28" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="I47" s="28" t="n">
-        <v>51.63</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H47" s="29" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="I47" s="27" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>코윈로보틱스</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4689,25 +4649,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H48" s="28" t="n">
-        <v>0.16</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H48" s="27" t="n">
+        <v>6.47</v>
       </c>
       <c r="I48" s="27" t="n">
-        <v>-6.8</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>하이젠알앤엠</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4724,25 +4684,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H49" s="27" t="n">
-        <v>-2.35</v>
-      </c>
-      <c r="I49" s="28" t="n">
-        <v>25.64</v>
+        <v>27.11</v>
+      </c>
+      <c r="I49" s="27" t="n">
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>우리넷</t>
+          <t>한컴</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4759,25 +4719,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H50" s="28" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="I50" s="28" t="n">
-        <v>24.69</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H50" s="27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I50" s="27" t="n">
+        <v>3.74</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>카프로</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4794,54 +4754,54 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H51" s="27" t="n">
-        <v>-40.83</v>
+        <v>32.24</v>
       </c>
       <c r="I51" s="27" t="n">
-        <v>-98.06</v>
+        <v>44.28</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>위메이드맥스</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C52" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H52" s="28" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="I52" s="28" t="n">
-        <v>35.8</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H52" s="29" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="I52" s="27" t="n">
+        <v>25.31</v>
       </c>
     </row>
   </sheetData>
@@ -4925,19 +4885,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4956,19 +4916,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4987,19 +4947,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5018,19 +4978,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5042,26 +5002,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5073,26 +5033,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5104,26 +5064,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5135,26 +5095,26 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B10" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G10" s="37" t="inlineStr">
@@ -5166,92 +5126,100 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="35" t="inlineStr">
         <is>
+          <t>철강</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F11" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G11" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B12" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="E12" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F12" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G12" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
           <t>인공지능</t>
         </is>
       </c>
-      <c r="B11" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="D11" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F11" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G11" s="37" t="inlineStr">
+      <c r="B13" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>16</v>
+      </c>
+      <c r="D13" s="36" t="n">
+        <v>16</v>
+      </c>
+      <c r="E13" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F13" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G13" s="37" t="inlineStr">
         <is>
           <t>⚡ 관심</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>이차전지</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="29" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G12" s="29" t="inlineStr"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
-        <is>
-          <t>AI반도체</t>
-        </is>
-      </c>
-      <c r="B13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="29" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G13" s="29" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5268,17 +5236,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="29" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G14" s="29" t="inlineStr"/>
+      <c r="G14" s="28" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5295,17 +5263,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="29" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G15" s="29" t="inlineStr"/>
+      <c r="G15" s="28" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5322,17 +5290,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="29" t="inlineStr">
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G16" s="29" t="inlineStr"/>
+      <c r="G16" s="28" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5349,17 +5317,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="29" t="inlineStr">
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G17" s="29" t="inlineStr"/>
+      <c r="G17" s="28" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5376,17 +5344,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="29" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G18" s="29" t="inlineStr"/>
+      <c r="G18" s="28" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -5403,17 +5371,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="29" t="inlineStr">
+      <c r="F19" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G19" s="29" t="inlineStr"/>
+      <c r="G19" s="28" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -5430,12 +5398,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="29" t="inlineStr">
+      <c r="F20" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G20" s="29" t="inlineStr"/>
+      <c r="G20" s="28" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -5457,12 +5425,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F21" s="29" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G21" s="29" t="inlineStr"/>
+      <c r="G21" s="28" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -5484,12 +5452,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F22" s="29" t="inlineStr">
+      <c r="F22" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G22" s="29" t="inlineStr"/>
+      <c r="G22" s="28" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -5511,12 +5479,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F23" s="29" t="inlineStr">
+      <c r="F23" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G23" s="29" t="inlineStr"/>
+      <c r="G23" s="28" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -5538,12 +5506,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F24" s="29" t="inlineStr">
+      <c r="F24" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G24" s="29" t="inlineStr"/>
+      <c r="G24" s="28" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -261,11 +261,11 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-16 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-17 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-16) 상위: 반도체  점수 32.0점</t>
+          <t>⚡ 최신(2026-09-17) 상위: 반도체  점수 30.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-16) 상위: 바이오  점수 27.0점</t>
+          <t>⚡ 최신(2026-09-17) 상위: 바이오  점수 26.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-16) 상위: 제약  점수 18.0점</t>
+          <t>⚡ 최신(2026-09-17) 상위: SK하이닉스  점수 17.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1025,27 +1025,25 @@
       <c r="G16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="15" t="n">
+      <c r="H16" s="18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>-5.33</v>
+      </c>
+      <c r="J16" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="n">
         <v/>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,14 +1051,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1076,7 +1074,7 @@
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
@@ -1088,7 +1086,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1096,7 +1094,7 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
@@ -1111,15 +1109,15 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="18" t="n">
-        <v>0.8</v>
+      <c r="H18" s="19" t="n">
+        <v>-2.96</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>-7.05</v>
+        <v>-8.76</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
@@ -1131,7 +1129,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1139,14 +1137,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1154,15 +1152,15 @@
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v/>
+      <c r="H19" s="18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>-5.94</v>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="n">
@@ -1172,7 +1170,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1180,7 +1178,7 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
@@ -1195,25 +1193,27 @@
       <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="I20" s="19" t="n">
-        <v>-4.46</v>
+      <c r="H20" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v/>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="n">
-        <v/>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1221,14 +1221,14 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1237,14 +1237,14 @@
         <v>0</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>-6.43</v>
+        <v>-0.34</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>-12.46</v>
+        <v>-1.85</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="n">
@@ -1254,7 +1254,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1262,14 +1262,14 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1277,25 +1277,27 @@
       <c r="G22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v/>
+      <c r="H22" s="19" t="n">
+        <v>-4.71</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>38.38</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="n">
-        <v/>
+          <t>네이버 검색 당일 +194% / 중요공시 2건 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1303,14 +1305,14 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F23" s="15" t="n">
         <v>0</v>
@@ -1318,27 +1320,27 @@
       <c r="G23" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I23" s="15" t="n">
-        <v/>
+      <c r="H23" s="19" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <v>18.92</v>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +103% / 중요공시 2건 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K23" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1346,14 +1348,14 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F24" s="15" t="n">
         <v>0</v>
@@ -1361,25 +1363,27 @@
       <c r="G24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="18" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="I24" s="19" t="n">
-        <v>-1.46</v>
+      <c r="H24" s="19" t="n">
+        <v>-3.54</v>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>3.52</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="n">
-        <v/>
+          <t>중요공시 2건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1387,42 +1391,40 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>KS인더스트리</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="18" t="n">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="I25" s="18" t="n">
-        <v>63.37</v>
+        <v>0</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v/>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +200%</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1430,251 +1432,251 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>-5.04</v>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>YTN</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="22" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="I27" s="23" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="J27" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K27" s="24" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>카카오</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="22" t="n">
+        <v>-3.03</v>
+      </c>
+      <c r="I28" s="22" t="n">
+        <v>-3.99</v>
+      </c>
+      <c r="J28" s="24" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="24" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>보령</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I29" s="22" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="J29" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 5건 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>비투엔</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="22" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="I30" s="22" t="n">
+        <v>-10.58</v>
+      </c>
+      <c r="J30" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
           <t>현대건설</t>
         </is>
       </c>
-      <c r="D26" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="15" t="n">
+      <c r="D31" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" s="18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="I26" s="19" t="n">
-        <v>-1.98</v>
-      </c>
-      <c r="J26" s="17" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +200%</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="inlineStr">
+      <c r="G31" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="22" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="I31" s="22" t="n">
+        <v>-7.19</v>
+      </c>
+      <c r="J31" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K31" s="24" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>대한항공</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="F27" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="19" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="I27" s="19" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="J27" s="17" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>시지트로닉스</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="18" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="I28" s="18" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K28" s="17" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>방산</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I29" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J29" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K29" s="17" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="n">
-        <v>17</v>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>카카오</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="18" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="I30" s="19" t="n">
-        <v>-1.98</v>
-      </c>
-      <c r="J30" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K30" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>SK이노베이션</t>
-        </is>
-      </c>
-      <c r="D31" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F31" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="18" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="I31" s="18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J31" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K31" s="17" t="n">
-        <v/>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1682,33 +1684,33 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>엠젠솔루션</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>-14.46</v>
+        <v>-3.65</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>-15.82</v>
-      </c>
-      <c r="J32" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 6건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K32" s="23" t="inlineStr">
+        <v>-4.95</v>
+      </c>
+      <c r="J32" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K32" s="24" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1717,7 +1719,7 @@
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1725,7 +1727,7 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>보령</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
@@ -1741,26 +1743,26 @@
         <v>0</v>
       </c>
       <c r="H33" s="22" t="n">
-        <v>-5.04</v>
+        <v>-4.86</v>
       </c>
       <c r="I33" s="22" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J33" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 4건 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K33" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+        <v>-17.68</v>
+      </c>
+      <c r="J33" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1768,7 +1770,7 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
@@ -1783,25 +1785,25 @@
       <c r="G34" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="24" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="I34" s="24" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="J34" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="n">
+      <c r="H34" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I34" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J34" s="24" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K34" s="24" t="n">
         <v/>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1809,14 +1811,14 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F35" s="20" t="n">
         <v>0</v>
@@ -1824,27 +1826,25 @@
       <c r="G35" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="24" t="n">
-        <v>34.11</v>
-      </c>
-      <c r="I35" s="24" t="n">
-        <v>58.66</v>
-      </c>
-      <c r="J35" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K35" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
+      <c r="H35" s="22" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="I35" s="22" t="n">
+        <v>-6.57</v>
+      </c>
+      <c r="J35" s="24" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K35" s="24" t="n">
+        <v/>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>YTN</t>
+          <t>defense stock</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
@@ -1867,25 +1867,27 @@
       <c r="G36" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="24" t="n">
-        <v>18.96</v>
-      </c>
-      <c r="I36" s="24" t="n">
-        <v>32.21</v>
-      </c>
-      <c r="J36" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="n">
+      <c r="H36" s="20" t="n">
         <v/>
+      </c>
+      <c r="I36" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J36" s="24" t="inlineStr">
+        <is>
+          <t>Google 급상승 검색어 등장 (US)</t>
+        </is>
+      </c>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1893,7 +1895,7 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
@@ -1908,25 +1910,25 @@
       <c r="G37" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="24" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I37" s="22" t="n">
-        <v>-2.92</v>
-      </c>
-      <c r="J37" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K37" s="23" t="n">
+      <c r="H37" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I37" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J37" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K37" s="24" t="n">
         <v/>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1934,14 +1936,14 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>DB하이텍</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F38" s="20" t="n">
         <v>0</v>
@@ -1949,27 +1951,25 @@
       <c r="G38" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="24" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="I38" s="24" t="n">
-        <v>8.23</v>
-      </c>
-      <c r="J38" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K38" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H38" s="23" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="I38" s="23" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="J38" s="24" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K38" s="24" t="n">
+        <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1977,14 +1977,14 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F39" s="20" t="n">
         <v>0</v>
@@ -1992,27 +1992,25 @@
       <c r="G39" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="24" t="n">
-        <v>11.85</v>
-      </c>
-      <c r="I39" s="24" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="J39" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K39" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H39" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I39" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J39" s="24" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K39" s="24" t="n">
+        <v/>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2020,42 +2018,42 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>코닉오토메이션</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F40" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H40" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I40" s="22" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="J40" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K40" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>0</v>
+      </c>
+      <c r="H40" s="22" t="n">
+        <v>-5.91</v>
+      </c>
+      <c r="I40" s="23" t="n">
+        <v>29.35</v>
+      </c>
+      <c r="J40" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +211% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K40" s="24" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2063,7 +2061,7 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>동아지질</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
@@ -2078,27 +2076,25 @@
       <c r="G41" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="24" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="I41" s="24" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="J41" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K41" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H41" s="23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I41" s="22" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="J41" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K41" s="24" t="n">
+        <v/>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -2106,42 +2102,42 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>태영건설</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E42" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F42" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I42" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J42" s="23" t="inlineStr">
-        <is>
-          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K42" s="23" t="inlineStr">
-        <is>
-          <t>네이버</t>
+        <v>3</v>
+      </c>
+      <c r="H42" s="23" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I42" s="22" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="J42" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K42" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B43" s="20" t="n">
@@ -2149,40 +2145,42 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="D43" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E43" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F43" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="24" t="n">
-        <v>0.35</v>
+        <v>3</v>
+      </c>
+      <c r="H43" s="22" t="n">
+        <v>-0.28</v>
       </c>
       <c r="I43" s="22" t="n">
-        <v>-7.79</v>
-      </c>
-      <c r="J43" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K43" s="23" t="n">
-        <v/>
+        <v>-3.24</v>
+      </c>
+      <c r="J43" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K43" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B44" s="20" t="n">
@@ -2190,7 +2188,7 @@
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="D44" s="20" t="n">
@@ -2205,25 +2203,27 @@
       <c r="G44" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I44" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J44" s="23" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K44" s="23" t="n">
-        <v/>
+      <c r="H44" s="22" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="I44" s="22" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="J44" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K44" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B45" s="20" t="n">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>카카오게임즈</t>
         </is>
       </c>
       <c r="D45" s="20" t="n">
@@ -2246,150 +2246,152 @@
       <c r="G45" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="24" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I45" s="22" t="n">
-        <v>-4.03</v>
-      </c>
-      <c r="J45" s="23" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K45" s="23" t="n">
+      <c r="H45" s="22" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="I45" s="23" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="J45" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K45" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>로봇</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="20" t="n">
         <v/>
       </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B46" s="25" t="n">
-        <v>33</v>
-      </c>
-      <c r="C46" s="26" t="inlineStr">
-        <is>
-          <t>삼익제약</t>
-        </is>
-      </c>
-      <c r="D46" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="27" t="n">
-        <v>20.46</v>
-      </c>
-      <c r="I46" s="27" t="n">
-        <v>30.51</v>
-      </c>
-      <c r="J46" s="28" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K46" s="28" t="n">
+      <c r="I46" s="20" t="n">
         <v/>
       </c>
+      <c r="J46" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K46" s="24" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B47" s="25" t="n">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="n">
         <v>34</v>
       </c>
-      <c r="C47" s="26" t="inlineStr">
-        <is>
-          <t>삼성중공업</t>
-        </is>
-      </c>
-      <c r="D47" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E47" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G47" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="29" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="I47" s="29" t="n">
-        <v>-1.64</v>
-      </c>
-      <c r="J47" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K47" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>전기차</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I47" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J47" s="24" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K47" s="24" t="n">
+        <v/>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B48" s="25" t="n">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="n">
         <v>35</v>
       </c>
-      <c r="C48" s="26" t="inlineStr">
-        <is>
-          <t>한컴위드</t>
-        </is>
-      </c>
-      <c r="D48" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F48" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="27" t="n">
-        <v>32.24</v>
-      </c>
-      <c r="I48" s="27" t="n">
-        <v>44.28</v>
-      </c>
-      <c r="J48" s="28" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K48" s="28" t="n">
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>LG전자</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="22" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="I48" s="22" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="J48" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K48" s="24" t="n">
         <v/>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -2397,7 +2399,7 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>동국산업</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
@@ -2413,14 +2415,14 @@
         <v>0</v>
       </c>
       <c r="H49" s="27" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="I49" s="29" t="n">
-        <v>-4.52</v>
+        <v>10.06</v>
+      </c>
+      <c r="I49" s="27" t="n">
+        <v>34.79</v>
       </c>
       <c r="J49" s="28" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
+          <t>네이버 검색 당일 +131%</t>
         </is>
       </c>
       <c r="K49" s="28" t="inlineStr">
@@ -2432,7 +2434,7 @@
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2440,7 +2442,7 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>하이젠알앤엠</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -2456,24 +2458,26 @@
         <v>0</v>
       </c>
       <c r="H50" s="27" t="n">
-        <v>27.11</v>
+        <v>6.27</v>
       </c>
       <c r="I50" s="27" t="n">
-        <v>8.029999999999999</v>
+        <v>66.36</v>
       </c>
       <c r="J50" s="28" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K50" s="28" t="n">
-        <v/>
+          <t>네이버 검색 당일 +108%</t>
+        </is>
+      </c>
+      <c r="K50" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2481,7 +2485,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2496,27 +2500,27 @@
       <c r="G51" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="29" t="n">
-        <v>-9.18</v>
+      <c r="H51" s="27" t="n">
+        <v>0.15</v>
       </c>
       <c r="I51" s="27" t="n">
-        <v>19.8</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="J51" s="28" t="inlineStr">
         <is>
-          <t>중요공시 6건</t>
+          <t>네이버 검색 당일 +88% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K51" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2524,7 +2528,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2539,27 +2543,25 @@
       <c r="G52" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="27" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="I52" s="29" t="n">
-        <v>-17.9</v>
+      <c r="H52" s="29" t="n">
+        <v>-9.890000000000001</v>
+      </c>
+      <c r="I52" s="27" t="n">
+        <v>14.21</v>
       </c>
       <c r="J52" s="28" t="inlineStr">
         <is>
-          <t>중요공시 6건</t>
-        </is>
-      </c>
-      <c r="K52" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K52" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2567,7 +2569,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>다보링크</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2582,27 +2584,25 @@
       <c r="G53" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="27" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I53" s="29" t="n">
-        <v>-9.289999999999999</v>
+      <c r="H53" s="29" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="I53" s="27" t="n">
+        <v>9.359999999999999</v>
       </c>
       <c r="J53" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K53" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K53" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2610,42 +2610,40 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>KEC</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E54" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F54" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G54" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="27" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="I54" s="29" t="n">
-        <v>-0.25</v>
+        <v>4.06</v>
+      </c>
+      <c r="I54" s="27" t="n">
+        <v>12.38</v>
       </c>
       <c r="J54" s="28" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K54" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K54" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2653,7 +2651,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>비투엔</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2669,10 +2667,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="29" t="n">
-        <v>-0.25</v>
+        <v>-2.86</v>
       </c>
       <c r="I55" s="29" t="n">
-        <v>-8.34</v>
+        <v>-5.79</v>
       </c>
       <c r="J55" s="28" t="inlineStr">
         <is>
@@ -2688,7 +2686,7 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2696,7 +2694,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>코윈로보틱스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2712,10 +2710,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="27" t="n">
-        <v>6.47</v>
+        <v>13.34</v>
       </c>
       <c r="I56" s="27" t="n">
-        <v>4.65</v>
+        <v>8.49</v>
       </c>
       <c r="J56" s="28" t="inlineStr">
         <is>
@@ -2729,7 +2727,7 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2737,7 +2735,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>원텍</t>
+          <t>아리바이오랩</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2752,11 +2750,11 @@
       <c r="G57" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="29" t="n">
-        <v>-0.8</v>
+      <c r="H57" s="27" t="n">
+        <v>8.01</v>
       </c>
       <c r="I57" s="27" t="n">
-        <v>0.8100000000000001</v>
+        <v>22.95</v>
       </c>
       <c r="J57" s="28" t="inlineStr">
         <is>
@@ -2772,7 +2770,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2780,7 +2778,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2796,24 +2794,26 @@
         <v>0</v>
       </c>
       <c r="H58" s="27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="I58" s="27" t="n">
-        <v>5.17</v>
+        <v>5.84</v>
+      </c>
+      <c r="I58" s="29" t="n">
+        <v>-2.37</v>
       </c>
       <c r="J58" s="28" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K58" s="28" t="n">
-        <v/>
+          <t>중요공시 5건</t>
+        </is>
+      </c>
+      <c r="K58" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>한컴</t>
+          <t>화일약품</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2836,25 +2836,27 @@
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="I59" s="27" t="n">
-        <v>3.74</v>
+      <c r="H59" s="29" t="n">
+        <v>-22.09</v>
+      </c>
+      <c r="I59" s="29" t="n">
+        <v>-12.79</v>
       </c>
       <c r="J59" s="28" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K59" s="28" t="n">
-        <v/>
+          <t>중요공시 4건</t>
+        </is>
+      </c>
+      <c r="K59" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2862,7 +2864,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2878,24 +2880,26 @@
         <v>0</v>
       </c>
       <c r="H60" s="29" t="n">
-        <v>-1.78</v>
+        <v>-5.97</v>
       </c>
       <c r="I60" s="29" t="n">
-        <v>-5.46</v>
+        <v>-22.8</v>
       </c>
       <c r="J60" s="28" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K60" s="28" t="n">
-        <v/>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K60" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2903,7 +2907,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>스테이블코인</t>
+          <t>한전산업</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2918,25 +2922,27 @@
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="25" t="n">
-        <v/>
-      </c>
-      <c r="I61" s="25" t="n">
-        <v/>
+      <c r="H61" s="29" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="I61" s="29" t="n">
+        <v>-5.72</v>
       </c>
       <c r="J61" s="28" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K61" s="28" t="n">
-        <v/>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K61" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2944,42 +2950,42 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E62" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F62" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="25" t="n">
-        <v/>
-      </c>
-      <c r="I62" s="25" t="n">
-        <v/>
+      <c r="H62" s="27" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I62" s="27" t="n">
+        <v>0.53</v>
       </c>
       <c r="J62" s="28" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
         </is>
       </c>
       <c r="K62" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -2987,35 +2993,35 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>위메이드맥스</t>
+          <t>크라우드웍스</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E63" s="25" t="n">
+      <c r="G63" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="27" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="I63" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="F63" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="29" t="n">
-        <v>-4.33</v>
-      </c>
-      <c r="I63" s="27" t="n">
-        <v>25.31</v>
-      </c>
       <c r="J63" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +70%</t>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
         </is>
       </c>
       <c r="K63" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
@@ -3112,22 +3118,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3143,22 +3149,22 @@
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H4" s="25" t="n"/>
@@ -3167,60 +3173,64 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H5" s="25" t="n"/>
-      <c r="I5" s="25" t="n"/>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="I5" s="29" t="n">
+        <v>-5.33</v>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H6" s="25" t="n"/>
@@ -3229,7 +3239,7 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
@@ -3246,60 +3256,60 @@
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>0.8</v>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H7" s="29" t="n">
+        <v>-2.96</v>
       </c>
       <c r="I7" s="29" t="n">
-        <v>-7.05</v>
+        <v>-8.76</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H8" s="27" t="n">
-        <v>1.88</v>
+        <v>1.2</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>-4.46</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
@@ -3316,144 +3326,148 @@
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H9" s="25" t="n"/>
-      <c r="I9" s="25" t="n"/>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="I9" s="29" t="n">
+        <v>-1.85</v>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H10" s="27" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="I10" s="29" t="n">
-        <v>-1.46</v>
-      </c>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H10" s="25" t="n"/>
+      <c r="I10" s="25" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H11" s="29" t="n">
-        <v>-6.43</v>
-      </c>
-      <c r="I11" s="29" t="n">
-        <v>-12.46</v>
+        <v>-3.54</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>3.52</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H12" s="25" t="n"/>
-      <c r="I12" s="25" t="n"/>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H12" s="29" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="I12" s="29" t="n">
+        <v>-5.04</v>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H13" s="25" t="n"/>
@@ -3462,248 +3476,248 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>KS인더스트리</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H14" s="27" t="n">
-        <v>8.460000000000001</v>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H14" s="29" t="n">
+        <v>-4.71</v>
       </c>
       <c r="I14" s="27" t="n">
-        <v>63.37</v>
+        <v>38.38</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H15" s="29" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="I15" s="29" t="n">
-        <v>-2.49</v>
+        <v>-2.56</v>
+      </c>
+      <c r="I15" s="27" t="n">
+        <v>18.92</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>YTN</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E16" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H16" s="27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="I16" s="29" t="n">
-        <v>-1.98</v>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H16" s="29" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="I16" s="27" t="n">
+        <v>19.98</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>보령</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H17" s="27" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="I17" s="27" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
+      </c>
+      <c r="I17" s="29" t="n">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H18" s="25" t="n"/>
-      <c r="I18" s="25" t="n"/>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H18" s="29" t="n">
+        <v>-3.65</v>
+      </c>
+      <c r="I18" s="29" t="n">
+        <v>-4.95</v>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>시지트로닉스</t>
+          <t>비투엔</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H19" s="27" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="I19" s="27" t="n">
-        <v>7.83</v>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H19" s="29" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="I19" s="29" t="n">
+        <v>-10.58</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H20" s="27" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>-1.98</v>
-      </c>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H20" s="25" t="n"/>
+      <c r="I20" s="25" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>보령</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -3720,25 +3734,25 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H21" s="29" t="n">
-        <v>-5.04</v>
+        <v>-4.86</v>
       </c>
       <c r="I21" s="29" t="n">
-        <v>-0.8</v>
+        <v>-17.68</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
@@ -3755,25 +3769,25 @@
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H22" s="27" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="I22" s="27" t="n">
-        <v>3.96</v>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H22" s="29" t="n">
+        <v>-3.03</v>
+      </c>
+      <c r="I22" s="29" t="n">
+        <v>-3.99</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>엠젠솔루션</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -3790,60 +3804,60 @@
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H23" s="29" t="n">
-        <v>-14.46</v>
+        <v>-3.73</v>
       </c>
       <c r="I23" s="29" t="n">
-        <v>-15.82</v>
+        <v>-7.19</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>YTN</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H24" s="27" t="n">
-        <v>18.96</v>
-      </c>
-      <c r="I24" s="27" t="n">
-        <v>32.21</v>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H24" s="29" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="I24" s="29" t="n">
+        <v>-6.57</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>DB하이텍</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
@@ -3860,25 +3874,25 @@
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H25" s="27" t="n">
-        <v>34.11</v>
+        <v>5.34</v>
       </c>
       <c r="I25" s="27" t="n">
-        <v>58.66</v>
+        <v>13.18</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>defense stock</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
@@ -3895,95 +3909,83 @@
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H26" s="27" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I26" s="29" t="n">
-        <v>-2.92</v>
-      </c>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H26" s="25" t="n"/>
+      <c r="I26" s="25" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H27" s="27" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I27" s="29" t="n">
-        <v>-7.79</v>
-      </c>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H27" s="25" t="n"/>
+      <c r="I27" s="25" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H28" s="27" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="I28" s="27" t="n">
-        <v>8.23</v>
-      </c>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H28" s="25" t="n"/>
+      <c r="I28" s="25" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
@@ -4000,21 +4002,25 @@
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H29" s="25" t="n"/>
-      <c r="I29" s="25" t="n"/>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H29" s="29" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="I29" s="29" t="n">
+        <v>-2.4</v>
+      </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>동아지질</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
@@ -4031,25 +4037,21 @@
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H30" s="27" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="I30" s="27" t="n">
-        <v>6.79</v>
-      </c>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="25" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
@@ -4066,19 +4068,19 @@
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H31" s="27" t="n">
-        <v>11.85</v>
-      </c>
-      <c r="I31" s="27" t="n">
-        <v>5.38</v>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H31" s="29" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="I31" s="29" t="n">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -4101,25 +4103,25 @@
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H32" s="27" t="n">
-        <v>0.5</v>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H32" s="29" t="n">
+        <v>-0.28</v>
       </c>
       <c r="I32" s="29" t="n">
-        <v>-2.15</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
@@ -4136,21 +4138,25 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H33" s="25" t="n"/>
-      <c r="I33" s="25" t="n"/>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H33" s="27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I33" s="29" t="n">
+        <v>-1.62</v>
+      </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
@@ -4167,130 +4173,126 @@
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H34" s="27" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I34" s="29" t="n">
-        <v>-4.03</v>
-      </c>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H34" s="25" t="n"/>
+      <c r="I34" s="25" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>카카오게임즈</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H35" s="29" t="n">
-        <v>-1.78</v>
-      </c>
-      <c r="I35" s="29" t="n">
-        <v>-5.46</v>
+        <v>-2.73</v>
+      </c>
+      <c r="I35" s="27" t="n">
+        <v>8.960000000000001</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>코닉오토메이션</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H36" s="27" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="I36" s="29" t="n">
-        <v>-4.52</v>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H36" s="29" t="n">
+        <v>-5.91</v>
+      </c>
+      <c r="I36" s="27" t="n">
+        <v>29.35</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>태영건설</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H37" s="27" t="n">
-        <v>0.37</v>
+        <v>0.18</v>
       </c>
       <c r="I37" s="29" t="n">
-        <v>-17.9</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>다보링크</t>
+          <t>KEC</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4307,25 +4309,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H38" s="27" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I38" s="29" t="n">
-        <v>-9.289999999999999</v>
+        <v>4.06</v>
+      </c>
+      <c r="I38" s="27" t="n">
+        <v>12.38</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4342,25 +4344,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H39" s="29" t="n">
-        <v>-9.18</v>
-      </c>
-      <c r="I39" s="27" t="n">
-        <v>19.8</v>
+        <v>-5.97</v>
+      </c>
+      <c r="I39" s="29" t="n">
+        <v>-22.8</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>비투엔</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4377,25 +4379,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H40" s="29" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="I40" s="29" t="n">
-        <v>-8.34</v>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H40" s="27" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="I40" s="27" t="n">
+        <v>8.49</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4412,25 +4414,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H41" s="29" t="n">
-        <v>-5.2</v>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H41" s="27" t="n">
+        <v>5.84</v>
       </c>
       <c r="I41" s="29" t="n">
-        <v>-1.64</v>
+        <v>-2.37</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>동국산업</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4447,25 +4449,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H42" s="27" t="n">
-        <v>20.46</v>
+        <v>10.06</v>
       </c>
       <c r="I42" s="27" t="n">
-        <v>30.51</v>
+        <v>34.79</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>스테이블코인</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4482,21 +4484,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H43" s="25" t="n"/>
-      <c r="I43" s="25" t="n"/>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H43" s="27" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I43" s="27" t="n">
+        <v>0.53</v>
+      </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4513,25 +4519,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H44" s="27" t="n">
-        <v>3.87</v>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H44" s="29" t="n">
+        <v>-2.86</v>
       </c>
       <c r="I44" s="29" t="n">
-        <v>-0.25</v>
+        <v>-5.79</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4548,25 +4554,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H45" s="27" t="n">
-        <v>2.62</v>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H45" s="29" t="n">
+        <v>-9.890000000000001</v>
       </c>
       <c r="I45" s="27" t="n">
-        <v>5.17</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4583,21 +4589,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H46" s="25" t="n"/>
-      <c r="I46" s="25" t="n"/>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H46" s="27" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="I46" s="27" t="n">
+        <v>66.36</v>
+      </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>원텍</t>
+          <t>아리바이오랩</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4614,25 +4624,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H47" s="29" t="n">
-        <v>-0.8</v>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H47" s="27" t="n">
+        <v>8.01</v>
       </c>
       <c r="I47" s="27" t="n">
-        <v>0.8100000000000001</v>
+        <v>22.95</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>코윈로보틱스</t>
+          <t>크라우드웍스</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4649,25 +4659,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H48" s="27" t="n">
-        <v>6.47</v>
+        <v>8.43</v>
       </c>
       <c r="I48" s="27" t="n">
-        <v>4.65</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>하이젠알앤엠</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4684,25 +4694,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H49" s="27" t="n">
-        <v>27.11</v>
+        <v>0.15</v>
       </c>
       <c r="I49" s="27" t="n">
-        <v>8.029999999999999</v>
+        <v>74.34999999999999</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>한컴</t>
+          <t>한전산업</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4719,25 +4729,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H50" s="27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="I50" s="27" t="n">
-        <v>3.74</v>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H50" s="29" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="I50" s="29" t="n">
+        <v>-5.72</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>화일약품</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4754,54 +4764,54 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H51" s="27" t="n">
-        <v>32.24</v>
-      </c>
-      <c r="I51" s="27" t="n">
-        <v>44.28</v>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H51" s="29" t="n">
+        <v>-22.09</v>
+      </c>
+      <c r="I51" s="29" t="n">
+        <v>-12.79</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>위메이드맥스</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C52" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D52" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H52" s="29" t="n">
-        <v>-4.33</v>
+        <v>-0.27</v>
       </c>
       <c r="I52" s="27" t="n">
-        <v>25.31</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -4885,19 +4895,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4916,19 +4926,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4947,19 +4957,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -4978,19 +4988,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5002,26 +5012,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5033,7 +5043,7 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
@@ -5047,12 +5057,12 @@
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5064,26 +5074,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5095,26 +5105,26 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B10" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="36" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G10" s="37" t="inlineStr">
@@ -5126,26 +5136,26 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B11" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E11" s="36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F11" s="37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G11" s="37" t="inlineStr">
@@ -5155,71 +5165,63 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>18</v>
-      </c>
-      <c r="D12" s="36" t="n">
-        <v>18</v>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="F12" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G12" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>이차전지</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G12" s="28" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="35" t="inlineStr">
-        <is>
-          <t>인공지능</t>
-        </is>
-      </c>
-      <c r="B13" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="36" t="n">
-        <v>16</v>
-      </c>
-      <c r="D13" s="36" t="n">
-        <v>16</v>
-      </c>
-      <c r="E13" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="F13" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G13" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>AI반도체</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G13" s="28" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>이차전지</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5246,7 +5248,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5273,7 +5275,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5300,7 +5302,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5327,7 +5329,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5354,7 +5356,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -5381,7 +5383,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -258,14 +258,14 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -273,14 +273,14 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-17 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-18 06:54</t>
         </is>
       </c>
     </row>
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-17) 상위: 반도체  점수 30.0점</t>
+          <t>⚡ 최신(2026-09-18) 상위: 반도체  점수 46.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-17) 상위: 바이오  점수 26.0점</t>
+          <t>⚡ 최신(2026-09-18) 상위: 인공지능  점수 17.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-17) 상위: SK하이닉스  점수 17.0점</t>
+          <t>⚡ 최신(2026-09-18) 상위: SK하이닉스  점수 16.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -967,14 +967,14 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1026,24 +1026,26 @@
         <v>0</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>2.63</v>
+        <v>0.51</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>-5.33</v>
+        <v>-4.7</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="n">
-        <v/>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1051,7 +1053,7 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
@@ -1066,27 +1068,25 @@
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="15" t="n">
+      <c r="H17" s="18" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>-4.83</v>
+      </c>
+      <c r="J17" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K17" s="17" t="n">
         <v/>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1109,27 +1109,25 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="19" t="n">
-        <v>-2.96</v>
-      </c>
-      <c r="I18" s="19" t="n">
-        <v>-8.76</v>
+      <c r="H18" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v/>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1137,14 +1135,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1152,15 +1150,15 @@
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I19" s="19" t="n">
-        <v>-5.94</v>
+      <c r="H19" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v/>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="n">
@@ -1170,7 +1168,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1178,14 +1176,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>네이버</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1201,19 +1199,17 @@
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1221,14 +1217,14 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1236,15 +1232,15 @@
       <c r="G21" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="19" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="I21" s="19" t="n">
-        <v>-1.85</v>
+      <c r="H21" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v/>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="n">
@@ -1254,7 +1250,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1262,42 +1258,42 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>비투엔</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="19" t="n">
-        <v>-4.71</v>
-      </c>
-      <c r="I22" s="18" t="n">
-        <v>38.38</v>
+      <c r="H22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="19" t="n">
+        <v>-8.470000000000001</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +194% / 중요공시 2건 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1305,42 +1301,42 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>KS인더스트리</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>-2.56</v>
+        <v>-3.39</v>
       </c>
       <c r="I23" s="18" t="n">
-        <v>18.92</v>
+        <v>39.51</v>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +103% / 중요공시 2건 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 3건 / 중요공시 3일 +50% / 중요공시 7일 +200%</t>
         </is>
       </c>
       <c r="K23" s="17" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1348,14 +1344,14 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F24" s="15" t="n">
         <v>0</v>
@@ -1363,27 +1359,27 @@
       <c r="G24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="19" t="n">
-        <v>-3.54</v>
-      </c>
-      <c r="I24" s="18" t="n">
-        <v>3.52</v>
+      <c r="H24" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v/>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1391,14 +1387,14 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F25" s="15" t="n">
         <v>0</v>
@@ -1406,25 +1402,27 @@
       <c r="G25" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I25" s="15" t="n">
-        <v/>
+      <c r="H25" s="18" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I25" s="19" t="n">
+        <v>-3.15</v>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="n">
-        <v/>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1432,7 +1430,7 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
@@ -1447,25 +1445,27 @@
       <c r="G26" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="19" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="I26" s="19" t="n">
-        <v>-5.04</v>
+      <c r="H26" s="18" t="n">
+        <v>18.49</v>
+      </c>
+      <c r="I26" s="18" t="n">
+        <v>67.90000000000001</v>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="n">
-        <v/>
+          <t>네이버 검색 당일 +484% / 중요공시 2건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B27" s="20" t="n">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>YTN</t>
+          <t>대모</t>
         </is>
       </c>
       <c r="D27" s="20" t="n">
@@ -1489,24 +1489,24 @@
         <v>0</v>
       </c>
       <c r="H27" s="22" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="I27" s="23" t="n">
-        <v>19.98</v>
-      </c>
-      <c r="J27" s="24" t="inlineStr">
+        <v>5.24</v>
+      </c>
+      <c r="I27" s="22" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J27" s="23" t="inlineStr">
         <is>
           <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
-      <c r="K27" s="24" t="n">
+      <c r="K27" s="23" t="n">
         <v/>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B28" s="20" t="n">
@@ -1514,40 +1514,42 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="D28" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E28" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F28" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G28" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="22" t="n">
-        <v>-3.03</v>
-      </c>
-      <c r="I28" s="22" t="n">
-        <v>-3.99</v>
-      </c>
-      <c r="J28" s="24" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K28" s="24" t="n">
-        <v/>
+        <v>2.02</v>
+      </c>
+      <c r="I28" s="24" t="n">
+        <v>-3.58</v>
+      </c>
+      <c r="J28" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B29" s="20" t="n">
@@ -1555,7 +1557,7 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>보령</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="D29" s="20" t="n">
@@ -1570,27 +1572,27 @@
       <c r="G29" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="23" t="n">
-        <v>1.5</v>
+      <c r="H29" s="22" t="n">
+        <v>15.53</v>
       </c>
       <c r="I29" s="22" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="J29" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 5건 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K29" s="24" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+        <v>9.94</v>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K29" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1598,42 +1600,40 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>비투엔</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G30" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="22" t="n">
-        <v>-1.64</v>
-      </c>
-      <c r="I30" s="22" t="n">
-        <v>-10.58</v>
-      </c>
-      <c r="J30" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K30" s="24" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
+      <c r="H30" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="24" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1641,42 +1641,40 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>제일기획</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F31" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H31" s="22" t="n">
-        <v>-3.73</v>
-      </c>
-      <c r="I31" s="22" t="n">
-        <v>-7.19</v>
-      </c>
-      <c r="J31" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K31" s="24" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H31" s="24" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="I31" s="24" t="n">
+        <v>-7.26</v>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K31" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1684,42 +1682,42 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G32" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H32" s="22" t="n">
-        <v>-3.65</v>
-      </c>
-      <c r="I32" s="22" t="n">
-        <v>-4.95</v>
-      </c>
-      <c r="J32" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K32" s="24" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>0</v>
+      </c>
+      <c r="H32" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I32" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1727,14 +1725,14 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>0</v>
@@ -1742,18 +1740,18 @@
       <c r="G33" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="22" t="n">
-        <v>-4.86</v>
-      </c>
-      <c r="I33" s="22" t="n">
-        <v>-17.68</v>
-      </c>
-      <c r="J33" s="24" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K33" s="24" t="inlineStr">
+      <c r="H33" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I33" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J33" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K33" s="23" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -1762,7 +1760,7 @@
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1770,14 +1768,14 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>0</v>
@@ -1785,25 +1783,25 @@
       <c r="G34" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I34" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J34" s="24" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K34" s="24" t="n">
+      <c r="H34" s="22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I34" s="22" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="J34" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="n">
         <v/>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1811,14 +1809,14 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F35" s="20" t="n">
         <v>0</v>
@@ -1827,24 +1825,26 @@
         <v>0</v>
       </c>
       <c r="H35" s="22" t="n">
-        <v>-1.89</v>
+        <v>2.34</v>
       </c>
       <c r="I35" s="22" t="n">
-        <v>-6.57</v>
-      </c>
-      <c r="J35" s="24" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K35" s="24" t="n">
-        <v/>
+        <v>23.2</v>
+      </c>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +261% / 중요공시 2건</t>
+        </is>
+      </c>
+      <c r="K35" s="23" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1852,14 +1852,14 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>defense stock</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>0</v>
@@ -1867,27 +1867,27 @@
       <c r="G36" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I36" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J36" s="24" t="inlineStr">
-        <is>
-          <t>Google 급상승 검색어 등장 (US)</t>
-        </is>
-      </c>
-      <c r="K36" s="24" t="inlineStr">
-        <is>
-          <t>Google</t>
+      <c r="H36" s="24" t="n">
+        <v>-8.470000000000001</v>
+      </c>
+      <c r="I36" s="22" t="n">
+        <v>61.76</v>
+      </c>
+      <c r="J36" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +190% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1895,14 +1895,14 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F37" s="20" t="n">
         <v>0</v>
@@ -1910,25 +1910,25 @@
       <c r="G37" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I37" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J37" s="24" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K37" s="24" t="n">
+      <c r="H37" s="24" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="I37" s="24" t="n">
+        <v>-5.91</v>
+      </c>
+      <c r="J37" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K37" s="23" t="n">
         <v/>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1936,40 +1936,42 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>DB하이텍</t>
+          <t>시선AI</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F38" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="23" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="I38" s="23" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="J38" s="24" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K38" s="24" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H38" s="24" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="I38" s="22" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="J38" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1977,14 +1979,14 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F39" s="20" t="n">
         <v>0</v>
@@ -1992,406 +1994,412 @@
       <c r="G39" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="20" t="n">
+      <c r="H39" s="22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I39" s="24" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="J39" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K39" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B40" s="25" t="n">
+        <v>27</v>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>아이티센피엔에스</t>
+        </is>
+      </c>
+      <c r="D40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="27" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="I40" s="28" t="n">
+        <v>74.28</v>
+      </c>
+      <c r="J40" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +316%</t>
+        </is>
+      </c>
+      <c r="K40" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="n">
+        <v>28</v>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>동국산업</t>
+        </is>
+      </c>
+      <c r="D41" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="28" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="I41" s="28" t="n">
+        <v>40.24</v>
+      </c>
+      <c r="J41" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +310%</t>
+        </is>
+      </c>
+      <c r="K41" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="n">
+        <v>29</v>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>빛샘전자</t>
+        </is>
+      </c>
+      <c r="D42" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="27" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="I42" s="28" t="n">
+        <v>47.26</v>
+      </c>
+      <c r="J42" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +245%</t>
+        </is>
+      </c>
+      <c r="K42" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="n">
+        <v>30</v>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>아톤</t>
+        </is>
+      </c>
+      <c r="D43" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="27" t="n">
+        <v>-3.81</v>
+      </c>
+      <c r="I43" s="28" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="J43" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +191%</t>
+        </is>
+      </c>
+      <c r="K43" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B44" s="25" t="n">
+        <v>31</v>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>한컴위드</t>
+        </is>
+      </c>
+      <c r="D44" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="27" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="I44" s="28" t="n">
+        <v>37.47</v>
+      </c>
+      <c r="J44" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +156%</t>
+        </is>
+      </c>
+      <c r="K44" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B45" s="25" t="n">
+        <v>32</v>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>뷰티스킨</t>
+        </is>
+      </c>
+      <c r="D45" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="27" t="n">
+        <v>-8.66</v>
+      </c>
+      <c r="I45" s="28" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="J45" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +74% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K45" s="29" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B46" s="25" t="n">
+        <v>33</v>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>아티스트컴퍼니</t>
+        </is>
+      </c>
+      <c r="D46" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="27" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="I46" s="28" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="J46" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K46" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B47" s="25" t="n">
+        <v>34</v>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>센서뷰</t>
+        </is>
+      </c>
+      <c r="D47" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="28" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="I47" s="28" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="J47" s="29" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K47" s="29" t="n">
         <v/>
       </c>
-      <c r="I39" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J39" s="24" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K39" s="24" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B40" s="20" t="n">
-        <v>27</v>
-      </c>
-      <c r="C40" s="21" t="inlineStr">
-        <is>
-          <t>코닉오토메이션</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E40" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="22" t="n">
-        <v>-5.91</v>
-      </c>
-      <c r="I40" s="23" t="n">
-        <v>29.35</v>
-      </c>
-      <c r="J40" s="24" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +211% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K40" s="24" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B41" s="20" t="n">
-        <v>28</v>
-      </c>
-      <c r="C41" s="21" t="inlineStr">
-        <is>
-          <t>삼성전자우</t>
-        </is>
-      </c>
-      <c r="D41" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I41" s="22" t="n">
-        <v>-1.62</v>
-      </c>
-      <c r="J41" s="24" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K41" s="24" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="n">
-        <v>29</v>
-      </c>
-      <c r="C42" s="21" t="inlineStr">
-        <is>
-          <t>태영건설</t>
-        </is>
-      </c>
-      <c r="D42" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E42" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H42" s="23" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I42" s="22" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="J42" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K42" s="24" t="inlineStr">
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B48" s="25" t="n">
+        <v>35</v>
+      </c>
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="D48" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="28" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I48" s="28" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J48" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K48" s="29" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B43" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="C43" s="21" t="inlineStr">
-        <is>
-          <t>삼성바이오로직스</t>
-        </is>
-      </c>
-      <c r="D43" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E43" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H43" s="22" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="I43" s="22" t="n">
-        <v>-3.24</v>
-      </c>
-      <c r="J43" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K43" s="24" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B44" s="20" t="n">
-        <v>31</v>
-      </c>
-      <c r="C44" s="21" t="inlineStr">
-        <is>
-          <t>삼성E&amp;A</t>
-        </is>
-      </c>
-      <c r="D44" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E44" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F44" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="22" t="n">
-        <v>-1.76</v>
-      </c>
-      <c r="I44" s="22" t="n">
-        <v>-1.18</v>
-      </c>
-      <c r="J44" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K44" s="24" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="n">
-        <v>32</v>
-      </c>
-      <c r="C45" s="21" t="inlineStr">
-        <is>
-          <t>카카오게임즈</t>
-        </is>
-      </c>
-      <c r="D45" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E45" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F45" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="22" t="n">
-        <v>-2.73</v>
-      </c>
-      <c r="I45" s="23" t="n">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="J45" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K45" s="24" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B46" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="C46" s="21" t="inlineStr">
-        <is>
-          <t>로봇</t>
-        </is>
-      </c>
-      <c r="D46" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E46" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I46" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J46" s="24" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K46" s="24" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B47" s="20" t="n">
-        <v>34</v>
-      </c>
-      <c r="C47" s="21" t="inlineStr">
-        <is>
-          <t>전기차</t>
-        </is>
-      </c>
-      <c r="D47" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F47" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I47" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J47" s="24" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K47" s="24" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B48" s="20" t="n">
-        <v>35</v>
-      </c>
-      <c r="C48" s="21" t="inlineStr">
-        <is>
-          <t>LG전자</t>
-        </is>
-      </c>
-      <c r="D48" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E48" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F48" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="22" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="I48" s="22" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="J48" s="24" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K48" s="24" t="n">
-        <v/>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -2399,7 +2407,7 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>동국산업</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
@@ -2414,27 +2422,25 @@
       <c r="G49" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="27" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="I49" s="27" t="n">
-        <v>34.79</v>
-      </c>
-      <c r="J49" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +131%</t>
-        </is>
-      </c>
-      <c r="K49" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="H49" s="28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I49" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="29" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K49" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2442,42 +2448,42 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E50" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F50" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G50" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="27" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="I50" s="27" t="n">
-        <v>66.36</v>
-      </c>
-      <c r="J50" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +108%</t>
-        </is>
-      </c>
-      <c r="K50" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H50" s="28" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="I50" s="28" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="J50" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K50" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2485,7 +2491,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2500,27 +2506,25 @@
       <c r="G51" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="27" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I51" s="27" t="n">
-        <v>74.34999999999999</v>
-      </c>
-      <c r="J51" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +88% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K51" s="28" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
+      <c r="H51" s="28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I51" s="28" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="J51" s="29" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K51" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2528,7 +2532,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2543,25 +2547,25 @@
       <c r="G52" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="29" t="n">
-        <v>-9.890000000000001</v>
-      </c>
-      <c r="I52" s="27" t="n">
-        <v>14.21</v>
-      </c>
-      <c r="J52" s="28" t="inlineStr">
+      <c r="H52" s="28" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="I52" s="28" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="J52" s="29" t="inlineStr">
         <is>
           <t>매일경제 헤드라인 언급</t>
         </is>
       </c>
-      <c r="K52" s="28" t="n">
+      <c r="K52" s="29" t="n">
         <v/>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2569,7 +2573,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2584,25 +2588,25 @@
       <c r="G53" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="29" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="I53" s="27" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="J53" s="28" t="inlineStr">
+      <c r="H53" s="28" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="I53" s="28" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J53" s="29" t="inlineStr">
         <is>
           <t>매일경제 헤드라인 언급</t>
         </is>
       </c>
-      <c r="K53" s="28" t="n">
+      <c r="K53" s="29" t="n">
         <v/>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2610,7 +2614,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>KEC</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2625,25 +2629,27 @@
       <c r="G54" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="27" t="n">
-        <v>4.06</v>
+      <c r="H54" s="28" t="n">
+        <v>5.38</v>
       </c>
       <c r="I54" s="27" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="J54" s="28" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K54" s="28" t="n">
-        <v/>
+        <v>-20.83</v>
+      </c>
+      <c r="J54" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 7건</t>
+        </is>
+      </c>
+      <c r="K54" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2651,33 +2657,33 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>모티브링크</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E55" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F55" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G55" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="29" t="n">
-        <v>-2.86</v>
-      </c>
-      <c r="I55" s="29" t="n">
-        <v>-5.79</v>
-      </c>
-      <c r="J55" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K55" s="28" t="inlineStr">
+      <c r="H55" s="28" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="I55" s="28" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="J55" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K55" s="29" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -2686,7 +2692,7 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2694,7 +2700,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>한전산업</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2709,25 +2715,27 @@
       <c r="G56" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="27" t="n">
-        <v>13.34</v>
+      <c r="H56" s="28" t="n">
+        <v>2.29</v>
       </c>
       <c r="I56" s="27" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="J56" s="28" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K56" s="28" t="n">
-        <v/>
+        <v>-1.74</v>
+      </c>
+      <c r="J56" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K56" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2735,7 +2743,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>아리바이오랩</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2750,27 +2758,27 @@
       <c r="G57" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="27" t="n">
-        <v>8.01</v>
+      <c r="H57" s="28" t="n">
+        <v>1.81</v>
       </c>
       <c r="I57" s="27" t="n">
-        <v>22.95</v>
-      </c>
-      <c r="J57" s="28" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K57" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
+        <v>-5.53</v>
+      </c>
+      <c r="J57" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K57" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2778,7 +2786,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2793,18 +2801,18 @@
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="27" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="I58" s="29" t="n">
-        <v>-2.37</v>
-      </c>
-      <c r="J58" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 5건</t>
-        </is>
-      </c>
-      <c r="K58" s="28" t="inlineStr">
+      <c r="H58" s="28" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I58" s="28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="J58" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K58" s="29" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -2813,7 +2821,7 @@
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2821,7 +2829,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>화일약품</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2836,27 +2844,27 @@
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="29" t="n">
-        <v>-22.09</v>
-      </c>
-      <c r="I59" s="29" t="n">
-        <v>-12.79</v>
-      </c>
-      <c r="J59" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 4건</t>
-        </is>
-      </c>
-      <c r="K59" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="H59" s="25" t="n">
+        <v/>
+      </c>
+      <c r="I59" s="25" t="n">
+        <v/>
+      </c>
+      <c r="J59" s="29" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K59" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2864,7 +2872,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2879,27 +2887,25 @@
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="29" t="n">
-        <v>-5.97</v>
-      </c>
-      <c r="I60" s="29" t="n">
-        <v>-22.8</v>
-      </c>
-      <c r="J60" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K60" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H60" s="28" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="I60" s="27" t="n">
+        <v>-10.45</v>
+      </c>
+      <c r="J60" s="29" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K60" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2907,7 +2913,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>한전산업</t>
+          <t>카카오뱅크</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2922,27 +2928,25 @@
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="29" t="n">
-        <v>-3.06</v>
-      </c>
-      <c r="I61" s="29" t="n">
-        <v>-5.72</v>
-      </c>
-      <c r="J61" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K61" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H61" s="27" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="I61" s="27" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="J61" s="29" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K61" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2950,42 +2954,40 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>RFHIC</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E62" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="27" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="I62" s="27" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="J62" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K62" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H62" s="28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I62" s="28" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="J62" s="29" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K62" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -2993,36 +2995,34 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>크라우드웍스</t>
+          <t>비츠로셀</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E63" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F63" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="27" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="I63" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K63" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H63" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="I63" s="28" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="J63" s="29" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K63" s="29" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3118,22 +3118,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3142,29 +3142,29 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H4" s="25" t="n"/>
@@ -3180,35 +3180,35 @@
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H5" s="27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="I5" s="29" t="n">
-        <v>-5.33</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I5" s="27" t="n">
+        <v>-4.7</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
@@ -3225,148 +3225,140 @@
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H6" s="25" t="n"/>
-      <c r="I6" s="25" t="n"/>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I6" s="27" t="n">
+        <v>-4.83</v>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H7" s="29" t="n">
-        <v>-2.96</v>
-      </c>
-      <c r="I7" s="29" t="n">
-        <v>-8.76</v>
-      </c>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H7" s="25" t="n"/>
+      <c r="I7" s="25" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I8" s="29" t="n">
-        <v>-5.94</v>
-      </c>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="25" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>네이버</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H9" s="29" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="I9" s="29" t="n">
-        <v>-1.85</v>
-      </c>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H9" s="25" t="n"/>
+      <c r="I9" s="25" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H10" s="25" t="n"/>
@@ -3375,99 +3367,99 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>KS인더스트리</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H11" s="29" t="n">
-        <v>-3.54</v>
-      </c>
-      <c r="I11" s="27" t="n">
-        <v>3.52</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>-3.39</v>
+      </c>
+      <c r="I11" s="28" t="n">
+        <v>39.51</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>비투엔</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H12" s="29" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="I12" s="29" t="n">
-        <v>-5.04</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="27" t="n">
+        <v>-8.470000000000001</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H13" s="25" t="n"/>
@@ -3476,42 +3468,42 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H14" s="29" t="n">
-        <v>-4.71</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H14" s="28" t="n">
+        <v>0.45</v>
       </c>
       <c r="I14" s="27" t="n">
-        <v>38.38</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -3528,25 +3520,25 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H15" s="29" t="n">
-        <v>-2.56</v>
-      </c>
-      <c r="I15" s="27" t="n">
-        <v>18.92</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H15" s="28" t="n">
+        <v>18.49</v>
+      </c>
+      <c r="I15" s="28" t="n">
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>YTN</t>
+          <t>대모</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -3563,25 +3555,25 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H16" s="29" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="I16" s="27" t="n">
-        <v>19.98</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H16" s="28" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="I16" s="28" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>보령</t>
+          <t>제일기획</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -3598,25 +3590,25 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H17" s="27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>-1.01</v>
+        <v>-0.57</v>
+      </c>
+      <c r="I17" s="27" t="n">
+        <v>-7.26</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -3633,25 +3625,21 @@
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H18" s="29" t="n">
-        <v>-3.65</v>
-      </c>
-      <c r="I18" s="29" t="n">
-        <v>-4.95</v>
-      </c>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="25" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>비투엔</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -3668,25 +3656,25 @@
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H19" s="29" t="n">
-        <v>-1.64</v>
-      </c>
-      <c r="I19" s="29" t="n">
-        <v>-10.58</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H19" s="28" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="I19" s="28" t="n">
+        <v>9.94</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -3703,21 +3691,25 @@
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H20" s="25" t="n"/>
-      <c r="I20" s="25" t="n"/>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H20" s="28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I20" s="27" t="n">
+        <v>-3.58</v>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -3734,565 +3726,581 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H21" s="29" t="n">
-        <v>-4.86</v>
-      </c>
-      <c r="I21" s="29" t="n">
-        <v>-17.68</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H21" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="27" t="n">
+        <v>-7.7</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H22" s="29" t="n">
-        <v>-3.03</v>
-      </c>
-      <c r="I22" s="29" t="n">
-        <v>-3.99</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H22" s="28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I22" s="28" t="n">
+        <v>3.08</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H23" s="29" t="n">
-        <v>-3.73</v>
-      </c>
-      <c r="I23" s="29" t="n">
-        <v>-7.19</v>
-      </c>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="25" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E24" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H24" s="29" t="n">
-        <v>-1.89</v>
-      </c>
-      <c r="I24" s="29" t="n">
-        <v>-6.57</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H24" s="27" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="I24" s="27" t="n">
+        <v>-5.91</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>DB하이텍</t>
+          <t>시선AI</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E25" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H25" s="27" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="I25" s="27" t="n">
-        <v>13.18</v>
+        <v>-2.27</v>
+      </c>
+      <c r="I25" s="28" t="n">
+        <v>5.01</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>defense stock</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H26" s="25" t="n"/>
-      <c r="I26" s="25" t="n"/>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H26" s="28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I26" s="27" t="n">
+        <v>-1.66</v>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H27" s="25" t="n"/>
-      <c r="I27" s="25" t="n"/>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H27" s="28" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I27" s="28" t="n">
+        <v>23.2</v>
+      </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H28" s="25" t="n"/>
-      <c r="I28" s="25" t="n"/>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H28" s="27" t="n">
+        <v>-8.470000000000001</v>
+      </c>
+      <c r="I28" s="28" t="n">
+        <v>61.76</v>
+      </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>RFHIC</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H29" s="29" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="I29" s="29" t="n">
-        <v>-2.4</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H29" s="28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I29" s="28" t="n">
+        <v>5.06</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H30" s="25" t="n"/>
-      <c r="I30" s="25" t="n"/>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H30" s="28" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="I30" s="27" t="n">
+        <v>-10.45</v>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H31" s="29" t="n">
-        <v>-1.76</v>
-      </c>
-      <c r="I31" s="29" t="n">
-        <v>-1.18</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H31" s="28" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I31" s="27" t="n">
+        <v>-5.53</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H32" s="29" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="I32" s="29" t="n">
-        <v>-3.24</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H32" s="28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I32" s="25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E33" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H33" s="27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I33" s="29" t="n">
-        <v>-1.62</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H33" s="28" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="I33" s="27" t="n">
+        <v>-20.83</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>동국산업</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H34" s="25" t="n"/>
-      <c r="I34" s="25" t="n"/>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H34" s="28" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="I34" s="28" t="n">
+        <v>40.24</v>
+      </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>카카오게임즈</t>
+          <t>모티브링크</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H35" s="29" t="n">
-        <v>-2.73</v>
-      </c>
-      <c r="I35" s="27" t="n">
-        <v>8.960000000000001</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H35" s="28" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="I35" s="28" t="n">
+        <v>6.19</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>코닉오토메이션</t>
+          <t>뷰티스킨</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H36" s="29" t="n">
-        <v>-5.91</v>
-      </c>
-      <c r="I36" s="27" t="n">
-        <v>29.35</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H36" s="27" t="n">
+        <v>-8.66</v>
+      </c>
+      <c r="I36" s="28" t="n">
+        <v>23.34</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>태영건설</t>
+          <t>비츠로셀</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E37" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H37" s="27" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I37" s="29" t="n">
-        <v>-1.06</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H37" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="I37" s="28" t="n">
+        <v>3.89</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>KEC</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4309,25 +4317,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H38" s="27" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="I38" s="27" t="n">
-        <v>12.38</v>
+        <v>-3.24</v>
+      </c>
+      <c r="I38" s="28" t="n">
+        <v>47.26</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4344,25 +4352,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H39" s="29" t="n">
-        <v>-5.97</v>
-      </c>
-      <c r="I39" s="29" t="n">
-        <v>-22.8</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H39" s="28" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I39" s="28" t="n">
+        <v>1.98</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4379,25 +4387,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H40" s="27" t="n">
-        <v>13.34</v>
-      </c>
-      <c r="I40" s="27" t="n">
-        <v>8.49</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H40" s="28" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I40" s="28" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4414,25 +4422,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H41" s="27" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="I41" s="29" t="n">
-        <v>-2.37</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H41" s="28" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="I41" s="28" t="n">
+        <v>45.38</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>동국산업</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4449,25 +4457,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H42" s="27" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="I42" s="27" t="n">
-        <v>34.79</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H42" s="28" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="I42" s="28" t="n">
+        <v>17.85</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>아이티센피엔에스</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4484,25 +4492,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H43" s="27" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="I43" s="27" t="n">
-        <v>0.53</v>
+        <v>-4.6</v>
+      </c>
+      <c r="I43" s="28" t="n">
+        <v>74.28</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4519,25 +4527,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H44" s="29" t="n">
-        <v>-2.86</v>
-      </c>
-      <c r="I44" s="29" t="n">
-        <v>-5.79</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H44" s="27" t="n">
+        <v>-3.81</v>
+      </c>
+      <c r="I44" s="28" t="n">
+        <v>25.49</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>아티스트컴퍼니</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4554,25 +4562,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H45" s="29" t="n">
-        <v>-9.890000000000001</v>
-      </c>
-      <c r="I45" s="27" t="n">
-        <v>14.21</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H45" s="27" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="I45" s="28" t="n">
+        <v>13.04</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4589,25 +4597,21 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H46" s="27" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="I46" s="27" t="n">
-        <v>66.36</v>
-      </c>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H46" s="25" t="n"/>
+      <c r="I46" s="25" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>아리바이오랩</t>
+          <t>카카오뱅크</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4624,25 +4628,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H47" s="27" t="n">
-        <v>8.01</v>
+        <v>-0.48</v>
       </c>
       <c r="I47" s="27" t="n">
-        <v>22.95</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>크라우드웍스</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4659,25 +4663,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H48" s="27" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="I48" s="27" t="n">
-        <v>2</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H48" s="28" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="I48" s="28" t="n">
+        <v>5.42</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>한전산업</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4694,25 +4698,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H49" s="27" t="n">
-        <v>0.15</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H49" s="28" t="n">
+        <v>2.29</v>
       </c>
       <c r="I49" s="27" t="n">
-        <v>74.34999999999999</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>한전산업</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4729,25 +4733,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H50" s="29" t="n">
-        <v>-3.06</v>
-      </c>
-      <c r="I50" s="29" t="n">
-        <v>-5.72</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H50" s="27" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="I50" s="28" t="n">
+        <v>37.47</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>화일약품</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4764,25 +4768,25 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H51" s="29" t="n">
-        <v>-22.09</v>
-      </c>
-      <c r="I51" s="29" t="n">
-        <v>-12.79</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H51" s="28" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="I51" s="28" t="n">
+        <v>11.27</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -4799,19 +4803,19 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H52" s="29" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="I52" s="27" t="n">
-        <v>9.359999999999999</v>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H52" s="28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I52" s="28" t="n">
+        <v>7.47</v>
       </c>
     </row>
   </sheetData>
@@ -4895,19 +4899,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4926,19 +4930,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4957,19 +4961,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -4988,19 +4992,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5019,19 +5023,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5050,19 +5054,19 @@
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5074,7 +5078,7 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
@@ -5088,12 +5092,12 @@
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5105,26 +5109,26 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B10" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="36" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G10" s="37" t="inlineStr">
@@ -5143,19 +5147,19 @@
         <v>1</v>
       </c>
       <c r="C11" s="36" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E11" s="36" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F11" s="37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G11" s="37" t="inlineStr">
@@ -5184,12 +5188,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="28" t="inlineStr">
+      <c r="F12" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G12" s="28" t="inlineStr"/>
+      <c r="G12" s="29" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
@@ -5211,17 +5215,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="28" t="inlineStr">
+      <c r="F13" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G13" s="28" t="inlineStr"/>
+      <c r="G13" s="29" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5238,17 +5242,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="28" t="inlineStr">
+      <c r="F14" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G14" s="28" t="inlineStr"/>
+      <c r="G14" s="29" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5265,17 +5269,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="28" t="inlineStr">
+      <c r="F15" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G15" s="28" t="inlineStr"/>
+      <c r="G15" s="29" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5292,17 +5296,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="28" t="inlineStr">
+      <c r="F16" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G16" s="28" t="inlineStr"/>
+      <c r="G16" s="29" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5319,17 +5323,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="28" t="inlineStr">
+      <c r="F17" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G17" s="28" t="inlineStr"/>
+      <c r="G17" s="29" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5346,17 +5350,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="28" t="inlineStr">
+      <c r="F18" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G18" s="28" t="inlineStr"/>
+      <c r="G18" s="29" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -5373,17 +5377,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="28" t="inlineStr">
+      <c r="F19" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G19" s="28" t="inlineStr"/>
+      <c r="G19" s="29" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -5400,12 +5404,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="28" t="inlineStr">
+      <c r="F20" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G20" s="28" t="inlineStr"/>
+      <c r="G20" s="29" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -5427,12 +5431,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F21" s="28" t="inlineStr">
+      <c r="F21" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G21" s="28" t="inlineStr"/>
+      <c r="G21" s="29" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -5454,12 +5458,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F22" s="28" t="inlineStr">
+      <c r="F22" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G22" s="28" t="inlineStr"/>
+      <c r="G22" s="29" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -5481,12 +5485,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F23" s="28" t="inlineStr">
+      <c r="F23" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G23" s="28" t="inlineStr"/>
+      <c r="G23" s="29" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -5508,12 +5512,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F24" s="28" t="inlineStr">
+      <c r="F24" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G24" s="28" t="inlineStr"/>
+      <c r="G24" s="29" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -258,11 +258,11 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-18 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-19 06:54</t>
         </is>
       </c>
     </row>
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-18) 상위: 반도체  점수 46.0점</t>
+          <t>⚡ 최신(2026-09-19) 상위: 반도체  점수 50.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-18) 상위: 인공지능  점수 17.0점</t>
+          <t>⚡ 최신(2026-09-19) 상위: 바이오  점수 20.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-18) 상위: SK하이닉스  점수 16.0점</t>
+          <t>⚡ 최신(2026-09-19) 상위: 삼성전자  점수 19.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -967,14 +967,14 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1026,26 +1026,24 @@
         <v>0</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="I16" s="19" t="n">
-        <v>-4.7</v>
+        <v>1.56</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>0.19</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,14 +1051,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1068,25 +1066,27 @@
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="18" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <v>-4.83</v>
+      <c r="H17" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v/>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="n">
-        <v/>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K17" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1109,25 +1109,27 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v/>
+      <c r="H18" s="18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <v>2.04</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="n">
-        <v/>
+          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1135,14 +1137,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1150,15 +1152,15 @@
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v/>
+      <c r="H19" s="18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>-0.86</v>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="n">
@@ -1168,7 +1170,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1176,14 +1178,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1191,15 +1193,15 @@
       <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v/>
+      <c r="H20" s="19" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>-0.36</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K20" s="17" t="n">
@@ -1209,7 +1211,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1217,14 +1219,14 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1232,25 +1234,27 @@
       <c r="G21" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v/>
+      <c r="H21" s="18" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I21" s="18" t="n">
+        <v>12.69</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K21" s="17" t="n">
-        <v/>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K21" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1258,42 +1262,42 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>비투엔</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="19" t="n">
-        <v>-8.470000000000001</v>
+      <c r="H22" s="19" t="n">
+        <v>-8.24</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>52.37</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 한국경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +952% / 중요공시 2건 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1301,42 +1305,42 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>KS인더스트리</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" s="19" t="n">
-        <v>-3.39</v>
-      </c>
-      <c r="I23" s="18" t="n">
-        <v>39.51</v>
+        <v>0</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v/>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +50% / 중요공시 7일 +200%</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K23" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1344,14 +1348,14 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F24" s="15" t="n">
         <v>0</v>
@@ -1367,19 +1371,17 @@
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1387,14 +1389,14 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" s="15" t="n">
         <v>0</v>
@@ -1402,27 +1404,25 @@
       <c r="G25" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="18" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="I25" s="19" t="n">
-        <v>-3.15</v>
+      <c r="H25" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v/>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
@@ -1445,27 +1445,27 @@
       <c r="G26" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="18" t="n">
-        <v>18.49</v>
-      </c>
-      <c r="I26" s="18" t="n">
-        <v>67.90000000000001</v>
+      <c r="H26" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v/>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +484% / 중요공시 2건 / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K26" s="17" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B27" s="20" t="n">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>대모</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="D27" s="20" t="n">
@@ -1488,25 +1488,27 @@
       <c r="G27" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="22" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="I27" s="22" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="J27" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K27" s="23" t="n">
+      <c r="H27" s="20" t="n">
         <v/>
+      </c>
+      <c r="I27" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J27" s="22" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K27" s="22" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B28" s="20" t="n">
@@ -1514,42 +1516,42 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="D28" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E28" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F28" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G28" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="22" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="I28" s="24" t="n">
-        <v>-3.58</v>
-      </c>
-      <c r="J28" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K28" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="H28" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I28" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="22" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B29" s="20" t="n">
@@ -1557,33 +1559,33 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="D29" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F29" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G29" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="22" t="n">
-        <v>15.53</v>
-      </c>
-      <c r="I29" s="22" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="J29" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K29" s="23" t="inlineStr">
+      <c r="H29" s="23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I29" s="24" t="n">
+        <v>-3.38</v>
+      </c>
+      <c r="J29" s="22" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 3일 +50%</t>
+        </is>
+      </c>
+      <c r="K29" s="22" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1592,7 +1594,7 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1600,40 +1602,42 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>프리티</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="20" t="n">
-        <v>0</v>
+      <c r="H30" s="24" t="n">
+        <v>-29.91</v>
       </c>
       <c r="I30" s="24" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="n">
-        <v/>
+        <v>-35.77</v>
+      </c>
+      <c r="J30" s="22" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 3일 +200%</t>
+        </is>
+      </c>
+      <c r="K30" s="22" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1641,14 +1645,14 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>제일기획</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F31" s="20" t="n">
         <v>0</v>
@@ -1656,25 +1660,27 @@
       <c r="G31" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="24" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="I31" s="24" t="n">
-        <v>-7.26</v>
-      </c>
-      <c r="J31" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K31" s="23" t="n">
+      <c r="H31" s="20" t="n">
         <v/>
+      </c>
+      <c r="I31" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J31" s="22" t="inlineStr">
+        <is>
+          <t>Google 급상승 검색어 등장 (KR)</t>
+        </is>
+      </c>
+      <c r="K31" s="22" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1682,14 +1688,14 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F32" s="20" t="n">
         <v>0</v>
@@ -1697,27 +1703,25 @@
       <c r="G32" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="20" t="n">
+      <c r="H32" s="23" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I32" s="24" t="n">
+        <v>-4.18</v>
+      </c>
+      <c r="J32" s="22" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K32" s="22" t="n">
         <v/>
-      </c>
-      <c r="I32" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J32" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K32" s="23" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1725,14 +1729,14 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>뷰티스킨</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>0</v>
@@ -1740,27 +1744,27 @@
       <c r="G33" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I33" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J33" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K33" s="23" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H33" s="23" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="I33" s="23" t="n">
+        <v>28.54</v>
+      </c>
+      <c r="J33" s="22" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +173% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K33" s="22" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1768,14 +1772,14 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>비츠로테크</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>0</v>
@@ -1783,25 +1787,27 @@
       <c r="G34" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="I34" s="22" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="J34" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="n">
-        <v/>
+      <c r="H34" s="23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I34" s="23" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="J34" s="22" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +108% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K34" s="22" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1809,7 +1815,7 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
@@ -1824,27 +1830,25 @@
       <c r="G35" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="22" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="I35" s="22" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="J35" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +261% / 중요공시 2건</t>
-        </is>
-      </c>
-      <c r="K35" s="23" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
+      <c r="H35" s="24" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="I35" s="23" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J35" s="22" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K35" s="22" t="n">
+        <v/>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1852,7 +1856,7 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>한섬</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
@@ -1867,27 +1871,27 @@
       <c r="G36" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="24" t="n">
-        <v>-8.470000000000001</v>
-      </c>
-      <c r="I36" s="22" t="n">
-        <v>61.76</v>
-      </c>
-      <c r="J36" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +190% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
+      <c r="H36" s="23" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="I36" s="23" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="J36" s="22" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K36" s="22" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1895,7 +1899,7 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>LS마린솔루션</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
@@ -1910,25 +1914,27 @@
       <c r="G37" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="24" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="I37" s="24" t="n">
-        <v>-5.91</v>
-      </c>
-      <c r="J37" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K37" s="23" t="n">
-        <v/>
+      <c r="H37" s="23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I37" s="23" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="J37" s="22" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K37" s="22" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1936,85 +1942,83 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>시선AI</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F38" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H38" s="24" t="n">
-        <v>-2.27</v>
-      </c>
-      <c r="I38" s="22" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="J38" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K38" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H38" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I38" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J38" s="22" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K38" s="22" t="n">
+        <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="n">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B39" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="C39" s="21" t="inlineStr">
-        <is>
-          <t>에이피알</t>
-        </is>
-      </c>
-      <c r="D39" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E39" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="I39" s="24" t="n">
-        <v>-1.66</v>
-      </c>
-      <c r="J39" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K39" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>아이티센피엔에스</t>
+        </is>
+      </c>
+      <c r="D39" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="27" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="I39" s="28" t="n">
+        <v>66.41</v>
+      </c>
+      <c r="J39" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +700%</t>
+        </is>
+      </c>
+      <c r="K39" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -2022,7 +2026,7 @@
       </c>
       <c r="C40" s="26" t="inlineStr">
         <is>
-          <t>아이티센피엔에스</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="D40" s="25" t="n">
@@ -2037,15 +2041,15 @@
       <c r="G40" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="27" t="n">
-        <v>-4.6</v>
+      <c r="H40" s="28" t="n">
+        <v>3.86</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>74.28</v>
+        <v>57.08</v>
       </c>
       <c r="J40" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +316%</t>
+          <t>네이버 검색 당일 +366%</t>
         </is>
       </c>
       <c r="K40" s="29" t="inlineStr">
@@ -2057,7 +2061,7 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -2065,7 +2069,7 @@
       </c>
       <c r="C41" s="26" t="inlineStr">
         <is>
-          <t>동국산업</t>
+          <t>큐라티스</t>
         </is>
       </c>
       <c r="D41" s="25" t="n">
@@ -2080,15 +2084,15 @@
       <c r="G41" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="28" t="n">
-        <v>4.87</v>
+      <c r="H41" s="27" t="n">
+        <v>-5.09</v>
       </c>
       <c r="I41" s="28" t="n">
-        <v>40.24</v>
+        <v>58.13</v>
       </c>
       <c r="J41" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +310%</t>
+          <t>네이버 검색 당일 +261%</t>
         </is>
       </c>
       <c r="K41" s="29" t="inlineStr">
@@ -2100,7 +2104,7 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -2108,7 +2112,7 @@
       </c>
       <c r="C42" s="26" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>한켐</t>
         </is>
       </c>
       <c r="D42" s="25" t="n">
@@ -2124,14 +2128,14 @@
         <v>0</v>
       </c>
       <c r="H42" s="27" t="n">
-        <v>-3.24</v>
+        <v>-5.41</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>47.26</v>
+        <v>37.38</v>
       </c>
       <c r="J42" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +245%</t>
+          <t>네이버 검색 당일 +259%</t>
         </is>
       </c>
       <c r="K42" s="29" t="inlineStr">
@@ -2143,7 +2147,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -2167,14 +2171,14 @@
         <v>0</v>
       </c>
       <c r="H43" s="27" t="n">
-        <v>-3.81</v>
+        <v>-3.27</v>
       </c>
       <c r="I43" s="28" t="n">
-        <v>25.49</v>
+        <v>16.48</v>
       </c>
       <c r="J43" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +191%</t>
+          <t>네이버 검색 당일 +245%</t>
         </is>
       </c>
       <c r="K43" s="29" t="inlineStr">
@@ -2186,7 +2190,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -2194,7 +2198,7 @@
       </c>
       <c r="C44" s="26" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="D44" s="25" t="n">
@@ -2210,14 +2214,14 @@
         <v>0</v>
       </c>
       <c r="H44" s="27" t="n">
-        <v>-3.77</v>
+        <v>-2.92</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>37.47</v>
+        <v>50.25</v>
       </c>
       <c r="J44" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +156%</t>
+          <t>네이버 검색 당일 +244%</t>
         </is>
       </c>
       <c r="K44" s="29" t="inlineStr">
@@ -2229,7 +2233,7 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -2237,7 +2241,7 @@
       </c>
       <c r="C45" s="26" t="inlineStr">
         <is>
-          <t>뷰티스킨</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="D45" s="25" t="n">
@@ -2253,26 +2257,26 @@
         <v>0</v>
       </c>
       <c r="H45" s="27" t="n">
-        <v>-8.66</v>
+        <v>-3.33</v>
       </c>
       <c r="I45" s="28" t="n">
-        <v>23.34</v>
+        <v>25.13</v>
       </c>
       <c r="J45" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +74% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +219%</t>
         </is>
       </c>
       <c r="K45" s="29" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -2280,7 +2284,7 @@
       </c>
       <c r="C46" s="26" t="inlineStr">
         <is>
-          <t>아티스트컴퍼니</t>
+          <t>진양화학</t>
         </is>
       </c>
       <c r="D46" s="25" t="n">
@@ -2296,26 +2300,26 @@
         <v>0</v>
       </c>
       <c r="H46" s="27" t="n">
-        <v>-12.57</v>
+        <v>-6.03</v>
       </c>
       <c r="I46" s="28" t="n">
-        <v>13.04</v>
+        <v>22.47</v>
       </c>
       <c r="J46" s="29" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>네이버 검색 당일 +132%</t>
         </is>
       </c>
       <c r="K46" s="29" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -2323,7 +2327,7 @@
       </c>
       <c r="C47" s="26" t="inlineStr">
         <is>
-          <t>센서뷰</t>
+          <t>티엠씨</t>
         </is>
       </c>
       <c r="D47" s="25" t="n">
@@ -2339,24 +2343,26 @@
         <v>0</v>
       </c>
       <c r="H47" s="28" t="n">
-        <v>23.98</v>
+        <v>7.8</v>
       </c>
       <c r="I47" s="28" t="n">
-        <v>45.38</v>
+        <v>37.22</v>
       </c>
       <c r="J47" s="29" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K47" s="29" t="n">
-        <v/>
+          <t>네이버 검색 당일 +126%</t>
+        </is>
+      </c>
+      <c r="K47" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -2364,42 +2370,42 @@
       </c>
       <c r="C48" s="26" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E48" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F48" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G48" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>5.9</v>
+        <v>3.53</v>
       </c>
       <c r="I48" s="28" t="n">
-        <v>0.9399999999999999</v>
+        <v>33.67</v>
       </c>
       <c r="J48" s="29" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>네이버 검색 당일 +118%</t>
         </is>
       </c>
       <c r="K48" s="29" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -2407,7 +2413,7 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>한컴라이프케어</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
@@ -2423,24 +2429,26 @@
         <v>0</v>
       </c>
       <c r="H49" s="28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I49" s="25" t="n">
-        <v>0</v>
+        <v>4.85</v>
+      </c>
+      <c r="I49" s="28" t="n">
+        <v>20.23</v>
       </c>
       <c r="J49" s="29" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K49" s="29" t="n">
-        <v/>
+          <t>네이버 검색 당일 +116%</t>
+        </is>
+      </c>
+      <c r="K49" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2448,42 +2456,42 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>진영</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E50" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F50" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G50" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>18.43</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="I50" s="28" t="n">
-        <v>17.85</v>
+        <v>11.76</v>
       </c>
       <c r="J50" s="29" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>네이버 검색 당일 +57% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K50" s="29" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2491,7 +2499,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2507,24 +2515,26 @@
         <v>0</v>
       </c>
       <c r="H51" s="28" t="n">
-        <v>3.45</v>
+        <v>1.45</v>
       </c>
       <c r="I51" s="28" t="n">
-        <v>7.47</v>
+        <v>21.95</v>
       </c>
       <c r="J51" s="29" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K51" s="29" t="n">
-        <v/>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K51" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2532,7 +2542,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2548,24 +2558,26 @@
         <v>0</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>11.85</v>
+        <v>13.23</v>
       </c>
       <c r="I52" s="28" t="n">
-        <v>11.27</v>
+        <v>30.04</v>
       </c>
       <c r="J52" s="29" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K52" s="29" t="n">
-        <v/>
+          <t>네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K52" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2573,7 +2585,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2588,25 +2600,27 @@
       <c r="G53" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="28" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="I53" s="28" t="n">
-        <v>5.42</v>
+      <c r="H53" s="27" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="I53" s="27" t="n">
+        <v>-1.64</v>
       </c>
       <c r="J53" s="29" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K53" s="29" t="n">
-        <v/>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K53" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2614,7 +2628,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2630,26 +2644,24 @@
         <v>0</v>
       </c>
       <c r="H54" s="28" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="I54" s="27" t="n">
-        <v>-20.83</v>
+        <v>0.41</v>
+      </c>
+      <c r="I54" s="28" t="n">
+        <v>1.86</v>
       </c>
       <c r="J54" s="29" t="inlineStr">
         <is>
-          <t>중요공시 7건</t>
-        </is>
-      </c>
-      <c r="K54" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K54" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2657,7 +2669,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>모티브링크</t>
+          <t>엔에프씨</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2673,26 +2685,24 @@
         <v>0</v>
       </c>
       <c r="H55" s="28" t="n">
-        <v>5.93</v>
+        <v>28.91</v>
       </c>
       <c r="I55" s="28" t="n">
-        <v>6.19</v>
+        <v>16.2</v>
       </c>
       <c r="J55" s="29" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K55" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K55" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2700,7 +2710,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>한전산업</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2715,27 +2725,25 @@
       <c r="G56" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="28" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="I56" s="27" t="n">
-        <v>-1.74</v>
+      <c r="H56" s="27" t="n">
+        <v>-4.76</v>
+      </c>
+      <c r="I56" s="28" t="n">
+        <v>1.83</v>
       </c>
       <c r="J56" s="29" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K56" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K56" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2743,7 +2751,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2759,26 +2767,26 @@
         <v>0</v>
       </c>
       <c r="H57" s="28" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="I57" s="27" t="n">
-        <v>-5.53</v>
+        <v>10.28</v>
+      </c>
+      <c r="I57" s="28" t="n">
+        <v>7.29</v>
       </c>
       <c r="J57" s="29" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K57" s="29" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2786,7 +2794,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2801,15 +2809,15 @@
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="28" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="I58" s="28" t="n">
-        <v>1.98</v>
+      <c r="H58" s="27" t="n">
+        <v>-29.89</v>
+      </c>
+      <c r="I58" s="27" t="n">
+        <v>-44.49</v>
       </c>
       <c r="J58" s="29" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 10건</t>
         </is>
       </c>
       <c r="K58" s="29" t="inlineStr">
@@ -2821,7 +2829,7 @@
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2829,7 +2837,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>파이온엑스</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2844,27 +2852,27 @@
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="25" t="n">
-        <v/>
-      </c>
-      <c r="I59" s="25" t="n">
-        <v/>
+      <c r="H59" s="27" t="n">
+        <v>-22.35</v>
+      </c>
+      <c r="I59" s="27" t="n">
+        <v>-33.73</v>
       </c>
       <c r="J59" s="29" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급</t>
+          <t>중요공시 4건</t>
         </is>
       </c>
       <c r="K59" s="29" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2872,7 +2880,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>아티스트컴퍼니</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2887,25 +2895,27 @@
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="28" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="I60" s="27" t="n">
-        <v>-10.45</v>
+      <c r="H60" s="27" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="I60" s="28" t="n">
+        <v>11.13</v>
       </c>
       <c r="J60" s="29" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K60" s="29" t="n">
-        <v/>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K60" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2913,7 +2923,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>카카오뱅크</t>
+          <t>한전산업</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2928,25 +2938,27 @@
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="27" t="n">
-        <v>-0.48</v>
+      <c r="H61" s="28" t="n">
+        <v>0.31</v>
       </c>
       <c r="I61" s="27" t="n">
-        <v>-2.34</v>
+        <v>-4.05</v>
       </c>
       <c r="J61" s="29" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K61" s="29" t="n">
-        <v/>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K61" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2954,40 +2966,42 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>RFHIC</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E62" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F62" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="28" t="n">
-        <v>3.65</v>
+      <c r="H62" s="27" t="n">
+        <v>-1.57</v>
       </c>
       <c r="I62" s="28" t="n">
-        <v>5.06</v>
+        <v>2.87</v>
       </c>
       <c r="J62" s="29" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K62" s="29" t="n">
-        <v/>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K62" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -2995,7 +3009,7 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>비츠로셀</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
@@ -3010,19 +3024,21 @@
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="I63" s="28" t="n">
-        <v>3.89</v>
+      <c r="H63" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="27" t="n">
+        <v>-3.86</v>
       </c>
       <c r="J63" s="29" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K63" s="29" t="n">
-        <v/>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K63" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3118,22 +3134,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3142,29 +3158,29 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H4" s="25" t="n"/>
@@ -3173,337 +3189,341 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H5" s="28" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="I5" s="27" t="n">
-        <v>-4.7</v>
+        <v>1.56</v>
+      </c>
+      <c r="I5" s="28" t="n">
+        <v>0.19</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H6" s="28" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I6" s="27" t="n">
-        <v>-4.83</v>
-      </c>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H6" s="25" t="n"/>
+      <c r="I6" s="25" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H7" s="25" t="n"/>
-      <c r="I7" s="25" t="n"/>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I7" s="28" t="n">
+        <v>2.04</v>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H8" s="25" t="n"/>
-      <c r="I8" s="25" t="n"/>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I8" s="27" t="n">
+        <v>-0.86</v>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H9" s="25" t="n"/>
-      <c r="I9" s="25" t="n"/>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H9" s="27" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="I9" s="27" t="n">
+        <v>-0.36</v>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H10" s="25" t="n"/>
-      <c r="I10" s="25" t="n"/>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H10" s="28" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I10" s="28" t="n">
+        <v>12.69</v>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>KS인더스트리</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H11" s="27" t="n">
-        <v>-3.39</v>
-      </c>
-      <c r="I11" s="28" t="n">
-        <v>39.51</v>
-      </c>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H11" s="25" t="n"/>
+      <c r="I11" s="25" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>비투엔</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="27" t="n">
-        <v>-8.470000000000001</v>
-      </c>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H12" s="25" t="n"/>
+      <c r="I12" s="25" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H13" s="25" t="n"/>
-      <c r="I13" s="25" t="n"/>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H13" s="27" t="n">
+        <v>-8.24</v>
+      </c>
+      <c r="I13" s="28" t="n">
+        <v>52.37</v>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H14" s="28" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="I14" s="27" t="n">
-        <v>-3.15</v>
-      </c>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="25" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -3520,25 +3540,21 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H15" s="28" t="n">
-        <v>18.49</v>
-      </c>
-      <c r="I15" s="28" t="n">
-        <v>67.90000000000001</v>
-      </c>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H15" s="25" t="n"/>
+      <c r="I15" s="25" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>대모</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -3555,25 +3571,21 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H16" s="28" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="I16" s="28" t="n">
-        <v>0.48</v>
-      </c>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>제일기획</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -3590,227 +3602,227 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H17" s="27" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="I17" s="27" t="n">
-        <v>-7.26</v>
-      </c>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H18" s="25" t="n"/>
-      <c r="I18" s="25" t="n"/>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H18" s="28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I18" s="27" t="n">
+        <v>-3.38</v>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H19" s="28" t="n">
-        <v>15.53</v>
-      </c>
-      <c r="I19" s="28" t="n">
-        <v>9.94</v>
-      </c>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H19" s="25" t="n"/>
+      <c r="I19" s="25" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>프리티</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H20" s="28" t="n">
-        <v>2.02</v>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>-29.91</v>
       </c>
       <c r="I20" s="27" t="n">
-        <v>-3.58</v>
+        <v>-35.77</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H21" s="25" t="n">
-        <v>0</v>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H21" s="28" t="n">
+        <v>0.55</v>
       </c>
       <c r="I21" s="27" t="n">
-        <v>-7.7</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>LS마린솔루션</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H22" s="28" t="n">
-        <v>1.13</v>
+        <v>3.7</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>3.08</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H23" s="25" t="n"/>
-      <c r="I23" s="25" t="n"/>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H23" s="27" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="I23" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>뷰티스킨</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -3827,25 +3839,25 @@
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H24" s="27" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="I24" s="27" t="n">
-        <v>-5.91</v>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H24" s="28" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="I24" s="28" t="n">
+        <v>28.54</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>시선AI</t>
+          <t>비츠로테크</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
@@ -3862,25 +3874,25 @@
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H25" s="27" t="n">
-        <v>-2.27</v>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H25" s="28" t="n">
+        <v>1.66</v>
       </c>
       <c r="I25" s="28" t="n">
-        <v>5.01</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
@@ -3897,25 +3909,21 @@
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H26" s="28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="I26" s="27" t="n">
-        <v>-1.66</v>
-      </c>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H26" s="25" t="n"/>
+      <c r="I26" s="25" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>한섬</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
@@ -3932,60 +3940,60 @@
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H27" s="28" t="n">
-        <v>2.34</v>
+        <v>10.4</v>
       </c>
       <c r="I27" s="28" t="n">
-        <v>23.2</v>
+        <v>15.81</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H28" s="27" t="n">
-        <v>-8.470000000000001</v>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H28" s="28" t="n">
+        <v>3.53</v>
       </c>
       <c r="I28" s="28" t="n">
-        <v>61.76</v>
+        <v>33.67</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>RFHIC</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
@@ -4002,25 +4010,25 @@
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H29" s="28" t="n">
-        <v>3.65</v>
+        <v>13.23</v>
       </c>
       <c r="I29" s="28" t="n">
-        <v>5.06</v>
+        <v>30.04</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
@@ -4037,25 +4045,25 @@
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H30" s="28" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="I30" s="27" t="n">
-        <v>-10.45</v>
+        <v>10.28</v>
+      </c>
+      <c r="I30" s="28" t="n">
+        <v>7.29</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
@@ -4072,25 +4080,25 @@
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H31" s="28" t="n">
-        <v>1.81</v>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H31" s="27" t="n">
+        <v>-29.89</v>
       </c>
       <c r="I31" s="27" t="n">
-        <v>-5.53</v>
+        <v>-44.49</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
@@ -4107,25 +4115,25 @@
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H32" s="28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I32" s="25" t="n">
-        <v>0</v>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H32" s="27" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="I32" s="28" t="n">
+        <v>2.87</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
@@ -4142,25 +4150,25 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H33" s="28" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="I33" s="27" t="n">
-        <v>-20.83</v>
+        <v>3.86</v>
+      </c>
+      <c r="I33" s="28" t="n">
+        <v>57.08</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>동국산업</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
@@ -4177,25 +4185,25 @@
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H34" s="28" t="n">
-        <v>4.87</v>
+        <v>0.41</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>40.24</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>모티브링크</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
@@ -4212,25 +4220,25 @@
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H35" s="28" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="I35" s="28" t="n">
-        <v>6.19</v>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H35" s="27" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="I35" s="27" t="n">
+        <v>-1.64</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>뷰티스킨</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
@@ -4247,25 +4255,25 @@
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H36" s="27" t="n">
-        <v>-8.66</v>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H36" s="28" t="n">
+        <v>1.45</v>
       </c>
       <c r="I36" s="28" t="n">
-        <v>23.34</v>
+        <v>21.95</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>비츠로셀</t>
+          <t>아이티센피엔에스</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
@@ -4282,25 +4290,25 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H37" s="28" t="n">
-        <v>5</v>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H37" s="27" t="n">
+        <v>-3.01</v>
       </c>
       <c r="I37" s="28" t="n">
-        <v>3.89</v>
+        <v>66.41</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4317,25 +4325,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H38" s="27" t="n">
-        <v>-3.24</v>
+        <v>-3.27</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>47.26</v>
+        <v>16.48</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>아티스트컴퍼니</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4352,25 +4360,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H39" s="28" t="n">
-        <v>2.39</v>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H39" s="27" t="n">
+        <v>-3.18</v>
       </c>
       <c r="I39" s="28" t="n">
-        <v>1.98</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>엔에프씨</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4387,25 +4395,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H40" s="28" t="n">
-        <v>5.9</v>
+        <v>28.91</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>0.9399999999999999</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>센서뷰</t>
+          <t>진양화학</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4422,25 +4430,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H41" s="28" t="n">
-        <v>23.98</v>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H41" s="27" t="n">
+        <v>-6.03</v>
       </c>
       <c r="I41" s="28" t="n">
-        <v>45.38</v>
+        <v>22.47</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>진영</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4457,25 +4465,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H42" s="28" t="n">
-        <v>18.43</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>17.85</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>아이티센피엔에스</t>
+          <t>큐라티스</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4492,25 +4500,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H43" s="27" t="n">
-        <v>-4.6</v>
+        <v>-5.09</v>
       </c>
       <c r="I43" s="28" t="n">
-        <v>74.28</v>
+        <v>58.13</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>티엠씨</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4527,25 +4535,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H44" s="27" t="n">
-        <v>-3.81</v>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H44" s="28" t="n">
+        <v>7.8</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>25.49</v>
+        <v>37.22</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>아티스트컴퍼니</t>
+          <t>파이온엑스</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4562,25 +4570,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H45" s="27" t="n">
-        <v>-12.57</v>
-      </c>
-      <c r="I45" s="28" t="n">
-        <v>13.04</v>
+        <v>-22.35</v>
+      </c>
+      <c r="I45" s="27" t="n">
+        <v>-33.73</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4597,21 +4605,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H46" s="25" t="n"/>
-      <c r="I46" s="25" t="n"/>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H46" s="27" t="n">
+        <v>-2.92</v>
+      </c>
+      <c r="I46" s="28" t="n">
+        <v>50.25</v>
+      </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>카카오뱅크</t>
+          <t>한전산업</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4628,25 +4640,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H47" s="27" t="n">
-        <v>-0.48</v>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H47" s="28" t="n">
+        <v>0.31</v>
       </c>
       <c r="I47" s="27" t="n">
-        <v>-2.34</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>한컴라이프케어</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4663,25 +4675,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H48" s="28" t="n">
-        <v>6.75</v>
+        <v>4.85</v>
       </c>
       <c r="I48" s="28" t="n">
-        <v>5.42</v>
+        <v>20.23</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>한전산업</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4698,25 +4710,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H49" s="28" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="I49" s="27" t="n">
-        <v>-1.74</v>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H49" s="27" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="I49" s="28" t="n">
+        <v>25.13</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>한켐</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4733,25 +4745,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H50" s="27" t="n">
-        <v>-3.77</v>
+        <v>-5.41</v>
       </c>
       <c r="I50" s="28" t="n">
-        <v>37.47</v>
+        <v>37.38</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4768,19 +4780,19 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H51" s="28" t="n">
-        <v>11.85</v>
-      </c>
-      <c r="I51" s="28" t="n">
-        <v>11.27</v>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H51" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="27" t="n">
+        <v>-3.86</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -4803,19 +4815,19 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H52" s="28" t="n">
-        <v>3.45</v>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H52" s="27" t="n">
+        <v>-4.76</v>
       </c>
       <c r="I52" s="28" t="n">
-        <v>7.47</v>
+        <v>1.83</v>
       </c>
     </row>
   </sheetData>
@@ -4899,19 +4911,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4930,19 +4942,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4961,19 +4973,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -4985,26 +4997,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5016,26 +5028,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5047,26 +5059,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5085,19 +5097,19 @@
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5116,19 +5128,19 @@
         <v>1</v>
       </c>
       <c r="C10" s="36" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G10" s="37" t="inlineStr">
@@ -5140,65 +5152,69 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="35" t="inlineStr">
         <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F11" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G11" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
           <t>인공지능</t>
         </is>
       </c>
-      <c r="B11" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="D11" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="F11" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="G11" s="37" t="inlineStr">
+      <c r="B12" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="D12" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="E12" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F12" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G12" s="37" t="inlineStr">
         <is>
           <t>⚡ 관심</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>이차전지</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="29" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G12" s="29" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -5225,7 +5241,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5252,7 +5268,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5279,7 +5295,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5306,7 +5322,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5333,7 +5349,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5360,7 +5376,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -5387,7 +5403,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-19 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-20 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-19) 상위: 반도체  점수 50.0점</t>
+          <t>⚡ 최신(2026-09-20) 상위: 반도체  점수 47.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-19) 상위: 바이오  점수 20.0점</t>
+          <t>⚡ 최신(2026-09-20) 상위: 삼성전자  점수 17.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-19) 상위: 삼성전자  점수 19.0점</t>
+          <t>⚡ 최신(2026-09-20) 상위: SK하이닉스  점수 15.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -967,14 +967,14 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -982,27 +982,25 @@
       <c r="G15" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="15" t="n">
+      <c r="H15" s="18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J15" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K15" s="17" t="n">
         <v/>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J15" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K15" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1008,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1026,24 +1024,26 @@
         <v>0</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>1.56</v>
+        <v>4.7</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>0.19</v>
+        <v>2.04</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="n">
-        <v/>
+          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
@@ -1086,7 +1086,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1109,15 +1109,15 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I18" s="18" t="n">
-        <v>2.04</v>
+      <c r="H18" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v/>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
@@ -1129,7 +1129,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1170,7 +1170,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1178,14 +1178,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1193,25 +1193,27 @@
       <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="19" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="I20" s="19" t="n">
-        <v>-0.36</v>
+      <c r="H20" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v/>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="n">
-        <v/>
+          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1219,7 +1221,7 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
@@ -1235,26 +1237,26 @@
         <v>0</v>
       </c>
       <c r="H21" s="18" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I21" s="18" t="n">
-        <v>12.69</v>
+        <v>0.55</v>
+      </c>
+      <c r="I21" s="19" t="n">
+        <v>-4.18</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1262,14 +1264,14 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1278,26 +1280,26 @@
         <v>0</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>-8.24</v>
-      </c>
-      <c r="I22" s="18" t="n">
-        <v>52.37</v>
+        <v>-0.62</v>
+      </c>
+      <c r="I22" s="19" t="n">
+        <v>-0.36</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +952% / 중요공시 2건 / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1328,7 +1330,7 @@
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K23" s="17" t="inlineStr">
@@ -1340,7 +1342,7 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1348,7 +1350,7 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>스테이블코인</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
@@ -1371,17 +1373,19 @@
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="n">
-        <v/>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1389,7 +1393,7 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
@@ -1412,60 +1416,62 @@
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="n">
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="20" t="n">
         <v/>
       </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="n">
-        <v>13</v>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>로봇</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="15" t="n">
+      <c r="I26" s="20" t="n">
         <v/>
       </c>
-      <c r="I26" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J26" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>Google 급상승 검색어 등장 (KR) / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B27" s="20" t="n">
@@ -1473,7 +1479,7 @@
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="D27" s="20" t="n">
@@ -1496,7 +1502,7 @@
       </c>
       <c r="J27" s="22" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -1508,7 +1514,7 @@
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B28" s="20" t="n">
@@ -1516,14 +1522,14 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>진영</t>
         </is>
       </c>
       <c r="D28" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F28" s="20" t="n">
         <v>0</v>
@@ -1531,27 +1537,27 @@
       <c r="G28" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I28" s="20" t="n">
-        <v/>
+      <c r="H28" s="23" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="I28" s="23" t="n">
+        <v>11.76</v>
       </c>
       <c r="J28" s="22" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +96% / 중요공시 1건 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B29" s="20" t="n">
@@ -1594,7 +1600,7 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1602,7 +1608,7 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>프리티</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
@@ -1618,14 +1624,14 @@
         <v>0</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>-29.91</v>
+        <v>-29.89</v>
       </c>
       <c r="I30" s="24" t="n">
-        <v>-35.77</v>
+        <v>-44.49</v>
       </c>
       <c r="J30" s="22" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200%</t>
+          <t>중요공시 10건 / 중요공시 3일 +67%</t>
         </is>
       </c>
       <c r="K30" s="22" t="inlineStr">
@@ -1637,7 +1643,7 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1645,42 +1651,42 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>프리티</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
         <v>5</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F31" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I31" s="20" t="n">
-        <v/>
+      <c r="H31" s="24" t="n">
+        <v>-29.91</v>
+      </c>
+      <c r="I31" s="24" t="n">
+        <v>-35.77</v>
       </c>
       <c r="J31" s="22" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>중요공시 3건 / 중요공시 3일 +200%</t>
         </is>
       </c>
       <c r="K31" s="22" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1688,40 +1694,42 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>한전산업</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
         <v>5</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="23" t="n">
-        <v>0.55</v>
+        <v>0.31</v>
       </c>
       <c r="I32" s="24" t="n">
-        <v>-4.18</v>
+        <v>-4.05</v>
       </c>
       <c r="J32" s="22" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K32" s="22" t="n">
-        <v/>
+          <t>중요공시 3건 / 중요공시 3일 +200%</t>
+        </is>
+      </c>
+      <c r="K32" s="22" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1729,14 +1737,14 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>뷰티스킨</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>0</v>
@@ -1745,26 +1753,26 @@
         <v>0</v>
       </c>
       <c r="H33" s="23" t="n">
-        <v>9.699999999999999</v>
+        <v>0.38</v>
       </c>
       <c r="I33" s="23" t="n">
-        <v>28.54</v>
+        <v>12.69</v>
       </c>
       <c r="J33" s="22" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +173% / 중요공시 1건</t>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K33" s="22" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1772,7 +1780,7 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>비츠로테크</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
@@ -1787,15 +1795,15 @@
       <c r="G34" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="23" t="n">
-        <v>1.66</v>
+      <c r="H34" s="24" t="n">
+        <v>-8.24</v>
       </c>
       <c r="I34" s="23" t="n">
-        <v>33.07</v>
+        <v>52.37</v>
       </c>
       <c r="J34" s="22" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +108% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +1168% / 중요공시 2건</t>
         </is>
       </c>
       <c r="K34" s="22" t="inlineStr">
@@ -1807,7 +1815,7 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1815,7 +1823,7 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>뷰티스킨</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
@@ -1830,25 +1838,27 @@
       <c r="G35" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="24" t="n">
-        <v>-1.35</v>
+      <c r="H35" s="23" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="I35" s="23" t="n">
-        <v>0.6899999999999999</v>
+        <v>28.54</v>
       </c>
       <c r="J35" s="22" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K35" s="22" t="n">
-        <v/>
+          <t>네이버 검색 당일 +285% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K35" s="22" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1856,7 +1866,7 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>한섬</t>
+          <t>비츠로테크</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
@@ -1872,14 +1882,14 @@
         <v>0</v>
       </c>
       <c r="H36" s="23" t="n">
-        <v>10.4</v>
+        <v>1.66</v>
       </c>
       <c r="I36" s="23" t="n">
-        <v>15.81</v>
+        <v>33.07</v>
       </c>
       <c r="J36" s="22" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
+          <t>네이버 검색 당일 +209% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K36" s="22" t="inlineStr">
@@ -1891,7 +1901,7 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1899,7 +1909,7 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>LS마린솔루션</t>
+          <t>엔에프씨</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
@@ -1915,26 +1925,24 @@
         <v>0</v>
       </c>
       <c r="H37" s="23" t="n">
-        <v>3.7</v>
+        <v>28.91</v>
       </c>
       <c r="I37" s="23" t="n">
-        <v>4.18</v>
+        <v>16.2</v>
       </c>
       <c r="J37" s="22" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K37" s="22" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K37" s="22" t="n">
+        <v/>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1942,7 +1950,7 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
@@ -1957,197 +1965,197 @@
       <c r="G38" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="20" t="n">
+      <c r="H38" s="23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I38" s="23" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="J38" s="22" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K38" s="22" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>우진</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="23" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="I39" s="24" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="J39" s="22" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K39" s="22" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="n">
+        <v>27</v>
+      </c>
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>한전기술</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="24" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="I40" s="24" t="n">
+        <v>-11.45</v>
+      </c>
+      <c r="J40" s="22" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K40" s="22" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>LS마린솔루션</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I41" s="23" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="J41" s="22" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K41" s="22" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>삼성증권</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="24" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="I42" s="24" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="J42" s="22" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K42" s="22" t="n">
         <v/>
-      </c>
-      <c r="I38" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J38" s="22" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K38" s="22" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="B39" s="25" t="n">
-        <v>26</v>
-      </c>
-      <c r="C39" s="26" t="inlineStr">
-        <is>
-          <t>아이티센피엔에스</t>
-        </is>
-      </c>
-      <c r="D39" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E39" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F39" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="27" t="n">
-        <v>-3.01</v>
-      </c>
-      <c r="I39" s="28" t="n">
-        <v>66.41</v>
-      </c>
-      <c r="J39" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +700%</t>
-        </is>
-      </c>
-      <c r="K39" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="B40" s="25" t="n">
-        <v>27</v>
-      </c>
-      <c r="C40" s="26" t="inlineStr">
-        <is>
-          <t>빛샘전자</t>
-        </is>
-      </c>
-      <c r="D40" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E40" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F40" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="28" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="I40" s="28" t="n">
-        <v>57.08</v>
-      </c>
-      <c r="J40" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +366%</t>
-        </is>
-      </c>
-      <c r="K40" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="B41" s="25" t="n">
-        <v>28</v>
-      </c>
-      <c r="C41" s="26" t="inlineStr">
-        <is>
-          <t>큐라티스</t>
-        </is>
-      </c>
-      <c r="D41" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E41" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F41" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="27" t="n">
-        <v>-5.09</v>
-      </c>
-      <c r="I41" s="28" t="n">
-        <v>58.13</v>
-      </c>
-      <c r="J41" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +261%</t>
-        </is>
-      </c>
-      <c r="K41" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="B42" s="25" t="n">
-        <v>29</v>
-      </c>
-      <c r="C42" s="26" t="inlineStr">
-        <is>
-          <t>한켐</t>
-        </is>
-      </c>
-      <c r="D42" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E42" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F42" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="27" t="n">
-        <v>-5.41</v>
-      </c>
-      <c r="I42" s="28" t="n">
-        <v>37.38</v>
-      </c>
-      <c r="J42" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +259%</t>
-        </is>
-      </c>
-      <c r="K42" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -2155,7 +2163,7 @@
       </c>
       <c r="C43" s="26" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>아이티센피엔에스</t>
         </is>
       </c>
       <c r="D43" s="25" t="n">
@@ -2171,14 +2179,14 @@
         <v>0</v>
       </c>
       <c r="H43" s="27" t="n">
-        <v>-3.27</v>
+        <v>-3.01</v>
       </c>
       <c r="I43" s="28" t="n">
-        <v>16.48</v>
+        <v>66.41</v>
       </c>
       <c r="J43" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +245%</t>
+          <t>네이버 검색 당일 +859%</t>
         </is>
       </c>
       <c r="K43" s="29" t="inlineStr">
@@ -2190,7 +2198,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -2198,7 +2206,7 @@
       </c>
       <c r="C44" s="26" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="D44" s="25" t="n">
@@ -2213,15 +2221,15 @@
       <c r="G44" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="27" t="n">
-        <v>-2.92</v>
+      <c r="H44" s="28" t="n">
+        <v>3.86</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>50.25</v>
+        <v>57.08</v>
       </c>
       <c r="J44" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +244%</t>
+          <t>네이버 검색 당일 +505%</t>
         </is>
       </c>
       <c r="K44" s="29" t="inlineStr">
@@ -2233,7 +2241,7 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -2241,7 +2249,7 @@
       </c>
       <c r="C45" s="26" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>큐라티스</t>
         </is>
       </c>
       <c r="D45" s="25" t="n">
@@ -2257,14 +2265,14 @@
         <v>0</v>
       </c>
       <c r="H45" s="27" t="n">
-        <v>-3.33</v>
+        <v>-5.09</v>
       </c>
       <c r="I45" s="28" t="n">
-        <v>25.13</v>
+        <v>58.13</v>
       </c>
       <c r="J45" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +219%</t>
+          <t>네이버 검색 당일 +397%</t>
         </is>
       </c>
       <c r="K45" s="29" t="inlineStr">
@@ -2276,7 +2284,7 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -2284,7 +2292,7 @@
       </c>
       <c r="C46" s="26" t="inlineStr">
         <is>
-          <t>진양화학</t>
+          <t>한켐</t>
         </is>
       </c>
       <c r="D46" s="25" t="n">
@@ -2300,14 +2308,14 @@
         <v>0</v>
       </c>
       <c r="H46" s="27" t="n">
-        <v>-6.03</v>
+        <v>-5.41</v>
       </c>
       <c r="I46" s="28" t="n">
-        <v>22.47</v>
+        <v>37.38</v>
       </c>
       <c r="J46" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +132%</t>
+          <t>네이버 검색 당일 +341%</t>
         </is>
       </c>
       <c r="K46" s="29" t="inlineStr">
@@ -2319,7 +2327,7 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -2327,7 +2335,7 @@
       </c>
       <c r="C47" s="26" t="inlineStr">
         <is>
-          <t>티엠씨</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="D47" s="25" t="n">
@@ -2342,15 +2350,15 @@
       <c r="G47" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="28" t="n">
-        <v>7.8</v>
+      <c r="H47" s="27" t="n">
+        <v>-3.27</v>
       </c>
       <c r="I47" s="28" t="n">
-        <v>37.22</v>
+        <v>16.48</v>
       </c>
       <c r="J47" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +126%</t>
+          <t>네이버 검색 당일 +291%</t>
         </is>
       </c>
       <c r="K47" s="29" t="inlineStr">
@@ -2362,7 +2370,7 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -2370,7 +2378,7 @@
       </c>
       <c r="C48" s="26" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
@@ -2385,15 +2393,15 @@
       <c r="G48" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="28" t="n">
-        <v>3.53</v>
+      <c r="H48" s="27" t="n">
+        <v>-2.92</v>
       </c>
       <c r="I48" s="28" t="n">
-        <v>33.67</v>
+        <v>50.25</v>
       </c>
       <c r="J48" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +118%</t>
+          <t>네이버 검색 당일 +288%</t>
         </is>
       </c>
       <c r="K48" s="29" t="inlineStr">
@@ -2405,7 +2413,7 @@
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -2413,7 +2421,7 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>한컴라이프케어</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
@@ -2428,15 +2436,15 @@
       <c r="G49" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="28" t="n">
-        <v>4.85</v>
+      <c r="H49" s="27" t="n">
+        <v>-3.33</v>
       </c>
       <c r="I49" s="28" t="n">
-        <v>20.23</v>
+        <v>25.13</v>
       </c>
       <c r="J49" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +116%</t>
+          <t>네이버 검색 당일 +269%</t>
         </is>
       </c>
       <c r="K49" s="29" t="inlineStr">
@@ -2448,7 +2456,7 @@
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2456,7 +2464,7 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>진영</t>
+          <t>진양화학</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -2471,27 +2479,27 @@
       <c r="G50" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="28" t="n">
-        <v>8.460000000000001</v>
+      <c r="H50" s="27" t="n">
+        <v>-6.03</v>
       </c>
       <c r="I50" s="28" t="n">
-        <v>11.76</v>
+        <v>22.47</v>
       </c>
       <c r="J50" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +57% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +214%</t>
         </is>
       </c>
       <c r="K50" s="29" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2499,7 +2507,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>한컴라이프케어</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2515,26 +2523,26 @@
         <v>0</v>
       </c>
       <c r="H51" s="28" t="n">
-        <v>1.45</v>
+        <v>4.85</v>
       </c>
       <c r="I51" s="28" t="n">
-        <v>21.95</v>
+        <v>20.23</v>
       </c>
       <c r="J51" s="29" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +201%</t>
         </is>
       </c>
       <c r="K51" s="29" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2542,7 +2550,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>티엠씨</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2558,14 +2566,14 @@
         <v>0</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>13.23</v>
+        <v>7.8</v>
       </c>
       <c r="I52" s="28" t="n">
-        <v>30.04</v>
+        <v>37.22</v>
       </c>
       <c r="J52" s="29" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급</t>
+          <t>네이버 검색 당일 +180%</t>
         </is>
       </c>
       <c r="K52" s="29" t="inlineStr">
@@ -2577,7 +2585,7 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2585,7 +2593,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2600,27 +2608,27 @@
       <c r="G53" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="27" t="n">
-        <v>-2.32</v>
-      </c>
-      <c r="I53" s="27" t="n">
-        <v>-1.64</v>
+      <c r="H53" s="28" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="I53" s="28" t="n">
+        <v>56.85</v>
       </c>
       <c r="J53" s="29" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +177%</t>
         </is>
       </c>
       <c r="K53" s="29" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2628,7 +2636,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>나라스페이스테크놀로지</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2644,24 +2652,26 @@
         <v>0</v>
       </c>
       <c r="H54" s="28" t="n">
-        <v>0.41</v>
+        <v>1.81</v>
       </c>
       <c r="I54" s="28" t="n">
-        <v>1.86</v>
+        <v>36.89</v>
       </c>
       <c r="J54" s="29" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K54" s="29" t="n">
-        <v/>
+          <t>네이버 검색 당일 +176%</t>
+        </is>
+      </c>
+      <c r="K54" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2669,7 +2679,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>엔에프씨</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2685,24 +2695,26 @@
         <v>0</v>
       </c>
       <c r="H55" s="28" t="n">
-        <v>28.91</v>
+        <v>3.53</v>
       </c>
       <c r="I55" s="28" t="n">
-        <v>16.2</v>
+        <v>33.67</v>
       </c>
       <c r="J55" s="29" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K55" s="29" t="n">
-        <v/>
+          <t>네이버 검색 당일 +160%</t>
+        </is>
+      </c>
+      <c r="K55" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2710,7 +2722,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>오션인더블유</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2725,25 +2737,27 @@
       <c r="G56" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="27" t="n">
-        <v>-4.76</v>
+      <c r="H56" s="28" t="n">
+        <v>18.49</v>
       </c>
       <c r="I56" s="28" t="n">
-        <v>1.83</v>
+        <v>18.57</v>
       </c>
       <c r="J56" s="29" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K56" s="29" t="n">
-        <v/>
+          <t>네이버 검색 당일 +144%</t>
+        </is>
+      </c>
+      <c r="K56" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2751,7 +2765,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>에이스테크</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2767,14 +2781,14 @@
         <v>0</v>
       </c>
       <c r="H57" s="28" t="n">
-        <v>10.28</v>
+        <v>5.74</v>
       </c>
       <c r="I57" s="28" t="n">
-        <v>7.29</v>
+        <v>24.22</v>
       </c>
       <c r="J57" s="29" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급</t>
+          <t>네이버 검색 당일 +139%</t>
         </is>
       </c>
       <c r="K57" s="29" t="inlineStr">
@@ -2786,7 +2800,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2794,7 +2808,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>켄코아에어로스페이스</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2809,27 +2823,27 @@
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="27" t="n">
-        <v>-29.89</v>
-      </c>
-      <c r="I58" s="27" t="n">
-        <v>-44.49</v>
+      <c r="H58" s="28" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="I58" s="28" t="n">
+        <v>28.67</v>
       </c>
       <c r="J58" s="29" t="inlineStr">
         <is>
-          <t>중요공시 10건</t>
+          <t>네이버 검색 당일 +136%</t>
         </is>
       </c>
       <c r="K58" s="29" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2837,7 +2851,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>파이온엑스</t>
+          <t>아이씨티케이</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2852,27 +2866,27 @@
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="27" t="n">
-        <v>-22.35</v>
-      </c>
-      <c r="I59" s="27" t="n">
-        <v>-33.73</v>
+      <c r="H59" s="28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I59" s="28" t="n">
+        <v>29.94</v>
       </c>
       <c r="J59" s="29" t="inlineStr">
         <is>
-          <t>중요공시 4건</t>
+          <t>네이버 검색 당일 +119%</t>
         </is>
       </c>
       <c r="K59" s="29" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2880,7 +2894,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>아티스트컴퍼니</t>
+          <t>이엔셀</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2895,27 +2909,27 @@
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="27" t="n">
-        <v>-3.18</v>
+      <c r="H60" s="28" t="n">
+        <v>30.15</v>
       </c>
       <c r="I60" s="28" t="n">
-        <v>11.13</v>
+        <v>25.6</v>
       </c>
       <c r="J60" s="29" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>네이버 검색 당일 +114%</t>
         </is>
       </c>
       <c r="K60" s="29" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2923,7 +2937,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>한전산업</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2939,26 +2953,26 @@
         <v>0</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="I61" s="27" t="n">
-        <v>-4.05</v>
+        <v>18.92</v>
+      </c>
+      <c r="I61" s="28" t="n">
+        <v>51.03</v>
       </c>
       <c r="J61" s="29" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>네이버 검색 당일 +79% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K61" s="29" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2966,30 +2980,30 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E62" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H62" s="27" t="n">
-        <v>-1.57</v>
-      </c>
-      <c r="I62" s="28" t="n">
-        <v>2.87</v>
+        <v>-2.32</v>
+      </c>
+      <c r="I62" s="27" t="n">
+        <v>-1.64</v>
       </c>
       <c r="J62" s="29" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K62" s="29" t="inlineStr">
@@ -3001,7 +3015,7 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3009,7 +3023,7 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
@@ -3024,21 +3038,19 @@
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="27" t="n">
-        <v>-3.86</v>
+      <c r="H63" s="28" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I63" s="28" t="n">
+        <v>1.86</v>
       </c>
       <c r="J63" s="29" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K63" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K63" s="29" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3134,22 +3146,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3158,95 +3170,99 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H4" s="25" t="n"/>
-      <c r="I4" s="25" t="n"/>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H4" s="28" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I4" s="28" t="n">
+        <v>0.19</v>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H5" s="28" t="n">
-        <v>1.56</v>
+        <v>4.7</v>
       </c>
       <c r="I5" s="28" t="n">
-        <v>0.19</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H6" s="25" t="n"/>
@@ -3255,37 +3271,33 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H7" s="28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I7" s="28" t="n">
-        <v>2.04</v>
-      </c>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H7" s="25" t="n"/>
+      <c r="I7" s="25" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
@@ -3307,12 +3319,12 @@
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H8" s="28" t="n">
@@ -3325,42 +3337,38 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="I9" s="27" t="n">
-        <v>-0.36</v>
-      </c>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H9" s="25" t="n"/>
+      <c r="I9" s="25" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
@@ -3377,51 +3385,55 @@
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H10" s="28" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I10" s="28" t="n">
-        <v>12.69</v>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H10" s="27" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="I10" s="27" t="n">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H11" s="25" t="n"/>
-      <c r="I11" s="25" t="n"/>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H11" s="28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>-4.18</v>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
@@ -3443,12 +3455,12 @@
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H12" s="25" t="n"/>
@@ -3457,7 +3469,7 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -3474,25 +3486,21 @@
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H13" s="27" t="n">
-        <v>-8.24</v>
-      </c>
-      <c r="I13" s="28" t="n">
-        <v>52.37</v>
-      </c>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H13" s="25" t="n"/>
+      <c r="I13" s="25" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>스테이블코인</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -3509,12 +3517,12 @@
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H14" s="25" t="n"/>
@@ -3523,29 +3531,29 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H15" s="25" t="n"/>
@@ -3554,7 +3562,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -3571,12 +3579,12 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H16" s="25" t="n"/>
@@ -3585,38 +3593,42 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H17" s="25" t="n"/>
-      <c r="I17" s="25" t="n"/>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H17" s="28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I17" s="27" t="n">
+        <v>-3.38</v>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -3633,25 +3645,25 @@
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H18" s="28" t="n">
-        <v>1.5</v>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>-29.89</v>
       </c>
       <c r="I18" s="27" t="n">
-        <v>-3.38</v>
+        <v>-44.49</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>진영</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -3668,16 +3680,20 @@
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H19" s="25" t="n"/>
-      <c r="I19" s="25" t="n"/>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H19" s="28" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="I19" s="28" t="n">
+        <v>11.76</v>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
@@ -3699,12 +3715,12 @@
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H20" s="27" t="n">
@@ -3717,7 +3733,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>한전산업</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -3734,60 +3750,60 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H21" s="28" t="n">
-        <v>0.55</v>
+        <v>0.31</v>
       </c>
       <c r="I21" s="27" t="n">
-        <v>-4.18</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>LS마린솔루션</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H22" s="28" t="n">
-        <v>3.7</v>
+        <v>0.38</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>4.18</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>LS마린솔루션</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -3804,25 +3820,25 @@
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H23" s="27" t="n">
-        <v>-1.35</v>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H23" s="28" t="n">
+        <v>3.7</v>
       </c>
       <c r="I23" s="28" t="n">
-        <v>0.6899999999999999</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>뷰티스킨</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -3839,25 +3855,25 @@
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H24" s="28" t="n">
-        <v>9.699999999999999</v>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H24" s="27" t="n">
+        <v>-8.24</v>
       </c>
       <c r="I24" s="28" t="n">
-        <v>28.54</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>비츠로테크</t>
+          <t>뷰티스킨</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
@@ -3874,25 +3890,25 @@
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H25" s="28" t="n">
-        <v>1.66</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I25" s="28" t="n">
-        <v>33.07</v>
+        <v>28.54</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>비츠로테크</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
@@ -3909,21 +3925,25 @@
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H26" s="25" t="n"/>
-      <c r="I26" s="25" t="n"/>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H26" s="28" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I26" s="28" t="n">
+        <v>33.07</v>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>한섬</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
@@ -3940,165 +3960,165 @@
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H27" s="28" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="I27" s="28" t="n">
-        <v>15.81</v>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H27" s="27" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="I27" s="27" t="n">
+        <v>-2.06</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H28" s="28" t="n">
-        <v>3.53</v>
+        <v>1.45</v>
       </c>
       <c r="I28" s="28" t="n">
-        <v>33.67</v>
+        <v>21.95</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>엔에프씨</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H29" s="28" t="n">
-        <v>13.23</v>
+        <v>28.91</v>
       </c>
       <c r="I29" s="28" t="n">
-        <v>30.04</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>우진</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H30" s="28" t="n">
-        <v>10.28</v>
-      </c>
-      <c r="I30" s="28" t="n">
-        <v>7.29</v>
+        <v>5.55</v>
+      </c>
+      <c r="I30" s="27" t="n">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H31" s="27" t="n">
-        <v>-29.89</v>
+        <v>-2.6</v>
       </c>
       <c r="I31" s="27" t="n">
-        <v>-44.49</v>
+        <v>-11.45</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
@@ -4115,25 +4135,25 @@
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H32" s="27" t="n">
-        <v>-1.57</v>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H32" s="28" t="n">
+        <v>3.53</v>
       </c>
       <c r="I32" s="28" t="n">
-        <v>2.87</v>
+        <v>33.67</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>나라스페이스테크놀로지</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
@@ -4150,25 +4170,25 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H33" s="28" t="n">
-        <v>3.86</v>
+        <v>1.81</v>
       </c>
       <c r="I33" s="28" t="n">
-        <v>57.08</v>
+        <v>36.89</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
@@ -4185,25 +4205,25 @@
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H34" s="28" t="n">
-        <v>0.41</v>
+        <v>3.86</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>1.86</v>
+        <v>57.08</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
@@ -4220,25 +4240,25 @@
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H35" s="27" t="n">
-        <v>-2.32</v>
-      </c>
-      <c r="I35" s="27" t="n">
-        <v>-1.64</v>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H35" s="28" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I35" s="28" t="n">
+        <v>1.86</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
@@ -4255,25 +4275,25 @@
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H36" s="28" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="I36" s="28" t="n">
-        <v>21.95</v>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H36" s="27" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="I36" s="27" t="n">
+        <v>-1.64</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>아이티센피엔에스</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
@@ -4290,25 +4310,25 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H37" s="27" t="n">
-        <v>-3.01</v>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H37" s="28" t="n">
+        <v>18.92</v>
       </c>
       <c r="I37" s="28" t="n">
-        <v>66.41</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4325,25 +4345,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H38" s="27" t="n">
-        <v>-3.27</v>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H38" s="28" t="n">
+        <v>7.05</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>16.48</v>
+        <v>56.85</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>아티스트컴퍼니</t>
+          <t>아이씨티케이</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4360,25 +4380,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H39" s="27" t="n">
-        <v>-3.18</v>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H39" s="28" t="n">
+        <v>3.95</v>
       </c>
       <c r="I39" s="28" t="n">
-        <v>11.13</v>
+        <v>29.94</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>엔에프씨</t>
+          <t>아이티센피엔에스</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4395,25 +4415,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H40" s="28" t="n">
-        <v>28.91</v>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H40" s="27" t="n">
+        <v>-3.01</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>16.2</v>
+        <v>66.41</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>진양화학</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4430,25 +4450,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H41" s="27" t="n">
-        <v>-6.03</v>
+        <v>-3.27</v>
       </c>
       <c r="I41" s="28" t="n">
-        <v>22.47</v>
+        <v>16.48</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>진영</t>
+          <t>에이스테크</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4465,25 +4485,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H42" s="28" t="n">
-        <v>8.460000000000001</v>
+        <v>5.74</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>11.76</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>큐라티스</t>
+          <t>오션인더블유</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4500,25 +4520,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H43" s="27" t="n">
-        <v>-5.09</v>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H43" s="28" t="n">
+        <v>18.49</v>
       </c>
       <c r="I43" s="28" t="n">
-        <v>58.13</v>
+        <v>18.57</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>티엠씨</t>
+          <t>이엔셀</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4535,25 +4555,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H44" s="28" t="n">
-        <v>7.8</v>
+        <v>30.15</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>37.22</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>파이온엑스</t>
+          <t>진양화학</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4570,25 +4590,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H45" s="27" t="n">
-        <v>-22.35</v>
-      </c>
-      <c r="I45" s="27" t="n">
-        <v>-33.73</v>
+        <v>-6.03</v>
+      </c>
+      <c r="I45" s="28" t="n">
+        <v>22.47</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>켄코아에어로스페이스</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4605,25 +4625,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H46" s="27" t="n">
-        <v>-2.92</v>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H46" s="28" t="n">
+        <v>12.69</v>
       </c>
       <c r="I46" s="28" t="n">
-        <v>50.25</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>한전산업</t>
+          <t>큐라티스</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4640,25 +4660,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H47" s="28" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="I47" s="27" t="n">
-        <v>-4.05</v>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H47" s="27" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="I47" s="28" t="n">
+        <v>58.13</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>한컴라이프케어</t>
+          <t>티엠씨</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4675,25 +4695,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H48" s="28" t="n">
-        <v>4.85</v>
+        <v>7.8</v>
       </c>
       <c r="I48" s="28" t="n">
-        <v>20.23</v>
+        <v>37.22</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4710,25 +4730,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H49" s="27" t="n">
-        <v>-3.33</v>
+        <v>-2.92</v>
       </c>
       <c r="I49" s="28" t="n">
-        <v>25.13</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>한켐</t>
+          <t>한컴라이프케어</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4745,25 +4765,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H50" s="27" t="n">
-        <v>-5.41</v>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H50" s="28" t="n">
+        <v>4.85</v>
       </c>
       <c r="I50" s="28" t="n">
-        <v>37.38</v>
+        <v>20.23</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4780,25 +4800,25 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H51" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="27" t="n">
-        <v>-3.86</v>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H51" s="27" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="I51" s="28" t="n">
+        <v>25.13</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>한켐</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -4815,19 +4835,19 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H52" s="27" t="n">
-        <v>-4.76</v>
+        <v>-5.41</v>
       </c>
       <c r="I52" s="28" t="n">
-        <v>1.83</v>
+        <v>37.38</v>
       </c>
     </row>
   </sheetData>
@@ -4911,19 +4931,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4942,19 +4962,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4966,7 +4986,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B5" s="36" t="n">
@@ -4980,12 +5000,12 @@
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5011,12 +5031,12 @@
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5028,26 +5048,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5059,7 +5079,7 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
@@ -5073,12 +5093,12 @@
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5090,26 +5110,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5121,26 +5141,26 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B10" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="36" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G10" s="37" t="inlineStr">
@@ -5150,71 +5170,63 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="B11" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F11" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="G11" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>이차전지</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="29" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G11" s="29" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>인공지능</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>19</v>
-      </c>
-      <c r="D12" s="36" t="n">
-        <v>19</v>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F12" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="G12" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>AI반도체</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="29" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G12" s="29" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>이차전지</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -5241,7 +5253,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5268,7 +5280,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5295,7 +5307,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5322,7 +5334,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5349,7 +5361,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5376,7 +5388,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -5403,7 +5415,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-20 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-21 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-20) 상위: 반도체  점수 47.0점</t>
+          <t>⚡ 최신(2026-09-21) 상위: 반도체  점수 78.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-20) 상위: 삼성전자  점수 17.0점</t>
+          <t>⚡ 최신(2026-09-21) 상위: 삼성전자  점수 34.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-20) 상위: SK하이닉스  점수 15.0점</t>
+          <t>⚡ 최신(2026-09-21) 상위: 바이오  점수 22.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -990,17 +990,19 @@
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K15" s="17" t="n">
-        <v/>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K15" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1008,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1023,15 +1025,15 @@
       <c r="G16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>2.04</v>
+      <c r="H16" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v/>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -1043,7 +1045,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1055,10 +1057,10 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1074,7 +1076,7 @@
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
@@ -1086,7 +1088,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1094,14 +1096,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1109,15 +1111,15 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v/>
+      <c r="H18" s="18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <v>2.04</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
@@ -1129,7 +1131,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1137,7 +1139,7 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
@@ -1152,15 +1154,15 @@
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="18" t="n">
-        <v>2.74</v>
+      <c r="H19" s="19" t="n">
+        <v>-0.62</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>-0.86</v>
+        <v>-0.36</v>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="n">
@@ -1170,7 +1172,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1178,7 +1180,7 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
@@ -1201,7 +1203,7 @@
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K20" s="17" t="inlineStr">
@@ -1213,7 +1215,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1221,42 +1223,42 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
         <v>8</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21" s="18" t="n">
-        <v>0.55</v>
+        <v>1.5</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>-4.18</v>
+        <v>-3.38</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 3건 / 중요공시 3일 +50% / 중요공시 7일 +50%</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1264,162 +1266,158 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
         <v>8</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>-0.62</v>
+        <v>-29.89</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>-0.36</v>
+        <v>-44.49</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 10건 / 중요공시 3일 +100% / 중요공시 7일 +67%</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="n">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="15" t="n">
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>로봇</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="20" t="n">
         <v/>
       </c>
-      <c r="I23" s="15" t="n">
+      <c r="I23" s="20" t="n">
         <v/>
       </c>
-      <c r="J23" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K23" s="22" t="n">
+        <v/>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="n">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>철강</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="15" t="n">
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>삼성전기</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="23" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I24" s="24" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K24" s="22" t="n">
         <v/>
       </c>
-      <c r="I24" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J24" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="n">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>로봇</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I25" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J25" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>SFA반도체</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="23" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="I25" s="23" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +86% / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K25" s="22" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -1428,7 +1426,7 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B26" s="20" t="n">
@@ -1436,14 +1434,14 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D26" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F26" s="20" t="n">
         <v>0</v>
@@ -1459,7 +1457,7 @@
       </c>
       <c r="J26" s="22" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR) / 매일경제 기사 언급</t>
+          <t>Google 급상승 검색어 등장 (KR)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -1471,7 +1469,7 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B27" s="20" t="n">
@@ -1479,14 +1477,14 @@
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="D27" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F27" s="20" t="n">
         <v>0</v>
@@ -1494,27 +1492,27 @@
       <c r="G27" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I27" s="20" t="n">
-        <v/>
+      <c r="H27" s="24" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="I27" s="24" t="n">
+        <v>-4.2</v>
       </c>
       <c r="J27" s="22" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>Google 급상승 검색어 등장 (US)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B28" s="20" t="n">
@@ -1522,7 +1520,7 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>진영</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="D28" s="20" t="n">
@@ -1537,27 +1535,25 @@
       <c r="G28" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="23" t="n">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="I28" s="23" t="n">
-        <v>11.76</v>
+      <c r="H28" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I28" s="20" t="n">
+        <v/>
       </c>
       <c r="J28" s="22" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +96% / 중요공시 1건 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K28" s="22" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="22" t="n">
+        <v/>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B29" s="20" t="n">
@@ -1565,42 +1561,40 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D29" s="20" t="n">
         <v>5</v>
       </c>
       <c r="E29" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F29" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G29" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="23" t="n">
-        <v>1.5</v>
+        <v>0.55</v>
       </c>
       <c r="I29" s="24" t="n">
-        <v>-3.38</v>
+        <v>-4.18</v>
       </c>
       <c r="J29" s="22" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +50%</t>
-        </is>
-      </c>
-      <c r="K29" s="22" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K29" s="22" t="n">
+        <v/>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1608,42 +1602,42 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G30" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>-29.89</v>
-      </c>
-      <c r="I30" s="24" t="n">
-        <v>-44.49</v>
+        <v>-8.24</v>
+      </c>
+      <c r="I30" s="23" t="n">
+        <v>52.37</v>
       </c>
       <c r="J30" s="22" t="inlineStr">
         <is>
-          <t>중요공시 10건 / 중요공시 3일 +67%</t>
+          <t>네이버 검색 당일 +1205% / 중요공시 2건</t>
         </is>
       </c>
       <c r="K30" s="22" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1651,42 +1645,42 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>프리티</t>
+          <t>뷰티스킨</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="24" t="n">
-        <v>-29.91</v>
-      </c>
-      <c r="I31" s="24" t="n">
-        <v>-35.77</v>
+      <c r="H31" s="23" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="I31" s="23" t="n">
+        <v>28.54</v>
       </c>
       <c r="J31" s="22" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200%</t>
+          <t>네이버 검색 당일 +303% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K31" s="22" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1694,42 +1688,42 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>한전산업</t>
+          <t>비츠로테크</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G32" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="23" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="I32" s="24" t="n">
-        <v>-4.05</v>
+        <v>1.66</v>
+      </c>
+      <c r="I32" s="23" t="n">
+        <v>33.07</v>
       </c>
       <c r="J32" s="22" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200%</t>
+          <t>네이버 검색 당일 +228% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K32" s="22" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1737,14 +1731,14 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>진영</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>0</v>
@@ -1753,26 +1747,26 @@
         <v>0</v>
       </c>
       <c r="H33" s="23" t="n">
-        <v>0.38</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="I33" s="23" t="n">
-        <v>12.69</v>
+        <v>11.76</v>
       </c>
       <c r="J33" s="22" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>네이버 검색 당일 +144% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K33" s="22" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1780,42 +1774,42 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="24" t="n">
-        <v>-8.24</v>
-      </c>
-      <c r="I34" s="23" t="n">
-        <v>52.37</v>
+        <v>3</v>
+      </c>
+      <c r="H34" s="23" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I34" s="24" t="n">
+        <v>-8.359999999999999</v>
       </c>
       <c r="J34" s="22" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1168% / 중요공시 2건</t>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K34" s="22" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1823,42 +1817,42 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>뷰티스킨</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F35" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="23" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="I35" s="23" t="n">
-        <v>28.54</v>
+        <v>3</v>
+      </c>
+      <c r="H35" s="24" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="I35" s="24" t="n">
+        <v>-6.89</v>
       </c>
       <c r="J35" s="22" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +285% / 중요공시 1건</t>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K35" s="22" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1866,7 +1860,7 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>비츠로테크</t>
+          <t>제주항공</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
@@ -1881,27 +1875,27 @@
       <c r="G36" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="23" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="I36" s="23" t="n">
-        <v>33.07</v>
+      <c r="H36" s="24" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="I36" s="24" t="n">
+        <v>-7.07</v>
       </c>
       <c r="J36" s="22" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +209% / 중요공시 1건</t>
+          <t>중요공시 2건 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K36" s="22" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1909,7 +1903,7 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>엔에프씨</t>
+          <t>LS마린솔루션</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
@@ -1925,24 +1919,26 @@
         <v>0</v>
       </c>
       <c r="H37" s="23" t="n">
-        <v>28.91</v>
+        <v>3.7</v>
       </c>
       <c r="I37" s="23" t="n">
-        <v>16.2</v>
+        <v>4.18</v>
       </c>
       <c r="J37" s="22" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K37" s="22" t="n">
-        <v/>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K37" s="22" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1950,7 +1946,7 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
@@ -1966,196 +1962,198 @@
         <v>0</v>
       </c>
       <c r="H38" s="23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="I38" s="23" t="n">
-        <v>21.95</v>
+        <v>0.37</v>
+      </c>
+      <c r="I38" s="24" t="n">
+        <v>-1.21</v>
       </c>
       <c r="J38" s="22" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K38" s="22" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="n">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B39" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="C39" s="21" t="inlineStr">
-        <is>
-          <t>우진</t>
-        </is>
-      </c>
-      <c r="D39" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E39" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="23" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="I39" s="24" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="J39" s="22" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K39" s="22" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>아이티센피엔에스</t>
+        </is>
+      </c>
+      <c r="D39" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="27" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="I39" s="28" t="n">
+        <v>66.41</v>
+      </c>
+      <c r="J39" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +884%</t>
+        </is>
+      </c>
+      <c r="K39" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="B40" s="20" t="n">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B40" s="25" t="n">
         <v>27</v>
       </c>
-      <c r="C40" s="21" t="inlineStr">
-        <is>
-          <t>한전기술</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E40" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="24" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="I40" s="24" t="n">
-        <v>-11.45</v>
-      </c>
-      <c r="J40" s="22" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K40" s="22" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>빛샘전자</t>
+        </is>
+      </c>
+      <c r="D40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="28" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="I40" s="28" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="J40" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +531%</t>
+        </is>
+      </c>
+      <c r="K40" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="B41" s="20" t="n">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="n">
         <v>28</v>
       </c>
-      <c r="C41" s="21" t="inlineStr">
-        <is>
-          <t>LS마린솔루션</t>
-        </is>
-      </c>
-      <c r="D41" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I41" s="23" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="J41" s="22" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K41" s="22" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>큐라티스</t>
+        </is>
+      </c>
+      <c r="D41" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="27" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="I41" s="28" t="n">
+        <v>58.13</v>
+      </c>
+      <c r="J41" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +414%</t>
+        </is>
+      </c>
+      <c r="K41" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="n">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="n">
         <v>29</v>
       </c>
-      <c r="C42" s="21" t="inlineStr">
-        <is>
-          <t>삼성증권</t>
-        </is>
-      </c>
-      <c r="D42" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E42" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F42" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="24" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="I42" s="24" t="n">
-        <v>-2.06</v>
-      </c>
-      <c r="J42" s="22" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K42" s="22" t="n">
-        <v/>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>한켐</t>
+        </is>
+      </c>
+      <c r="D42" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="27" t="n">
+        <v>-5.41</v>
+      </c>
+      <c r="I42" s="28" t="n">
+        <v>37.38</v>
+      </c>
+      <c r="J42" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +355%</t>
+        </is>
+      </c>
+      <c r="K42" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -2163,7 +2161,7 @@
       </c>
       <c r="C43" s="26" t="inlineStr">
         <is>
-          <t>아이티센피엔에스</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="D43" s="25" t="n">
@@ -2179,14 +2177,14 @@
         <v>0</v>
       </c>
       <c r="H43" s="27" t="n">
-        <v>-3.01</v>
+        <v>-3.27</v>
       </c>
       <c r="I43" s="28" t="n">
-        <v>66.41</v>
+        <v>16.48</v>
       </c>
       <c r="J43" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +859%</t>
+          <t>네이버 검색 당일 +302%</t>
         </is>
       </c>
       <c r="K43" s="29" t="inlineStr">
@@ -2198,7 +2196,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -2206,7 +2204,7 @@
       </c>
       <c r="C44" s="26" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="D44" s="25" t="n">
@@ -2221,15 +2219,15 @@
       <c r="G44" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="28" t="n">
-        <v>3.86</v>
+      <c r="H44" s="27" t="n">
+        <v>-2.92</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>57.08</v>
+        <v>50.25</v>
       </c>
       <c r="J44" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +505%</t>
+          <t>네이버 검색 당일 +296%</t>
         </is>
       </c>
       <c r="K44" s="29" t="inlineStr">
@@ -2241,7 +2239,7 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -2249,7 +2247,7 @@
       </c>
       <c r="C45" s="26" t="inlineStr">
         <is>
-          <t>큐라티스</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="D45" s="25" t="n">
@@ -2265,14 +2263,14 @@
         <v>0</v>
       </c>
       <c r="H45" s="27" t="n">
-        <v>-5.09</v>
+        <v>-3.33</v>
       </c>
       <c r="I45" s="28" t="n">
-        <v>58.13</v>
+        <v>25.13</v>
       </c>
       <c r="J45" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +397%</t>
+          <t>네이버 검색 당일 +280%</t>
         </is>
       </c>
       <c r="K45" s="29" t="inlineStr">
@@ -2284,7 +2282,7 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -2292,7 +2290,7 @@
       </c>
       <c r="C46" s="26" t="inlineStr">
         <is>
-          <t>한켐</t>
+          <t>한컴라이프케어</t>
         </is>
       </c>
       <c r="D46" s="25" t="n">
@@ -2307,15 +2305,15 @@
       <c r="G46" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="27" t="n">
-        <v>-5.41</v>
+      <c r="H46" s="28" t="n">
+        <v>4.85</v>
       </c>
       <c r="I46" s="28" t="n">
-        <v>37.38</v>
+        <v>20.23</v>
       </c>
       <c r="J46" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +341%</t>
+          <t>네이버 검색 당일 +226%</t>
         </is>
       </c>
       <c r="K46" s="29" t="inlineStr">
@@ -2327,7 +2325,7 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -2335,7 +2333,7 @@
       </c>
       <c r="C47" s="26" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>진양화학</t>
         </is>
       </c>
       <c r="D47" s="25" t="n">
@@ -2351,14 +2349,14 @@
         <v>0</v>
       </c>
       <c r="H47" s="27" t="n">
-        <v>-3.27</v>
+        <v>-6.03</v>
       </c>
       <c r="I47" s="28" t="n">
-        <v>16.48</v>
+        <v>22.47</v>
       </c>
       <c r="J47" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +291%</t>
+          <t>네이버 검색 당일 +225%</t>
         </is>
       </c>
       <c r="K47" s="29" t="inlineStr">
@@ -2370,7 +2368,7 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -2378,7 +2376,7 @@
       </c>
       <c r="C48" s="26" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>티엠씨</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
@@ -2393,15 +2391,15 @@
       <c r="G48" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="27" t="n">
-        <v>-2.92</v>
+      <c r="H48" s="28" t="n">
+        <v>7.8</v>
       </c>
       <c r="I48" s="28" t="n">
-        <v>50.25</v>
+        <v>37.22</v>
       </c>
       <c r="J48" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +288%</t>
+          <t>네이버 검색 당일 +195%</t>
         </is>
       </c>
       <c r="K48" s="29" t="inlineStr">
@@ -2413,7 +2411,7 @@
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -2421,7 +2419,7 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
@@ -2436,15 +2434,15 @@
       <c r="G49" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="27" t="n">
-        <v>-3.33</v>
+      <c r="H49" s="28" t="n">
+        <v>7.05</v>
       </c>
       <c r="I49" s="28" t="n">
-        <v>25.13</v>
+        <v>56.85</v>
       </c>
       <c r="J49" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +269%</t>
+          <t>네이버 검색 당일 +194%</t>
         </is>
       </c>
       <c r="K49" s="29" t="inlineStr">
@@ -2456,7 +2454,7 @@
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2464,7 +2462,7 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>진양화학</t>
+          <t>나라스페이스테크놀로지</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -2479,15 +2477,15 @@
       <c r="G50" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="27" t="n">
-        <v>-6.03</v>
+      <c r="H50" s="28" t="n">
+        <v>1.81</v>
       </c>
       <c r="I50" s="28" t="n">
-        <v>22.47</v>
+        <v>36.89</v>
       </c>
       <c r="J50" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +214%</t>
+          <t>네이버 검색 당일 +191%</t>
         </is>
       </c>
       <c r="K50" s="29" t="inlineStr">
@@ -2499,7 +2497,7 @@
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2507,7 +2505,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>한컴라이프케어</t>
+          <t>오션인더블유</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2523,14 +2521,14 @@
         <v>0</v>
       </c>
       <c r="H51" s="28" t="n">
-        <v>4.85</v>
+        <v>18.49</v>
       </c>
       <c r="I51" s="28" t="n">
-        <v>20.23</v>
+        <v>18.57</v>
       </c>
       <c r="J51" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +201%</t>
+          <t>네이버 검색 당일 +179%</t>
         </is>
       </c>
       <c r="K51" s="29" t="inlineStr">
@@ -2542,7 +2540,7 @@
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2550,7 +2548,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>티엠씨</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2566,14 +2564,14 @@
         <v>0</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>7.8</v>
+        <v>3.53</v>
       </c>
       <c r="I52" s="28" t="n">
-        <v>37.22</v>
+        <v>33.67</v>
       </c>
       <c r="J52" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +180%</t>
+          <t>네이버 검색 당일 +166%</t>
         </is>
       </c>
       <c r="K52" s="29" t="inlineStr">
@@ -2585,7 +2583,7 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2593,7 +2591,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>센서뷰</t>
+          <t>켄코아에어로스페이스</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2609,14 +2607,14 @@
         <v>0</v>
       </c>
       <c r="H53" s="28" t="n">
-        <v>7.05</v>
+        <v>12.69</v>
       </c>
       <c r="I53" s="28" t="n">
-        <v>56.85</v>
+        <v>28.67</v>
       </c>
       <c r="J53" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +177%</t>
+          <t>네이버 검색 당일 +158%</t>
         </is>
       </c>
       <c r="K53" s="29" t="inlineStr">
@@ -2628,7 +2626,7 @@
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2636,7 +2634,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>나라스페이스테크놀로지</t>
+          <t>에이스테크</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2652,14 +2650,14 @@
         <v>0</v>
       </c>
       <c r="H54" s="28" t="n">
-        <v>1.81</v>
+        <v>5.74</v>
       </c>
       <c r="I54" s="28" t="n">
-        <v>36.89</v>
+        <v>24.22</v>
       </c>
       <c r="J54" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +176%</t>
+          <t>네이버 검색 당일 +148%</t>
         </is>
       </c>
       <c r="K54" s="29" t="inlineStr">
@@ -2671,7 +2669,7 @@
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2679,7 +2677,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>이엔셀</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2695,14 +2693,14 @@
         <v>0</v>
       </c>
       <c r="H55" s="28" t="n">
-        <v>3.53</v>
+        <v>30.15</v>
       </c>
       <c r="I55" s="28" t="n">
-        <v>33.67</v>
+        <v>25.6</v>
       </c>
       <c r="J55" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +160%</t>
+          <t>네이버 검색 당일 +146%</t>
         </is>
       </c>
       <c r="K55" s="29" t="inlineStr">
@@ -2714,7 +2712,7 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2722,7 +2720,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>오션인더블유</t>
+          <t>아이씨티케이</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2738,14 +2736,14 @@
         <v>0</v>
       </c>
       <c r="H56" s="28" t="n">
-        <v>18.49</v>
+        <v>3.95</v>
       </c>
       <c r="I56" s="28" t="n">
-        <v>18.57</v>
+        <v>29.94</v>
       </c>
       <c r="J56" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +144%</t>
+          <t>네이버 검색 당일 +133%</t>
         </is>
       </c>
       <c r="K56" s="29" t="inlineStr">
@@ -2757,7 +2755,7 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2765,7 +2763,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>에이스테크</t>
+          <t>우리넷</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2781,14 +2779,14 @@
         <v>0</v>
       </c>
       <c r="H57" s="28" t="n">
-        <v>5.74</v>
+        <v>8.26</v>
       </c>
       <c r="I57" s="28" t="n">
-        <v>24.22</v>
+        <v>23.13</v>
       </c>
       <c r="J57" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +139%</t>
+          <t>네이버 검색 당일 +104%</t>
         </is>
       </c>
       <c r="K57" s="29" t="inlineStr">
@@ -2800,7 +2798,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2808,7 +2806,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>켄코아에어로스페이스</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2824,26 +2822,26 @@
         <v>0</v>
       </c>
       <c r="H58" s="28" t="n">
-        <v>12.69</v>
+        <v>18.92</v>
       </c>
       <c r="I58" s="28" t="n">
-        <v>28.67</v>
+        <v>51.03</v>
       </c>
       <c r="J58" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +136%</t>
+          <t>네이버 검색 당일 +92% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K58" s="29" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2851,7 +2849,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>아이씨티케이</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2867,26 +2865,26 @@
         <v>0</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>3.95</v>
+        <v>1.45</v>
       </c>
       <c r="I59" s="28" t="n">
-        <v>29.94</v>
+        <v>21.95</v>
       </c>
       <c r="J59" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +119%</t>
+          <t>네이버 검색 당일 +50% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K59" s="29" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2894,7 +2892,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>이엔셀</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2910,26 +2908,24 @@
         <v>0</v>
       </c>
       <c r="H60" s="28" t="n">
-        <v>30.15</v>
+        <v>0.41</v>
       </c>
       <c r="I60" s="28" t="n">
-        <v>25.6</v>
+        <v>1.86</v>
       </c>
       <c r="J60" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +114%</t>
-        </is>
-      </c>
-      <c r="K60" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K60" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2937,7 +2933,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>파이온엑스</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2952,27 +2948,27 @@
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="28" t="n">
-        <v>18.92</v>
-      </c>
-      <c r="I61" s="28" t="n">
-        <v>51.03</v>
+      <c r="H61" s="27" t="n">
+        <v>-22.35</v>
+      </c>
+      <c r="I61" s="27" t="n">
+        <v>-33.73</v>
       </c>
       <c r="J61" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +79% / 중요공시 1건</t>
+          <t>중요공시 4건</t>
         </is>
       </c>
       <c r="K61" s="29" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2980,7 +2976,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>프리티</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2996,14 +2992,14 @@
         <v>0</v>
       </c>
       <c r="H62" s="27" t="n">
-        <v>-2.32</v>
+        <v>-29.91</v>
       </c>
       <c r="I62" s="27" t="n">
-        <v>-1.64</v>
+        <v>-35.77</v>
       </c>
       <c r="J62" s="29" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K62" s="29" t="inlineStr">
@@ -3015,7 +3011,7 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3023,7 +3019,7 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>아티스트컴퍼니</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
@@ -3038,19 +3034,21 @@
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="28" t="n">
-        <v>0.41</v>
+      <c r="H63" s="27" t="n">
+        <v>-3.18</v>
       </c>
       <c r="I63" s="28" t="n">
-        <v>1.86</v>
+        <v>11.13</v>
       </c>
       <c r="J63" s="29" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K63" s="29" t="n">
-        <v/>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K63" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3146,22 +3144,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3177,22 +3175,22 @@
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H4" s="28" t="n">
@@ -3205,64 +3203,60 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H5" s="28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I5" s="28" t="n">
-        <v>2.04</v>
-      </c>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H5" s="25" t="n"/>
+      <c r="I5" s="25" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H6" s="25" t="n"/>
@@ -3271,38 +3265,42 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H7" s="25" t="n"/>
-      <c r="I7" s="25" t="n"/>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I7" s="28" t="n">
+        <v>2.04</v>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
@@ -3319,25 +3317,25 @@
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H8" s="28" t="n">
-        <v>2.74</v>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>-0.62</v>
       </c>
       <c r="I8" s="27" t="n">
-        <v>-0.86</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
@@ -3354,12 +3352,12 @@
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H9" s="25" t="n"/>
@@ -3368,7 +3366,7 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
@@ -3385,25 +3383,25 @@
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H10" s="27" t="n">
-        <v>-0.62</v>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H10" s="28" t="n">
+        <v>1.5</v>
       </c>
       <c r="I10" s="27" t="n">
-        <v>-0.36</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
@@ -3420,19 +3418,19 @@
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H11" s="28" t="n">
-        <v>0.55</v>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>-29.89</v>
       </c>
       <c r="I11" s="27" t="n">
-        <v>-4.18</v>
+        <v>-44.49</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -3445,22 +3443,22 @@
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H12" s="25" t="n"/>
@@ -3469,91 +3467,99 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H13" s="25" t="n"/>
-      <c r="I13" s="25" t="n"/>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H13" s="28" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I13" s="27" t="n">
+        <v>-0.86</v>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H14" s="25" t="n"/>
-      <c r="I14" s="25" t="n"/>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H14" s="27" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="I14" s="27" t="n">
+        <v>-4.2</v>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H15" s="25" t="n"/>
@@ -3562,38 +3568,42 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H16" s="25" t="n"/>
-      <c r="I16" s="25" t="n"/>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H16" s="28" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="I16" s="28" t="n">
+        <v>27.7</v>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -3610,25 +3620,21 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H17" s="28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I17" s="27" t="n">
-        <v>-3.38</v>
-      </c>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -3645,165 +3651,165 @@
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H18" s="27" t="n">
-        <v>-29.89</v>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H18" s="28" t="n">
+        <v>0.55</v>
       </c>
       <c r="I18" s="27" t="n">
-        <v>-44.49</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>진영</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H19" s="28" t="n">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="I19" s="28" t="n">
-        <v>11.76</v>
+        <v>0.37</v>
+      </c>
+      <c r="I19" s="27" t="n">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>프리티</t>
+          <t>LS마린솔루션</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H20" s="27" t="n">
-        <v>-29.91</v>
-      </c>
-      <c r="I20" s="27" t="n">
-        <v>-35.77</v>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H20" s="28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I20" s="28" t="n">
+        <v>4.18</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>한전산업</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H21" s="28" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="I21" s="27" t="n">
-        <v>-4.05</v>
+        <v>-8.359999999999999</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H22" s="28" t="n">
-        <v>0.38</v>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H22" s="27" t="n">
+        <v>-8.24</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>12.69</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>LS마린솔루션</t>
+          <t>뷰티스킨</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -3820,25 +3826,25 @@
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H23" s="28" t="n">
-        <v>3.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I23" s="28" t="n">
-        <v>4.18</v>
+        <v>28.54</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>비츠로테크</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -3855,25 +3861,25 @@
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H24" s="27" t="n">
-        <v>-8.24</v>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H24" s="28" t="n">
+        <v>1.66</v>
       </c>
       <c r="I24" s="28" t="n">
-        <v>52.37</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>뷰티스킨</t>
+          <t>제주항공</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
@@ -3890,25 +3896,25 @@
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H25" s="28" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="I25" s="28" t="n">
-        <v>28.54</v>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H25" s="27" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="I25" s="27" t="n">
+        <v>-7.07</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>비츠로테크</t>
+          <t>진영</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
@@ -3925,25 +3931,25 @@
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H26" s="28" t="n">
-        <v>1.66</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="I26" s="28" t="n">
-        <v>33.07</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
@@ -3960,165 +3966,165 @@
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H27" s="27" t="n">
-        <v>-1.04</v>
+        <v>-0.71</v>
       </c>
       <c r="I27" s="27" t="n">
-        <v>-2.06</v>
+        <v>-6.89</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H28" s="28" t="n">
-        <v>1.45</v>
+        <v>3.53</v>
       </c>
       <c r="I28" s="28" t="n">
-        <v>21.95</v>
+        <v>33.67</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>엔에프씨</t>
+          <t>나라스페이스테크놀로지</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H29" s="28" t="n">
-        <v>28.91</v>
+        <v>1.81</v>
       </c>
       <c r="I29" s="28" t="n">
-        <v>16.2</v>
+        <v>36.89</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>우진</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H30" s="28" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="I30" s="27" t="n">
-        <v>-0.45</v>
+        <v>3.86</v>
+      </c>
+      <c r="I30" s="28" t="n">
+        <v>57.08</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H31" s="27" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="I31" s="27" t="n">
-        <v>-11.45</v>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H31" s="28" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I31" s="28" t="n">
+        <v>1.86</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
@@ -4135,25 +4141,25 @@
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H32" s="28" t="n">
-        <v>3.53</v>
+        <v>18.92</v>
       </c>
       <c r="I32" s="28" t="n">
-        <v>33.67</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>나라스페이스테크놀로지</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
@@ -4170,25 +4176,25 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H33" s="28" t="n">
-        <v>1.81</v>
+        <v>7.05</v>
       </c>
       <c r="I33" s="28" t="n">
-        <v>36.89</v>
+        <v>56.85</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
@@ -4205,25 +4211,25 @@
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H34" s="28" t="n">
-        <v>3.86</v>
+        <v>1.45</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>57.08</v>
+        <v>21.95</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>아이씨티케이</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
@@ -4240,25 +4246,25 @@
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H35" s="28" t="n">
-        <v>0.41</v>
+        <v>3.95</v>
       </c>
       <c r="I35" s="28" t="n">
-        <v>1.86</v>
+        <v>29.94</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>아이티센피엔에스</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
@@ -4275,25 +4281,25 @@
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H36" s="27" t="n">
-        <v>-2.32</v>
-      </c>
-      <c r="I36" s="27" t="n">
-        <v>-1.64</v>
+        <v>-3.01</v>
+      </c>
+      <c r="I36" s="28" t="n">
+        <v>66.41</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
@@ -4310,25 +4316,25 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H37" s="28" t="n">
-        <v>18.92</v>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H37" s="27" t="n">
+        <v>-3.27</v>
       </c>
       <c r="I37" s="28" t="n">
-        <v>51.03</v>
+        <v>16.48</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>센서뷰</t>
+          <t>아티스트컴퍼니</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4345,25 +4351,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H38" s="28" t="n">
-        <v>7.05</v>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H38" s="27" t="n">
+        <v>-3.18</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>56.85</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>아이씨티케이</t>
+          <t>에이스테크</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4380,25 +4386,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H39" s="28" t="n">
-        <v>3.95</v>
+        <v>5.74</v>
       </c>
       <c r="I39" s="28" t="n">
-        <v>29.94</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>아이티센피엔에스</t>
+          <t>오션인더블유</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4415,25 +4421,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H40" s="27" t="n">
-        <v>-3.01</v>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H40" s="28" t="n">
+        <v>18.49</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>66.41</v>
+        <v>18.57</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>우리넷</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4450,25 +4456,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H41" s="27" t="n">
-        <v>-3.27</v>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H41" s="28" t="n">
+        <v>8.26</v>
       </c>
       <c r="I41" s="28" t="n">
-        <v>16.48</v>
+        <v>23.13</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>에이스테크</t>
+          <t>이엔셀</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4485,25 +4491,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H42" s="28" t="n">
-        <v>5.74</v>
+        <v>30.15</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>24.22</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>오션인더블유</t>
+          <t>진양화학</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4520,25 +4526,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H43" s="28" t="n">
-        <v>18.49</v>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H43" s="27" t="n">
+        <v>-6.03</v>
       </c>
       <c r="I43" s="28" t="n">
-        <v>18.57</v>
+        <v>22.47</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>이엔셀</t>
+          <t>켄코아에어로스페이스</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4555,25 +4561,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H44" s="28" t="n">
-        <v>30.15</v>
+        <v>12.69</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>25.6</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>진양화학</t>
+          <t>큐라티스</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4590,25 +4596,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H45" s="27" t="n">
-        <v>-6.03</v>
+        <v>-5.09</v>
       </c>
       <c r="I45" s="28" t="n">
-        <v>22.47</v>
+        <v>58.13</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>켄코아에어로스페이스</t>
+          <t>티엠씨</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4625,25 +4631,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H46" s="28" t="n">
-        <v>12.69</v>
+        <v>7.8</v>
       </c>
       <c r="I46" s="28" t="n">
-        <v>28.67</v>
+        <v>37.22</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>큐라티스</t>
+          <t>파이온엑스</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4660,25 +4666,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H47" s="27" t="n">
-        <v>-5.09</v>
-      </c>
-      <c r="I47" s="28" t="n">
-        <v>58.13</v>
+        <v>-22.35</v>
+      </c>
+      <c r="I47" s="27" t="n">
+        <v>-33.73</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>티엠씨</t>
+          <t>프리티</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4695,19 +4701,19 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="H48" s="28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="I48" s="28" t="n">
-        <v>37.22</v>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H48" s="27" t="n">
+        <v>-29.91</v>
+      </c>
+      <c r="I48" s="27" t="n">
+        <v>-35.77</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -4730,12 +4736,12 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H49" s="27" t="n">
@@ -4765,12 +4771,12 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H50" s="28" t="n">
@@ -4800,12 +4806,12 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H51" s="27" t="n">
@@ -4835,12 +4841,12 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H52" s="27" t="n">
@@ -4931,19 +4937,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4962,19 +4968,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4986,7 +4992,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B5" s="36" t="n">
@@ -5000,12 +5006,12 @@
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5017,26 +5023,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5048,7 +5054,7 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
@@ -5062,12 +5068,12 @@
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5079,26 +5085,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5108,71 +5114,63 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="35" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="B9" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="D9" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="E9" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="F9" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="G9" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>이차전지</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="29" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G9" s="29" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="35" t="inlineStr">
-        <is>
-          <t>인공지능</t>
-        </is>
-      </c>
-      <c r="B10" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="D10" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="E10" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="F10" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="G10" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>AI반도체</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="29" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G10" s="29" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>이차전지</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
@@ -5199,7 +5197,7 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
@@ -5226,7 +5224,7 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -5253,7 +5251,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5280,7 +5278,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5307,7 +5305,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5334,7 +5332,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5361,7 +5359,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5388,7 +5386,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -5415,7 +5413,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -258,14 +258,14 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-21 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-22 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-21) 상위: 반도체  점수 78.0점</t>
+          <t>⚡ 최신(2026-09-22) 상위: 반도체  점수 74.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-21) 상위: 삼성전자  점수 34.0점</t>
+          <t>⚡ 최신(2026-09-22) 상위: 삼성전자  점수 36.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-21) 상위: 바이오  점수 22.0점</t>
+          <t>⚡ 최신(2026-09-22) 상위: 인공지능  점수 19.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -983,14 +983,14 @@
         <v>0</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>1.56</v>
+        <v>5.77</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>0.19</v>
+        <v>10.66</v>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,14 +1053,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>네이버</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1076,19 +1076,17 @@
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K17" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1100,10 +1098,10 @@
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1112,14 +1110,14 @@
         <v>0</v>
       </c>
       <c r="H18" s="18" t="n">
-        <v>4.7</v>
+        <v>1.62</v>
       </c>
       <c r="I18" s="18" t="n">
-        <v>2.04</v>
+        <v>11.65</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
@@ -1131,7 +1129,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1139,14 +1137,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1154,25 +1152,27 @@
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="19" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="I19" s="19" t="n">
-        <v>-0.36</v>
+      <c r="H19" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v/>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="n">
-        <v/>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K19" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
@@ -1203,19 +1203,17 @@
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1223,42 +1221,40 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H21" s="18" t="n">
-        <v>1.5</v>
+        <v>0</v>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>-1.36</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>-3.38</v>
+        <v>-1.63</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +50% / 중요공시 7일 +50%</t>
-        </is>
-      </c>
-      <c r="K21" s="17" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K21" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1266,7 +1262,7 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
@@ -1281,15 +1277,15 @@
       <c r="G22" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="H22" s="19" t="n">
-        <v>-29.89</v>
-      </c>
-      <c r="I22" s="19" t="n">
-        <v>-44.49</v>
+      <c r="H22" s="18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>2.61</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>중요공시 10건 / 중요공시 3일 +100% / 중요공시 7일 +67%</t>
+          <t>중요공시 4건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
@@ -1299,177 +1295,179 @@
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="n">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>로봇</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E23" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F23" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="20" t="n">
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>-2.84</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J23" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +50%</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>GS건설</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J24" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +50%</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="15" t="n">
         <v/>
       </c>
-      <c r="I23" s="20" t="n">
+      <c r="I25" s="15" t="n">
         <v/>
       </c>
-      <c r="J23" s="22" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K23" s="22" t="n">
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>삼성전기</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="18" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="I26" s="18" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="n">
         <v/>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="n">
-        <v>11</v>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E24" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F24" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="23" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="I24" s="24" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="J24" s="22" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K24" s="22" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>SFA반도체</t>
-        </is>
-      </c>
-      <c r="D25" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="E25" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="F25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="23" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="I25" s="23" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="J25" s="22" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +86% / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K25" s="22" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="C26" s="21" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="E26" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="F26" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I26" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J26" s="22" t="inlineStr">
-        <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
-        </is>
-      </c>
-      <c r="K26" s="22" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B27" s="20" t="n">
@@ -1477,14 +1475,14 @@
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>앤씨앤</t>
         </is>
       </c>
       <c r="D27" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F27" s="20" t="n">
         <v>0</v>
@@ -1492,27 +1490,27 @@
       <c r="G27" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="24" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="I27" s="24" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="J27" s="22" t="inlineStr">
-        <is>
-          <t>Google 급상승 검색어 등장 (US)</t>
-        </is>
-      </c>
-      <c r="K27" s="22" t="inlineStr">
-        <is>
-          <t>Google</t>
+      <c r="H27" s="22" t="n">
+        <v>-12.81</v>
+      </c>
+      <c r="I27" s="23" t="n">
+        <v>27.74</v>
+      </c>
+      <c r="J27" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +204% / 중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B28" s="20" t="n">
@@ -1520,40 +1518,42 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>인벤테라</t>
         </is>
       </c>
       <c r="D28" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E28" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F28" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G28" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I28" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J28" s="22" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K28" s="22" t="n">
-        <v/>
+      <c r="H28" s="23" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="I28" s="23" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="J28" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +199% / 중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B29" s="20" t="n">
@@ -1561,40 +1561,42 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="D29" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29" s="20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F29" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="23" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I29" s="24" t="n">
-        <v>-4.18</v>
-      </c>
-      <c r="J29" s="22" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K29" s="22" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H29" s="22" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="I29" s="22" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="J29" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1602,42 +1604,42 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="24" t="n">
-        <v>-8.24</v>
-      </c>
-      <c r="I30" s="23" t="n">
-        <v>52.37</v>
-      </c>
-      <c r="J30" s="22" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +1205% / 중요공시 2건</t>
-        </is>
-      </c>
-      <c r="K30" s="22" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
+        <v>3</v>
+      </c>
+      <c r="H30" s="22" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="I30" s="22" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="J30" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1645,14 +1647,14 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>뷰티스킨</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F31" s="20" t="n">
         <v>0</v>
@@ -1660,27 +1662,27 @@
       <c r="G31" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="23" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="I31" s="23" t="n">
-        <v>28.54</v>
-      </c>
-      <c r="J31" s="22" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +303% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K31" s="22" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
+      <c r="H31" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I31" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J31" s="24" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1688,14 +1690,14 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>비츠로테크</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F32" s="20" t="n">
         <v>0</v>
@@ -1704,26 +1706,24 @@
         <v>0</v>
       </c>
       <c r="H32" s="23" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="I32" s="23" t="n">
-        <v>33.07</v>
-      </c>
-      <c r="J32" s="22" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +228% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K32" s="22" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
+        <v>6.32</v>
+      </c>
+      <c r="J32" s="24" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K32" s="24" t="n">
+        <v/>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1731,14 +1731,14 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>진영</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>0</v>
@@ -1746,27 +1746,27 @@
       <c r="G33" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="23" t="n">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="I33" s="23" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="J33" s="22" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +144% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K33" s="22" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
+      <c r="H33" s="22" t="n">
+        <v>-29.01</v>
+      </c>
+      <c r="I33" s="22" t="n">
+        <v>-46.04</v>
+      </c>
+      <c r="J33" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +618% / 중요공시 1건 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1774,33 +1774,33 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F34" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H34" s="23" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I34" s="24" t="n">
-        <v>-8.359999999999999</v>
-      </c>
-      <c r="J34" s="22" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K34" s="22" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H34" s="22" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="I34" s="22" t="n">
+        <v>-8.56</v>
+      </c>
+      <c r="J34" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 5건 / 중요공시 3일 +67%</t>
+        </is>
+      </c>
+      <c r="K34" s="24" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1809,7 +1809,7 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1817,33 +1817,33 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>우진</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G35" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H35" s="24" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="I35" s="24" t="n">
-        <v>-6.89</v>
-      </c>
-      <c r="J35" s="22" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K35" s="22" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H35" s="22" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="I35" s="23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="J35" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 3일 +50%</t>
+        </is>
+      </c>
+      <c r="K35" s="24" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1852,7 +1852,7 @@
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1860,14 +1860,14 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>제주항공</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>0</v>
@@ -1875,27 +1875,27 @@
       <c r="G36" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="24" t="n">
-        <v>-5.07</v>
-      </c>
-      <c r="I36" s="24" t="n">
-        <v>-7.07</v>
-      </c>
-      <c r="J36" s="22" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K36" s="22" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="H36" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I36" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J36" s="24" t="inlineStr">
+        <is>
+          <t>Google 급상승 검색어 등장 (KR)</t>
+        </is>
+      </c>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1903,14 +1903,14 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>LS마린솔루션</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F37" s="20" t="n">
         <v>0</v>
@@ -1918,27 +1918,25 @@
       <c r="G37" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I37" s="23" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="J37" s="22" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K37" s="22" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H37" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I37" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J37" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K37" s="24" t="n">
+        <v/>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1946,515 +1944,503 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E38" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="22" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="I38" s="23" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J38" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K38" s="24" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>기업은행</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="22" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="J39" s="24" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K39" s="24" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="n">
+        <v>27</v>
+      </c>
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="23" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="I40" s="23" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J40" s="24" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K40" s="24" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>미투온</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E38" s="20" t="n">
+      <c r="E41" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="F38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="23" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="I38" s="24" t="n">
-        <v>-1.21</v>
-      </c>
-      <c r="J38" s="22" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K38" s="22" t="inlineStr">
+      <c r="F41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="22" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="I41" s="23" t="n">
+        <v>35.77</v>
+      </c>
+      <c r="J41" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +1240% / 중요공시 2건</t>
+        </is>
+      </c>
+      <c r="K41" s="24" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>뷰티스킨</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="22" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="I42" s="23" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="J42" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +325% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K42" s="24" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>비츠로테크</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="22" t="n">
+        <v>-5.16</v>
+      </c>
+      <c r="I43" s="23" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="J43" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +247% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K43" s="24" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="n">
+        <v>31</v>
+      </c>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>나라스페이스테크놀로지</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="23" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I44" s="23" t="n">
+        <v>37.43</v>
+      </c>
+      <c r="J44" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +205% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K44" s="24" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>성호전자</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="23" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I45" s="23" t="n">
+        <v>61.32</v>
+      </c>
+      <c r="J45" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +104% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K45" s="24" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>LG전자</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I46" s="23" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="J46" s="24" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K46" s="24" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>방산</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I47" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J47" s="24" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K47" s="24" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B39" s="25" t="n">
-        <v>26</v>
-      </c>
-      <c r="C39" s="26" t="inlineStr">
-        <is>
-          <t>아이티센피엔에스</t>
-        </is>
-      </c>
-      <c r="D39" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E39" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F39" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="27" t="n">
-        <v>-3.01</v>
-      </c>
-      <c r="I39" s="28" t="n">
-        <v>66.41</v>
-      </c>
-      <c r="J39" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +884%</t>
-        </is>
-      </c>
-      <c r="K39" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B40" s="25" t="n">
-        <v>27</v>
-      </c>
-      <c r="C40" s="26" t="inlineStr">
-        <is>
-          <t>빛샘전자</t>
-        </is>
-      </c>
-      <c r="D40" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E40" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F40" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="28" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="I40" s="28" t="n">
-        <v>57.08</v>
-      </c>
-      <c r="J40" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +531%</t>
-        </is>
-      </c>
-      <c r="K40" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B41" s="25" t="n">
-        <v>28</v>
-      </c>
-      <c r="C41" s="26" t="inlineStr">
-        <is>
-          <t>큐라티스</t>
-        </is>
-      </c>
-      <c r="D41" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E41" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F41" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="27" t="n">
-        <v>-5.09</v>
-      </c>
-      <c r="I41" s="28" t="n">
-        <v>58.13</v>
-      </c>
-      <c r="J41" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +414%</t>
-        </is>
-      </c>
-      <c r="K41" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B42" s="25" t="n">
-        <v>29</v>
-      </c>
-      <c r="C42" s="26" t="inlineStr">
-        <is>
-          <t>한켐</t>
-        </is>
-      </c>
-      <c r="D42" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E42" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F42" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="27" t="n">
-        <v>-5.41</v>
-      </c>
-      <c r="I42" s="28" t="n">
-        <v>37.38</v>
-      </c>
-      <c r="J42" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +355%</t>
-        </is>
-      </c>
-      <c r="K42" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B43" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="C43" s="26" t="inlineStr">
-        <is>
-          <t>아톤</t>
-        </is>
-      </c>
-      <c r="D43" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E43" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F43" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="27" t="n">
-        <v>-3.27</v>
-      </c>
-      <c r="I43" s="28" t="n">
-        <v>16.48</v>
-      </c>
-      <c r="J43" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +302%</t>
-        </is>
-      </c>
-      <c r="K43" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B44" s="25" t="n">
-        <v>31</v>
-      </c>
-      <c r="C44" s="26" t="inlineStr">
-        <is>
-          <t>한국첨단소재</t>
-        </is>
-      </c>
-      <c r="D44" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E44" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F44" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="27" t="n">
-        <v>-2.92</v>
-      </c>
-      <c r="I44" s="28" t="n">
-        <v>50.25</v>
-      </c>
-      <c r="J44" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +296%</t>
-        </is>
-      </c>
-      <c r="K44" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B45" s="25" t="n">
-        <v>32</v>
-      </c>
-      <c r="C45" s="26" t="inlineStr">
-        <is>
-          <t>한컴위드</t>
-        </is>
-      </c>
-      <c r="D45" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E45" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="27" t="n">
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>카카오</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="22" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="I48" s="22" t="n">
         <v>-3.33</v>
       </c>
-      <c r="I45" s="28" t="n">
-        <v>25.13</v>
-      </c>
-      <c r="J45" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +280%</t>
-        </is>
-      </c>
-      <c r="K45" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B46" s="25" t="n">
-        <v>33</v>
-      </c>
-      <c r="C46" s="26" t="inlineStr">
-        <is>
-          <t>한컴라이프케어</t>
-        </is>
-      </c>
-      <c r="D46" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="28" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="I46" s="28" t="n">
-        <v>20.23</v>
-      </c>
-      <c r="J46" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +226%</t>
-        </is>
-      </c>
-      <c r="K46" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B47" s="25" t="n">
-        <v>34</v>
-      </c>
-      <c r="C47" s="26" t="inlineStr">
-        <is>
-          <t>진양화학</t>
-        </is>
-      </c>
-      <c r="D47" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E47" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F47" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="27" t="n">
-        <v>-6.03</v>
-      </c>
-      <c r="I47" s="28" t="n">
-        <v>22.47</v>
-      </c>
-      <c r="J47" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +225%</t>
-        </is>
-      </c>
-      <c r="K47" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B48" s="25" t="n">
-        <v>35</v>
-      </c>
-      <c r="C48" s="26" t="inlineStr">
-        <is>
-          <t>티엠씨</t>
-        </is>
-      </c>
-      <c r="D48" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F48" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="I48" s="28" t="n">
-        <v>37.22</v>
-      </c>
-      <c r="J48" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +195%</t>
-        </is>
-      </c>
-      <c r="K48" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="J48" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K48" s="24" t="n">
+        <v/>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B49" s="25" t="n">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="n">
         <v>36</v>
       </c>
-      <c r="C49" s="26" t="inlineStr">
-        <is>
-          <t>센서뷰</t>
-        </is>
-      </c>
-      <c r="D49" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E49" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F49" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="28" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="I49" s="28" t="n">
-        <v>56.85</v>
-      </c>
-      <c r="J49" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +194%</t>
-        </is>
-      </c>
-      <c r="K49" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="C49" s="21" t="inlineStr">
+        <is>
+          <t>코웨이</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="22" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="I49" s="23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J49" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K49" s="24" t="n">
+        <v/>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2462,7 +2448,7 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>나라스페이스테크놀로지</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -2477,15 +2463,15 @@
       <c r="G50" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="28" t="n">
-        <v>1.81</v>
+      <c r="H50" s="27" t="n">
+        <v>-1.43</v>
       </c>
       <c r="I50" s="28" t="n">
-        <v>36.89</v>
+        <v>19.1</v>
       </c>
       <c r="J50" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +191%</t>
+          <t>네이버 검색 당일 +553%</t>
         </is>
       </c>
       <c r="K50" s="29" t="inlineStr">
@@ -2497,7 +2483,7 @@
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2505,7 +2491,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>오션인더블유</t>
+          <t>큐라티스</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2520,15 +2506,15 @@
       <c r="G51" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="28" t="n">
-        <v>18.49</v>
+      <c r="H51" s="27" t="n">
+        <v>-6.56</v>
       </c>
       <c r="I51" s="28" t="n">
-        <v>18.57</v>
+        <v>43.29</v>
       </c>
       <c r="J51" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +179%</t>
+          <t>네이버 검색 당일 +428%</t>
         </is>
       </c>
       <c r="K51" s="29" t="inlineStr">
@@ -2540,7 +2526,7 @@
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2548,7 +2534,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>한켐</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2563,15 +2549,15 @@
       <c r="G52" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="28" t="n">
-        <v>3.53</v>
+      <c r="H52" s="27" t="n">
+        <v>-1.73</v>
       </c>
       <c r="I52" s="28" t="n">
-        <v>33.67</v>
+        <v>40.87</v>
       </c>
       <c r="J52" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +166%</t>
+          <t>네이버 검색 당일 +367%</t>
         </is>
       </c>
       <c r="K52" s="29" t="inlineStr">
@@ -2583,7 +2569,7 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2591,7 +2577,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>켄코아에어로스페이스</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2607,14 +2593,14 @@
         <v>0</v>
       </c>
       <c r="H53" s="28" t="n">
-        <v>12.69</v>
+        <v>0.53</v>
       </c>
       <c r="I53" s="28" t="n">
-        <v>28.67</v>
+        <v>15.31</v>
       </c>
       <c r="J53" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +158%</t>
+          <t>네이버 검색 당일 +311%</t>
         </is>
       </c>
       <c r="K53" s="29" t="inlineStr">
@@ -2626,7 +2612,7 @@
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2634,7 +2620,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>에이스테크</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2649,15 +2635,15 @@
       <c r="G54" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="28" t="n">
-        <v>5.74</v>
+      <c r="H54" s="27" t="n">
+        <v>-1.67</v>
       </c>
       <c r="I54" s="28" t="n">
-        <v>24.22</v>
+        <v>13.73</v>
       </c>
       <c r="J54" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +148%</t>
+          <t>네이버 검색 당일 +304%</t>
         </is>
       </c>
       <c r="K54" s="29" t="inlineStr">
@@ -2669,7 +2655,7 @@
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2677,7 +2663,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>이엔셀</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2693,14 +2679,14 @@
         <v>0</v>
       </c>
       <c r="H55" s="28" t="n">
-        <v>30.15</v>
+        <v>1.22</v>
       </c>
       <c r="I55" s="28" t="n">
-        <v>25.6</v>
+        <v>26.17</v>
       </c>
       <c r="J55" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +146%</t>
+          <t>네이버 검색 당일 +291%</t>
         </is>
       </c>
       <c r="K55" s="29" t="inlineStr">
@@ -2712,7 +2698,7 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2720,7 +2706,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>아이씨티케이</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2735,15 +2721,15 @@
       <c r="G56" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="28" t="n">
-        <v>3.95</v>
+      <c r="H56" s="27" t="n">
+        <v>-6.59</v>
       </c>
       <c r="I56" s="28" t="n">
-        <v>29.94</v>
+        <v>47.78</v>
       </c>
       <c r="J56" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +133%</t>
+          <t>네이버 검색 당일 +211%</t>
         </is>
       </c>
       <c r="K56" s="29" t="inlineStr">
@@ -2755,7 +2741,7 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2763,7 +2749,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>우리넷</t>
+          <t>티엠씨</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2778,15 +2764,15 @@
       <c r="G57" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="28" t="n">
-        <v>8.26</v>
+      <c r="H57" s="27" t="n">
+        <v>-3.28</v>
       </c>
       <c r="I57" s="28" t="n">
-        <v>23.13</v>
+        <v>9.73</v>
       </c>
       <c r="J57" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +104%</t>
+          <t>네이버 검색 당일 +209%</t>
         </is>
       </c>
       <c r="K57" s="29" t="inlineStr">
@@ -2798,7 +2784,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2806,7 +2792,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>한선엔지니어링</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2822,26 +2808,26 @@
         <v>0</v>
       </c>
       <c r="H58" s="28" t="n">
-        <v>18.92</v>
+        <v>0.59</v>
       </c>
       <c r="I58" s="28" t="n">
-        <v>51.03</v>
+        <v>27.28</v>
       </c>
       <c r="J58" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +92% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +184%</t>
         </is>
       </c>
       <c r="K58" s="29" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2849,7 +2835,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2865,26 +2851,26 @@
         <v>0</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>1.45</v>
+        <v>3.98</v>
       </c>
       <c r="I59" s="28" t="n">
-        <v>21.95</v>
+        <v>6.91</v>
       </c>
       <c r="J59" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +50% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +171%</t>
         </is>
       </c>
       <c r="K59" s="29" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2892,7 +2878,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>드림텍</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2908,24 +2894,26 @@
         <v>0</v>
       </c>
       <c r="H60" s="28" t="n">
-        <v>0.41</v>
+        <v>6.41</v>
       </c>
       <c r="I60" s="28" t="n">
-        <v>1.86</v>
+        <v>28.39</v>
       </c>
       <c r="J60" s="29" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K60" s="29" t="n">
-        <v/>
+          <t>네이버 검색 당일 +100%</t>
+        </is>
+      </c>
+      <c r="K60" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2933,7 +2921,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>파이온엑스</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2949,26 +2937,26 @@
         <v>0</v>
       </c>
       <c r="H61" s="27" t="n">
-        <v>-22.35</v>
-      </c>
-      <c r="I61" s="27" t="n">
-        <v>-33.73</v>
+        <v>-3.38</v>
+      </c>
+      <c r="I61" s="28" t="n">
+        <v>5.32</v>
       </c>
       <c r="J61" s="29" t="inlineStr">
         <is>
-          <t>중요공시 4건</t>
+          <t>네이버 검색 당일 +51% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K61" s="29" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2976,7 +2964,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>프리티</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2991,27 +2979,25 @@
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="27" t="n">
-        <v>-29.91</v>
-      </c>
-      <c r="I62" s="27" t="n">
-        <v>-35.77</v>
+      <c r="H62" s="25" t="n">
+        <v/>
+      </c>
+      <c r="I62" s="25" t="n">
+        <v/>
       </c>
       <c r="J62" s="29" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K62" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K62" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3019,7 +3005,7 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>아티스트컴퍼니</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
@@ -3035,14 +3021,14 @@
         <v>0</v>
       </c>
       <c r="H63" s="27" t="n">
-        <v>-3.18</v>
-      </c>
-      <c r="I63" s="28" t="n">
-        <v>11.13</v>
+        <v>-4.74</v>
+      </c>
+      <c r="I63" s="27" t="n">
+        <v>-32.34</v>
       </c>
       <c r="J63" s="29" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>중요공시 8건</t>
         </is>
       </c>
       <c r="K63" s="29" t="inlineStr">
@@ -3144,22 +3130,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3175,57 +3161,57 @@
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H4" s="28" t="n">
-        <v>1.56</v>
+        <v>5.77</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>0.19</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H5" s="25" t="n"/>
@@ -3234,29 +3220,29 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>네이버</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H6" s="25" t="n"/>
@@ -3272,70 +3258,66 @@
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H7" s="28" t="n">
-        <v>4.7</v>
+        <v>1.62</v>
       </c>
       <c r="I7" s="28" t="n">
-        <v>2.04</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="I8" s="27" t="n">
-        <v>-0.36</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="25" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
@@ -3352,12 +3334,12 @@
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H9" s="25" t="n"/>
@@ -3366,42 +3348,42 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H10" s="28" t="n">
-        <v>1.5</v>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H10" s="27" t="n">
+        <v>-1.36</v>
       </c>
       <c r="I10" s="27" t="n">
-        <v>-3.38</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
@@ -3418,958 +3400,950 @@
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H11" s="27" t="n">
-        <v>-29.89</v>
-      </c>
-      <c r="I11" s="27" t="n">
-        <v>-44.49</v>
+        <v>-1.08</v>
+      </c>
+      <c r="I11" s="28" t="n">
+        <v>1.66</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H12" s="25" t="n"/>
-      <c r="I12" s="25" t="n"/>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H12" s="28" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I12" s="28" t="n">
+        <v>2.61</v>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H13" s="28" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="I13" s="27" t="n">
-        <v>-0.86</v>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H13" s="27" t="n">
+        <v>-2.84</v>
+      </c>
+      <c r="I13" s="28" t="n">
+        <v>0.76</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H14" s="27" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="I14" s="27" t="n">
-        <v>-4.2</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="25" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H15" s="25" t="n"/>
-      <c r="I15" s="25" t="n"/>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H15" s="28" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="I15" s="28" t="n">
+        <v>8.32</v>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H16" s="28" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="I16" s="28" t="n">
-        <v>27.7</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H17" s="25" t="n"/>
-      <c r="I17" s="25" t="n"/>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="I17" s="27" t="n">
+        <v>-2.8</v>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H18" s="28" t="n">
-        <v>0.55</v>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>-2.96</v>
       </c>
       <c r="I18" s="27" t="n">
-        <v>-4.18</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H19" s="28" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="I19" s="27" t="n">
-        <v>-1.21</v>
+        <v>1.67</v>
+      </c>
+      <c r="I19" s="28" t="n">
+        <v>6.32</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>LS마린솔루션</t>
+          <t>앤씨앤</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H20" s="28" t="n">
-        <v>3.7</v>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>-12.81</v>
       </c>
       <c r="I20" s="28" t="n">
-        <v>4.18</v>
+        <v>27.74</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>인벤테라</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H21" s="28" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I21" s="27" t="n">
-        <v>-8.359999999999999</v>
+        <v>18.51</v>
+      </c>
+      <c r="I21" s="28" t="n">
+        <v>42.5</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H22" s="27" t="n">
-        <v>-8.24</v>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H22" s="28" t="n">
+        <v>0.19</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>52.37</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>뷰티스킨</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H23" s="28" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="I23" s="28" t="n">
-        <v>28.54</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="25" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>비츠로테크</t>
+          <t>기업은행</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E24" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H24" s="28" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="I24" s="28" t="n">
-        <v>33.07</v>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="27" t="n">
+        <v>-3.12</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>제주항공</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H25" s="27" t="n">
-        <v>-5.07</v>
+        <v>-4.47</v>
       </c>
       <c r="I25" s="27" t="n">
-        <v>-7.07</v>
+        <v>-8.56</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>진영</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H26" s="28" t="n">
-        <v>8.460000000000001</v>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H26" s="27" t="n">
+        <v>-1.11</v>
       </c>
       <c r="I26" s="28" t="n">
-        <v>11.76</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H27" s="27" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="I27" s="27" t="n">
-        <v>-6.89</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H27" s="25" t="n"/>
+      <c r="I27" s="25" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H28" s="28" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="I28" s="28" t="n">
-        <v>33.67</v>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H28" s="27" t="n">
+        <v>-29.01</v>
+      </c>
+      <c r="I28" s="27" t="n">
+        <v>-46.04</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>나라스페이스테크놀로지</t>
+          <t>우진</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E29" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H29" s="28" t="n">
-        <v>1.81</v>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H29" s="27" t="n">
+        <v>-3.57</v>
       </c>
       <c r="I29" s="28" t="n">
-        <v>36.89</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H30" s="28" t="n">
-        <v>3.86</v>
+        <v>2.16</v>
       </c>
       <c r="I30" s="28" t="n">
-        <v>57.08</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>나라스페이스테크놀로지</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H31" s="28" t="n">
-        <v>0.41</v>
+        <v>0.78</v>
       </c>
       <c r="I31" s="28" t="n">
-        <v>1.86</v>
+        <v>37.43</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H32" s="28" t="n">
-        <v>18.92</v>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H32" s="27" t="n">
+        <v>-2.28</v>
       </c>
       <c r="I32" s="28" t="n">
-        <v>51.03</v>
+        <v>35.77</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>센서뷰</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H33" s="28" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="I33" s="28" t="n">
-        <v>56.85</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H33" s="25" t="n"/>
+      <c r="I33" s="25" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>뷰티스킨</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H34" s="28" t="n">
-        <v>1.45</v>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H34" s="27" t="n">
+        <v>-1.57</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>21.95</v>
+        <v>25.38</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>아이씨티케이</t>
+          <t>비츠로테크</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H35" s="28" t="n">
-        <v>3.95</v>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H35" s="27" t="n">
+        <v>-5.16</v>
       </c>
       <c r="I35" s="28" t="n">
-        <v>29.94</v>
+        <v>30.53</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>아이티센피엔에스</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H36" s="27" t="n">
-        <v>-3.01</v>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H36" s="28" t="n">
+        <v>2.84</v>
       </c>
       <c r="I36" s="28" t="n">
-        <v>66.41</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H37" s="27" t="n">
-        <v>-3.27</v>
-      </c>
-      <c r="I37" s="28" t="n">
-        <v>16.48</v>
+        <v>-0.6</v>
+      </c>
+      <c r="I37" s="27" t="n">
+        <v>-3.33</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>아티스트컴퍼니</t>
+          <t>코웨이</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D38" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H38" s="27" t="n">
-        <v>-3.18</v>
+        <v>-0.39</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>11.13</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>에이스테크</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4386,25 +4360,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H39" s="28" t="n">
-        <v>5.74</v>
+        <v>3.98</v>
       </c>
       <c r="I39" s="28" t="n">
-        <v>24.22</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>오션인더블유</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4421,25 +4395,21 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H40" s="28" t="n">
-        <v>18.49</v>
-      </c>
-      <c r="I40" s="28" t="n">
-        <v>18.57</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H40" s="25" t="n"/>
+      <c r="I40" s="25" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>우리넷</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4456,25 +4426,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H41" s="28" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="I41" s="28" t="n">
-        <v>23.13</v>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H41" s="27" t="n">
+        <v>-4.74</v>
+      </c>
+      <c r="I41" s="27" t="n">
+        <v>-32.34</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>이엔셀</t>
+          <t>드림텍</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4491,25 +4461,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H42" s="28" t="n">
-        <v>30.15</v>
+        <v>6.41</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>25.6</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>진양화학</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4526,25 +4496,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H43" s="27" t="n">
-        <v>-6.03</v>
+        <v>-1.43</v>
       </c>
       <c r="I43" s="28" t="n">
-        <v>22.47</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>켄코아에어로스페이스</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4561,25 +4531,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H44" s="28" t="n">
-        <v>12.69</v>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H44" s="27" t="n">
+        <v>-6.59</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>28.67</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>큐라티스</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4596,25 +4566,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H45" s="27" t="n">
-        <v>-5.09</v>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H45" s="28" t="n">
+        <v>0.53</v>
       </c>
       <c r="I45" s="28" t="n">
-        <v>58.13</v>
+        <v>15.31</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>티엠씨</t>
+          <t>큐라티스</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4631,25 +4601,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H46" s="28" t="n">
-        <v>7.8</v>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H46" s="27" t="n">
+        <v>-6.56</v>
       </c>
       <c r="I46" s="28" t="n">
-        <v>37.22</v>
+        <v>43.29</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>파이온엑스</t>
+          <t>티엠씨</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4666,25 +4636,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H47" s="27" t="n">
-        <v>-22.35</v>
-      </c>
-      <c r="I47" s="27" t="n">
-        <v>-33.73</v>
+        <v>-3.28</v>
+      </c>
+      <c r="I47" s="28" t="n">
+        <v>9.73</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>프리티</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4701,25 +4671,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H48" s="27" t="n">
-        <v>-29.91</v>
-      </c>
-      <c r="I48" s="27" t="n">
-        <v>-35.77</v>
+        <v>-1.67</v>
+      </c>
+      <c r="I48" s="28" t="n">
+        <v>13.73</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>한선엔지니어링</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4736,25 +4706,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="H49" s="27" t="n">
-        <v>-2.92</v>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H49" s="28" t="n">
+        <v>0.59</v>
       </c>
       <c r="I49" s="28" t="n">
-        <v>50.25</v>
+        <v>27.28</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>한컴라이프케어</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4771,25 +4741,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H50" s="28" t="n">
-        <v>4.85</v>
+        <v>1.22</v>
       </c>
       <c r="I50" s="28" t="n">
-        <v>20.23</v>
+        <v>26.17</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>한켐</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4806,25 +4776,25 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H51" s="27" t="n">
-        <v>-3.33</v>
+        <v>-1.73</v>
       </c>
       <c r="I51" s="28" t="n">
-        <v>25.13</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>한켐</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -4841,19 +4811,19 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H52" s="27" t="n">
-        <v>-5.41</v>
+        <v>-3.38</v>
       </c>
       <c r="I52" s="28" t="n">
-        <v>37.38</v>
+        <v>5.32</v>
       </c>
     </row>
   </sheetData>
@@ -4937,19 +4907,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4968,19 +4938,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4992,26 +4962,26 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B5" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5023,26 +4993,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5054,26 +5024,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5085,119 +5055,131 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
+          <t>게임</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="F8" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G8" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="F9" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G9" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
           <t>인공지능</t>
         </is>
       </c>
-      <c r="B8" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="36" t="n">
+      <c r="B10" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="36" t="n">
         <v>19</v>
       </c>
-      <c r="D8" s="36" t="n">
+      <c r="D10" s="36" t="n">
         <v>19</v>
       </c>
-      <c r="E8" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="F8" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G8" s="37" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G10" s="37" t="inlineStr">
         <is>
           <t>⚡ 관심</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
-        <is>
-          <t>이차전지</t>
-        </is>
-      </c>
-      <c r="B9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="29" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G9" s="29" t="inlineStr"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>AI반도체</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="29" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G10" s="29" t="inlineStr"/>
-    </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>전기차</t>
-        </is>
-      </c>
-      <c r="B11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="29" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G11" s="29" t="inlineStr"/>
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="F11" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G11" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
@@ -5224,7 +5206,7 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -5251,7 +5233,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5278,7 +5260,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5305,7 +5287,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5332,7 +5314,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5359,7 +5341,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5386,7 +5368,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -5413,7 +5395,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -5440,7 +5422,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>의료기기</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -5467,7 +5449,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>의료기기</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
@@ -5494,7 +5476,7 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -5521,7 +5503,7 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -258,14 +258,14 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -276,11 +276,11 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-22 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-23 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-22) 상위: 반도체  점수 74.0점</t>
+          <t>⚡ 최신(2026-09-23) 상위: 반도체  점수 75.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-22) 상위: 삼성전자  점수 36.0점</t>
+          <t>⚡ 최신(2026-09-23) 상위: 원전  점수 24.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-22) 상위: 인공지능  점수 19.0점</t>
+          <t>⚡ 최신(2026-09-23) 상위: 삼성전자  점수 21.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -967,14 +967,14 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -982,27 +982,25 @@
       <c r="G15" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="18" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>10.66</v>
+      <c r="H15" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v/>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K15" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K15" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1008,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1025,27 +1023,25 @@
       <c r="G16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="15" t="n">
+      <c r="H16" s="18" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="J16" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="n">
         <v/>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,14 +1049,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1068,15 +1064,15 @@
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v/>
+      <c r="H17" s="19" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>7.54</v>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="n">
@@ -1086,7 +1082,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1094,14 +1090,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1110,26 +1106,24 @@
         <v>0</v>
       </c>
       <c r="H18" s="18" t="n">
-        <v>1.62</v>
+        <v>3.66</v>
       </c>
       <c r="I18" s="18" t="n">
-        <v>11.65</v>
+        <v>2.38</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1137,14 +1131,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1160,7 +1154,7 @@
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="inlineStr">
@@ -1172,7 +1166,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1180,14 +1174,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1195,25 +1189,27 @@
       <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v/>
+      <c r="H20" s="18" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="I20" s="18" t="n">
+        <v>24.62</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="n">
-        <v/>
+          <t>중요공시 4건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1221,14 +1217,14 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1236,15 +1232,15 @@
       <c r="G21" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="19" t="n">
-        <v>-1.36</v>
-      </c>
-      <c r="I21" s="19" t="n">
-        <v>-1.63</v>
+      <c r="H21" s="18" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="I21" s="18" t="n">
+        <v>11.95</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="n">
@@ -1254,7 +1250,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1262,42 +1258,40 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="I22" s="18" t="n">
-        <v>2.61</v>
+        <v>0</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v/>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>중요공시 4건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1305,42 +1299,40 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" s="19" t="n">
-        <v>-2.84</v>
-      </c>
-      <c r="I23" s="18" t="n">
-        <v>0.76</v>
+        <v>0</v>
+      </c>
+      <c r="H23" s="18" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I23" s="19" t="n">
+        <v>-1.3</v>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +50%</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1348,42 +1340,42 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H24" s="19" t="n">
-        <v>-1.08</v>
-      </c>
-      <c r="I24" s="18" t="n">
-        <v>1.66</v>
+        <v>0</v>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v/>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +50%</t>
+          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1391,14 +1383,14 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F25" s="15" t="n">
         <v>0</v>
@@ -1426,7 +1418,7 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1434,126 +1426,126 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="18" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="I26" s="18" t="n">
-        <v>8.32</v>
+        <v>3</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>-3.42</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>-1.78</v>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="n">
+          <t>중요공시 3건 / 중요공시 3일 +50% / 중요공시 7일 +50%</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" s="18" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 3일 +50% / 중요공시 7일 +50%</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>KT&amp;G</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I28" s="18" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="J28" s="17" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="17" t="n">
         <v/>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="C27" s="21" t="inlineStr">
-        <is>
-          <t>앤씨앤</t>
-        </is>
-      </c>
-      <c r="D27" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E27" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="22" t="n">
-        <v>-12.81</v>
-      </c>
-      <c r="I27" s="23" t="n">
-        <v>27.74</v>
-      </c>
-      <c r="J27" s="24" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +204% / 중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K27" s="24" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>인벤테라</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E28" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F28" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="23" t="n">
-        <v>18.51</v>
-      </c>
-      <c r="I28" s="23" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="J28" s="24" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +199% / 중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K28" s="24" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B29" s="20" t="n">
@@ -1561,42 +1553,40 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="D29" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E29" s="20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F29" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G29" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H29" s="22" t="n">
-        <v>-2.96</v>
+        <v>5.91</v>
       </c>
       <c r="I29" s="22" t="n">
-        <v>-2.66</v>
-      </c>
-      <c r="J29" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K29" s="24" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+        <v>6.44</v>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K29" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1604,33 +1594,33 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G30" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="22" t="n">
-        <v>-1.99</v>
-      </c>
-      <c r="I30" s="22" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="J30" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K30" s="24" t="inlineStr">
+      <c r="H30" s="24" t="n">
+        <v>-20.08</v>
+      </c>
+      <c r="I30" s="24" t="n">
+        <v>-40.46</v>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 9건 / 중요공시 7일 +50%</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1639,7 +1629,7 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1647,42 +1637,42 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>우성머티리얼스</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F31" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I31" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J31" s="24" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K31" s="24" t="inlineStr">
-        <is>
-          <t>네이버</t>
+        <v>3</v>
+      </c>
+      <c r="H31" s="22" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="I31" s="22" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 7건 / 중요공시 7일 +600%</t>
+        </is>
+      </c>
+      <c r="K31" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1690,40 +1680,42 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F32" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="I32" s="23" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="J32" s="24" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K32" s="24" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H32" s="22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I32" s="24" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 4건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1731,42 +1723,42 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="22" t="n">
-        <v>-29.01</v>
-      </c>
-      <c r="I33" s="22" t="n">
-        <v>-46.04</v>
-      </c>
-      <c r="J33" s="24" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +618% / 중요공시 1건 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K33" s="24" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+        <v>3</v>
+      </c>
+      <c r="H33" s="24" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="I33" s="24" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="J33" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 7일 +200%</t>
+        </is>
+      </c>
+      <c r="K33" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1774,33 +1766,33 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>2</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="22" t="n">
-        <v>-4.47</v>
+        <v>3</v>
+      </c>
+      <c r="H34" s="24" t="n">
+        <v>-3.62</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>-8.56</v>
-      </c>
-      <c r="J34" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 5건 / 중요공시 3일 +67%</t>
-        </is>
-      </c>
-      <c r="K34" s="24" t="inlineStr">
+        <v>12.16</v>
+      </c>
+      <c r="J34" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1809,7 +1801,7 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1817,33 +1809,33 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>우진</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" s="20" t="n">
         <v>2</v>
       </c>
       <c r="G35" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H35" s="22" t="n">
-        <v>-3.57</v>
-      </c>
-      <c r="I35" s="23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="J35" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 3일 +50%</t>
-        </is>
-      </c>
-      <c r="K35" s="24" t="inlineStr">
+        <v>3.22</v>
+      </c>
+      <c r="I35" s="24" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K35" s="23" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1852,7 +1844,7 @@
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1860,14 +1852,14 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>0</v>
@@ -1881,21 +1873,19 @@
       <c r="I36" s="20" t="n">
         <v/>
       </c>
-      <c r="J36" s="24" t="inlineStr">
-        <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
-        </is>
-      </c>
-      <c r="K36" s="24" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
+      <c r="J36" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1903,14 +1893,14 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F37" s="20" t="n">
         <v>0</v>
@@ -1924,19 +1914,19 @@
       <c r="I37" s="20" t="n">
         <v/>
       </c>
-      <c r="J37" s="24" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K37" s="24" t="n">
+      <c r="J37" s="23" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K37" s="23" t="n">
         <v/>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1944,14 +1934,14 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F38" s="20" t="n">
         <v>0</v>
@@ -1960,24 +1950,24 @@
         <v>0</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>-1.11</v>
-      </c>
-      <c r="I38" s="23" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="J38" s="24" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K38" s="24" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I38" s="24" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="J38" s="23" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="n">
         <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1985,40 +1975,42 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>기업은행</t>
+          <t>우진</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
         <v>5</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F39" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G39" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="22" t="n">
-        <v>-3.12</v>
-      </c>
-      <c r="J39" s="24" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K39" s="24" t="n">
-        <v/>
+      <c r="H39" s="24" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="I39" s="24" t="n">
+        <v>-2.87</v>
+      </c>
+      <c r="J39" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 3일 +50%</t>
+        </is>
+      </c>
+      <c r="K39" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2026,7 +2018,7 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
@@ -2041,25 +2033,27 @@
       <c r="G40" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="23" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I40" s="23" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="J40" s="24" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K40" s="24" t="n">
+      <c r="H40" s="20" t="n">
         <v/>
+      </c>
+      <c r="I40" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
+          <t>Google 급상승 검색어 등장 (KR)</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2067,14 +2061,14 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E41" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F41" s="20" t="n">
         <v>0</v>
@@ -2082,27 +2076,27 @@
       <c r="G41" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="22" t="n">
-        <v>-2.28</v>
-      </c>
-      <c r="I41" s="23" t="n">
-        <v>35.77</v>
-      </c>
-      <c r="J41" s="24" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +1240% / 중요공시 2건</t>
-        </is>
-      </c>
-      <c r="K41" s="24" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+      <c r="H41" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I41" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J41" s="23" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K41" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -2110,14 +2104,14 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>뷰티스킨</t>
+          <t>네이버</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E42" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F42" s="20" t="n">
         <v>0</v>
@@ -2125,27 +2119,25 @@
       <c r="G42" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="22" t="n">
-        <v>-1.57</v>
-      </c>
-      <c r="I42" s="23" t="n">
-        <v>25.38</v>
-      </c>
-      <c r="J42" s="24" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +325% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K42" s="24" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
+      <c r="H42" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I42" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J42" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K42" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B43" s="20" t="n">
@@ -2153,7 +2145,7 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>비츠로테크</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="D43" s="20" t="n">
@@ -2168,27 +2160,27 @@
       <c r="G43" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="22" t="n">
-        <v>-5.16</v>
-      </c>
-      <c r="I43" s="23" t="n">
-        <v>30.53</v>
-      </c>
-      <c r="J43" s="24" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +247% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K43" s="24" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+      <c r="H43" s="24" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="I43" s="22" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="J43" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K43" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B44" s="20" t="n">
@@ -2196,7 +2188,7 @@
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>나라스페이스테크놀로지</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="D44" s="20" t="n">
@@ -2211,27 +2203,25 @@
       <c r="G44" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="23" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="I44" s="23" t="n">
-        <v>37.43</v>
-      </c>
-      <c r="J44" s="24" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +205% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K44" s="24" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
+      <c r="H44" s="22" t="n">
+        <v>25.52</v>
+      </c>
+      <c r="I44" s="22" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="J44" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K44" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B45" s="20" t="n">
@@ -2239,42 +2229,42 @@
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>광진실업</t>
         </is>
       </c>
       <c r="D45" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E45" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F45" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="23" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="I45" s="23" t="n">
-        <v>61.32</v>
-      </c>
-      <c r="J45" s="24" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +104% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K45" s="24" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+        <v>3</v>
+      </c>
+      <c r="H45" s="24" t="n">
+        <v>-12.46</v>
+      </c>
+      <c r="I45" s="24" t="n">
+        <v>-18.87</v>
+      </c>
+      <c r="J45" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K45" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B46" s="20" t="n">
@@ -2282,7 +2272,7 @@
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>핑거</t>
         </is>
       </c>
       <c r="D46" s="20" t="n">
@@ -2297,25 +2287,27 @@
       <c r="G46" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="23" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="I46" s="23" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="J46" s="24" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K46" s="24" t="n">
-        <v/>
+      <c r="H46" s="22" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="I46" s="22" t="n">
+        <v>27.73</v>
+      </c>
+      <c r="J46" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K46" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B47" s="20" t="n">
@@ -2323,7 +2315,7 @@
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>자이에스앤디</t>
         </is>
       </c>
       <c r="D47" s="20" t="n">
@@ -2338,27 +2330,27 @@
       <c r="G47" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I47" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J47" s="24" t="inlineStr">
-        <is>
-          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K47" s="24" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H47" s="22" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="I47" s="24" t="n">
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="J47" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K47" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B48" s="20" t="n">
@@ -2366,7 +2358,7 @@
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>디지털대성</t>
         </is>
       </c>
       <c r="D48" s="20" t="n">
@@ -2382,24 +2374,26 @@
         <v>0</v>
       </c>
       <c r="H48" s="22" t="n">
-        <v>-0.6</v>
+        <v>1.06</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="J48" s="24" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K48" s="24" t="n">
-        <v/>
+        <v>7.43</v>
+      </c>
+      <c r="J48" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K48" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B49" s="20" t="n">
@@ -2407,7 +2401,7 @@
       </c>
       <c r="C49" s="21" t="inlineStr">
         <is>
-          <t>코웨이</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="D49" s="20" t="n">
@@ -2422,68 +2416,66 @@
       <c r="G49" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="22" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="I49" s="23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J49" s="24" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K49" s="24" t="n">
+      <c r="H49" s="20" t="n">
         <v/>
       </c>
+      <c r="I49" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J49" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K49" s="23" t="n">
+        <v/>
+      </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B50" s="25" t="n">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="n">
         <v>37</v>
       </c>
-      <c r="C50" s="26" t="inlineStr">
-        <is>
-          <t>빛샘전자</t>
-        </is>
-      </c>
-      <c r="D50" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E50" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F50" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="27" t="n">
-        <v>-1.43</v>
-      </c>
-      <c r="I50" s="28" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="J50" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +553%</t>
-        </is>
-      </c>
-      <c r="K50" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t>카카오페이</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F50" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I50" s="24" t="n">
+        <v>-10.59</v>
+      </c>
+      <c r="J50" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K50" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2491,7 +2483,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>큐라티스</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2507,17 +2499,17 @@
         <v>0</v>
       </c>
       <c r="H51" s="27" t="n">
-        <v>-6.56</v>
-      </c>
-      <c r="I51" s="28" t="n">
-        <v>43.29</v>
-      </c>
-      <c r="J51" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +428%</t>
-        </is>
-      </c>
-      <c r="K51" s="29" t="inlineStr">
+        <v>-19.24</v>
+      </c>
+      <c r="I51" s="27" t="n">
+        <v>-19.24</v>
+      </c>
+      <c r="J51" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +598%</t>
+        </is>
+      </c>
+      <c r="K51" s="28" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -2526,7 +2518,7 @@
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2534,7 +2526,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>한켐</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2549,27 +2541,25 @@
       <c r="G52" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="27" t="n">
-        <v>-1.73</v>
-      </c>
-      <c r="I52" s="28" t="n">
-        <v>40.87</v>
-      </c>
-      <c r="J52" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +367%</t>
-        </is>
-      </c>
-      <c r="K52" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="H52" s="29" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="I52" s="29" t="n">
+        <v>23.23</v>
+      </c>
+      <c r="J52" s="28" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K52" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2577,7 +2567,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>노타</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2592,27 +2582,25 @@
       <c r="G53" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="28" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="I53" s="28" t="n">
-        <v>15.31</v>
-      </c>
-      <c r="J53" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +311%</t>
-        </is>
-      </c>
-      <c r="K53" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="H53" s="29" t="n">
+        <v>28.93</v>
+      </c>
+      <c r="I53" s="29" t="n">
+        <v>32.96</v>
+      </c>
+      <c r="J53" s="28" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K53" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2620,7 +2608,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2635,27 +2623,25 @@
       <c r="G54" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="27" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="I54" s="28" t="n">
-        <v>13.73</v>
-      </c>
-      <c r="J54" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +304%</t>
-        </is>
-      </c>
-      <c r="K54" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="H54" s="29" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="I54" s="29" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="J54" s="28" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K54" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2663,7 +2649,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2678,27 +2664,27 @@
       <c r="G55" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="I55" s="28" t="n">
-        <v>26.17</v>
-      </c>
-      <c r="J55" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +291%</t>
-        </is>
-      </c>
-      <c r="K55" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H55" s="27" t="n">
+        <v>-2.41</v>
+      </c>
+      <c r="I55" s="27" t="n">
+        <v>-11.08</v>
+      </c>
+      <c r="J55" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 5건</t>
+        </is>
+      </c>
+      <c r="K55" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2706,7 +2692,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>센서뷰</t>
+          <t>앤씨앤</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2722,26 +2708,26 @@
         <v>0</v>
       </c>
       <c r="H56" s="27" t="n">
-        <v>-6.59</v>
-      </c>
-      <c r="I56" s="28" t="n">
-        <v>47.78</v>
-      </c>
-      <c r="J56" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +211%</t>
-        </is>
-      </c>
-      <c r="K56" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
+        <v>-12.5</v>
+      </c>
+      <c r="I56" s="29" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="J56" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 4건</t>
+        </is>
+      </c>
+      <c r="K56" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2749,7 +2735,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>티엠씨</t>
+          <t>한전산업</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2764,27 +2750,27 @@
       <c r="G57" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="27" t="n">
-        <v>-3.28</v>
-      </c>
-      <c r="I57" s="28" t="n">
-        <v>9.73</v>
-      </c>
-      <c r="J57" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +209%</t>
-        </is>
-      </c>
-      <c r="K57" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H57" s="29" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I57" s="27" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="J57" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K57" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2792,7 +2778,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>한선엔지니어링</t>
+          <t>서희건설</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2807,27 +2793,27 @@
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="28" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="I58" s="28" t="n">
-        <v>27.28</v>
-      </c>
-      <c r="J58" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +184%</t>
-        </is>
-      </c>
-      <c r="K58" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H58" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="27" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="J58" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K58" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2835,7 +2821,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>파이온엑스</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2850,27 +2836,27 @@
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="28" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="I59" s="28" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="J59" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +171%</t>
-        </is>
-      </c>
-      <c r="K59" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H59" s="27" t="n">
+        <v>-28.48</v>
+      </c>
+      <c r="I59" s="27" t="n">
+        <v>-57.95</v>
+      </c>
+      <c r="J59" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K59" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2878,42 +2864,42 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>드림텍</t>
+          <t>모아데이타</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E60" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F60" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="28" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="I60" s="28" t="n">
-        <v>28.39</v>
-      </c>
-      <c r="J60" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +100%</t>
-        </is>
-      </c>
-      <c r="K60" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H60" s="27" t="n">
+        <v>-4.18</v>
+      </c>
+      <c r="I60" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K60" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2921,42 +2907,42 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E61" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F61" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="27" t="n">
-        <v>-3.38</v>
-      </c>
-      <c r="I61" s="28" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="J61" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +51% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K61" s="29" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+        <v>-1.87</v>
+      </c>
+      <c r="I61" s="29" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J61" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K61" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2964,40 +2950,42 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
+          <t>아이엘</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E62" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F62" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="25" t="n">
-        <v/>
-      </c>
-      <c r="I62" s="25" t="n">
-        <v/>
-      </c>
-      <c r="J62" s="29" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K62" s="29" t="n">
-        <v/>
+      <c r="H62" s="27" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="I62" s="29" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="J62" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K62" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3005,33 +2993,33 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>삼성물산</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E63" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F63" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="27" t="n">
-        <v>-4.74</v>
-      </c>
-      <c r="I63" s="27" t="n">
-        <v>-32.34</v>
-      </c>
-      <c r="J63" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 8건</t>
-        </is>
-      </c>
-      <c r="K63" s="29" t="inlineStr">
+        <v>-1.09</v>
+      </c>
+      <c r="I63" s="29" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="J63" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K63" s="28" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -3130,22 +3118,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3154,99 +3142,103 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H4" s="28" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="I4" s="28" t="n">
-        <v>10.66</v>
-      </c>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H4" s="25" t="n"/>
+      <c r="I4" s="25" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H5" s="25" t="n"/>
-      <c r="I5" s="25" t="n"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H5" s="29" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I5" s="29" t="n">
+        <v>10.78</v>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H6" s="25" t="n"/>
-      <c r="I6" s="25" t="n"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H6" s="29" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="I6" s="29" t="n">
+        <v>2.38</v>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
@@ -3258,57 +3250,57 @@
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H7" s="28" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="I7" s="28" t="n">
-        <v>11.65</v>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="I7" s="29" t="n">
+        <v>7.54</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H8" s="25" t="n"/>
@@ -3317,200 +3309,196 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H9" s="25" t="n"/>
-      <c r="I9" s="25" t="n"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="I9" s="29" t="n">
+        <v>24.62</v>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H10" s="27" t="n">
-        <v>-1.36</v>
-      </c>
-      <c r="I10" s="27" t="n">
-        <v>-1.63</v>
-      </c>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H10" s="25" t="n"/>
+      <c r="I10" s="25" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H11" s="27" t="n">
-        <v>-1.08</v>
-      </c>
-      <c r="I11" s="28" t="n">
-        <v>1.66</v>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H11" s="29" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="I11" s="29" t="n">
+        <v>11.95</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H12" s="28" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="I12" s="28" t="n">
-        <v>2.61</v>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H12" s="29" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I12" s="27" t="n">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H13" s="27" t="n">
-        <v>-2.84</v>
-      </c>
-      <c r="I13" s="28" t="n">
-        <v>0.76</v>
-      </c>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H13" s="25" t="n"/>
+      <c r="I13" s="25" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H14" s="25" t="n"/>
@@ -3519,108 +3507,112 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>KT&amp;G</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H15" s="28" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="I15" s="28" t="n">
-        <v>8.32</v>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H15" s="29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I15" s="29" t="n">
+        <v>3.46</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H16" s="25" t="n"/>
-      <c r="I16" s="25" t="n"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>-3.42</v>
+      </c>
+      <c r="I16" s="27" t="n">
+        <v>-1.78</v>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H17" s="27" t="n">
-        <v>-1.99</v>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H17" s="29" t="n">
+        <v>2.33</v>
       </c>
       <c r="I17" s="27" t="n">
-        <v>-2.8</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -3637,25 +3629,21 @@
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H18" s="27" t="n">
-        <v>-2.96</v>
-      </c>
-      <c r="I18" s="27" t="n">
-        <v>-2.66</v>
-      </c>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="25" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -3672,25 +3660,25 @@
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H19" s="28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="I19" s="28" t="n">
-        <v>6.32</v>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H19" s="29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I19" s="27" t="n">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>앤씨앤</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -3707,25 +3695,25 @@
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H20" s="27" t="n">
-        <v>-12.81</v>
-      </c>
-      <c r="I20" s="28" t="n">
-        <v>27.74</v>
+        <v>-0.72</v>
+      </c>
+      <c r="I20" s="27" t="n">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>인벤테라</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -3742,227 +3730,231 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H21" s="28" t="n">
-        <v>18.51</v>
-      </c>
-      <c r="I21" s="28" t="n">
-        <v>42.5</v>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H21" s="29" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="I21" s="29" t="n">
+        <v>6.44</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H22" s="28" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I22" s="28" t="n">
-        <v>0.38</v>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H22" s="27" t="n">
+        <v>-20.08</v>
+      </c>
+      <c r="I22" s="27" t="n">
+        <v>-40.46</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H23" s="25" t="n"/>
-      <c r="I23" s="25" t="n"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H23" s="29" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="I23" s="27" t="n">
+        <v>-2.43</v>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>기업은행</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H24" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="27" t="n">
-        <v>-3.12</v>
-      </c>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H24" s="25" t="n"/>
+      <c r="I24" s="25" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H25" s="27" t="n">
-        <v>-4.47</v>
-      </c>
-      <c r="I25" s="27" t="n">
-        <v>-8.56</v>
+        <v>-3.62</v>
+      </c>
+      <c r="I25" s="29" t="n">
+        <v>12.16</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>우성머티리얼스</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H26" s="27" t="n">
-        <v>-1.11</v>
-      </c>
-      <c r="I26" s="28" t="n">
-        <v>0.9399999999999999</v>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H26" s="29" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <v>12.08</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H27" s="25" t="n"/>
-      <c r="I27" s="25" t="n"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H27" s="29" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I27" s="27" t="n">
+        <v>-2.03</v>
+      </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>네이버</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
@@ -3979,20 +3971,16 @@
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H28" s="27" t="n">
-        <v>-29.01</v>
-      </c>
-      <c r="I28" s="27" t="n">
-        <v>-46.04</v>
-      </c>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H28" s="25" t="n"/>
+      <c r="I28" s="25" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
@@ -4014,95 +4002,87 @@
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H29" s="27" t="n">
-        <v>-3.57</v>
-      </c>
-      <c r="I29" s="28" t="n">
-        <v>1.23</v>
+        <v>-1.95</v>
+      </c>
+      <c r="I29" s="27" t="n">
+        <v>-2.87</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H30" s="28" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="I30" s="28" t="n">
-        <v>4.16</v>
-      </c>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="25" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>나라스페이스테크놀로지</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H31" s="28" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="I31" s="28" t="n">
-        <v>37.43</v>
-      </c>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H31" s="25" t="n"/>
+      <c r="I31" s="25" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>광진실업</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
@@ -4119,25 +4099,25 @@
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H32" s="27" t="n">
-        <v>-2.28</v>
-      </c>
-      <c r="I32" s="28" t="n">
-        <v>35.77</v>
+        <v>-12.46</v>
+      </c>
+      <c r="I32" s="27" t="n">
+        <v>-18.87</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>디지털대성</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
@@ -4154,21 +4134,25 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H33" s="25" t="n"/>
-      <c r="I33" s="25" t="n"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H33" s="29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="I33" s="29" t="n">
+        <v>7.43</v>
+      </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>뷰티스킨</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
@@ -4185,25 +4169,21 @@
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H34" s="27" t="n">
-        <v>-1.57</v>
-      </c>
-      <c r="I34" s="28" t="n">
-        <v>25.38</v>
-      </c>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H34" s="25" t="n"/>
+      <c r="I34" s="25" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>비츠로테크</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
@@ -4220,25 +4200,25 @@
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H35" s="27" t="n">
-        <v>-5.16</v>
-      </c>
-      <c r="I35" s="28" t="n">
-        <v>30.53</v>
+        <v>-0.37</v>
+      </c>
+      <c r="I35" s="29" t="n">
+        <v>59.59</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>자이에스앤디</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
@@ -4255,25 +4235,25 @@
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H36" s="28" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="I36" s="28" t="n">
-        <v>61.32</v>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H36" s="29" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="I36" s="27" t="n">
+        <v>-8.720000000000001</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>카카오페이</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
@@ -4290,25 +4270,25 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H37" s="27" t="n">
-        <v>-0.6</v>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H37" s="29" t="n">
+        <v>1.61</v>
       </c>
       <c r="I37" s="27" t="n">
-        <v>-3.33</v>
+        <v>-10.59</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>코웨이</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4325,54 +4305,54 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H38" s="27" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="I38" s="28" t="n">
-        <v>1.4</v>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H38" s="29" t="n">
+        <v>25.52</v>
+      </c>
+      <c r="I38" s="29" t="n">
+        <v>32.53</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>핑거</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D39" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H39" s="28" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="I39" s="28" t="n">
-        <v>6.91</v>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H39" s="29" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="I39" s="29" t="n">
+        <v>27.73</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -4395,21 +4375,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H40" s="25" t="n"/>
-      <c r="I40" s="25" t="n"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H40" s="27" t="n">
+        <v>-19.24</v>
+      </c>
+      <c r="I40" s="27" t="n">
+        <v>-19.24</v>
+      </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4426,25 +4410,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H41" s="27" t="n">
-        <v>-4.74</v>
+        <v>-2.41</v>
       </c>
       <c r="I41" s="27" t="n">
-        <v>-32.34</v>
+        <v>-11.08</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>드림텍</t>
+          <t>노타</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4461,25 +4445,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H42" s="28" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="I42" s="28" t="n">
-        <v>28.39</v>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H42" s="29" t="n">
+        <v>28.93</v>
+      </c>
+      <c r="I42" s="29" t="n">
+        <v>32.96</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4496,25 +4480,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H43" s="27" t="n">
-        <v>-1.43</v>
-      </c>
-      <c r="I43" s="28" t="n">
-        <v>19.1</v>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H43" s="29" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="I43" s="29" t="n">
+        <v>7.84</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>센서뷰</t>
+          <t>모아데이타</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4531,25 +4515,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H44" s="27" t="n">
-        <v>-6.59</v>
-      </c>
-      <c r="I44" s="28" t="n">
-        <v>47.78</v>
+        <v>-4.18</v>
+      </c>
+      <c r="I44" s="25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>삼성물산</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4566,25 +4550,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H45" s="28" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="I45" s="28" t="n">
-        <v>15.31</v>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H45" s="27" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="I45" s="29" t="n">
+        <v>4.44</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>큐라티스</t>
+          <t>서희건설</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4601,25 +4585,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H46" s="27" t="n">
-        <v>-6.56</v>
-      </c>
-      <c r="I46" s="28" t="n">
-        <v>43.29</v>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="27" t="n">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>티엠씨</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4636,25 +4620,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H47" s="27" t="n">
-        <v>-3.28</v>
-      </c>
-      <c r="I47" s="28" t="n">
-        <v>9.73</v>
+        <v>-1.87</v>
+      </c>
+      <c r="I47" s="29" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>아이엘</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4671,25 +4655,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H48" s="27" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="I48" s="28" t="n">
-        <v>13.73</v>
+        <v>-0.86</v>
+      </c>
+      <c r="I48" s="29" t="n">
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>한선엔지니어링</t>
+          <t>앤씨앤</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4706,25 +4690,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H49" s="28" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="I49" s="28" t="n">
-        <v>27.28</v>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H49" s="27" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="I49" s="29" t="n">
+        <v>31.15</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4741,25 +4725,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H50" s="28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="I50" s="28" t="n">
-        <v>26.17</v>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H50" s="29" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="I50" s="29" t="n">
+        <v>23.23</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>한켐</t>
+          <t>파이온엑스</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4776,25 +4760,25 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H51" s="27" t="n">
-        <v>-1.73</v>
-      </c>
-      <c r="I51" s="28" t="n">
-        <v>40.87</v>
+        <v>-28.48</v>
+      </c>
+      <c r="I51" s="27" t="n">
+        <v>-57.95</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>한전산업</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -4811,19 +4795,19 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H52" s="27" t="n">
-        <v>-3.38</v>
-      </c>
-      <c r="I52" s="28" t="n">
-        <v>5.32</v>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H52" s="29" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I52" s="27" t="n">
+        <v>-0.31</v>
       </c>
     </row>
   </sheetData>
@@ -4907,19 +4891,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4938,19 +4922,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4976,12 +4960,12 @@
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -4993,26 +4977,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5024,26 +5008,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5055,26 +5039,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5086,26 +5070,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5117,26 +5101,26 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B10" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="36" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G10" s="37" t="inlineStr">
@@ -5148,65 +5132,69 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="35" t="inlineStr">
         <is>
+          <t>인공지능</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>14</v>
+      </c>
+      <c r="D11" s="36" t="n">
+        <v>14</v>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="F11" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G11" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="B11" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="36" t="n">
+      <c r="B12" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="36" t="n">
+      <c r="D12" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="F11" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G11" s="37" t="inlineStr">
+      <c r="E12" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="F12" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G12" s="37" t="inlineStr">
         <is>
           <t>⚡ 관심</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>이차전지</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="29" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G12" s="29" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -5223,17 +5211,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="29" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G13" s="29" t="inlineStr"/>
+      <c r="G13" s="28" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5250,17 +5238,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="29" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G14" s="29" t="inlineStr"/>
+      <c r="G14" s="28" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5277,17 +5265,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="29" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G15" s="29" t="inlineStr"/>
+      <c r="G15" s="28" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5304,17 +5292,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="29" t="inlineStr">
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G16" s="29" t="inlineStr"/>
+      <c r="G16" s="28" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5331,17 +5319,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="29" t="inlineStr">
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G17" s="29" t="inlineStr"/>
+      <c r="G17" s="28" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5358,17 +5346,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="29" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G18" s="29" t="inlineStr"/>
+      <c r="G18" s="28" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -5385,17 +5373,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="29" t="inlineStr">
+      <c r="F19" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G19" s="29" t="inlineStr"/>
+      <c r="G19" s="28" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -5412,12 +5400,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="29" t="inlineStr">
+      <c r="F20" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G20" s="29" t="inlineStr"/>
+      <c r="G20" s="28" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -5439,12 +5427,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F21" s="29" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G21" s="29" t="inlineStr"/>
+      <c r="G21" s="28" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -5466,12 +5454,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F22" s="29" t="inlineStr">
+      <c r="F22" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G22" s="29" t="inlineStr"/>
+      <c r="G22" s="28" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -5493,12 +5481,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F23" s="29" t="inlineStr">
+      <c r="F23" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G23" s="29" t="inlineStr"/>
+      <c r="G23" s="28" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -5520,12 +5508,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F24" s="29" t="inlineStr">
+      <c r="F24" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G24" s="29" t="inlineStr"/>
+      <c r="G24" s="28" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -258,13 +258,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-23 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-24 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-23) 상위: 반도체  점수 75.0점</t>
+          <t>⚡ 최신(2026-09-24) 상위: 반도체  점수 51.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-23) 상위: 원전  점수 24.0점</t>
+          <t>⚡ 최신(2026-09-24) 상위: 삼성전자  점수 32.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-23) 상위: 삼성전자  점수 21.0점</t>
+          <t>⚡ 최신(2026-09-24) 상위: SK하이닉스  점수 18.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -967,14 +967,14 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -982,25 +982,27 @@
       <c r="G15" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v/>
+      <c r="H15" s="18" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>13.02</v>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K15" s="17" t="n">
-        <v/>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K15" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1008,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1024,24 +1026,26 @@
         <v>0</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>0.91</v>
+        <v>1.2</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>10.78</v>
+        <v>6.03</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="n">
-        <v/>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1049,14 +1053,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1064,15 +1068,15 @@
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="19" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>7.54</v>
+      <c r="H17" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v/>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="n">
@@ -1082,7 +1086,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1090,14 +1094,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1105,25 +1109,27 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="18" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="I18" s="18" t="n">
-        <v>2.38</v>
+      <c r="H18" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v/>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="n">
-        <v/>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1131,7 +1137,7 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
@@ -1146,27 +1152,25 @@
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="15" t="n">
+      <c r="H19" s="19" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="J19" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K19" s="17" t="n">
         <v/>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J19" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1174,14 +1178,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1189,27 +1193,25 @@
       <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="18" t="n">
-        <v>14.94</v>
+      <c r="H20" s="19" t="n">
+        <v>-2.09</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>24.62</v>
+        <v>5.46</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>중요공시 4건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1221,10 +1223,10 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1233,14 +1235,14 @@
         <v>0</v>
       </c>
       <c r="H21" s="18" t="n">
-        <v>3.98</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I21" s="18" t="n">
-        <v>11.95</v>
+        <v>9.4</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="n">
@@ -1250,7 +1252,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1258,14 +1260,14 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1273,25 +1275,27 @@
       <c r="G22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v/>
+      <c r="H22" s="19" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>0.45</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="n">
-        <v/>
+          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1299,14 +1303,14 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F23" s="15" t="n">
         <v>0</v>
@@ -1314,25 +1318,27 @@
       <c r="G23" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="18" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="I23" s="19" t="n">
-        <v>-1.3</v>
+      <c r="H23" s="19" t="n">
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <v>17.08</v>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="n">
-        <v/>
+          <t>중요공시 4건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1340,42 +1346,42 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F24" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I24" s="15" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>-0.67</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 3건 / 중요공시 7일 +200% / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1383,42 +1389,42 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I25" s="15" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="I25" s="19" t="n">
+        <v>-4.89</v>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>중요공시 3건 / 중요공시 3일 +50% / 중요공시 7일 +50%</t>
         </is>
       </c>
       <c r="K25" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1426,7 +1432,7 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
@@ -1441,15 +1447,15 @@
       <c r="G26" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="19" t="n">
-        <v>-3.42</v>
-      </c>
-      <c r="I26" s="19" t="n">
-        <v>-1.78</v>
+      <c r="H26" s="18" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I26" s="18" t="n">
+        <v>15.23</v>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +50% / 중요공시 7일 +50%</t>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +200%</t>
         </is>
       </c>
       <c r="K26" s="17" t="inlineStr">
@@ -1461,7 +1467,7 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
@@ -1469,7 +1475,7 @@
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
@@ -1484,11 +1490,11 @@
       <c r="G27" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="H27" s="18" t="n">
-        <v>2.33</v>
+      <c r="H27" s="19" t="n">
+        <v>-1.73</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>-2.12</v>
+        <v>-5.09</v>
       </c>
       <c r="J27" s="17" t="inlineStr">
         <is>
@@ -1504,7 +1510,7 @@
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B28" s="15" t="n">
@@ -1512,7 +1518,7 @@
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>KT&amp;G</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
@@ -1527,15 +1533,15 @@
       <c r="G28" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="18" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="I28" s="18" t="n">
-        <v>3.46</v>
+      <c r="H28" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I28" s="15" t="n">
+        <v/>
       </c>
       <c r="J28" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K28" s="17" t="n">
@@ -1543,222 +1549,224 @@
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="n">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="C29" s="21" t="inlineStr">
-        <is>
-          <t>LG전자</t>
-        </is>
-      </c>
-      <c r="D29" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E29" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="22" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="I29" s="22" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="J29" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K29" s="23" t="n">
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>바이오</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="15" t="n">
         <v/>
       </c>
+      <c r="I29" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J29" s="17" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K29" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="n">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="C30" s="21" t="inlineStr">
-        <is>
-          <t>더코디</t>
-        </is>
-      </c>
-      <c r="D30" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E30" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F30" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" s="24" t="n">
-        <v>-20.08</v>
-      </c>
-      <c r="I30" s="24" t="n">
-        <v>-40.46</v>
-      </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 9건 / 중요공시 7일 +50%</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>한화시스템</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="19" t="n">
+        <v>-4.12</v>
+      </c>
+      <c r="I30" s="18" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="J30" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100% / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K30" s="17" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="n">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>우성머티리얼스</t>
-        </is>
-      </c>
-      <c r="D31" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E31" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H31" s="22" t="n">
-        <v>11.39</v>
-      </c>
-      <c r="I31" s="22" t="n">
-        <v>12.08</v>
-      </c>
-      <c r="J31" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 7건 / 중요공시 7일 +600%</t>
-        </is>
-      </c>
-      <c r="K31" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J31" s="17" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K31" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="n">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>GS건설</t>
-        </is>
-      </c>
-      <c r="D32" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E32" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F32" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H32" s="22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="I32" s="24" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="J32" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 4건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K32" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>방산</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J32" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K32" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B33" s="20" t="n">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="C33" s="21" t="inlineStr">
-        <is>
-          <t>HJ중공업</t>
-        </is>
-      </c>
-      <c r="D33" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E33" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H33" s="24" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="I33" s="24" t="n">
-        <v>-0.79</v>
-      </c>
-      <c r="J33" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 7일 +200%</t>
-        </is>
-      </c>
-      <c r="K33" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J33" s="17" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K33" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1766,30 +1774,30 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>대양금속</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F34" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G34" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="24" t="n">
-        <v>-3.62</v>
+      <c r="H34" s="22" t="n">
+        <v>-14.85</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>12.16</v>
+        <v>-11.08</v>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
+          <t>중요공시 3건 / 중요공시 7일 +200%</t>
         </is>
       </c>
       <c r="K34" s="23" t="inlineStr">
@@ -1801,7 +1809,7 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1809,30 +1817,30 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G35" s="20" t="n">
         <v>3</v>
       </c>
       <c r="H35" s="22" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="I35" s="24" t="n">
-        <v>-2.43</v>
+        <v>-7.33</v>
+      </c>
+      <c r="I35" s="22" t="n">
+        <v>-5.57</v>
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
+          <t>중요공시 4건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K35" s="23" t="inlineStr">
@@ -1844,7 +1852,7 @@
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1852,7 +1860,7 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>스테이블코인</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
@@ -1875,7 +1883,7 @@
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K36" s="23" t="n">
@@ -1885,7 +1893,7 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1893,40 +1901,42 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F37" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I37" s="20" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H37" s="22" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="I37" s="22" t="n">
+        <v>-4.57</v>
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K37" s="23" t="n">
-        <v/>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K37" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1934,40 +1944,42 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>삼성물산</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F38" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G38" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="22" t="n">
-        <v>0.14</v>
+      <c r="H38" s="24" t="n">
+        <v>1.1</v>
       </c>
       <c r="I38" s="24" t="n">
-        <v>-2.03</v>
+        <v>4.84</v>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K38" s="23" t="n">
-        <v/>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1975,42 +1987,40 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>우진</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F39" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G39" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="24" t="n">
-        <v>-1.95</v>
-      </c>
-      <c r="I39" s="24" t="n">
-        <v>-2.87</v>
+      <c r="H39" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I39" s="20" t="n">
+        <v/>
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +50%</t>
-        </is>
-      </c>
-      <c r="K39" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K39" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2018,7 +2028,7 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
@@ -2033,11 +2043,11 @@
       <c r="G40" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I40" s="20" t="n">
-        <v/>
+      <c r="H40" s="22" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="I40" s="22" t="n">
+        <v>-1.66</v>
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
@@ -2053,7 +2063,7 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2061,42 +2071,42 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>우진</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
         <v>5</v>
       </c>
       <c r="E41" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F41" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G41" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I41" s="20" t="n">
-        <v/>
+      <c r="H41" s="22" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="I41" s="22" t="n">
+        <v>-2.59</v>
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>중요공시 3건 / 중요공시 3일 +50%</t>
         </is>
       </c>
       <c r="K41" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -2104,7 +2114,7 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
@@ -2119,25 +2129,27 @@
       <c r="G42" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I42" s="20" t="n">
-        <v/>
+      <c r="H42" s="22" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="I42" s="22" t="n">
+        <v>-4.24</v>
       </c>
       <c r="J42" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K42" s="23" t="n">
-        <v/>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K42" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B43" s="20" t="n">
@@ -2145,7 +2157,7 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>노타</t>
         </is>
       </c>
       <c r="D43" s="20" t="n">
@@ -2160,27 +2172,25 @@
       <c r="G43" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="24" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="I43" s="22" t="n">
-        <v>59.59</v>
+      <c r="H43" s="22" t="n">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="I43" s="24" t="n">
+        <v>21.21</v>
       </c>
       <c r="J43" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K43" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K43" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B44" s="20" t="n">
@@ -2188,7 +2198,7 @@
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D44" s="20" t="n">
@@ -2203,15 +2213,15 @@
       <c r="G44" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="22" t="n">
-        <v>25.52</v>
-      </c>
-      <c r="I44" s="22" t="n">
-        <v>32.53</v>
+      <c r="H44" s="24" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="I44" s="24" t="n">
+        <v>8.619999999999999</v>
       </c>
       <c r="J44" s="23" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K44" s="23" t="n">
@@ -2221,7 +2231,7 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B45" s="20" t="n">
@@ -2229,253 +2239,255 @@
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>광진실업</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="D45" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E45" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F45" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H45" s="24" t="n">
-        <v>-12.46</v>
-      </c>
-      <c r="I45" s="24" t="n">
-        <v>-18.87</v>
+        <v>0</v>
+      </c>
+      <c r="H45" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I45" s="20" t="n">
+        <v/>
       </c>
       <c r="J45" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K45" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K45" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B46" s="20" t="n">
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B46" s="25" t="n">
         <v>33</v>
       </c>
-      <c r="C46" s="21" t="inlineStr">
-        <is>
-          <t>핑거</t>
-        </is>
-      </c>
-      <c r="D46" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E46" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="22" t="n">
-        <v>10.87</v>
-      </c>
-      <c r="I46" s="22" t="n">
-        <v>27.73</v>
-      </c>
-      <c r="J46" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K46" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>한국제17호스팩</t>
+        </is>
+      </c>
+      <c r="D46" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="27" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="I46" s="27" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="J46" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +4057%</t>
+        </is>
+      </c>
+      <c r="K46" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B47" s="20" t="n">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B47" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="C47" s="21" t="inlineStr">
-        <is>
-          <t>자이에스앤디</t>
-        </is>
-      </c>
-      <c r="D47" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F47" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="22" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="I47" s="24" t="n">
-        <v>-8.720000000000001</v>
-      </c>
-      <c r="J47" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K47" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>KB제34호스팩</t>
+        </is>
+      </c>
+      <c r="D47" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="27" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="I47" s="27" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="J47" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +2698%</t>
+        </is>
+      </c>
+      <c r="K47" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B48" s="20" t="n">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B48" s="25" t="n">
         <v>35</v>
       </c>
-      <c r="C48" s="21" t="inlineStr">
-        <is>
-          <t>디지털대성</t>
-        </is>
-      </c>
-      <c r="D48" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E48" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F48" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I48" s="22" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="J48" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K48" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>네오사피엔스</t>
+        </is>
+      </c>
+      <c r="D48" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="27" t="n">
+        <v>-16.78</v>
+      </c>
+      <c r="I48" s="27" t="n">
+        <v>-32.79</v>
+      </c>
+      <c r="J48" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +810%</t>
+        </is>
+      </c>
+      <c r="K48" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="n">
+      <c r="A49" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B49" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="C49" s="21" t="inlineStr">
-        <is>
-          <t>방산</t>
-        </is>
-      </c>
-      <c r="D49" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E49" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F49" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I49" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J49" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K49" s="23" t="n">
-        <v/>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>동국생명과학</t>
+        </is>
+      </c>
+      <c r="D49" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="27" t="n">
+        <v>-9.06</v>
+      </c>
+      <c r="I49" s="29" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="J49" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +295%</t>
+        </is>
+      </c>
+      <c r="K49" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B50" s="20" t="n">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B50" s="25" t="n">
         <v>37</v>
       </c>
-      <c r="C50" s="21" t="inlineStr">
-        <is>
-          <t>카카오페이</t>
-        </is>
-      </c>
-      <c r="D50" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E50" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F50" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="I50" s="24" t="n">
-        <v>-10.59</v>
-      </c>
-      <c r="J50" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K50" s="23" t="n">
-        <v/>
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>토마토시스템</t>
+        </is>
+      </c>
+      <c r="D50" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="29" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="I50" s="29" t="n">
+        <v>65.84999999999999</v>
+      </c>
+      <c r="J50" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +214%</t>
+        </is>
+      </c>
+      <c r="K50" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2483,7 +2495,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
+          <t>케이쓰리아이</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2498,27 +2510,27 @@
       <c r="G51" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="27" t="n">
-        <v>-19.24</v>
-      </c>
-      <c r="I51" s="27" t="n">
-        <v>-19.24</v>
+      <c r="H51" s="29" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="I51" s="29" t="n">
+        <v>26.25</v>
       </c>
       <c r="J51" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +598%</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K51" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2526,7 +2538,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2542,14 +2554,14 @@
         <v>0</v>
       </c>
       <c r="H52" s="29" t="n">
-        <v>7.26</v>
+        <v>6.52</v>
       </c>
       <c r="I52" s="29" t="n">
-        <v>23.23</v>
+        <v>2.62</v>
       </c>
       <c r="J52" s="28" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
+          <t>한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K52" s="28" t="n">
@@ -2559,7 +2571,7 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2567,7 +2579,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>노타</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2582,25 +2594,27 @@
       <c r="G53" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="29" t="n">
-        <v>28.93</v>
-      </c>
-      <c r="I53" s="29" t="n">
-        <v>32.96</v>
+      <c r="H53" s="27" t="n">
+        <v>-3.31</v>
+      </c>
+      <c r="I53" s="27" t="n">
+        <v>-1.2</v>
       </c>
       <c r="J53" s="28" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K53" s="28" t="n">
-        <v/>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K53" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2608,7 +2622,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2624,24 +2638,26 @@
         <v>0</v>
       </c>
       <c r="H54" s="29" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="I54" s="29" t="n">
-        <v>7.84</v>
+        <v>5.14</v>
+      </c>
+      <c r="I54" s="27" t="n">
+        <v>-40.85</v>
       </c>
       <c r="J54" s="28" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K54" s="28" t="n">
-        <v/>
+          <t>중요공시 8건</t>
+        </is>
+      </c>
+      <c r="K54" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2664,11 +2680,11 @@
       <c r="G55" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="27" t="n">
-        <v>-2.41</v>
+      <c r="H55" s="29" t="n">
+        <v>0.41</v>
       </c>
       <c r="I55" s="27" t="n">
-        <v>-11.08</v>
+        <v>-5.05</v>
       </c>
       <c r="J55" s="28" t="inlineStr">
         <is>
@@ -2684,7 +2700,7 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2692,7 +2708,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>앤씨앤</t>
+          <t>비케이홀딩스</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2708,14 +2724,14 @@
         <v>0</v>
       </c>
       <c r="H56" s="27" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="I56" s="29" t="n">
-        <v>31.15</v>
+        <v>-15.35</v>
+      </c>
+      <c r="I56" s="27" t="n">
+        <v>-17.21</v>
       </c>
       <c r="J56" s="28" t="inlineStr">
         <is>
-          <t>중요공시 4건</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K56" s="28" t="inlineStr">
@@ -2727,7 +2743,7 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2735,7 +2751,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>한전산업</t>
+          <t>앤씨앤</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2751,10 +2767,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="29" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I57" s="27" t="n">
-        <v>-0.31</v>
+        <v>5.18</v>
+      </c>
+      <c r="I57" s="29" t="n">
+        <v>35.4</v>
       </c>
       <c r="J57" s="28" t="inlineStr">
         <is>
@@ -2770,7 +2786,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2793,11 +2809,11 @@
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="25" t="n">
-        <v>0</v>
+      <c r="H58" s="27" t="n">
+        <v>-1.3</v>
       </c>
       <c r="I58" s="27" t="n">
-        <v>-1.5</v>
+        <v>-2.16</v>
       </c>
       <c r="J58" s="28" t="inlineStr">
         <is>
@@ -2813,7 +2829,7 @@
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2821,30 +2837,30 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>파이온엑스</t>
+          <t>모아데이타</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E59" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F59" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="27" t="n">
-        <v>-28.48</v>
+        <v>-2.38</v>
       </c>
       <c r="I59" s="27" t="n">
-        <v>-57.95</v>
+        <v>-13.38</v>
       </c>
       <c r="J59" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
         </is>
       </c>
       <c r="K59" s="28" t="inlineStr">
@@ -2856,7 +2872,7 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2864,7 +2880,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>모아데이타</t>
+          <t>삼일씨엔에스</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2879,11 +2895,11 @@
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="27" t="n">
-        <v>-4.18</v>
-      </c>
-      <c r="I60" s="25" t="n">
-        <v>0</v>
+      <c r="H60" s="29" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="I60" s="29" t="n">
+        <v>9.49</v>
       </c>
       <c r="J60" s="28" t="inlineStr">
         <is>
@@ -2899,7 +2915,7 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2923,10 +2939,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="27" t="n">
-        <v>-1.87</v>
+        <v>-0.11</v>
       </c>
       <c r="I61" s="29" t="n">
-        <v>0.17</v>
+        <v>0.39</v>
       </c>
       <c r="J61" s="28" t="inlineStr">
         <is>
@@ -2942,7 +2958,7 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2950,30 +2966,30 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>아이엘</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E62" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H62" s="27" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="I62" s="29" t="n">
-        <v>9.279999999999999</v>
+        <v>-1.19</v>
+      </c>
+      <c r="I62" s="27" t="n">
+        <v>-2.59</v>
       </c>
       <c r="J62" s="28" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>중요공시 2건 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K62" s="28" t="inlineStr">
@@ -2985,7 +3001,7 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -2993,35 +3009,35 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>삼성물산</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E63" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F63" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="27" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="I63" s="29" t="n">
-        <v>4.44</v>
+        <v>-1.88</v>
+      </c>
+      <c r="I63" s="27" t="n">
+        <v>-4.58</v>
       </c>
       <c r="J63" s="28" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K63" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
@@ -3118,22 +3134,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3142,143 +3158,139 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H4" s="25" t="n"/>
-      <c r="I4" s="25" t="n"/>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H4" s="29" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="I4" s="29" t="n">
+        <v>13.02</v>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H5" s="29" t="n">
-        <v>0.91</v>
+        <v>1.2</v>
       </c>
       <c r="I5" s="29" t="n">
-        <v>10.78</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H6" s="29" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="I6" s="29" t="n">
-        <v>2.38</v>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H6" s="25" t="n"/>
+      <c r="I6" s="25" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="I7" s="29" t="n">
-        <v>7.54</v>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H7" s="25" t="n"/>
+      <c r="I7" s="25" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
@@ -3295,219 +3307,235 @@
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H8" s="25" t="n"/>
-      <c r="I8" s="25" t="n"/>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>5.46</v>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H9" s="29" t="n">
-        <v>14.94</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H9" s="27" t="n">
+        <v>-0.47</v>
       </c>
       <c r="I9" s="29" t="n">
-        <v>24.62</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H10" s="25" t="n"/>
-      <c r="I10" s="25" t="n"/>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H10" s="29" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I10" s="29" t="n">
+        <v>9.4</v>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H11" s="29" t="n">
-        <v>3.98</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>-1.31</v>
       </c>
       <c r="I11" s="29" t="n">
-        <v>11.95</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H12" s="29" t="n">
-        <v>2.54</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H12" s="27" t="n">
+        <v>-1.78</v>
       </c>
       <c r="I12" s="27" t="n">
-        <v>-1.3</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H13" s="25" t="n"/>
-      <c r="I13" s="25" t="n"/>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H13" s="27" t="n">
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="I13" s="29" t="n">
+        <v>17.08</v>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H14" s="25" t="n"/>
-      <c r="I14" s="25" t="n"/>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H14" s="27" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="I14" s="27" t="n">
+        <v>-5.09</v>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>KT&amp;G</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -3524,25 +3552,25 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H15" s="29" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="I15" s="29" t="n">
-        <v>3.46</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="I15" s="27" t="n">
+        <v>-4.89</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -3559,25 +3587,21 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H16" s="27" t="n">
-        <v>-3.42</v>
-      </c>
-      <c r="I16" s="27" t="n">
-        <v>-1.78</v>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -3594,47 +3618,47 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H17" s="29" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="I17" s="27" t="n">
-        <v>-2.12</v>
+        <v>3.76</v>
+      </c>
+      <c r="I17" s="29" t="n">
+        <v>15.23</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H18" s="25" t="n"/>
@@ -3643,147 +3667,135 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H19" s="29" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="I19" s="27" t="n">
-        <v>-1.7</v>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H19" s="25" t="n"/>
+      <c r="I19" s="25" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H20" s="27" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="I20" s="27" t="n">
-        <v>-0.79</v>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H20" s="25" t="n"/>
+      <c r="I20" s="25" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H21" s="29" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="I21" s="29" t="n">
-        <v>6.44</v>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="25" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H22" s="27" t="n">
-        <v>-20.08</v>
-      </c>
-      <c r="I22" s="27" t="n">
-        <v>-40.46</v>
+        <v>-4.12</v>
+      </c>
+      <c r="I22" s="29" t="n">
+        <v>7.98</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -3800,25 +3812,25 @@
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H23" s="29" t="n">
-        <v>3.22</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H23" s="27" t="n">
+        <v>-7.33</v>
       </c>
       <c r="I23" s="27" t="n">
-        <v>-2.43</v>
+        <v>-5.57</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>스테이블코인</t>
+          <t>대양금속</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -3835,21 +3847,25 @@
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H24" s="25" t="n"/>
-      <c r="I24" s="25" t="n"/>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H24" s="27" t="n">
+        <v>-14.85</v>
+      </c>
+      <c r="I24" s="27" t="n">
+        <v>-11.08</v>
+      </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
@@ -3866,25 +3882,21 @@
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H25" s="27" t="n">
-        <v>-3.62</v>
-      </c>
-      <c r="I25" s="29" t="n">
-        <v>12.16</v>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H25" s="25" t="n"/>
+      <c r="I25" s="25" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>우성머티리얼스</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
@@ -3901,25 +3913,25 @@
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H26" s="29" t="n">
-        <v>11.39</v>
-      </c>
-      <c r="I26" s="29" t="n">
-        <v>12.08</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H26" s="27" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="I26" s="27" t="n">
+        <v>-4.57</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>삼성물산</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
@@ -3936,47 +3948,47 @@
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H27" s="29" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I27" s="27" t="n">
-        <v>-2.03</v>
+        <v>1.1</v>
+      </c>
+      <c r="I27" s="29" t="n">
+        <v>4.84</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H28" s="25" t="n"/>
@@ -3985,7 +3997,7 @@
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>우진</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
@@ -4002,25 +4014,25 @@
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H29" s="27" t="n">
-        <v>-1.95</v>
+        <v>-4.5</v>
       </c>
       <c r="I29" s="27" t="n">
-        <v>-2.87</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>우진</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
@@ -4037,21 +4049,25 @@
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H30" s="25" t="n"/>
-      <c r="I30" s="25" t="n"/>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H30" s="27" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="I30" s="27" t="n">
+        <v>-2.59</v>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
@@ -4068,21 +4084,25 @@
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H31" s="25" t="n"/>
-      <c r="I31" s="25" t="n"/>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H31" s="27" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="I31" s="27" t="n">
+        <v>-4.24</v>
+      </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>광진실업</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
@@ -4099,25 +4119,25 @@
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H32" s="27" t="n">
-        <v>-12.46</v>
-      </c>
-      <c r="I32" s="27" t="n">
-        <v>-18.87</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H32" s="29" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="I32" s="29" t="n">
+        <v>8.619999999999999</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>디지털대성</t>
+          <t>노타</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
@@ -4134,25 +4154,25 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H33" s="29" t="n">
-        <v>1.06</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H33" s="27" t="n">
+        <v>-9.529999999999999</v>
       </c>
       <c r="I33" s="29" t="n">
-        <v>7.43</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
@@ -4169,12 +4189,12 @@
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H34" s="25" t="n"/>
@@ -4183,182 +4203,182 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>KB제34호스팩</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H35" s="27" t="n">
         <v>-0.37</v>
       </c>
-      <c r="I35" s="29" t="n">
-        <v>59.59</v>
+      <c r="I35" s="27" t="n">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H36" s="29" t="n">
-        <v>3.08</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H36" s="27" t="n">
+        <v>-16.78</v>
       </c>
       <c r="I36" s="27" t="n">
-        <v>-8.720000000000001</v>
+        <v>-32.79</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>카카오페이</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E37" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H37" s="29" t="n">
-        <v>1.61</v>
+        <v>0.41</v>
       </c>
       <c r="I37" s="27" t="n">
-        <v>-10.59</v>
+        <v>-5.05</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D38" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H38" s="29" t="n">
-        <v>25.52</v>
-      </c>
-      <c r="I38" s="29" t="n">
-        <v>32.53</v>
+        <v>5.14</v>
+      </c>
+      <c r="I38" s="27" t="n">
+        <v>-40.85</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>핑거</t>
+          <t>동국생명과학</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D39" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H39" s="29" t="n">
-        <v>10.87</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H39" s="27" t="n">
+        <v>-9.06</v>
       </c>
       <c r="I39" s="29" t="n">
-        <v>27.73</v>
+        <v>20.52</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
+          <t>모아데이타</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4375,25 +4395,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H40" s="27" t="n">
-        <v>-19.24</v>
+        <v>-2.38</v>
       </c>
       <c r="I40" s="27" t="n">
-        <v>-19.24</v>
+        <v>-13.38</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>비케이홀딩스</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4410,25 +4430,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H41" s="27" t="n">
-        <v>-2.41</v>
+        <v>-15.35</v>
       </c>
       <c r="I41" s="27" t="n">
-        <v>-11.08</v>
+        <v>-17.21</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>노타</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4445,25 +4465,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H42" s="29" t="n">
-        <v>28.93</v>
-      </c>
-      <c r="I42" s="29" t="n">
-        <v>32.96</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H42" s="27" t="n">
+        <v>-3.31</v>
+      </c>
+      <c r="I42" s="27" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4480,25 +4500,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H43" s="29" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="I43" s="29" t="n">
-        <v>7.84</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H43" s="27" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="I43" s="27" t="n">
+        <v>-4.58</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>모아데이타</t>
+          <t>삼일씨엔에스</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4515,25 +4535,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H44" s="27" t="n">
-        <v>-4.18</v>
-      </c>
-      <c r="I44" s="25" t="n">
-        <v>0</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H44" s="29" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="I44" s="29" t="n">
+        <v>9.49</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>삼성물산</t>
+          <t>서희건설</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4550,25 +4570,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H45" s="27" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="I45" s="29" t="n">
-        <v>4.44</v>
+        <v>-1.3</v>
+      </c>
+      <c r="I45" s="27" t="n">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>서희건설</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4585,25 +4605,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="27" t="n">
-        <v>-1.5</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H46" s="27" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="I46" s="29" t="n">
+        <v>0.39</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>앤씨앤</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4620,25 +4640,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H47" s="27" t="n">
-        <v>-1.87</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H47" s="29" t="n">
+        <v>5.18</v>
       </c>
       <c r="I47" s="29" t="n">
-        <v>0.17</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>아이엘</t>
+          <t>케이쓰리아이</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4655,25 +4675,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H48" s="27" t="n">
-        <v>-0.86</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H48" s="29" t="n">
+        <v>11.96</v>
       </c>
       <c r="I48" s="29" t="n">
-        <v>9.279999999999999</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>앤씨앤</t>
+          <t>토마토시스템</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4690,25 +4710,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H49" s="27" t="n">
-        <v>-12.5</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H49" s="29" t="n">
+        <v>12.07</v>
       </c>
       <c r="I49" s="29" t="n">
-        <v>31.15</v>
+        <v>65.84999999999999</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4725,25 +4745,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H50" s="29" t="n">
-        <v>7.26</v>
-      </c>
-      <c r="I50" s="29" t="n">
-        <v>23.23</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H50" s="27" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="I50" s="27" t="n">
+        <v>-1.91</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>파이온엑스</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4760,25 +4780,25 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H51" s="27" t="n">
-        <v>-28.48</v>
-      </c>
-      <c r="I51" s="27" t="n">
-        <v>-57.95</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H51" s="29" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="I51" s="29" t="n">
+        <v>2.62</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>한전산업</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -4795,19 +4815,19 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H52" s="29" t="n">
-        <v>0.54</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H52" s="27" t="n">
+        <v>-1.19</v>
       </c>
       <c r="I52" s="27" t="n">
-        <v>-0.31</v>
+        <v>-2.59</v>
       </c>
     </row>
   </sheetData>
@@ -4891,19 +4911,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4922,19 +4942,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4953,19 +4973,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -4984,19 +5004,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5015,19 +5035,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5046,19 +5066,19 @@
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5070,26 +5090,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5101,26 +5121,26 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B10" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="36" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G10" s="37" t="inlineStr">
@@ -5132,26 +5152,26 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B11" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="36" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E11" s="36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F11" s="37" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G11" s="37" t="inlineStr">
@@ -5161,40 +5181,36 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>6</v>
-      </c>
-      <c r="D12" s="36" t="n">
-        <v>6</v>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="F12" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G12" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>이차전지</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G12" s="28" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>이차전지</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -5221,7 +5237,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5248,7 +5264,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5275,7 +5291,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5302,7 +5318,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5329,7 +5345,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5356,7 +5372,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -5383,7 +5399,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -261,11 +261,11 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-24 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-25 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-24) 상위: 반도체  점수 51.0점</t>
+          <t>⚡ 최신(2026-09-25) 상위: 반도체  점수 47.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-24) 상위: 삼성전자  점수 32.0점</t>
+          <t>⚡ 최신(2026-09-25) 상위: 삼성전자  점수 30.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-24) 상위: SK하이닉스  점수 18.0점</t>
+          <t>⚡ 최신(2026-09-25) 상위: 제약  점수 15.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1025,15 +1025,15 @@
       <c r="G16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>6.03</v>
+      <c r="H16" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v/>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,14 +1053,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1068,15 +1068,15 @@
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v/>
+      <c r="H17" s="19" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>5.46</v>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="n">
@@ -1086,7 +1086,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
@@ -1129,7 +1129,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1153,24 +1153,26 @@
         <v>0</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>-0.47</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="I19" s="18" t="n">
-        <v>7.69</v>
+        <v>17.08</v>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="n">
-        <v/>
+          <t>네이버 검색 당일 +63% / 중요공시 4건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K19" s="17" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1178,14 +1180,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1194,14 +1196,14 @@
         <v>0</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>-2.09</v>
+        <v>-0.47</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>5.46</v>
+        <v>7.69</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K20" s="17" t="n">
@@ -1211,7 +1213,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1219,14 +1221,14 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1234,25 +1236,27 @@
       <c r="G21" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="18" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="I21" s="18" t="n">
-        <v>9.4</v>
+      <c r="H21" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v/>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K21" s="17" t="n">
-        <v/>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K21" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1260,7 +1264,7 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
@@ -1275,15 +1279,15 @@
       <c r="G22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="19" t="n">
-        <v>-1.31</v>
-      </c>
-      <c r="I22" s="18" t="n">
-        <v>0.45</v>
+      <c r="H22" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v/>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
@@ -1295,7 +1299,7 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1303,7 +1307,7 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
@@ -1318,27 +1322,25 @@
       <c r="G23" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="19" t="n">
-        <v>-9.710000000000001</v>
-      </c>
-      <c r="I23" s="18" t="n">
-        <v>17.08</v>
+      <c r="H23" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v/>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>중요공시 4건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1346,42 +1348,40 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F24" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H24" s="19" t="n">
-        <v>-1.78</v>
-      </c>
-      <c r="I24" s="19" t="n">
-        <v>-0.67</v>
+        <v>0</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>6.03</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 7일 +200% / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
@@ -1404,15 +1404,15 @@
       <c r="G25" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="19" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="I25" s="19" t="n">
-        <v>-4.89</v>
+      <c r="H25" s="18" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I25" s="18" t="n">
+        <v>15.23</v>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +50% / 중요공시 7일 +50%</t>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +200%</t>
         </is>
       </c>
       <c r="K25" s="17" t="inlineStr">
@@ -1424,7 +1424,7 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
@@ -1447,15 +1447,15 @@
       <c r="G26" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="18" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="I26" s="18" t="n">
-        <v>15.23</v>
+      <c r="H26" s="19" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>-5.09</v>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +200%</t>
+          <t>중요공시 3건 / 중요공시 3일 +50% / 중요공시 7일 +50%</t>
         </is>
       </c>
       <c r="K26" s="17" t="inlineStr">
@@ -1467,7 +1467,7 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
@@ -1475,42 +1475,42 @@
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
         <v>8</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>-1.73</v>
+        <v>-1.38</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>-5.09</v>
+        <v>-1.52</v>
       </c>
       <c r="J27" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +50% / 중요공시 7일 +50%</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K27" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B28" s="15" t="n">
@@ -1518,14 +1518,14 @@
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F28" s="15" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="J28" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K28" s="17" t="n">
@@ -1551,7 +1551,7 @@
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B29" s="15" t="n">
@@ -1559,14 +1559,14 @@
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F29" s="15" t="n">
         <v>0</v>
@@ -1574,199 +1574,199 @@
       <c r="G29" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I29" s="15" t="n">
-        <v/>
+      <c r="H29" s="18" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I29" s="19" t="n">
+        <v>-0.72</v>
       </c>
       <c r="J29" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>Google 급상승 검색어 등장 (US) / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K29" s="17" t="inlineStr">
         <is>
+          <t>Google</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>노타</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="22" t="n">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="I30" s="23" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="J30" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +152% / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
           <t>네이버</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="n">
-        <v>17</v>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>한화시스템</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G30" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" s="19" t="n">
-        <v>-4.12</v>
-      </c>
-      <c r="I30" s="18" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="J30" s="17" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100% / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K30" s="17" t="inlineStr">
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>GS건설</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="22" t="n">
+        <v>-7.33</v>
+      </c>
+      <c r="I31" s="22" t="n">
+        <v>-5.57</v>
+      </c>
+      <c r="J31" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 7일 +50%</t>
+        </is>
+      </c>
+      <c r="K31" s="24" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="D31" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F31" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I31" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J31" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K31" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="n">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="n">
         <v>19</v>
       </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>방산</t>
-        </is>
-      </c>
-      <c r="D32" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I32" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J32" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K32" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>HJ중공업</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="22" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="I32" s="22" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="J32" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="n">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="D33" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E33" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F33" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I33" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J33" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K33" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>비케이홀딩스</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" s="22" t="n">
+        <v>-15.35</v>
+      </c>
+      <c r="I33" s="22" t="n">
+        <v>-17.21</v>
+      </c>
+      <c r="J33" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 7일 +200%</t>
+        </is>
+      </c>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1774,33 +1774,33 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>대양금속</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G34" s="20" t="n">
         <v>3</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>-14.85</v>
-      </c>
-      <c r="I34" s="22" t="n">
-        <v>-11.08</v>
-      </c>
-      <c r="J34" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 7일 +200%</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="inlineStr">
+        <v>-4.12</v>
+      </c>
+      <c r="I34" s="23" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="J34" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K34" s="24" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1809,7 +1809,7 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1817,33 +1817,33 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G35" s="20" t="n">
         <v>3</v>
       </c>
       <c r="H35" s="22" t="n">
-        <v>-7.33</v>
+        <v>-5.76</v>
       </c>
       <c r="I35" s="22" t="n">
-        <v>-5.57</v>
-      </c>
-      <c r="J35" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 4건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K35" s="23" t="inlineStr">
+        <v>-4.57</v>
+      </c>
+      <c r="J35" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K35" s="24" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1852,7 +1852,7 @@
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1860,40 +1860,42 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>삼성물산</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F36" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G36" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I36" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J36" s="23" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="n">
-        <v/>
+      <c r="H36" s="23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I36" s="23" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="J36" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1901,33 +1903,33 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F37" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G37" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H37" s="22" t="n">
-        <v>-5.76</v>
+        <v>-2.96</v>
       </c>
       <c r="I37" s="22" t="n">
-        <v>-4.57</v>
-      </c>
-      <c r="J37" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K37" s="23" t="inlineStr">
+        <v>-4.24</v>
+      </c>
+      <c r="J37" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K37" s="24" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1936,7 +1938,7 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1944,42 +1946,40 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>삼성물산</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F38" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G38" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I38" s="24" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="J38" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K38" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H38" s="22" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="I38" s="23" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J38" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K38" s="24" t="n">
+        <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1987,14 +1987,14 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>디에이테크놀로지</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F39" s="20" t="n">
         <v>0</v>
@@ -2002,25 +2002,27 @@
       <c r="G39" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I39" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J39" s="23" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K39" s="23" t="n">
-        <v/>
+      <c r="H39" s="22" t="n">
+        <v>-96.68000000000001</v>
+      </c>
+      <c r="I39" s="22" t="n">
+        <v>-96.68000000000001</v>
+      </c>
+      <c r="J39" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +533% / 중요공시 2건</t>
+        </is>
+      </c>
+      <c r="K39" s="24" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2028,14 +2030,14 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대양금속</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F40" s="20" t="n">
         <v>0</v>
@@ -2044,26 +2046,26 @@
         <v>0</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>-4.5</v>
+        <v>-14.85</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>-1.66</v>
-      </c>
-      <c r="J40" s="23" t="inlineStr">
-        <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
-        </is>
-      </c>
-      <c r="K40" s="23" t="inlineStr">
-        <is>
-          <t>Google</t>
+        <v>-11.08</v>
+      </c>
+      <c r="J40" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K40" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2071,33 +2073,33 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>우진</t>
+          <t>케이쓰리아이</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E41" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G41" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="22" t="n">
-        <v>-4.46</v>
-      </c>
-      <c r="I41" s="22" t="n">
-        <v>-2.59</v>
-      </c>
-      <c r="J41" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 3일 +50%</t>
-        </is>
-      </c>
-      <c r="K41" s="23" t="inlineStr">
+      <c r="H41" s="23" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="I41" s="23" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="J41" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K41" s="24" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -2106,7 +2108,7 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -2114,14 +2116,14 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>포스코퓨처엠</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E42" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F42" s="20" t="n">
         <v>0</v>
@@ -2130,26 +2132,26 @@
         <v>0</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>-2.96</v>
-      </c>
-      <c r="I42" s="22" t="n">
-        <v>-4.24</v>
-      </c>
-      <c r="J42" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K42" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>-3.35</v>
+      </c>
+      <c r="I42" s="23" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J42" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K42" s="24" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B43" s="20" t="n">
@@ -2157,7 +2159,7 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>노타</t>
+          <t>삼성제약</t>
         </is>
       </c>
       <c r="D43" s="20" t="n">
@@ -2173,24 +2175,26 @@
         <v>0</v>
       </c>
       <c r="H43" s="22" t="n">
-        <v>-9.529999999999999</v>
-      </c>
-      <c r="I43" s="24" t="n">
-        <v>21.21</v>
-      </c>
-      <c r="J43" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K43" s="23" t="n">
-        <v/>
+        <v>-2.66</v>
+      </c>
+      <c r="I43" s="22" t="n">
+        <v>-8.380000000000001</v>
+      </c>
+      <c r="J43" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K43" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B44" s="20" t="n">
@@ -2198,7 +2202,7 @@
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D44" s="20" t="n">
@@ -2213,25 +2217,25 @@
       <c r="G44" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="24" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="I44" s="24" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="J44" s="23" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K44" s="23" t="n">
+      <c r="H44" s="23" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I44" s="23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J44" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K44" s="24" t="n">
         <v/>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B45" s="20" t="n">
@@ -2239,7 +2243,7 @@
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>스테이블코인</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="D45" s="20" t="n">
@@ -2260,148 +2264,144 @@
       <c r="I45" s="20" t="n">
         <v/>
       </c>
-      <c r="J45" s="23" t="inlineStr">
+      <c r="J45" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K45" s="24" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>태양광</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I46" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J46" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K46" s="24" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="23" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="I47" s="23" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="J47" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K47" s="24" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>스테이블코인</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I48" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J48" s="24" t="inlineStr">
         <is>
           <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
-      <c r="K45" s="23" t="n">
+      <c r="K48" s="24" t="n">
         <v/>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B46" s="25" t="n">
-        <v>33</v>
-      </c>
-      <c r="C46" s="26" t="inlineStr">
-        <is>
-          <t>한국제17호스팩</t>
-        </is>
-      </c>
-      <c r="D46" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="27" t="n">
-        <v>-1.91</v>
-      </c>
-      <c r="I46" s="27" t="n">
-        <v>-1.91</v>
-      </c>
-      <c r="J46" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +4057%</t>
-        </is>
-      </c>
-      <c r="K46" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B47" s="25" t="n">
-        <v>34</v>
-      </c>
-      <c r="C47" s="26" t="inlineStr">
-        <is>
-          <t>KB제34호스팩</t>
-        </is>
-      </c>
-      <c r="D47" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E47" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F47" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="27" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="I47" s="27" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="J47" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +2698%</t>
-        </is>
-      </c>
-      <c r="K47" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B48" s="25" t="n">
-        <v>35</v>
-      </c>
-      <c r="C48" s="26" t="inlineStr">
-        <is>
-          <t>네오사피엔스</t>
-        </is>
-      </c>
-      <c r="D48" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F48" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="27" t="n">
-        <v>-16.78</v>
-      </c>
-      <c r="I48" s="27" t="n">
-        <v>-32.79</v>
-      </c>
-      <c r="J48" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +810%</t>
-        </is>
-      </c>
-      <c r="K48" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>동국생명과학</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
@@ -2425,14 +2425,14 @@
         <v>0</v>
       </c>
       <c r="H49" s="27" t="n">
-        <v>-9.06</v>
-      </c>
-      <c r="I49" s="29" t="n">
-        <v>20.52</v>
+        <v>-1.91</v>
+      </c>
+      <c r="I49" s="27" t="n">
+        <v>-1.91</v>
       </c>
       <c r="J49" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +295%</t>
+          <t>네이버 검색 당일 +4633%</t>
         </is>
       </c>
       <c r="K49" s="28" t="inlineStr">
@@ -2444,7 +2444,7 @@
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>토마토시스템</t>
+          <t>KB제34호스팩</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -2467,15 +2467,15 @@
       <c r="G50" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="29" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="I50" s="29" t="n">
-        <v>65.84999999999999</v>
+      <c r="H50" s="27" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="I50" s="27" t="n">
+        <v>-0.37</v>
       </c>
       <c r="J50" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +214%</t>
+          <t>네이버 검색 당일 +3094%</t>
         </is>
       </c>
       <c r="K50" s="28" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>케이쓰리아이</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2510,27 +2510,27 @@
       <c r="G51" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="29" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="I51" s="29" t="n">
-        <v>26.25</v>
+      <c r="H51" s="27" t="n">
+        <v>-16.78</v>
+      </c>
+      <c r="I51" s="27" t="n">
+        <v>-32.79</v>
       </c>
       <c r="J51" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>네이버 검색 당일 +930%</t>
         </is>
       </c>
       <c r="K51" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>동국생명과학</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2553,25 +2553,27 @@
       <c r="G52" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="29" t="n">
-        <v>6.52</v>
+      <c r="H52" s="27" t="n">
+        <v>-9.06</v>
       </c>
       <c r="I52" s="29" t="n">
-        <v>2.62</v>
+        <v>20.52</v>
       </c>
       <c r="J52" s="28" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K52" s="28" t="n">
-        <v/>
+          <t>네이버 검색 당일 +554%</t>
+        </is>
+      </c>
+      <c r="K52" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2579,7 +2581,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>토마토시스템</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2594,27 +2596,27 @@
       <c r="G53" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="27" t="n">
-        <v>-3.31</v>
-      </c>
-      <c r="I53" s="27" t="n">
-        <v>-1.2</v>
+      <c r="H53" s="29" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="I53" s="29" t="n">
+        <v>65.84999999999999</v>
       </c>
       <c r="J53" s="28" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +477%</t>
         </is>
       </c>
       <c r="K53" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2622,7 +2624,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2638,26 +2640,26 @@
         <v>0</v>
       </c>
       <c r="H54" s="29" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="I54" s="27" t="n">
-        <v>-40.85</v>
+        <v>18.12</v>
+      </c>
+      <c r="I54" s="29" t="n">
+        <v>21.39</v>
       </c>
       <c r="J54" s="28" t="inlineStr">
         <is>
-          <t>중요공시 8건</t>
+          <t>네이버 검색 당일 +130%</t>
         </is>
       </c>
       <c r="K54" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2665,7 +2667,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2680,27 +2682,27 @@
       <c r="G55" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="29" t="n">
-        <v>0.41</v>
+      <c r="H55" s="27" t="n">
+        <v>-4.5</v>
       </c>
       <c r="I55" s="27" t="n">
-        <v>-5.05</v>
+        <v>-1.66</v>
       </c>
       <c r="J55" s="28" t="inlineStr">
         <is>
-          <t>중요공시 5건</t>
+          <t>네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K55" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2708,7 +2710,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>비케이홀딩스</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2723,27 +2725,25 @@
       <c r="G56" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="27" t="n">
-        <v>-15.35</v>
-      </c>
-      <c r="I56" s="27" t="n">
-        <v>-17.21</v>
+      <c r="H56" s="29" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="I56" s="29" t="n">
+        <v>2.62</v>
       </c>
       <c r="J56" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K56" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K56" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>앤씨앤</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2766,15 +2766,15 @@
       <c r="G57" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="29" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="I57" s="29" t="n">
-        <v>35.4</v>
+      <c r="H57" s="27" t="n">
+        <v>-3.31</v>
+      </c>
+      <c r="I57" s="27" t="n">
+        <v>-1.2</v>
       </c>
       <c r="J57" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K57" s="28" t="inlineStr">
@@ -2786,7 +2786,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>서희건설</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2809,15 +2809,15 @@
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="27" t="n">
-        <v>-1.3</v>
+      <c r="H58" s="29" t="n">
+        <v>5.14</v>
       </c>
       <c r="I58" s="27" t="n">
-        <v>-2.16</v>
+        <v>-40.85</v>
       </c>
       <c r="J58" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>중요공시 6건</t>
         </is>
       </c>
       <c r="K58" s="28" t="inlineStr">
@@ -2829,7 +2829,7 @@
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2837,30 +2837,30 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>모아데이타</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E59" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F59" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="27" t="n">
-        <v>-2.38</v>
+      <c r="H59" s="29" t="n">
+        <v>0.41</v>
       </c>
       <c r="I59" s="27" t="n">
-        <v>-13.38</v>
+        <v>-5.05</v>
       </c>
       <c r="J59" s="28" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>중요공시 5건</t>
         </is>
       </c>
       <c r="K59" s="28" t="inlineStr">
@@ -2872,7 +2872,7 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2880,30 +2880,30 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>삼일씨엔에스</t>
+          <t>앤씨앤</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E60" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H60" s="29" t="n">
-        <v>5.45</v>
+        <v>5.18</v>
       </c>
       <c r="I60" s="29" t="n">
-        <v>9.49</v>
+        <v>35.4</v>
       </c>
       <c r="J60" s="28" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K60" s="28" t="inlineStr">
@@ -2915,7 +2915,7 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2923,30 +2923,30 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>서희건설</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E61" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="27" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="I61" s="29" t="n">
-        <v>0.39</v>
+        <v>-1.3</v>
+      </c>
+      <c r="I61" s="27" t="n">
+        <v>-2.16</v>
       </c>
       <c r="J61" s="28" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K61" s="28" t="inlineStr">
@@ -2958,7 +2958,7 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2966,30 +2966,30 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>모아데이타</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E62" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F62" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H62" s="27" t="n">
-        <v>-1.19</v>
+        <v>-2.38</v>
       </c>
       <c r="I62" s="27" t="n">
-        <v>-2.59</v>
+        <v>-13.38</v>
       </c>
       <c r="J62" s="28" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
         </is>
       </c>
       <c r="K62" s="28" t="inlineStr">
@@ -3001,7 +3001,7 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3009,35 +3009,35 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼일씨엔에스</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E63" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F63" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="27" t="n">
-        <v>-1.88</v>
-      </c>
-      <c r="I63" s="27" t="n">
-        <v>-4.58</v>
+      <c r="H63" s="29" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="I63" s="29" t="n">
+        <v>9.49</v>
       </c>
       <c r="J63" s="28" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
         </is>
       </c>
       <c r="K63" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
@@ -3134,22 +3134,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3165,22 +3165,22 @@
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H4" s="29" t="n">
@@ -3193,95 +3193,95 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H5" s="29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I5" s="29" t="n">
-        <v>6.03</v>
-      </c>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H5" s="25" t="n"/>
+      <c r="I5" s="25" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H6" s="25" t="n"/>
-      <c r="I6" s="25" t="n"/>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="I6" s="29" t="n">
+        <v>5.46</v>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H7" s="25" t="n"/>
@@ -3290,112 +3290,108 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H8" s="27" t="n">
-        <v>-2.09</v>
+        <v>-0.47</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>5.46</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H9" s="27" t="n">
-        <v>-0.47</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="I9" s="29" t="n">
-        <v>7.69</v>
+        <v>17.08</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H10" s="29" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="I10" s="29" t="n">
-        <v>9.4</v>
-      </c>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H10" s="25" t="n"/>
+      <c r="I10" s="25" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
@@ -3412,25 +3408,21 @@
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H11" s="27" t="n">
-        <v>-1.31</v>
-      </c>
-      <c r="I11" s="29" t="n">
-        <v>0.45</v>
-      </c>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H11" s="25" t="n"/>
+      <c r="I11" s="25" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
@@ -3447,54 +3439,50 @@
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H12" s="27" t="n">
-        <v>-1.78</v>
-      </c>
-      <c r="I12" s="27" t="n">
-        <v>-0.67</v>
-      </c>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H12" s="25" t="n"/>
+      <c r="I12" s="25" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H13" s="27" t="n">
-        <v>-9.710000000000001</v>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H13" s="29" t="n">
+        <v>1.2</v>
       </c>
       <c r="I13" s="29" t="n">
-        <v>17.08</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -3517,12 +3505,12 @@
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H14" s="27" t="n">
@@ -3535,7 +3523,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -3552,25 +3540,25 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H15" s="27" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="I15" s="27" t="n">
-        <v>-4.89</v>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H15" s="29" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I15" s="29" t="n">
+        <v>15.23</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -3587,78 +3575,82 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H16" s="25" t="n"/>
-      <c r="I16" s="25" t="n"/>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="I16" s="27" t="n">
+        <v>-1.52</v>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H17" s="29" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>15.23</v>
+        <v>0.91</v>
+      </c>
+      <c r="I17" s="27" t="n">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H18" s="25" t="n"/>
@@ -3667,135 +3659,147 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H19" s="25" t="n"/>
-      <c r="I19" s="25" t="n"/>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H19" s="27" t="n">
+        <v>-7.33</v>
+      </c>
+      <c r="I19" s="27" t="n">
+        <v>-5.57</v>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H20" s="25" t="n"/>
-      <c r="I20" s="25" t="n"/>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="I20" s="27" t="n">
+        <v>-0.67</v>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>노타</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H21" s="25" t="n"/>
-      <c r="I21" s="25" t="n"/>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H21" s="27" t="n">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="I21" s="29" t="n">
+        <v>21.21</v>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H22" s="27" t="n">
-        <v>-4.12</v>
-      </c>
-      <c r="I22" s="29" t="n">
-        <v>7.98</v>
+        <v>-5.76</v>
+      </c>
+      <c r="I22" s="27" t="n">
+        <v>-4.57</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>비케이홀딩스</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -3812,25 +3816,25 @@
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H23" s="27" t="n">
-        <v>-7.33</v>
+        <v>-15.35</v>
       </c>
       <c r="I23" s="27" t="n">
-        <v>-5.57</v>
+        <v>-17.21</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>대양금속</t>
+          <t>삼성물산</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -3847,25 +3851,25 @@
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H24" s="27" t="n">
-        <v>-14.85</v>
-      </c>
-      <c r="I24" s="27" t="n">
-        <v>-11.08</v>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H24" s="29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I24" s="29" t="n">
+        <v>4.84</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
@@ -3882,227 +3886,231 @@
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H25" s="25" t="n"/>
-      <c r="I25" s="25" t="n"/>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H25" s="27" t="n">
+        <v>-4.12</v>
+      </c>
+      <c r="I25" s="29" t="n">
+        <v>7.98</v>
+      </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H26" s="27" t="n">
-        <v>-5.76</v>
-      </c>
-      <c r="I26" s="27" t="n">
-        <v>-4.57</v>
+        <v>-1.31</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>삼성물산</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H27" s="29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I27" s="29" t="n">
-        <v>4.84</v>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H27" s="27" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="I27" s="27" t="n">
+        <v>-4.24</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>대양금속</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H28" s="25" t="n"/>
-      <c r="I28" s="25" t="n"/>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H28" s="27" t="n">
+        <v>-14.85</v>
+      </c>
+      <c r="I28" s="27" t="n">
+        <v>-11.08</v>
+      </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>디에이테크놀로지</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E29" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H29" s="27" t="n">
-        <v>-4.5</v>
+        <v>-96.68000000000001</v>
       </c>
       <c r="I29" s="27" t="n">
-        <v>-1.66</v>
+        <v>-96.68000000000001</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>우진</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H30" s="27" t="n">
-        <v>-4.46</v>
-      </c>
-      <c r="I30" s="27" t="n">
-        <v>-2.59</v>
-      </c>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="25" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>포스코퓨처엠</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H31" s="27" t="n">
-        <v>-2.96</v>
-      </c>
-      <c r="I31" s="27" t="n">
-        <v>-4.24</v>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H31" s="29" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I31" s="29" t="n">
+        <v>9.4</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>삼성제약</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
@@ -4119,25 +4127,25 @@
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H32" s="29" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="I32" s="29" t="n">
-        <v>8.619999999999999</v>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H32" s="27" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="I32" s="27" t="n">
+        <v>-8.380000000000001</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>노타</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
@@ -4154,25 +4162,21 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H33" s="27" t="n">
-        <v>-9.529999999999999</v>
-      </c>
-      <c r="I33" s="29" t="n">
-        <v>21.21</v>
-      </c>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H33" s="25" t="n"/>
+      <c r="I33" s="25" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>스테이블코인</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
@@ -4189,126 +4193,126 @@
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H34" s="25" t="n"/>
-      <c r="I34" s="25" t="n"/>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H34" s="27" t="n">
+        <v>-3.35</v>
+      </c>
+      <c r="I34" s="29" t="n">
+        <v>0.54</v>
+      </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>KB제34호스팩</t>
+          <t>케이쓰리아이</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H35" s="27" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="I35" s="27" t="n">
-        <v>-0.37</v>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H35" s="29" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="I35" s="29" t="n">
+        <v>26.25</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H36" s="27" t="n">
-        <v>-16.78</v>
-      </c>
-      <c r="I36" s="27" t="n">
-        <v>-32.79</v>
-      </c>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H36" s="25" t="n"/>
+      <c r="I36" s="25" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H37" s="29" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="I37" s="27" t="n">
-        <v>-5.05</v>
+        <v>8.949999999999999</v>
+      </c>
+      <c r="I37" s="29" t="n">
+        <v>19.31</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>KB제34호스팩</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4325,25 +4329,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H38" s="29" t="n">
-        <v>5.14</v>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H38" s="27" t="n">
+        <v>-0.37</v>
       </c>
       <c r="I38" s="27" t="n">
-        <v>-40.85</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>동국생명과학</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4360,25 +4364,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H39" s="27" t="n">
-        <v>-9.06</v>
-      </c>
-      <c r="I39" s="29" t="n">
-        <v>20.52</v>
+        <v>-16.78</v>
+      </c>
+      <c r="I39" s="27" t="n">
+        <v>-32.79</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>모아데이타</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4395,25 +4399,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H40" s="27" t="n">
-        <v>-2.38</v>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H40" s="29" t="n">
+        <v>0.41</v>
       </c>
       <c r="I40" s="27" t="n">
-        <v>-13.38</v>
+        <v>-5.05</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>비케이홀딩스</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4430,25 +4434,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H41" s="27" t="n">
-        <v>-15.35</v>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H41" s="29" t="n">
+        <v>5.14</v>
       </c>
       <c r="I41" s="27" t="n">
-        <v>-17.21</v>
+        <v>-40.85</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>동국생명과학</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4465,25 +4469,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H42" s="27" t="n">
-        <v>-3.31</v>
-      </c>
-      <c r="I42" s="27" t="n">
-        <v>-1.2</v>
+        <v>-9.06</v>
+      </c>
+      <c r="I42" s="29" t="n">
+        <v>20.52</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4500,25 +4504,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H43" s="27" t="n">
-        <v>-1.88</v>
+        <v>-4.5</v>
       </c>
       <c r="I43" s="27" t="n">
-        <v>-4.58</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>삼일씨엔에스</t>
+          <t>모아데이타</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4535,25 +4539,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H44" s="29" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="I44" s="29" t="n">
-        <v>9.49</v>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H44" s="27" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="I44" s="27" t="n">
+        <v>-13.38</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>서희건설</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4570,25 +4574,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H45" s="27" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="I45" s="27" t="n">
-        <v>-2.16</v>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H45" s="29" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="I45" s="29" t="n">
+        <v>21.39</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4605,25 +4609,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H46" s="27" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="I46" s="29" t="n">
-        <v>0.39</v>
+        <v>-3.31</v>
+      </c>
+      <c r="I46" s="27" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>앤씨앤</t>
+          <t>삼일씨엔에스</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4640,25 +4644,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H47" s="29" t="n">
-        <v>5.18</v>
+        <v>5.45</v>
       </c>
       <c r="I47" s="29" t="n">
-        <v>35.4</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>케이쓰리아이</t>
+          <t>서희건설</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4675,25 +4679,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H48" s="29" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="I48" s="29" t="n">
-        <v>26.25</v>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H48" s="27" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="I48" s="27" t="n">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>토마토시스템</t>
+          <t>앤씨앤</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4710,25 +4714,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H49" s="29" t="n">
-        <v>12.07</v>
+        <v>5.18</v>
       </c>
       <c r="I49" s="29" t="n">
-        <v>65.84999999999999</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>토마토시스템</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4745,25 +4749,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H50" s="27" t="n">
-        <v>-1.91</v>
-      </c>
-      <c r="I50" s="27" t="n">
-        <v>-1.91</v>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H50" s="29" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="I50" s="29" t="n">
+        <v>65.84999999999999</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4780,25 +4784,25 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H51" s="29" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="I51" s="29" t="n">
-        <v>2.62</v>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H51" s="27" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="I51" s="27" t="n">
+        <v>-1.91</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -4815,19 +4819,19 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H52" s="27" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="I52" s="27" t="n">
-        <v>-2.59</v>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H52" s="29" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="I52" s="29" t="n">
+        <v>2.62</v>
       </c>
     </row>
   </sheetData>
@@ -4911,19 +4915,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4942,19 +4946,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4973,19 +4977,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5004,19 +5008,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5035,19 +5039,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5066,19 +5070,19 @@
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5097,19 +5101,19 @@
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5128,19 +5132,19 @@
         <v>1</v>
       </c>
       <c r="C10" s="36" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G10" s="37" t="inlineStr">
@@ -5150,40 +5154,36 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="B11" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="F11" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="G11" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>이차전지</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G11" s="28" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>이차전지</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
@@ -5210,7 +5210,7 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -5237,7 +5237,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5264,7 +5264,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5291,7 +5291,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5318,7 +5318,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5345,7 +5345,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5372,7 +5372,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -5399,7 +5399,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -5426,7 +5426,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>의료기기</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -5453,7 +5453,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>의료기기</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
@@ -5480,7 +5480,7 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -5507,7 +5507,7 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -261,11 +261,11 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-25 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-26 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-25) 상위: 반도체  점수 47.0점</t>
+          <t>⚡ 최신(2026-09-26) 상위: 반도체  점수 55.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-25) 상위: 삼성전자  점수 30.0점</t>
+          <t>⚡ 최신(2026-09-26) 상위: 삼성전자  점수 29.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-25) 상위: 제약  점수 15.0점</t>
+          <t>⚡ 최신(2026-09-26) 상위: 인공지능  점수 18.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,14 +1053,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1068,25 +1068,27 @@
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="19" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>5.46</v>
+      <c r="H17" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v/>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="n">
-        <v/>
+          <t>한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K17" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1094,14 +1096,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1117,7 +1119,7 @@
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
@@ -1129,7 +1131,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1137,14 +1139,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1153,26 +1155,24 @@
         <v>0</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>-9.710000000000001</v>
+        <v>-0.47</v>
       </c>
       <c r="I19" s="18" t="n">
-        <v>17.08</v>
+        <v>7.69</v>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +63% / 중요공시 4건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K19" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1180,40 +1180,42 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="19" t="n">
-        <v>-0.47</v>
+        <v>3</v>
+      </c>
+      <c r="H20" s="18" t="n">
+        <v>3.76</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>7.69</v>
+        <v>15.23</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="n">
-        <v/>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +50%</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1221,42 +1223,42 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v/>
+      <c r="H21" s="19" t="n">
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="I21" s="18" t="n">
+        <v>17.08</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>네이버 검색 당일 +73% / 중요공시 4건 / 중요공시 3일 +100%</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1264,42 +1266,42 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>대양금속</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v/>
+      <c r="H22" s="19" t="n">
+        <v>-14.85</v>
+      </c>
+      <c r="I22" s="19" t="n">
+        <v>-11.08</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +56% / 중요공시 3건 / 중요공시 3일 +200%</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1307,40 +1309,42 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F23" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I23" s="15" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="I23" s="19" t="n">
+        <v>-0.67</v>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="n">
-        <v/>
+          <t>중요공시 2건 / 중요공시 7일 +100% / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1348,14 +1352,14 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F24" s="15" t="n">
         <v>0</v>
@@ -1363,238 +1367,238 @@
       <c r="G24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I24" s="18" t="n">
-        <v>6.03</v>
+      <c r="H24" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v/>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="n">
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>네오사피엔스</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="22" t="n">
+        <v>-16.78</v>
+      </c>
+      <c r="I25" s="22" t="n">
+        <v>-32.79</v>
+      </c>
+      <c r="J25" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +949% / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K25" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>LG전자</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="22" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="I26" s="24" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="J26" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K26" s="23" t="n">
         <v/>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>스피어</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="18" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="I25" s="18" t="n">
-        <v>15.23</v>
-      </c>
-      <c r="J25" s="17" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +200%</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="n">
-        <v>13</v>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>금호건설</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G26" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" s="19" t="n">
-        <v>-1.73</v>
-      </c>
-      <c r="I26" s="19" t="n">
-        <v>-5.09</v>
-      </c>
-      <c r="J26" s="17" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 3일 +50% / 중요공시 7일 +50%</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="n">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>현대차</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="F27" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="19" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="I27" s="19" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="J27" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>바이오</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I27" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J27" s="23" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K27" s="23" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="n">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>와이즈플래닛컴퍼니</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="15" t="n">
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>로봇</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="20" t="n">
         <v/>
       </c>
-      <c r="I28" s="15" t="n">
+      <c r="I28" s="20" t="n">
         <v/>
       </c>
-      <c r="J28" s="17" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K28" s="17" t="n">
+      <c r="J28" s="23" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="n">
         <v/>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="n">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="18" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I29" s="19" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="J29" s="17" t="inlineStr">
-        <is>
-          <t>Google 급상승 검색어 등장 (US) / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K29" s="17" t="inlineStr">
-        <is>
-          <t>Google</t>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>케이쓰리아이</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="24" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="I29" s="24" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +60% / 중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K29" s="23" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1602,42 +1606,42 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>노타</t>
+          <t>서희건설</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>-9.529999999999999</v>
-      </c>
-      <c r="I30" s="23" t="n">
-        <v>21.21</v>
-      </c>
-      <c r="J30" s="24" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +152% / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K30" s="24" t="inlineStr">
-        <is>
-          <t>네이버</t>
+        <v>-1.3</v>
+      </c>
+      <c r="I30" s="22" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 3일 +50%</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1645,33 +1649,33 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F31" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H31" s="22" t="n">
-        <v>-7.33</v>
+        <v>-7.21</v>
       </c>
       <c r="I31" s="22" t="n">
-        <v>-5.57</v>
-      </c>
-      <c r="J31" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 7일 +50%</t>
-        </is>
-      </c>
-      <c r="K31" s="24" t="inlineStr">
+        <v>-1.37</v>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K31" s="23" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1680,7 +1684,7 @@
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1688,14 +1692,14 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F32" s="20" t="n">
         <v>0</v>
@@ -1703,27 +1707,27 @@
       <c r="G32" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="22" t="n">
-        <v>-1.78</v>
-      </c>
-      <c r="I32" s="22" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="J32" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K32" s="24" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="H32" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I32" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
+          <t>Google 급상승 검색어 등장 (US)</t>
+        </is>
+      </c>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1731,42 +1735,40 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>비케이홀딩스</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H33" s="22" t="n">
-        <v>-15.35</v>
-      </c>
-      <c r="I33" s="22" t="n">
-        <v>-17.21</v>
-      </c>
-      <c r="J33" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 7일 +200%</t>
-        </is>
-      </c>
-      <c r="K33" s="24" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+        <v>-1.31</v>
+      </c>
+      <c r="I33" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J33" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K33" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1774,42 +1776,40 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F34" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H34" s="22" t="n">
-        <v>-4.12</v>
-      </c>
-      <c r="I34" s="23" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="J34" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K34" s="24" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H34" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I34" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J34" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1817,42 +1817,42 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>디에이테크놀로지</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F35" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G35" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H35" s="22" t="n">
-        <v>-5.76</v>
+        <v>-96.68000000000001</v>
       </c>
       <c r="I35" s="22" t="n">
-        <v>-4.57</v>
-      </c>
-      <c r="J35" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K35" s="24" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>-96.68000000000001</v>
+      </c>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +593% / 중요공시 2건</t>
+        </is>
+      </c>
+      <c r="K35" s="23" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1860,42 +1860,40 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>삼성물산</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E36" s="20" t="n">
         <v>4</v>
       </c>
       <c r="F36" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G36" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I36" s="23" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="J36" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K36" s="24" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H36" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I36" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J36" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1903,33 +1901,33 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>포스코퓨처엠</t>
+          <t>삼일씨엔에스</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F37" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="22" t="n">
-        <v>-2.96</v>
-      </c>
-      <c r="I37" s="22" t="n">
-        <v>-4.24</v>
-      </c>
-      <c r="J37" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K37" s="24" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="H37" s="24" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="I37" s="24" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="J37" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K37" s="23" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1938,7 +1936,7 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1946,40 +1944,42 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F38" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>-1.31</v>
-      </c>
-      <c r="I38" s="23" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J38" s="24" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K38" s="24" t="n">
-        <v/>
+        <v>-5.76</v>
+      </c>
+      <c r="I38" s="22" t="n">
+        <v>-4.57</v>
+      </c>
+      <c r="J38" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>디에이테크놀로지</t>
+          <t>삼성제약</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
@@ -2003,26 +2003,26 @@
         <v>0</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>-96.68000000000001</v>
+        <v>-2.66</v>
       </c>
       <c r="I39" s="22" t="n">
-        <v>-96.68000000000001</v>
-      </c>
-      <c r="J39" s="24" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +533% / 중요공시 2건</t>
-        </is>
-      </c>
-      <c r="K39" s="24" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
+        <v>-8.380000000000001</v>
+      </c>
+      <c r="J39" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K39" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>대양금속</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
@@ -2045,27 +2045,27 @@
       <c r="G40" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="22" t="n">
-        <v>-14.85</v>
+      <c r="H40" s="24" t="n">
+        <v>0.91</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>-11.08</v>
-      </c>
-      <c r="J40" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K40" s="24" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>-0.72</v>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>케이쓰리아이</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
@@ -2088,27 +2088,25 @@
       <c r="G41" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="23" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="I41" s="23" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="J41" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K41" s="24" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H41" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I41" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J41" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K41" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -2116,7 +2114,7 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
@@ -2131,27 +2129,27 @@
       <c r="G42" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="22" t="n">
-        <v>-3.35</v>
-      </c>
-      <c r="I42" s="23" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="J42" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K42" s="24" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
+      <c r="H42" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I42" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J42" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K42" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B43" s="20" t="n">
@@ -2159,7 +2157,7 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>삼성제약</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="D43" s="20" t="n">
@@ -2174,234 +2172,240 @@
       <c r="G43" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="22" t="n">
-        <v>-2.66</v>
-      </c>
-      <c r="I43" s="22" t="n">
-        <v>-8.380000000000001</v>
-      </c>
-      <c r="J43" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K43" s="24" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H43" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I43" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J43" s="23" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K43" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B44" s="20" t="n">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B44" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="C44" s="21" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="D44" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E44" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F44" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="23" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="I44" s="23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J44" s="24" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K44" s="24" t="n">
-        <v/>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>한국제17호스팩</t>
+        </is>
+      </c>
+      <c r="D44" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="27" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="I44" s="27" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="J44" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +4696%</t>
+        </is>
+      </c>
+      <c r="K44" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="n">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B45" s="25" t="n">
         <v>32</v>
       </c>
-      <c r="C45" s="21" t="inlineStr">
-        <is>
-          <t>방산</t>
-        </is>
-      </c>
-      <c r="D45" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E45" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F45" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I45" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J45" s="24" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K45" s="24" t="n">
-        <v/>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>KB제34호스팩</t>
+        </is>
+      </c>
+      <c r="D45" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="27" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="I45" s="27" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="J45" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +3123%</t>
+        </is>
+      </c>
+      <c r="K45" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B46" s="20" t="n">
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B46" s="25" t="n">
         <v>33</v>
       </c>
-      <c r="C46" s="21" t="inlineStr">
-        <is>
-          <t>태양광</t>
-        </is>
-      </c>
-      <c r="D46" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E46" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I46" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J46" s="24" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K46" s="24" t="n">
-        <v/>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>동국생명과학</t>
+        </is>
+      </c>
+      <c r="D46" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="27" t="n">
+        <v>-9.06</v>
+      </c>
+      <c r="I46" s="29" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="J46" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +596%</t>
+        </is>
+      </c>
+      <c r="K46" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B47" s="20" t="n">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B47" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="C47" s="21" t="inlineStr">
-        <is>
-          <t>테스</t>
-        </is>
-      </c>
-      <c r="D47" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F47" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="23" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="I47" s="23" t="n">
-        <v>19.31</v>
-      </c>
-      <c r="J47" s="24" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K47" s="24" t="inlineStr">
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>토마토시스템</t>
+        </is>
+      </c>
+      <c r="D47" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="29" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="I47" s="29" t="n">
+        <v>65.84999999999999</v>
+      </c>
+      <c r="J47" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +507%</t>
+        </is>
+      </c>
+      <c r="K47" s="28" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B48" s="20" t="n">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B48" s="25" t="n">
         <v>35</v>
       </c>
-      <c r="C48" s="21" t="inlineStr">
-        <is>
-          <t>스테이블코인</t>
-        </is>
-      </c>
-      <c r="D48" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E48" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F48" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I48" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J48" s="24" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K48" s="24" t="n">
-        <v/>
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>노타</t>
+        </is>
+      </c>
+      <c r="D48" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="27" t="n">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="I48" s="29" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="J48" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +166%</t>
+        </is>
+      </c>
+      <c r="K48" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -2409,7 +2413,7 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
@@ -2424,15 +2428,15 @@
       <c r="G49" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="27" t="n">
-        <v>-1.91</v>
-      </c>
-      <c r="I49" s="27" t="n">
-        <v>-1.91</v>
+      <c r="H49" s="29" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="I49" s="29" t="n">
+        <v>21.39</v>
       </c>
       <c r="J49" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +4633%</t>
+          <t>네이버 검색 당일 +153%</t>
         </is>
       </c>
       <c r="K49" s="28" t="inlineStr">
@@ -2444,7 +2448,7 @@
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2452,7 +2456,7 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>KB제34호스팩</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -2467,15 +2471,15 @@
       <c r="G50" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="27" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="I50" s="27" t="n">
-        <v>-0.37</v>
+      <c r="H50" s="29" t="n">
+        <v>30.09</v>
+      </c>
+      <c r="I50" s="29" t="n">
+        <v>28.42</v>
       </c>
       <c r="J50" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +3094%</t>
+          <t>네이버 검색 당일 +120%</t>
         </is>
       </c>
       <c r="K50" s="28" t="inlineStr">
@@ -2487,7 +2491,7 @@
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2495,7 +2499,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
+          <t>더블유에스아이</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2511,14 +2515,14 @@
         <v>0</v>
       </c>
       <c r="H51" s="27" t="n">
-        <v>-16.78</v>
-      </c>
-      <c r="I51" s="27" t="n">
-        <v>-32.79</v>
+        <v>-11.72</v>
+      </c>
+      <c r="I51" s="29" t="n">
+        <v>20.18</v>
       </c>
       <c r="J51" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +930%</t>
+          <t>네이버 검색 당일 +110%</t>
         </is>
       </c>
       <c r="K51" s="28" t="inlineStr">
@@ -2530,7 +2534,7 @@
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2538,7 +2542,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>동국생명과학</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2553,27 +2557,25 @@
       <c r="G52" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="27" t="n">
-        <v>-9.06</v>
+      <c r="H52" s="29" t="n">
+        <v>6.52</v>
       </c>
       <c r="I52" s="29" t="n">
-        <v>20.52</v>
+        <v>2.62</v>
       </c>
       <c r="J52" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +554%</t>
-        </is>
-      </c>
-      <c r="K52" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K52" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2581,7 +2583,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>토마토시스템</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2597,14 +2599,14 @@
         <v>0</v>
       </c>
       <c r="H53" s="29" t="n">
-        <v>12.07</v>
+        <v>1.2</v>
       </c>
       <c r="I53" s="29" t="n">
-        <v>65.84999999999999</v>
+        <v>6.03</v>
       </c>
       <c r="J53" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +477%</t>
+          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K53" s="28" t="inlineStr">
@@ -2616,7 +2618,7 @@
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2624,7 +2626,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2640,26 +2642,26 @@
         <v>0</v>
       </c>
       <c r="H54" s="29" t="n">
-        <v>18.12</v>
-      </c>
-      <c r="I54" s="29" t="n">
-        <v>21.39</v>
+        <v>5.14</v>
+      </c>
+      <c r="I54" s="27" t="n">
+        <v>-40.85</v>
       </c>
       <c r="J54" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +130%</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K54" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2667,7 +2669,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>비케이홀딩스</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2683,26 +2685,26 @@
         <v>0</v>
       </c>
       <c r="H55" s="27" t="n">
-        <v>-4.5</v>
+        <v>-15.35</v>
       </c>
       <c r="I55" s="27" t="n">
-        <v>-1.66</v>
+        <v>-17.21</v>
       </c>
       <c r="J55" s="28" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K55" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2710,7 +2712,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2726,24 +2728,26 @@
         <v>0</v>
       </c>
       <c r="H56" s="29" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="I56" s="29" t="n">
-        <v>2.62</v>
+        <v>0.41</v>
+      </c>
+      <c r="I56" s="27" t="n">
+        <v>-5.05</v>
       </c>
       <c r="J56" s="28" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K56" s="28" t="n">
-        <v/>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K56" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2751,30 +2755,30 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E57" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F57" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G57" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="27" t="n">
-        <v>-3.31</v>
+        <v>-1.19</v>
       </c>
       <c r="I57" s="27" t="n">
-        <v>-1.2</v>
+        <v>-2.59</v>
       </c>
       <c r="J57" s="28" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
         </is>
       </c>
       <c r="K57" s="28" t="inlineStr">
@@ -2786,7 +2790,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2794,7 +2798,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2809,15 +2813,15 @@
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="29" t="n">
-        <v>5.14</v>
+      <c r="H58" s="27" t="n">
+        <v>-2.96</v>
       </c>
       <c r="I58" s="27" t="n">
-        <v>-40.85</v>
+        <v>-4.24</v>
       </c>
       <c r="J58" s="28" t="inlineStr">
         <is>
-          <t>중요공시 6건</t>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K58" s="28" t="inlineStr">
@@ -2829,7 +2833,7 @@
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2837,7 +2841,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2853,26 +2857,26 @@
         <v>0</v>
       </c>
       <c r="H59" s="29" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="I59" s="27" t="n">
-        <v>-5.05</v>
+        <v>12.59</v>
+      </c>
+      <c r="I59" s="29" t="n">
+        <v>37.27</v>
       </c>
       <c r="J59" s="28" t="inlineStr">
         <is>
-          <t>중요공시 5건</t>
+          <t>네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K59" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2880,7 +2884,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>앤씨앤</t>
+          <t>이수페타시스</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2896,26 +2900,26 @@
         <v>0</v>
       </c>
       <c r="H60" s="29" t="n">
-        <v>5.18</v>
+        <v>5.02</v>
       </c>
       <c r="I60" s="29" t="n">
-        <v>35.4</v>
+        <v>10.88</v>
       </c>
       <c r="J60" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K60" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2923,7 +2927,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>서희건설</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2938,27 +2942,25 @@
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="27" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="I61" s="27" t="n">
-        <v>-2.16</v>
+      <c r="H61" s="29" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="I61" s="29" t="n">
+        <v>19.31</v>
       </c>
       <c r="J61" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K61" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K61" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2966,42 +2968,40 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>모아데이타</t>
+          <t>OCI홀딩스</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E62" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="27" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="I62" s="27" t="n">
-        <v>-13.38</v>
+      <c r="H62" s="29" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="I62" s="29" t="n">
+        <v>2.48</v>
       </c>
       <c r="J62" s="28" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K62" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K62" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3009,35 +3009,35 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>삼일씨엔에스</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E63" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F63" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="29" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="I63" s="29" t="n">
-        <v>9.49</v>
+        <v>0.48</v>
+      </c>
+      <c r="I63" s="27" t="n">
+        <v>-2.33</v>
       </c>
       <c r="J63" s="28" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K63" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
@@ -3134,22 +3134,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3165,22 +3165,22 @@
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H4" s="29" t="n">
@@ -3193,29 +3193,29 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H5" s="25" t="n"/>
@@ -3224,64 +3224,60 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="I6" s="29" t="n">
-        <v>5.46</v>
-      </c>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H6" s="25" t="n"/>
+      <c r="I6" s="25" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H7" s="25" t="n"/>
@@ -3297,22 +3293,22 @@
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H8" s="27" t="n">
@@ -3325,332 +3321,332 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>-9.710000000000001</v>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>3.76</v>
       </c>
       <c r="I9" s="29" t="n">
-        <v>17.08</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H10" s="25" t="n"/>
-      <c r="I10" s="25" t="n"/>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H10" s="27" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="I10" s="27" t="n">
+        <v>-0.67</v>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>대양금속</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H11" s="25" t="n"/>
-      <c r="I11" s="25" t="n"/>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>-14.85</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>-11.08</v>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H12" s="25" t="n"/>
-      <c r="I12" s="25" t="n"/>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H12" s="27" t="n">
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="I12" s="29" t="n">
+        <v>17.08</v>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H13" s="29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I13" s="29" t="n">
-        <v>6.03</v>
-      </c>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H13" s="25" t="n"/>
+      <c r="I13" s="25" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H14" s="27" t="n">
-        <v>-1.73</v>
-      </c>
-      <c r="I14" s="27" t="n">
-        <v>-5.09</v>
+        <v>-2.09</v>
+      </c>
+      <c r="I14" s="29" t="n">
+        <v>5.46</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H15" s="29" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="I15" s="29" t="n">
-        <v>15.23</v>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>-16.78</v>
+      </c>
+      <c r="I15" s="27" t="n">
+        <v>-32.79</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E16" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H16" s="27" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="I16" s="27" t="n">
-        <v>-1.52</v>
-      </c>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H17" s="29" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I17" s="27" t="n">
-        <v>-0.72</v>
-      </c>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H18" s="25" t="n"/>
@@ -3659,322 +3655,314 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>서희건설</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H19" s="27" t="n">
-        <v>-7.33</v>
+        <v>-1.3</v>
       </c>
       <c r="I19" s="27" t="n">
-        <v>-5.57</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H20" s="27" t="n">
-        <v>-1.78</v>
-      </c>
-      <c r="I20" s="27" t="n">
-        <v>-0.67</v>
-      </c>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H20" s="25" t="n"/>
+      <c r="I20" s="25" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>노타</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H21" s="27" t="n">
-        <v>-9.529999999999999</v>
+        <v>-1.31</v>
       </c>
       <c r="I21" s="29" t="n">
-        <v>21.21</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>케이쓰리아이</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H22" s="27" t="n">
-        <v>-5.76</v>
-      </c>
-      <c r="I22" s="27" t="n">
-        <v>-4.57</v>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H22" s="29" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="I22" s="29" t="n">
+        <v>26.25</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>비케이홀딩스</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H23" s="27" t="n">
-        <v>-15.35</v>
+        <v>-7.21</v>
       </c>
       <c r="I23" s="27" t="n">
-        <v>-17.21</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>삼성물산</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E24" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H24" s="29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I24" s="29" t="n">
-        <v>4.84</v>
+        <v>0.91</v>
+      </c>
+      <c r="I24" s="27" t="n">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>디에이테크놀로지</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E25" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H25" s="27" t="n">
-        <v>-4.12</v>
-      </c>
-      <c r="I25" s="29" t="n">
-        <v>7.98</v>
+        <v>-96.68000000000001</v>
+      </c>
+      <c r="I25" s="27" t="n">
+        <v>-96.68000000000001</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H26" s="27" t="n">
-        <v>-1.31</v>
-      </c>
-      <c r="I26" s="29" t="n">
-        <v>0.45</v>
-      </c>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H26" s="25" t="n"/>
+      <c r="I26" s="25" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>포스코퓨처엠</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H27" s="27" t="n">
-        <v>-2.96</v>
+        <v>-5.76</v>
       </c>
       <c r="I27" s="27" t="n">
-        <v>-4.24</v>
+        <v>-4.57</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>대양금속</t>
+          <t>삼성제약</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
@@ -3991,25 +3979,25 @@
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H28" s="27" t="n">
-        <v>-14.85</v>
+        <v>-2.66</v>
       </c>
       <c r="I28" s="27" t="n">
-        <v>-11.08</v>
+        <v>-8.380000000000001</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>디에이테크놀로지</t>
+          <t>삼일씨엔에스</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
@@ -4026,25 +4014,25 @@
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H29" s="27" t="n">
-        <v>-96.68000000000001</v>
-      </c>
-      <c r="I29" s="27" t="n">
-        <v>-96.68000000000001</v>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H29" s="29" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="I29" s="29" t="n">
+        <v>9.49</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
@@ -4061,12 +4049,12 @@
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H30" s="25" t="n"/>
@@ -4075,7 +4063,7 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
@@ -4092,25 +4080,21 @@
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H31" s="29" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="I31" s="29" t="n">
-        <v>9.4</v>
-      </c>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H31" s="25" t="n"/>
+      <c r="I31" s="25" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>삼성제약</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
@@ -4127,192 +4111,196 @@
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H32" s="27" t="n">
-        <v>-2.66</v>
-      </c>
-      <c r="I32" s="27" t="n">
-        <v>-8.380000000000001</v>
-      </c>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H32" s="25" t="n"/>
+      <c r="I32" s="25" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>스테이블코인</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E33" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H33" s="25" t="n"/>
-      <c r="I33" s="25" t="n"/>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H33" s="29" t="n">
+        <v>30.09</v>
+      </c>
+      <c r="I33" s="29" t="n">
+        <v>28.42</v>
+      </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>KB제34호스팩</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H34" s="27" t="n">
-        <v>-3.35</v>
-      </c>
-      <c r="I34" s="29" t="n">
-        <v>0.54</v>
+        <v>-0.37</v>
+      </c>
+      <c r="I34" s="27" t="n">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>케이쓰리아이</t>
+          <t>OCI홀딩스</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H35" s="29" t="n">
-        <v>11.96</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="I35" s="29" t="n">
-        <v>26.25</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H36" s="25" t="n"/>
-      <c r="I36" s="25" t="n"/>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H36" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I36" s="29" t="n">
+        <v>6.03</v>
+      </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E37" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H37" s="29" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="I37" s="29" t="n">
-        <v>19.31</v>
+        <v>0.41</v>
+      </c>
+      <c r="I37" s="27" t="n">
+        <v>-5.05</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>KB제34호스팩</t>
+          <t>노타</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4329,25 +4317,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H38" s="27" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="I38" s="27" t="n">
-        <v>-0.37</v>
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="I38" s="29" t="n">
+        <v>21.21</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
+          <t>더블유에스아이</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4364,25 +4352,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H39" s="27" t="n">
-        <v>-16.78</v>
-      </c>
-      <c r="I39" s="27" t="n">
-        <v>-32.79</v>
+        <v>-11.72</v>
+      </c>
+      <c r="I39" s="29" t="n">
+        <v>20.18</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4399,25 +4387,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H40" s="29" t="n">
-        <v>0.41</v>
+        <v>5.14</v>
       </c>
       <c r="I40" s="27" t="n">
-        <v>-5.05</v>
+        <v>-40.85</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>동국생명과학</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4434,25 +4422,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H41" s="29" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="I41" s="27" t="n">
-        <v>-40.85</v>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H41" s="27" t="n">
+        <v>-9.06</v>
+      </c>
+      <c r="I41" s="29" t="n">
+        <v>20.52</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>동국생명과학</t>
+          <t>비케이홀딩스</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4469,25 +4457,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H42" s="27" t="n">
-        <v>-9.06</v>
-      </c>
-      <c r="I42" s="29" t="n">
-        <v>20.52</v>
+        <v>-15.35</v>
+      </c>
+      <c r="I42" s="27" t="n">
+        <v>-17.21</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4504,25 +4492,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H43" s="27" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="I43" s="27" t="n">
-        <v>-1.66</v>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H43" s="29" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="I43" s="29" t="n">
+        <v>21.39</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>모아데이타</t>
+          <t>이수페타시스</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4539,25 +4527,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H44" s="27" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="I44" s="27" t="n">
-        <v>-13.38</v>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H44" s="29" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="I44" s="29" t="n">
+        <v>10.88</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4574,25 +4562,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H45" s="29" t="n">
-        <v>18.12</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="I45" s="29" t="n">
-        <v>21.39</v>
+        <v>19.31</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>토마토시스템</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4609,25 +4597,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H46" s="27" t="n">
-        <v>-3.31</v>
-      </c>
-      <c r="I46" s="27" t="n">
-        <v>-1.2</v>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H46" s="29" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="I46" s="29" t="n">
+        <v>65.84999999999999</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>삼일씨엔에스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4644,25 +4632,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H47" s="29" t="n">
-        <v>5.45</v>
+        <v>12.59</v>
       </c>
       <c r="I47" s="29" t="n">
-        <v>9.49</v>
+        <v>37.27</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>서희건설</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4679,25 +4667,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H48" s="27" t="n">
-        <v>-1.3</v>
+        <v>-2.96</v>
       </c>
       <c r="I48" s="27" t="n">
-        <v>-2.16</v>
+        <v>-4.24</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>앤씨앤</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4714,25 +4702,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H49" s="29" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="I49" s="29" t="n">
-        <v>35.4</v>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H49" s="27" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="I49" s="27" t="n">
+        <v>-1.91</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>토마토시스템</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4749,25 +4737,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H50" s="29" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="I50" s="29" t="n">
-        <v>65.84999999999999</v>
+        <v>0.48</v>
+      </c>
+      <c r="I50" s="27" t="n">
+        <v>-2.33</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4784,25 +4772,25 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H51" s="27" t="n">
-        <v>-1.91</v>
-      </c>
-      <c r="I51" s="27" t="n">
-        <v>-1.91</v>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H51" s="29" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="I51" s="29" t="n">
+        <v>2.62</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -4819,19 +4807,19 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H52" s="29" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="I52" s="29" t="n">
-        <v>2.62</v>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H52" s="27" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="I52" s="27" t="n">
+        <v>-2.59</v>
       </c>
     </row>
   </sheetData>
@@ -4915,19 +4903,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4946,19 +4934,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4984,12 +4972,12 @@
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5008,19 +4996,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5039,19 +5027,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5070,19 +5058,19 @@
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5094,26 +5082,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5125,92 +5113,100 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="35" t="inlineStr">
         <is>
+          <t>엔터</t>
+        </is>
+      </c>
+      <c r="B10" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="G10" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F11" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="G11" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
           <t>인공지능</t>
         </is>
       </c>
-      <c r="B10" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="36" t="n">
-        <v>11</v>
-      </c>
-      <c r="D10" s="36" t="n">
-        <v>11</v>
-      </c>
-      <c r="E10" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="F10" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G10" s="37" t="inlineStr">
+      <c r="B12" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="E12" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F12" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="G12" s="37" t="inlineStr">
         <is>
           <t>⚡ 관심</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>이차전지</t>
-        </is>
-      </c>
-      <c r="B11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="28" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G11" s="28" t="inlineStr"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>AI반도체</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="28" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G12" s="28" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -5237,7 +5233,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5264,7 +5260,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5291,7 +5287,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -261,11 +261,11 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-26 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-27 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-26) 상위: 반도체  점수 55.0점</t>
+          <t>⚡ 최신(2026-09-27) 상위: 반도체  점수 43.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-26) 상위: 삼성전자  점수 29.0점</t>
+          <t>⚡ 최신(2026-09-27) 상위: 삼성전자  점수 35.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-26) 상위: 인공지능  점수 18.0점</t>
+          <t>⚡ 최신(2026-09-27) 상위: 게임  점수 13.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -986,11 +986,11 @@
         <v>3.24</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>13.02</v>
+        <v>11.91</v>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1033,19 +1033,19 @@
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>Google 급상승 검색어 등장 (KR) / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,14 +1053,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
@@ -1131,7 +1131,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1158,7 +1158,7 @@
         <v>-0.47</v>
       </c>
       <c r="I19" s="18" t="n">
-        <v>7.69</v>
+        <v>6.6</v>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1198,12 +1198,12 @@
       <c r="H20" s="18" t="n">
         <v>3.76</v>
       </c>
-      <c r="I20" s="18" t="n">
-        <v>15.23</v>
+      <c r="I20" s="19" t="n">
+        <v>-2.7</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +50%</t>
+          <t>중요공시 3건 / 중요공시 3일 +50% / 중요공시 7일 +50%</t>
         </is>
       </c>
       <c r="K20" s="17" t="inlineStr">
@@ -1215,7 +1215,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1223,42 +1223,42 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="19" t="n">
-        <v>-9.710000000000001</v>
-      </c>
-      <c r="I21" s="18" t="n">
-        <v>17.08</v>
+      <c r="H21" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v/>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +73% / 중요공시 4건 / 중요공시 3일 +100%</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1266,42 +1266,42 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>대양금속</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
         <v>7</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="19" t="n">
-        <v>-14.85</v>
-      </c>
-      <c r="I22" s="19" t="n">
-        <v>-11.08</v>
+      <c r="H22" s="18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>5.49</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +56% / 중요공시 3건 / 중요공시 3일 +200%</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1328,7 +1328,7 @@
         <v>-1.78</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>-0.67</v>
+        <v>-5.1</v>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
@@ -1342,52 +1342,50 @@
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="n">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>태양광</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="15" t="n">
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>LG전자</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="22" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="I24" s="23" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="J24" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K24" s="24" t="n">
         <v/>
-      </c>
-      <c r="I24" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J24" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B25" s="20" t="n">
@@ -1395,7 +1393,7 @@
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D25" s="20" t="n">
@@ -1410,18 +1408,18 @@
       <c r="G25" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="22" t="n">
-        <v>-16.78</v>
-      </c>
-      <c r="I25" s="22" t="n">
-        <v>-32.79</v>
-      </c>
-      <c r="J25" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +949% / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K25" s="23" t="inlineStr">
+      <c r="H25" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I25" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J25" s="24" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K25" s="24" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -1430,7 +1428,7 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B26" s="20" t="n">
@@ -1438,14 +1436,14 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="D26" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F26" s="20" t="n">
         <v>0</v>
@@ -1454,24 +1452,26 @@
         <v>0</v>
       </c>
       <c r="H26" s="22" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="I26" s="24" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="J26" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K26" s="23" t="n">
-        <v/>
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="I26" s="23" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="J26" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +80% / 중요공시 4건</t>
+        </is>
+      </c>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B27" s="20" t="n">
@@ -1479,14 +1479,14 @@
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>케이쓰리아이</t>
         </is>
       </c>
       <c r="D27" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F27" s="20" t="n">
         <v>0</v>
@@ -1494,27 +1494,27 @@
       <c r="G27" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I27" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J27" s="23" t="inlineStr">
-        <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K27" s="23" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H27" s="23" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="I27" s="23" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="J27" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +70% / 중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B28" s="20" t="n">
@@ -1522,14 +1522,14 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>대양금속</t>
         </is>
       </c>
       <c r="D28" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F28" s="20" t="n">
         <v>0</v>
@@ -1537,25 +1537,27 @@
       <c r="G28" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I28" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J28" s="23" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K28" s="23" t="n">
-        <v/>
+      <c r="H28" s="22" t="n">
+        <v>-14.85</v>
+      </c>
+      <c r="I28" s="22" t="n">
+        <v>-12.69</v>
+      </c>
+      <c r="J28" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +60% / 중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B29" s="20" t="n">
@@ -1563,7 +1565,7 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>케이쓰리아이</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="D29" s="20" t="n">
@@ -1578,27 +1580,27 @@
       <c r="G29" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="24" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="I29" s="24" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="J29" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +60% / 중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K29" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+      <c r="H29" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I29" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J29" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1606,42 +1608,40 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>서희건설</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
         <v>5</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G30" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="I30" s="22" t="n">
-        <v>-2.16</v>
-      </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 3일 +50%</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+        <v>-1.31</v>
+      </c>
+      <c r="I30" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K30" s="24" t="n">
+        <v/>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>디에이테크놀로지</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F31" s="20" t="n">
         <v>0</v>
@@ -1665,26 +1665,26 @@
         <v>0</v>
       </c>
       <c r="H31" s="22" t="n">
-        <v>-7.21</v>
+        <v>-96.68000000000001</v>
       </c>
       <c r="I31" s="22" t="n">
-        <v>-1.37</v>
-      </c>
-      <c r="J31" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K31" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>-96.68000000000001</v>
+      </c>
+      <c r="J31" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +628% / 중요공시 2건</t>
+        </is>
+      </c>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1692,14 +1692,14 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F32" s="20" t="n">
         <v>0</v>
@@ -1713,21 +1713,19 @@
       <c r="I32" s="20" t="n">
         <v/>
       </c>
-      <c r="J32" s="23" t="inlineStr">
-        <is>
-          <t>Google 급상승 검색어 등장 (US)</t>
-        </is>
-      </c>
-      <c r="K32" s="23" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
+      <c r="J32" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K32" s="24" t="n">
+        <v/>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1735,40 +1733,42 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H33" s="22" t="n">
-        <v>-1.31</v>
-      </c>
-      <c r="I33" s="24" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J33" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K33" s="23" t="n">
-        <v/>
+        <v>-0.11</v>
+      </c>
+      <c r="I33" s="22" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="J33" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1776,14 +1776,14 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>삼성제약</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>0</v>
@@ -1791,25 +1791,27 @@
       <c r="G34" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I34" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J34" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="n">
-        <v/>
+      <c r="H34" s="22" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="I34" s="22" t="n">
+        <v>-6.91</v>
+      </c>
+      <c r="J34" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1817,7 +1819,7 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>디에이테크놀로지</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
@@ -1832,27 +1834,25 @@
       <c r="G35" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="22" t="n">
-        <v>-96.68000000000001</v>
-      </c>
-      <c r="I35" s="22" t="n">
-        <v>-96.68000000000001</v>
-      </c>
-      <c r="J35" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +593% / 중요공시 2건</t>
-        </is>
-      </c>
-      <c r="K35" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
+      <c r="H35" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I35" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J35" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K35" s="24" t="n">
+        <v/>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
@@ -1881,316 +1881,322 @@
       <c r="I36" s="20" t="n">
         <v/>
       </c>
-      <c r="J36" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="n">
-        <v/>
+      <c r="J36" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="B37" s="20" t="n">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B37" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="C37" s="21" t="inlineStr">
-        <is>
-          <t>삼일씨엔에스</t>
-        </is>
-      </c>
-      <c r="D37" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E37" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H37" s="24" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="I37" s="24" t="n">
-        <v>9.49</v>
-      </c>
-      <c r="J37" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K37" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>한국제17호스팩</t>
+        </is>
+      </c>
+      <c r="D37" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="27" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="I37" s="27" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="J37" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +4732%</t>
+        </is>
+      </c>
+      <c r="K37" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="n">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B38" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="C38" s="21" t="inlineStr">
-        <is>
-          <t>비에이치아이</t>
-        </is>
-      </c>
-      <c r="D38" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E38" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H38" s="22" t="n">
-        <v>-5.76</v>
-      </c>
-      <c r="I38" s="22" t="n">
-        <v>-4.57</v>
-      </c>
-      <c r="J38" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K38" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>KB제34호스팩</t>
+        </is>
+      </c>
+      <c r="D38" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="27" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="I38" s="27" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="J38" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +3142%</t>
+        </is>
+      </c>
+      <c r="K38" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="n">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B39" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="C39" s="21" t="inlineStr">
-        <is>
-          <t>삼성제약</t>
-        </is>
-      </c>
-      <c r="D39" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E39" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="22" t="n">
-        <v>-2.66</v>
-      </c>
-      <c r="I39" s="22" t="n">
-        <v>-8.380000000000001</v>
-      </c>
-      <c r="J39" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K39" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>네오사피엔스</t>
+        </is>
+      </c>
+      <c r="D39" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="27" t="n">
+        <v>-16.78</v>
+      </c>
+      <c r="I39" s="27" t="n">
+        <v>-32.79</v>
+      </c>
+      <c r="J39" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +961%</t>
+        </is>
+      </c>
+      <c r="K39" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="B40" s="20" t="n">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B40" s="25" t="n">
         <v>27</v>
       </c>
-      <c r="C40" s="21" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E40" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="24" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I40" s="22" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="J40" s="23" t="inlineStr">
-        <is>
-          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K40" s="23" t="inlineStr">
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>동국생명과학</t>
+        </is>
+      </c>
+      <c r="D40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="27" t="n">
+        <v>-9.06</v>
+      </c>
+      <c r="I40" s="29" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="J40" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +618%</t>
+        </is>
+      </c>
+      <c r="K40" s="28" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="B41" s="20" t="n">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="n">
         <v>28</v>
       </c>
-      <c r="C41" s="21" t="inlineStr">
-        <is>
-          <t>방산</t>
-        </is>
-      </c>
-      <c r="D41" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I41" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J41" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K41" s="23" t="n">
-        <v/>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>토마토시스템</t>
+        </is>
+      </c>
+      <c r="D41" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="29" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="I41" s="29" t="n">
+        <v>71.98999999999999</v>
+      </c>
+      <c r="J41" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +524%</t>
+        </is>
+      </c>
+      <c r="K41" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="n">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="n">
         <v>29</v>
       </c>
-      <c r="C42" s="21" t="inlineStr">
-        <is>
-          <t>엔터</t>
-        </is>
-      </c>
-      <c r="D42" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E42" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F42" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I42" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J42" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K42" s="23" t="inlineStr">
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>노타</t>
+        </is>
+      </c>
+      <c r="D42" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="27" t="n">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="I42" s="29" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="J42" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +176%</t>
+        </is>
+      </c>
+      <c r="K42" s="28" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="B43" s="20" t="n">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="C43" s="21" t="inlineStr">
-        <is>
-          <t>스테이블코인</t>
-        </is>
-      </c>
-      <c r="D43" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E43" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F43" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I43" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J43" s="23" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K43" s="23" t="n">
-        <v/>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>삼기에너지솔루션즈</t>
+        </is>
+      </c>
+      <c r="D43" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="29" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="I43" s="29" t="n">
+        <v>20.69</v>
+      </c>
+      <c r="J43" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +168%</t>
+        </is>
+      </c>
+      <c r="K43" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -2198,7 +2204,7 @@
       </c>
       <c r="C44" s="26" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="D44" s="25" t="n">
@@ -2213,15 +2219,15 @@
       <c r="G44" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="27" t="n">
-        <v>-1.91</v>
-      </c>
-      <c r="I44" s="27" t="n">
-        <v>-1.91</v>
+      <c r="H44" s="29" t="n">
+        <v>30.09</v>
+      </c>
+      <c r="I44" s="29" t="n">
+        <v>25.86</v>
       </c>
       <c r="J44" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +4696%</t>
+          <t>네이버 검색 당일 +143%</t>
         </is>
       </c>
       <c r="K44" s="28" t="inlineStr">
@@ -2233,7 +2239,7 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -2241,7 +2247,7 @@
       </c>
       <c r="C45" s="26" t="inlineStr">
         <is>
-          <t>KB제34호스팩</t>
+          <t>더블유에스아이</t>
         </is>
       </c>
       <c r="D45" s="25" t="n">
@@ -2257,14 +2263,14 @@
         <v>0</v>
       </c>
       <c r="H45" s="27" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="I45" s="27" t="n">
-        <v>-0.37</v>
+        <v>-11.72</v>
+      </c>
+      <c r="I45" s="29" t="n">
+        <v>17.69</v>
       </c>
       <c r="J45" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +3123%</t>
+          <t>네이버 검색 당일 +116%</t>
         </is>
       </c>
       <c r="K45" s="28" t="inlineStr">
@@ -2276,7 +2282,7 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -2284,7 +2290,7 @@
       </c>
       <c r="C46" s="26" t="inlineStr">
         <is>
-          <t>동국생명과학</t>
+          <t>에이에프더블류</t>
         </is>
       </c>
       <c r="D46" s="25" t="n">
@@ -2299,27 +2305,27 @@
       <c r="G46" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="27" t="n">
-        <v>-9.06</v>
-      </c>
-      <c r="I46" s="29" t="n">
-        <v>20.52</v>
+      <c r="H46" s="29" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I46" s="27" t="n">
+        <v>-7.02</v>
       </c>
       <c r="J46" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +596%</t>
+          <t>네이버 검색 당일 +53% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K46" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -2327,7 +2333,7 @@
       </c>
       <c r="C47" s="26" t="inlineStr">
         <is>
-          <t>토마토시스템</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="D47" s="25" t="n">
@@ -2343,26 +2349,24 @@
         <v>0</v>
       </c>
       <c r="H47" s="29" t="n">
-        <v>12.07</v>
+        <v>6.52</v>
       </c>
       <c r="I47" s="29" t="n">
-        <v>65.84999999999999</v>
+        <v>2.62</v>
       </c>
       <c r="J47" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +507%</t>
-        </is>
-      </c>
-      <c r="K47" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K47" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -2370,7 +2374,7 @@
       </c>
       <c r="C48" s="26" t="inlineStr">
         <is>
-          <t>노타</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
@@ -2385,27 +2389,27 @@
       <c r="G48" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="27" t="n">
-        <v>-9.529999999999999</v>
-      </c>
-      <c r="I48" s="29" t="n">
-        <v>21.21</v>
+      <c r="H48" s="29" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="I48" s="27" t="n">
+        <v>-43.87</v>
       </c>
       <c r="J48" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +166%</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K48" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -2413,7 +2417,7 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>비케이홀딩스</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
@@ -2428,27 +2432,27 @@
       <c r="G49" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="29" t="n">
-        <v>18.12</v>
-      </c>
-      <c r="I49" s="29" t="n">
-        <v>21.39</v>
+      <c r="H49" s="27" t="n">
+        <v>-15.35</v>
+      </c>
+      <c r="I49" s="27" t="n">
+        <v>-17.3</v>
       </c>
       <c r="J49" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +153%</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K49" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2456,7 +2460,7 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -2472,26 +2476,26 @@
         <v>0</v>
       </c>
       <c r="H50" s="29" t="n">
-        <v>30.09</v>
-      </c>
-      <c r="I50" s="29" t="n">
-        <v>28.42</v>
+        <v>0.41</v>
+      </c>
+      <c r="I50" s="27" t="n">
+        <v>-6.74</v>
       </c>
       <c r="J50" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +120%</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K50" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2499,7 +2503,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>더블유에스아이</t>
+          <t>서희건설</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2515,26 +2519,26 @@
         <v>0</v>
       </c>
       <c r="H51" s="27" t="n">
-        <v>-11.72</v>
-      </c>
-      <c r="I51" s="29" t="n">
-        <v>20.18</v>
+        <v>-1.3</v>
+      </c>
+      <c r="I51" s="27" t="n">
+        <v>-3.4</v>
       </c>
       <c r="J51" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +110%</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K51" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2542,40 +2546,42 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E52" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F52" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G52" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="29" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="I52" s="29" t="n">
-        <v>2.62</v>
+      <c r="H52" s="27" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="I52" s="27" t="n">
+        <v>-5.04</v>
       </c>
       <c r="J52" s="28" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K52" s="28" t="n">
-        <v/>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K52" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2583,7 +2589,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2598,27 +2604,25 @@
       <c r="G53" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I53" s="29" t="n">
-        <v>6.03</v>
+      <c r="H53" s="27" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="I53" s="27" t="n">
+        <v>-2.06</v>
       </c>
       <c r="J53" s="28" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K53" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K53" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2626,7 +2630,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2641,27 +2645,27 @@
       <c r="G54" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="29" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="I54" s="27" t="n">
-        <v>-40.85</v>
+      <c r="H54" s="25" t="n">
+        <v/>
+      </c>
+      <c r="I54" s="25" t="n">
+        <v/>
       </c>
       <c r="J54" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K54" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2669,7 +2673,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>비케이홀딩스</t>
+          <t>OCI홀딩스</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2684,27 +2688,25 @@
       <c r="G55" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="27" t="n">
-        <v>-15.35</v>
-      </c>
-      <c r="I55" s="27" t="n">
-        <v>-17.21</v>
+      <c r="H55" s="29" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="I55" s="29" t="n">
+        <v>1.72</v>
       </c>
       <c r="J55" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K55" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K55" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2712,7 +2714,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2728,26 +2730,26 @@
         <v>0</v>
       </c>
       <c r="H56" s="29" t="n">
-        <v>0.41</v>
+        <v>0.48</v>
       </c>
       <c r="I56" s="27" t="n">
-        <v>-5.05</v>
+        <v>-0.88</v>
       </c>
       <c r="J56" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K56" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2755,42 +2757,42 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E57" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G57" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="27" t="n">
-        <v>-1.19</v>
+        <v>-0.32</v>
       </c>
       <c r="I57" s="27" t="n">
-        <v>-2.59</v>
+        <v>-2.36</v>
       </c>
       <c r="J57" s="28" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K57" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2798,7 +2800,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>포스코퓨처엠</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2813,27 +2815,25 @@
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="27" t="n">
-        <v>-2.96</v>
-      </c>
-      <c r="I58" s="27" t="n">
-        <v>-4.24</v>
+      <c r="H58" s="29" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="I58" s="29" t="n">
+        <v>15.9</v>
       </c>
       <c r="J58" s="28" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K58" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K58" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>대성하이텍</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2857,26 +2857,24 @@
         <v>0</v>
       </c>
       <c r="H59" s="29" t="n">
-        <v>12.59</v>
+        <v>15.65</v>
       </c>
       <c r="I59" s="29" t="n">
-        <v>37.27</v>
+        <v>19.29</v>
       </c>
       <c r="J59" s="28" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K59" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K59" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2884,7 +2882,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>이수페타시스</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2899,27 +2897,25 @@
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="29" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I60" s="29" t="n">
-        <v>10.88</v>
+      <c r="H60" s="25" t="n">
+        <v/>
+      </c>
+      <c r="I60" s="25" t="n">
+        <v/>
       </c>
       <c r="J60" s="28" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K60" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K60" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2927,7 +2923,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2942,15 +2938,15 @@
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="29" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="I61" s="29" t="n">
-        <v>19.31</v>
+      <c r="H61" s="27" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="I61" s="27" t="n">
+        <v>-4.28</v>
       </c>
       <c r="J61" s="28" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
+          <t>한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K61" s="28" t="n">
@@ -2960,7 +2956,7 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2968,7 +2964,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>OCI홀딩스</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2984,10 +2980,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="29" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="I62" s="29" t="n">
-        <v>2.48</v>
+        <v>0.38</v>
+      </c>
+      <c r="I62" s="27" t="n">
+        <v>-5.51</v>
       </c>
       <c r="J62" s="28" t="inlineStr">
         <is>
@@ -3001,7 +2997,7 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3009,7 +3005,7 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
@@ -3024,21 +3020,19 @@
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="29" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="I63" s="27" t="n">
-        <v>-2.33</v>
+      <c r="H63" s="27" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="I63" s="29" t="n">
+        <v>20.99</v>
       </c>
       <c r="J63" s="28" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K63" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K63" s="28" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3134,22 +3128,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3165,57 +3159,57 @@
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H4" s="29" t="n">
         <v>3.24</v>
       </c>
       <c r="I4" s="29" t="n">
-        <v>13.02</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H5" s="25" t="n"/>
@@ -3224,29 +3218,29 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H6" s="25" t="n"/>
@@ -3255,7 +3249,7 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
@@ -3272,12 +3266,12 @@
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H7" s="25" t="n"/>
@@ -3303,25 +3297,25 @@
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H8" s="27" t="n">
         <v>-0.47</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>7.69</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
@@ -3338,60 +3332,56 @@
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H9" s="29" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="I9" s="29" t="n">
-        <v>15.23</v>
-      </c>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H9" s="25" t="n"/>
+      <c r="I9" s="25" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H10" s="27" t="n">
-        <v>-1.78</v>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H10" s="29" t="n">
+        <v>3.76</v>
       </c>
       <c r="I10" s="27" t="n">
-        <v>-0.67</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>대양금속</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
@@ -3408,25 +3398,25 @@
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H11" s="27" t="n">
-        <v>-14.85</v>
+        <v>-1.78</v>
       </c>
       <c r="I11" s="27" t="n">
-        <v>-11.08</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
@@ -3443,56 +3433,60 @@
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H12" s="27" t="n">
-        <v>-9.710000000000001</v>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H12" s="29" t="n">
+        <v>1.2</v>
       </c>
       <c r="I12" s="29" t="n">
-        <v>17.08</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H13" s="25" t="n"/>
-      <c r="I13" s="25" t="n"/>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H13" s="27" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="I13" s="29" t="n">
+        <v>5.57</v>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -3509,113 +3503,113 @@
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H14" s="27" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="I14" s="29" t="n">
-        <v>5.46</v>
-      </c>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="25" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
+          <t>대양금속</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H15" s="27" t="n">
-        <v>-16.78</v>
+        <v>-14.85</v>
       </c>
       <c r="I15" s="27" t="n">
-        <v>-32.79</v>
+        <v>-12.69</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H16" s="25" t="n"/>
-      <c r="I16" s="25" t="n"/>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="I16" s="29" t="n">
+        <v>13.26</v>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H17" s="25" t="n"/>
@@ -3624,7 +3618,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -3641,21 +3635,25 @@
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H18" s="25" t="n"/>
-      <c r="I18" s="25" t="n"/>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="I18" s="25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>서희건설</t>
+          <t>케이쓰리아이</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -3672,161 +3670,161 @@
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H19" s="27" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="I19" s="27" t="n">
-        <v>-2.16</v>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H19" s="29" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="I19" s="29" t="n">
+        <v>23.71</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>디에이테크놀로지</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H20" s="25" t="n"/>
-      <c r="I20" s="25" t="n"/>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>-96.68000000000001</v>
+      </c>
+      <c r="I20" s="27" t="n">
+        <v>-96.68000000000001</v>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>삼성제약</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H21" s="27" t="n">
-        <v>-1.31</v>
-      </c>
-      <c r="I21" s="29" t="n">
-        <v>0.45</v>
+        <v>-2.66</v>
+      </c>
+      <c r="I21" s="27" t="n">
+        <v>-6.91</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>케이쓰리아이</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H22" s="29" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="I22" s="29" t="n">
-        <v>26.25</v>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H22" s="27" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="I22" s="27" t="n">
+        <v>-1.77</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H23" s="27" t="n">
-        <v>-7.21</v>
-      </c>
-      <c r="I23" s="27" t="n">
-        <v>-1.37</v>
-      </c>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="25" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -3843,25 +3841,21 @@
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H24" s="29" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I24" s="27" t="n">
-        <v>-0.72</v>
-      </c>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H24" s="25" t="n"/>
+      <c r="I24" s="25" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>디에이테크놀로지</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
@@ -3878,254 +3872,266 @@
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H25" s="27" t="n">
-        <v>-96.68000000000001</v>
-      </c>
-      <c r="I25" s="27" t="n">
-        <v>-96.68000000000001</v>
-      </c>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H25" s="25" t="n"/>
+      <c r="I25" s="25" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H26" s="25" t="n"/>
-      <c r="I26" s="25" t="n"/>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H26" s="27" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="I26" s="27" t="n">
+        <v>-2.36</v>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H27" s="27" t="n">
-        <v>-5.76</v>
-      </c>
-      <c r="I27" s="27" t="n">
-        <v>-4.57</v>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H27" s="29" t="n">
+        <v>30.09</v>
+      </c>
+      <c r="I27" s="29" t="n">
+        <v>25.86</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>삼성제약</t>
+          <t>KB제34호스팩</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H28" s="27" t="n">
-        <v>-2.66</v>
+        <v>-0.37</v>
       </c>
       <c r="I28" s="27" t="n">
-        <v>-8.380000000000001</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>삼일씨엔에스</t>
+          <t>OCI홀딩스</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H29" s="29" t="n">
-        <v>5.45</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="I29" s="29" t="n">
-        <v>9.49</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>스테이블코인</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H30" s="25" t="n"/>
-      <c r="I30" s="25" t="n"/>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H30" s="29" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="I30" s="29" t="n">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H31" s="25" t="n"/>
-      <c r="I31" s="25" t="n"/>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H31" s="27" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="I31" s="27" t="n">
+        <v>-4.28</v>
+      </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H32" s="25" t="n"/>
-      <c r="I32" s="25" t="n"/>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H32" s="27" t="n">
+        <v>-16.78</v>
+      </c>
+      <c r="I32" s="27" t="n">
+        <v>-32.79</v>
+      </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
@@ -4142,25 +4148,25 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H33" s="29" t="n">
-        <v>30.09</v>
-      </c>
-      <c r="I33" s="29" t="n">
-        <v>28.42</v>
+        <v>0.41</v>
+      </c>
+      <c r="I33" s="27" t="n">
+        <v>-6.74</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>KB제34호스팩</t>
+          <t>노타</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
@@ -4177,25 +4183,25 @@
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H34" s="27" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="I34" s="27" t="n">
-        <v>-0.37</v>
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="I34" s="29" t="n">
+        <v>17.85</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>OCI홀딩스</t>
+          <t>대성하이텍</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
@@ -4212,25 +4218,25 @@
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H35" s="29" t="n">
-        <v>9.720000000000001</v>
+        <v>15.65</v>
       </c>
       <c r="I35" s="29" t="n">
-        <v>2.48</v>
+        <v>19.29</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>더블유에스아이</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
@@ -4247,25 +4253,25 @@
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H36" s="29" t="n">
-        <v>1.2</v>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H36" s="27" t="n">
+        <v>-11.72</v>
       </c>
       <c r="I36" s="29" t="n">
-        <v>6.03</v>
+        <v>17.69</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
@@ -4282,25 +4288,25 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H37" s="29" t="n">
-        <v>0.41</v>
+        <v>5.14</v>
       </c>
       <c r="I37" s="27" t="n">
-        <v>-5.05</v>
+        <v>-43.87</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>노타</t>
+          <t>동국생명과학</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4317,25 +4323,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H38" s="27" t="n">
-        <v>-9.529999999999999</v>
+        <v>-9.06</v>
       </c>
       <c r="I38" s="29" t="n">
-        <v>21.21</v>
+        <v>18.45</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>더블유에스아이</t>
+          <t>비케이홀딩스</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4352,25 +4358,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H39" s="27" t="n">
-        <v>-11.72</v>
-      </c>
-      <c r="I39" s="29" t="n">
-        <v>20.18</v>
+        <v>-15.35</v>
+      </c>
+      <c r="I39" s="27" t="n">
+        <v>-17.3</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4387,25 +4393,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H40" s="29" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="I40" s="27" t="n">
-        <v>-40.85</v>
+        <v>18.12</v>
+      </c>
+      <c r="I40" s="29" t="n">
+        <v>20.69</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>동국생명과학</t>
+          <t>서희건설</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4422,25 +4428,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H41" s="27" t="n">
-        <v>-9.06</v>
-      </c>
-      <c r="I41" s="29" t="n">
-        <v>20.52</v>
+        <v>-1.3</v>
+      </c>
+      <c r="I41" s="27" t="n">
+        <v>-3.4</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>비케이홀딩스</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4457,25 +4463,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H42" s="27" t="n">
-        <v>-15.35</v>
-      </c>
-      <c r="I42" s="27" t="n">
-        <v>-17.21</v>
+        <v>-0.31</v>
+      </c>
+      <c r="I42" s="29" t="n">
+        <v>20.99</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>에이에프더블류</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4492,25 +4498,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H43" s="29" t="n">
-        <v>18.12</v>
-      </c>
-      <c r="I43" s="29" t="n">
-        <v>21.39</v>
+        <v>19.1</v>
+      </c>
+      <c r="I43" s="27" t="n">
+        <v>-7.02</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>이수페타시스</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4527,25 +4533,21 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H44" s="29" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I44" s="29" t="n">
-        <v>10.88</v>
-      </c>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H44" s="25" t="n"/>
+      <c r="I44" s="25" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4562,20 +4564,16 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H45" s="29" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="I45" s="29" t="n">
-        <v>19.31</v>
-      </c>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H45" s="25" t="n"/>
+      <c r="I45" s="25" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
@@ -4597,25 +4595,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H46" s="29" t="n">
         <v>12.07</v>
       </c>
       <c r="I46" s="29" t="n">
-        <v>65.84999999999999</v>
+        <v>71.98999999999999</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4632,25 +4630,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H47" s="29" t="n">
-        <v>12.59</v>
-      </c>
-      <c r="I47" s="29" t="n">
-        <v>37.27</v>
+        <v>0.38</v>
+      </c>
+      <c r="I47" s="27" t="n">
+        <v>-5.51</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>포스코퓨처엠</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4667,25 +4665,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H48" s="27" t="n">
-        <v>-2.96</v>
+        <v>-1.91</v>
       </c>
       <c r="I48" s="27" t="n">
-        <v>-4.24</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4702,25 +4700,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H49" s="27" t="n">
-        <v>-1.91</v>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H49" s="29" t="n">
+        <v>0.48</v>
       </c>
       <c r="I49" s="27" t="n">
-        <v>-1.91</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4737,25 +4735,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H50" s="29" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="I50" s="27" t="n">
-        <v>-2.33</v>
+        <v>6.52</v>
+      </c>
+      <c r="I50" s="29" t="n">
+        <v>2.62</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4772,25 +4770,25 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H51" s="29" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="I51" s="29" t="n">
-        <v>2.62</v>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H51" s="27" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="I51" s="27" t="n">
+        <v>-5.04</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -4807,19 +4805,19 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H52" s="27" t="n">
-        <v>-1.19</v>
+        <v>-1.38</v>
       </c>
       <c r="I52" s="27" t="n">
-        <v>-2.59</v>
+        <v>-2.06</v>
       </c>
     </row>
   </sheetData>
@@ -4903,19 +4901,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4941,12 +4939,12 @@
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4958,26 +4956,26 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B5" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -4996,19 +4994,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5027,19 +5025,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5058,19 +5056,19 @@
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5096,12 +5094,12 @@
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5127,12 +5125,12 @@
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G10" s="37" t="inlineStr">
@@ -5144,26 +5142,26 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B11" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="36" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E11" s="36" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F11" s="37" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G11" s="37" t="inlineStr">
@@ -5175,65 +5173,69 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="35" t="inlineStr">
         <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B12" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F12" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G12" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
           <t>인공지능</t>
         </is>
       </c>
-      <c r="B12" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>18</v>
-      </c>
-      <c r="D12" s="36" t="n">
-        <v>18</v>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="F12" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="G12" s="37" t="inlineStr">
+      <c r="B13" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F13" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G13" s="37" t="inlineStr">
         <is>
           <t>⚡ 관심</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
-        <is>
-          <t>이차전지</t>
-        </is>
-      </c>
-      <c r="B13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="28" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G13" s="28" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5260,7 +5262,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5287,7 +5289,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5314,7 +5316,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5341,7 +5343,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5368,7 +5370,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -57,13 +57,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="002563EB"/>
+      <color rgb="00E53935"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00E53935"/>
+      <color rgb="002563EB"/>
       <sz val="10"/>
     </font>
     <font>
@@ -258,13 +258,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-29 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-30 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-29) 상위: 반도체  점수 62.0점</t>
+          <t>⚡ 최신(2026-09-30) 상위: 반도체  점수 88.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-29) 상위: 바이오  점수 26.0점</t>
+          <t>⚡ 최신(2026-09-30) 상위: 인공지능  점수 29.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-29) 상위: 삼성전자  점수 24.0점</t>
+          <t>⚡ 최신(2026-09-30) 상위: 삼성전자  점수 20.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -967,14 +967,14 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1026,14 +1026,14 @@
         <v>0</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>-5.76</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>-1.82</v>
+        <v>1.85</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,14 +1053,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1068,27 +1068,27 @@
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="19" t="n">
-        <v>27.86</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <v>24.45</v>
+      <c r="H17" s="18" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>8.24</v>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
@@ -1111,27 +1111,25 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="18" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="I18" s="19" t="n">
-        <v>4.12</v>
+      <c r="H18" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v/>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1143,10 +1141,10 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1162,7 +1160,7 @@
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="inlineStr">
@@ -1174,7 +1172,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1182,14 +1180,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1205,7 +1203,7 @@
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K20" s="17" t="inlineStr">
@@ -1217,7 +1215,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1229,10 +1227,10 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1241,14 +1239,14 @@
         <v>0</v>
       </c>
       <c r="H21" s="18" t="n">
-        <v>-5.48</v>
-      </c>
-      <c r="I21" s="18" t="n">
-        <v>-6.28</v>
+        <v>1.65</v>
+      </c>
+      <c r="I21" s="19" t="n">
+        <v>-4.74</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
@@ -1260,7 +1258,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1268,14 +1266,14 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1283,15 +1281,15 @@
       <c r="G22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v/>
+      <c r="H22" s="18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>6.4</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K22" s="17" t="n">
@@ -1301,7 +1299,7 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1309,14 +1307,14 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F23" s="15" t="n">
         <v>0</v>
@@ -1332,19 +1330,17 @@
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1352,40 +1348,42 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>OCI홀딩스</t>
+          <t>모아데이타</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24" s="19" t="n">
-        <v>12.35</v>
+        <v>-5.96</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>20.21</v>
+        <v>-22.05</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="n">
-        <v/>
+          <t>중요공시 4건 / 중요공시 3일 +100% / 중요공시 7일 +300%</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1393,42 +1391,42 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F25" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="I25" s="18" t="n">
-        <v>-2.07</v>
+        <v>0.62</v>
+      </c>
+      <c r="I25" s="19" t="n">
+        <v>-1.49</v>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 2건 / 중요공시 7일 +100% / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K25" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1436,30 +1434,30 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>모아데이타</t>
+          <t>뷰노</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>-11.38</v>
+        <v>14.92</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>-17.11</v>
+        <v>52.94</v>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +50% / 중요공시 7일 +200%</t>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K26" s="17" t="inlineStr">
@@ -1471,7 +1469,7 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
@@ -1479,85 +1477,83 @@
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>핑거</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>대덕전자</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="F27" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="19" t="n">
-        <v>13.82</v>
-      </c>
-      <c r="I27" s="19" t="n">
-        <v>32.43</v>
-      </c>
-      <c r="J27" s="17" t="inlineStr">
-        <is>
-          <t>중요공시 4건 / 중요공시 3일 +100% / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>게임</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="F28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="15" t="n">
+      <c r="E28" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="22" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="I28" s="22" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="J28" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="n">
         <v/>
-      </c>
-      <c r="I28" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K28" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B29" s="20" t="n">
@@ -1565,7 +1561,7 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="D29" s="20" t="n">
@@ -1580,15 +1576,15 @@
       <c r="G29" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="I29" s="22" t="n">
-        <v>23.2</v>
+      <c r="H29" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I29" s="20" t="n">
+        <v/>
       </c>
       <c r="J29" s="23" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K29" s="23" t="n">
@@ -1598,7 +1594,7 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1606,42 +1602,40 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F30" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="I30" s="24" t="n">
-        <v>-4.9</v>
+        <v>-0.23</v>
+      </c>
+      <c r="I30" s="22" t="n">
+        <v>6.92</v>
       </c>
       <c r="J30" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 7일 +200%</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1649,42 +1643,40 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>삼성제약</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F31" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="22" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="I31" s="24" t="n">
-        <v>-0.15</v>
+      <c r="H31" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I31" s="20" t="n">
+        <v/>
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K31" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K31" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1692,30 +1684,30 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>-0.43</v>
+        <v>-10.85</v>
       </c>
       <c r="I32" s="24" t="n">
-        <v>-3.57</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 5건 / 중요공시 3일 +67%</t>
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr">
@@ -1727,7 +1719,7 @@
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1735,40 +1727,42 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>앤씨앤</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F33" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G33" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="22" t="n">
-        <v>0.77</v>
+      <c r="H33" s="24" t="n">
+        <v>-18.6</v>
       </c>
       <c r="I33" s="24" t="n">
-        <v>-2.74</v>
+        <v>-12.5</v>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K33" s="23" t="n">
-        <v/>
+          <t>중요공시 3건 / 중요공시 3일 +50%</t>
+        </is>
+      </c>
+      <c r="K33" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1776,14 +1770,14 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>OCI홀딩스</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>0</v>
@@ -1791,25 +1785,27 @@
       <c r="G34" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I34" s="20" t="n">
-        <v/>
+      <c r="H34" s="24" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="I34" s="22" t="n">
+        <v>13.47</v>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="n">
-        <v/>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1817,7 +1813,7 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
@@ -1832,27 +1828,25 @@
       <c r="G35" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="22" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="I35" s="22" t="n">
-        <v>5.98</v>
+      <c r="H35" s="24" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="I35" s="24" t="n">
+        <v>-3.54</v>
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +92% / 중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K35" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K35" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1860,7 +1854,7 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
@@ -1875,25 +1869,27 @@
       <c r="G36" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I36" s="22" t="n">
-        <v>5.55</v>
+      <c r="H36" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I36" s="20" t="n">
+        <v/>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="n">
-        <v/>
+          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1901,7 +1897,7 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
@@ -1924,19 +1920,17 @@
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K37" s="23" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K37" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1944,14 +1938,14 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>테라뷰</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F38" s="20" t="n">
         <v>0</v>
@@ -1960,24 +1954,26 @@
         <v>0</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>1.9</v>
+        <v>30.98</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>5.67</v>
+        <v>23.9</v>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K38" s="23" t="n">
-        <v/>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1985,42 +1981,42 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>스테이블코인</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F39" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I39" s="20" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H39" s="24" t="n">
+        <v>-4.26</v>
+      </c>
+      <c r="I39" s="24" t="n">
+        <v>-8.960000000000001</v>
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K39" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2028,7 +2024,7 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>미래산업</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
@@ -2044,14 +2040,14 @@
         <v>0</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>13.78</v>
+        <v>7.68</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>9.67</v>
+        <v>25.37</v>
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr">
@@ -2063,7 +2059,7 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2071,7 +2067,7 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
@@ -2087,26 +2083,26 @@
         <v>0</v>
       </c>
       <c r="H41" s="22" t="n">
-        <v>1.5</v>
+        <v>8.15</v>
       </c>
       <c r="I41" s="22" t="n">
-        <v>1.25</v>
+        <v>5.44</v>
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K41" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -2114,7 +2110,7 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>티로보틱스</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
@@ -2129,59 +2125,61 @@
       <c r="G42" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="24" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="I42" s="24" t="n">
-        <v>-0.9399999999999999</v>
+      <c r="H42" s="22" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="I42" s="22" t="n">
+        <v>12.03</v>
       </c>
       <c r="J42" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K42" s="23" t="n">
-        <v/>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K42" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B43" s="25" t="n">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="C43" s="26" t="inlineStr">
-        <is>
-          <t>네오사피엔스</t>
-        </is>
-      </c>
-      <c r="D43" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E43" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F43" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="27" t="n">
-        <v>-16.94</v>
-      </c>
-      <c r="I43" s="27" t="n">
-        <v>-44.17</v>
-      </c>
-      <c r="J43" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +986%</t>
-        </is>
-      </c>
-      <c r="K43" s="28" t="inlineStr">
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="24" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="I43" s="24" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="J43" s="23" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K43" s="23" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -2190,7 +2188,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -2198,7 +2196,7 @@
       </c>
       <c r="C44" s="26" t="inlineStr">
         <is>
-          <t>디에이테크놀로지</t>
+          <t>현대바이오랜드</t>
         </is>
       </c>
       <c r="D44" s="25" t="n">
@@ -2214,14 +2212,14 @@
         <v>0</v>
       </c>
       <c r="H44" s="27" t="n">
-        <v>-30.69</v>
+        <v>25.03</v>
       </c>
       <c r="I44" s="27" t="n">
-        <v>-97.7</v>
+        <v>45.2</v>
       </c>
       <c r="J44" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +690%</t>
+          <t>네이버 검색 당일 +189%</t>
         </is>
       </c>
       <c r="K44" s="28" t="inlineStr">
@@ -2233,7 +2231,7 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -2241,7 +2239,7 @@
       </c>
       <c r="C45" s="26" t="inlineStr">
         <is>
-          <t>동국생명과학</t>
+          <t>베노티앤알</t>
         </is>
       </c>
       <c r="D45" s="25" t="n">
@@ -2256,27 +2254,27 @@
       <c r="G45" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="29" t="n">
-        <v>19.93</v>
-      </c>
-      <c r="I45" s="29" t="n">
-        <v>39.08</v>
+      <c r="H45" s="27" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="I45" s="27" t="n">
+        <v>40.46</v>
       </c>
       <c r="J45" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +670%</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K45" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -2284,7 +2282,7 @@
       </c>
       <c r="C46" s="26" t="inlineStr">
         <is>
-          <t>토마토시스템</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="D46" s="25" t="n">
@@ -2299,27 +2297,25 @@
       <c r="G46" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="29" t="n">
-        <v>7.54</v>
-      </c>
-      <c r="I46" s="29" t="n">
-        <v>56.67</v>
+      <c r="H46" s="27" t="n">
+        <v>29.94</v>
+      </c>
+      <c r="I46" s="27" t="n">
+        <v>69.61</v>
       </c>
       <c r="J46" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +564%</t>
-        </is>
-      </c>
-      <c r="K46" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K46" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -2327,7 +2323,7 @@
       </c>
       <c r="C47" s="26" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="D47" s="25" t="n">
@@ -2342,27 +2338,25 @@
       <c r="G47" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="27" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="I47" s="29" t="n">
-        <v>22.76</v>
+      <c r="H47" s="25" t="n">
+        <v/>
+      </c>
+      <c r="I47" s="25" t="n">
+        <v/>
       </c>
       <c r="J47" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +198%</t>
-        </is>
-      </c>
-      <c r="K47" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K47" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -2370,42 +2364,42 @@
       </c>
       <c r="C48" s="26" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E48" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F48" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G48" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="27" t="n">
-        <v>-2</v>
-      </c>
-      <c r="I48" s="29" t="n">
-        <v>28.04</v>
+        <v>5.25</v>
+      </c>
+      <c r="I48" s="27" t="n">
+        <v>15.43</v>
       </c>
       <c r="J48" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +196%</t>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
         </is>
       </c>
       <c r="K48" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -2413,7 +2407,7 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>더블유에스아이</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
@@ -2428,27 +2422,25 @@
       <c r="G49" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="29" t="n">
-        <v>10.12</v>
-      </c>
-      <c r="I49" s="29" t="n">
-        <v>25.48</v>
+      <c r="H49" s="27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I49" s="27" t="n">
+        <v>28.37</v>
       </c>
       <c r="J49" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +129%</t>
-        </is>
-      </c>
-      <c r="K49" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K49" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2456,42 +2448,42 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>블루엠텍</t>
+          <t>아리바이오홀딩스</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E50" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F50" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G50" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="29" t="n">
-        <v>3.51</v>
+        <v>-25.47</v>
       </c>
       <c r="I50" s="29" t="n">
-        <v>1.45</v>
+        <v>-24.04</v>
       </c>
       <c r="J50" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +110%</t>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
         </is>
       </c>
       <c r="K50" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2499,7 +2491,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>MDS테크</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2515,10 +2507,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="27" t="n">
-        <v>-7.43</v>
+        <v>11.21</v>
       </c>
       <c r="I51" s="27" t="n">
-        <v>-2.38</v>
+        <v>11.21</v>
       </c>
       <c r="J51" s="28" t="inlineStr">
         <is>
@@ -2532,7 +2524,7 @@
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2540,30 +2532,30 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>미래산업</t>
+          <t>IBKS제25호스팩</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E52" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F52" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G52" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="29" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="I52" s="29" t="n">
-        <v>16.42</v>
+      <c r="H52" s="27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I52" s="27" t="n">
+        <v>2.06</v>
       </c>
       <c r="J52" s="28" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>중요공시 5건</t>
         </is>
       </c>
       <c r="K52" s="28" t="inlineStr">
@@ -2575,7 +2567,7 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2583,7 +2575,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>비케이홀딩스</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2599,14 +2591,14 @@
         <v>0</v>
       </c>
       <c r="H53" s="29" t="n">
-        <v>22.64</v>
+        <v>-27.91</v>
       </c>
       <c r="I53" s="29" t="n">
-        <v>3.06</v>
+        <v>-42.06</v>
       </c>
       <c r="J53" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>중요공시 4건</t>
         </is>
       </c>
       <c r="K53" s="28" t="inlineStr">
@@ -2618,7 +2610,7 @@
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2626,7 +2618,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>앤씨앤</t>
+          <t>모아라이프플러스</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2641,11 +2633,11 @@
       <c r="G54" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="29" t="n">
-        <v>16.81</v>
-      </c>
-      <c r="I54" s="29" t="n">
-        <v>7.5</v>
+      <c r="H54" s="27" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="I54" s="27" t="n">
+        <v>4.26</v>
       </c>
       <c r="J54" s="28" t="inlineStr">
         <is>
@@ -2661,7 +2653,7 @@
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2669,30 +2661,30 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>디티앤씨알오</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E55" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G55" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="29" t="n">
-        <v>14.38</v>
+        <v>-1.74</v>
       </c>
       <c r="I55" s="29" t="n">
-        <v>14.04</v>
+        <v>-4.12</v>
       </c>
       <c r="J55" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
         </is>
       </c>
       <c r="K55" s="28" t="inlineStr">
@@ -2704,7 +2696,7 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2712,7 +2704,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>케이쓰리아이</t>
+          <t>라메디텍</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2728,26 +2720,24 @@
         <v>0</v>
       </c>
       <c r="H56" s="27" t="n">
-        <v>-2.44</v>
-      </c>
-      <c r="I56" s="29" t="n">
-        <v>10.82</v>
+        <v>29.53</v>
+      </c>
+      <c r="I56" s="27" t="n">
+        <v>50.28</v>
       </c>
       <c r="J56" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K56" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K56" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2755,42 +2745,40 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>네이버</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E57" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G57" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="27" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="I57" s="27" t="n">
-        <v>-2.42</v>
+      <c r="H57" s="25" t="n">
+        <v/>
+      </c>
+      <c r="I57" s="25" t="n">
+        <v/>
       </c>
       <c r="J57" s="28" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K57" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K57" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2798,7 +2786,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2813,27 +2801,25 @@
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="27" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="I58" s="27" t="n">
-        <v>-1.95</v>
+      <c r="H58" s="29" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="I58" s="29" t="n">
+        <v>-3.65</v>
       </c>
       <c r="J58" s="28" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K58" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K58" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2841,7 +2827,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>에코프로비엠</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2857,14 +2843,14 @@
         <v>0</v>
       </c>
       <c r="H59" s="29" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="I59" s="29" t="n">
-        <v>6.35</v>
+        <v>-0.59</v>
+      </c>
+      <c r="I59" s="27" t="n">
+        <v>1.05</v>
       </c>
       <c r="J59" s="28" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급</t>
+          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K59" s="28" t="inlineStr">
@@ -2876,7 +2862,7 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2884,7 +2870,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2899,11 +2885,11 @@
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="25" t="n">
-        <v/>
-      </c>
-      <c r="I60" s="25" t="n">
-        <v/>
+      <c r="H60" s="29" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="I60" s="29" t="n">
+        <v>-1.31</v>
       </c>
       <c r="J60" s="28" t="inlineStr">
         <is>
@@ -2917,7 +2903,7 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2925,7 +2911,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>프롬바이오</t>
+          <t>KT&amp;G</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2941,14 +2927,14 @@
         <v>0</v>
       </c>
       <c r="H61" s="27" t="n">
-        <v>-10.98</v>
+        <v>0.86</v>
       </c>
       <c r="I61" s="27" t="n">
-        <v>-23.43</v>
+        <v>1.44</v>
       </c>
       <c r="J61" s="28" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K61" s="28" t="n">
@@ -2958,7 +2944,7 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2966,14 +2952,14 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>한국비엔씨</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F62" s="25" t="n">
         <v>0</v>
@@ -2981,25 +2967,27 @@
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="27" t="n">
-        <v>-5</v>
+      <c r="H62" s="29" t="n">
+        <v>-3.8</v>
       </c>
       <c r="I62" s="27" t="n">
-        <v>-2.37</v>
+        <v>14.01</v>
       </c>
       <c r="J62" s="28" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K62" s="28" t="n">
-        <v/>
+          <t>네이버 검색 당일 +80%</t>
+        </is>
+      </c>
+      <c r="K62" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3007,14 +2995,14 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F63" s="25" t="n">
         <v>0</v>
@@ -3022,19 +3010,21 @@
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="27" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="I63" s="27" t="n">
-        <v>-1.89</v>
+      <c r="H63" s="29" t="n">
+        <v>-3.27</v>
+      </c>
+      <c r="I63" s="29" t="n">
+        <v>-6.72</v>
       </c>
       <c r="J63" s="28" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K63" s="28" t="n">
-        <v/>
+          <t>중요공시 1건 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K63" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3130,22 +3120,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3154,29 +3144,29 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H4" s="25" t="n"/>
@@ -3192,70 +3182,70 @@
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H5" s="27" t="n">
-        <v>-5.76</v>
-      </c>
-      <c r="I5" s="27" t="n">
-        <v>-1.82</v>
+        <v>1.85</v>
+      </c>
+      <c r="I5" s="25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H6" s="29" t="n">
-        <v>27.86</v>
-      </c>
-      <c r="I6" s="29" t="n">
-        <v>24.45</v>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="I6" s="27" t="n">
+        <v>8.24</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
@@ -3272,20 +3262,16 @@
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="I7" s="29" t="n">
-        <v>4.12</v>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H7" s="25" t="n"/>
+      <c r="I7" s="25" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
@@ -3297,22 +3283,22 @@
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H8" s="25" t="n"/>
@@ -3321,29 +3307,29 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H9" s="25" t="n"/>
@@ -3352,95 +3338,99 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H10" s="27" t="n">
-        <v>-5.48</v>
+        <v>0.7</v>
       </c>
       <c r="I10" s="27" t="n">
-        <v>-6.28</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H11" s="25" t="n"/>
-      <c r="I11" s="25" t="n"/>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I11" s="29" t="n">
+        <v>-4.74</v>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H12" s="25" t="n"/>
@@ -3449,178 +3439,174 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>OCI홀딩스</t>
+          <t>모아데이타</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H13" s="29" t="n">
-        <v>12.35</v>
+        <v>-5.96</v>
       </c>
       <c r="I13" s="29" t="n">
-        <v>20.21</v>
+        <v>-22.05</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H14" s="27" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="I14" s="27" t="n">
-        <v>-2.07</v>
+        <v>0.62</v>
+      </c>
+      <c r="I14" s="29" t="n">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>뷰노</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H15" s="25" t="n"/>
-      <c r="I15" s="25" t="n"/>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="I15" s="27" t="n">
+        <v>52.94</v>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>모아데이타</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E16" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H16" s="27" t="n">
-        <v>-11.38</v>
-      </c>
-      <c r="I16" s="27" t="n">
-        <v>-17.11</v>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>핑거</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H17" s="29" t="n">
-        <v>13.82</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>32.43</v>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -3637,25 +3623,25 @@
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H18" s="29" t="n">
-        <v>0.77</v>
+        <v>-0.23</v>
       </c>
       <c r="I18" s="27" t="n">
-        <v>-2.74</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>삼성제약</t>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -3672,25 +3658,25 @@
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H19" s="29" t="n">
-        <v>4.38</v>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H19" s="27" t="n">
+        <v>8.710000000000001</v>
       </c>
       <c r="I19" s="27" t="n">
-        <v>-0.15</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -3707,12 +3693,12 @@
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H20" s="25" t="n"/>
@@ -3721,112 +3707,108 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>OCI홀딩스</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H21" s="27" t="n">
-        <v>-4.9</v>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H21" s="29" t="n">
+        <v>-5.6</v>
       </c>
       <c r="I21" s="27" t="n">
-        <v>-4.9</v>
+        <v>13.47</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H22" s="29" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="I22" s="29" t="n">
-        <v>23.2</v>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H22" s="25" t="n"/>
+      <c r="I22" s="25" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>더코디</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H23" s="27" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="I23" s="27" t="n">
-        <v>-3.57</v>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H23" s="29" t="n">
+        <v>-10.85</v>
+      </c>
+      <c r="I23" s="29" t="n">
+        <v>-8.130000000000001</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -3843,25 +3825,25 @@
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H24" s="29" t="n">
-        <v>1.9</v>
+        <v>-2.08</v>
       </c>
       <c r="I24" s="29" t="n">
-        <v>5.67</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>앤씨앤</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
@@ -3878,25 +3860,25 @@
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H25" s="29" t="n">
-        <v>1.4</v>
+        <v>-18.6</v>
       </c>
       <c r="I25" s="29" t="n">
-        <v>5.55</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
@@ -3913,12 +3895,12 @@
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H26" s="25" t="n"/>
@@ -3927,73 +3909,77 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>미래산업</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H27" s="29" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="I27" s="29" t="n">
-        <v>5.98</v>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H27" s="27" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="I27" s="27" t="n">
+        <v>25.37</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>스테이블코인</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H28" s="25" t="n"/>
-      <c r="I28" s="25" t="n"/>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H28" s="29" t="n">
+        <v>-4.26</v>
+      </c>
+      <c r="I28" s="29" t="n">
+        <v>-8.960000000000001</v>
+      </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>테라뷰</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
@@ -4010,25 +3996,25 @@
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H29" s="27" t="n">
-        <v>-0.19</v>
+        <v>30.98</v>
       </c>
       <c r="I29" s="27" t="n">
-        <v>-0.9399999999999999</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>티로보틱스</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
@@ -4045,25 +4031,25 @@
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H30" s="29" t="n">
-        <v>13.78</v>
-      </c>
-      <c r="I30" s="29" t="n">
-        <v>9.67</v>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H30" s="27" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="I30" s="27" t="n">
+        <v>12.03</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
@@ -4080,60 +4066,60 @@
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H31" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I31" s="29" t="n">
-        <v>1.25</v>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H31" s="27" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="I31" s="27" t="n">
+        <v>5.44</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H32" s="27" t="n">
-        <v>-2</v>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H32" s="29" t="n">
+        <v>-0.99</v>
       </c>
       <c r="I32" s="29" t="n">
-        <v>28.04</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
@@ -4150,25 +4136,25 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H33" s="27" t="n">
-        <v>-0.57</v>
+        <v>3.15</v>
       </c>
       <c r="I33" s="27" t="n">
-        <v>-1.89</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
@@ -4185,25 +4171,25 @@
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H34" s="27" t="n">
-        <v>-16.94</v>
+        <v>29.94</v>
       </c>
       <c r="I34" s="27" t="n">
-        <v>-44.17</v>
+        <v>69.61</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>더블유에스아이</t>
+          <t>IBKS제25호스팩</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
@@ -4220,25 +4206,25 @@
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H35" s="29" t="n">
-        <v>10.12</v>
-      </c>
-      <c r="I35" s="29" t="n">
-        <v>25.48</v>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H35" s="27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I35" s="27" t="n">
+        <v>2.06</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
@@ -4255,25 +4241,25 @@
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H36" s="29" t="n">
-        <v>22.64</v>
+        <v>-0.38</v>
       </c>
       <c r="I36" s="29" t="n">
-        <v>3.06</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>동국생명과학</t>
+          <t>KT&amp;G</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
@@ -4290,25 +4276,25 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H37" s="29" t="n">
-        <v>19.93</v>
-      </c>
-      <c r="I37" s="29" t="n">
-        <v>39.08</v>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H37" s="27" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I37" s="27" t="n">
+        <v>1.44</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>디에이테크놀로지</t>
+          <t>MDS테크</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4325,25 +4311,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H38" s="27" t="n">
-        <v>-30.69</v>
+        <v>11.21</v>
       </c>
       <c r="I38" s="27" t="n">
-        <v>-97.7</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>디티앤씨알오</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4360,25 +4346,21 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H39" s="29" t="n">
-        <v>14.38</v>
-      </c>
-      <c r="I39" s="29" t="n">
-        <v>14.04</v>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H39" s="25" t="n"/>
+      <c r="I39" s="25" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>미래산업</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4395,25 +4377,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H40" s="29" t="n">
-        <v>9.82</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="I40" s="29" t="n">
-        <v>16.42</v>
+        <v>-3.65</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>블루엠텍</t>
+          <t>네이버</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4430,25 +4412,21 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H41" s="29" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="I41" s="29" t="n">
-        <v>1.45</v>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H41" s="25" t="n"/>
+      <c r="I41" s="25" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>라메디텍</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4465,25 +4443,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H42" s="27" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="I42" s="29" t="n">
-        <v>22.76</v>
+        <v>29.53</v>
+      </c>
+      <c r="I42" s="27" t="n">
+        <v>50.28</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4500,25 +4478,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H43" s="27" t="n">
-        <v>-7.43</v>
+        <v>5.25</v>
       </c>
       <c r="I43" s="27" t="n">
-        <v>-2.38</v>
+        <v>15.43</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>모아라이프플러스</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4535,25 +4513,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H44" s="27" t="n">
-        <v>-0.2</v>
+        <v>4.03</v>
       </c>
       <c r="I44" s="27" t="n">
-        <v>-1.95</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>앤씨앤</t>
+          <t>베노티앤알</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4570,25 +4548,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H45" s="29" t="n">
-        <v>16.81</v>
-      </c>
-      <c r="I45" s="29" t="n">
-        <v>7.5</v>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H45" s="27" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="I45" s="27" t="n">
+        <v>40.46</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>에코프로비엠</t>
+          <t>비케이홀딩스</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4605,25 +4583,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H46" s="29" t="n">
-        <v>4.74</v>
+        <v>-27.91</v>
       </c>
       <c r="I46" s="29" t="n">
-        <v>6.35</v>
+        <v>-42.06</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>아리바이오홀딩스</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4640,21 +4618,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H47" s="25" t="n"/>
-      <c r="I47" s="25" t="n"/>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H47" s="29" t="n">
+        <v>-25.47</v>
+      </c>
+      <c r="I47" s="29" t="n">
+        <v>-24.04</v>
+      </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4671,25 +4653,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H48" s="27" t="n">
-        <v>-5</v>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H48" s="29" t="n">
+        <v>-0.59</v>
       </c>
       <c r="I48" s="27" t="n">
-        <v>-2.37</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>케이쓰리아이</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4706,25 +4688,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H49" s="27" t="n">
-        <v>-2.44</v>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H49" s="29" t="n">
+        <v>-1.74</v>
       </c>
       <c r="I49" s="29" t="n">
-        <v>10.82</v>
+        <v>-4.12</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>토마토시스템</t>
+          <t>현대바이오랜드</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4741,89 +4723,89 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H50" s="29" t="n">
-        <v>7.54</v>
-      </c>
-      <c r="I50" s="29" t="n">
-        <v>56.67</v>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H50" s="27" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="I50" s="27" t="n">
+        <v>45.2</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>프롬바이오</t>
+          <t>한국비엔씨</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C51" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D51" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H51" s="27" t="n">
-        <v>-10.98</v>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H51" s="29" t="n">
+        <v>-3.8</v>
       </c>
       <c r="I51" s="27" t="n">
-        <v>-23.43</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C52" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H52" s="27" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="I52" s="27" t="n">
-        <v>-2.42</v>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H52" s="29" t="n">
+        <v>-3.27</v>
+      </c>
+      <c r="I52" s="29" t="n">
+        <v>-6.72</v>
       </c>
     </row>
   </sheetData>
@@ -4907,19 +4889,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4938,19 +4920,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4962,26 +4944,26 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B5" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -4993,26 +4975,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5024,7 +5006,7 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
@@ -5038,12 +5020,12 @@
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5055,26 +5037,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5086,26 +5068,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5117,26 +5099,26 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B10" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="36" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G10" s="37" t="inlineStr">
@@ -5155,19 +5137,19 @@
         <v>1</v>
       </c>
       <c r="C11" s="36" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E11" s="36" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F11" s="37" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G11" s="37" t="inlineStr">
@@ -5186,19 +5168,19 @@
         <v>1</v>
       </c>
       <c r="C12" s="36" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E12" s="36" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F12" s="37" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G12" s="37" t="inlineStr">
@@ -5208,36 +5190,40 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
-        <is>
-          <t>이차전지</t>
-        </is>
-      </c>
-      <c r="B13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="28" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G13" s="28" t="inlineStr"/>
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B13" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F13" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G13" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5264,7 +5250,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5291,7 +5277,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5318,7 +5304,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5345,7 +5331,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5372,7 +5358,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -5399,7 +5385,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -5426,7 +5412,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>의료기기</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -5453,7 +5439,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>의료기기</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
@@ -5480,7 +5466,7 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -5507,7 +5493,7 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -261,11 +261,11 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -273,14 +273,14 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-09-30 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-10-01 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-30) 상위: 반도체  점수 88.0점</t>
+          <t>⚡ 최신(2026-10-01) 상위: 반도체  점수 46.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-30) 상위: 인공지능  점수 29.0점</t>
+          <t>⚡ 최신(2026-10-01) 상위: 로봇  점수 14.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-09-30) 상위: 삼성전자  점수 20.0점</t>
+          <t>⚡ 최신(2026-10-01) 상위: 원전  점수 14.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -967,14 +967,14 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1025,15 +1025,15 @@
       <c r="G16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="18" t="n">
-        <v>1.85</v>
+      <c r="H16" s="15" t="n">
+        <v/>
       </c>
       <c r="I16" s="15" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,14 +1053,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>모비스</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1069,26 +1069,26 @@
         <v>0</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>3.96</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>8.24</v>
+        <v>2.64</v>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 2건 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1096,14 +1096,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1111,25 +1111,27 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v/>
+      <c r="H18" s="18" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <v>2.67</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="n">
-        <v/>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1137,14 +1139,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1160,7 +1162,7 @@
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="inlineStr">
@@ -1172,7 +1174,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1180,14 +1182,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1195,15 +1197,15 @@
       <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v/>
+      <c r="H20" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K20" s="17" t="inlineStr">
@@ -1215,7 +1217,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1223,14 +1225,14 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1238,27 +1240,27 @@
       <c r="G21" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="18" t="n">
-        <v>1.65</v>
+      <c r="H21" s="19" t="n">
+        <v>-7.08</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>-4.74</v>
+        <v>-6.6</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>중요공시 2건 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1266,14 +1268,14 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1281,25 +1283,27 @@
       <c r="G22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="18" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I22" s="18" t="n">
-        <v>6.4</v>
+      <c r="H22" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v/>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="n">
-        <v/>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1307,14 +1311,14 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F23" s="15" t="n">
         <v>0</v>
@@ -1330,17 +1334,19 @@
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="n">
-        <v/>
+          <t>네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1348,42 +1354,40 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>모아데이타</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H24" s="19" t="n">
-        <v>-5.96</v>
+        <v>-0.27</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>-22.05</v>
+        <v>-1.16</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>중요공시 4건 / 중요공시 3일 +100% / 중요공시 7일 +300%</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1391,42 +1395,42 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F25" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I25" s="19" t="n">
-        <v>-1.49</v>
+        <v>0.98</v>
+      </c>
+      <c r="I25" s="18" t="n">
+        <v>29.62</v>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 7일 +100% / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K25" s="17" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1434,14 +1438,14 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>뷰노</t>
+          <t>한화투자증권</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F26" s="15" t="n">
         <v>0</v>
@@ -1450,26 +1454,26 @@
         <v>0</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>14.92</v>
-      </c>
-      <c r="I26" s="18" t="n">
-        <v>52.94</v>
+        <v>1.31</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>-1.91</v>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 3건 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K26" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
@@ -1477,206 +1481,212 @@
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>모아데이타</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>-23.57</v>
+      </c>
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 3일 +50% / 중요공시 7일 +200%</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>덕산넵코어스</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="E27" s="15" t="n">
+      <c r="E28" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="F27" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="15" t="n">
+      <c r="F28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="15" t="n">
         <v/>
       </c>
-      <c r="I27" s="15" t="n">
+      <c r="I28" s="15" t="n">
         <v/>
       </c>
-      <c r="J27" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="inlineStr">
+      <c r="J28" s="17" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="17" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>한미반도체</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I29" s="18" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="J29" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K29" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>대덕전자</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E28" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="22" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="I28" s="22" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="J28" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K28" s="23" t="n">
+      <c r="D30" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="15" t="n">
         <v/>
       </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="C29" s="21" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="D29" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E29" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="20" t="n">
+      <c r="I30" s="15" t="n">
         <v/>
       </c>
-      <c r="I29" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J29" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K29" s="23" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="n">
-        <v>17</v>
-      </c>
-      <c r="C30" s="21" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="D30" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E30" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F30" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="24" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="I30" s="22" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="n">
-        <v/>
+      <c r="J30" s="17" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K30" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="n">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>태양광</t>
-        </is>
-      </c>
-      <c r="D31" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E31" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I31" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J31" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K31" s="23" t="n">
-        <v/>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="18" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="I31" s="18" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="J31" s="17" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K31" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1684,14 +1694,14 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>아리바이오홀딩스</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" s="20" t="n">
         <v>2</v>
@@ -1699,18 +1709,18 @@
       <c r="G32" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="24" t="n">
-        <v>-10.85</v>
-      </c>
-      <c r="I32" s="24" t="n">
-        <v>-8.130000000000001</v>
-      </c>
-      <c r="J32" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 5건 / 중요공시 3일 +67%</t>
-        </is>
-      </c>
-      <c r="K32" s="23" t="inlineStr">
+      <c r="H32" s="22" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="I32" s="23" t="n">
+        <v>-13.43</v>
+      </c>
+      <c r="J32" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K32" s="24" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1719,7 +1729,7 @@
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1727,33 +1737,33 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>앤씨앤</t>
+          <t>제일기획</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F33" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G33" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="24" t="n">
-        <v>-18.6</v>
-      </c>
-      <c r="I33" s="24" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="J33" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 3일 +50%</t>
-        </is>
-      </c>
-      <c r="K33" s="23" t="inlineStr">
+      <c r="H33" s="22" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="I33" s="22" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="J33" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K33" s="24" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1762,7 +1772,7 @@
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1770,14 +1780,14 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>OCI홀딩스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>0</v>
@@ -1785,27 +1795,27 @@
       <c r="G34" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="24" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="I34" s="22" t="n">
-        <v>13.47</v>
-      </c>
-      <c r="J34" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="H34" s="22" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I34" s="23" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="J34" s="24" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1813,14 +1823,14 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>에코프로비엠</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F35" s="20" t="n">
         <v>0</v>
@@ -1828,25 +1838,27 @@
       <c r="G35" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="24" t="n">
-        <v>-2.08</v>
-      </c>
-      <c r="I35" s="24" t="n">
-        <v>-3.54</v>
-      </c>
-      <c r="J35" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K35" s="23" t="n">
-        <v/>
+      <c r="H35" s="22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I35" s="22" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="J35" s="24" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1854,14 +1866,14 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>0</v>
@@ -1875,21 +1887,19 @@
       <c r="I36" s="20" t="n">
         <v/>
       </c>
-      <c r="J36" s="23" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="J36" s="24" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K36" s="24" t="n">
+        <v/>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1897,7 +1907,7 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
@@ -1912,25 +1922,27 @@
       <c r="G37" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I37" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J37" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K37" s="23" t="n">
-        <v/>
+      <c r="H37" s="23" t="n">
+        <v>-6.96</v>
+      </c>
+      <c r="I37" s="22" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="J37" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +72% / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K37" s="24" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1938,14 +1950,14 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>테라뷰</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F38" s="20" t="n">
         <v>0</v>
@@ -1953,27 +1965,27 @@
       <c r="G38" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="22" t="n">
-        <v>30.98</v>
-      </c>
-      <c r="I38" s="22" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="J38" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K38" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="H38" s="23" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="I38" s="23" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="J38" s="24" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K38" s="24" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1981,42 +1993,42 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>태영건설</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F39" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H39" s="24" t="n">
-        <v>-4.26</v>
-      </c>
-      <c r="I39" s="24" t="n">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="J39" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K39" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>0</v>
+      </c>
+      <c r="H39" s="22" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="I39" s="22" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J39" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K39" s="24" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2024,42 +2036,42 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>미래산업</t>
+          <t>퀀텀레일</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G40" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="22" t="n">
-        <v>7.68</v>
-      </c>
-      <c r="I40" s="22" t="n">
-        <v>25.37</v>
-      </c>
-      <c r="J40" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K40" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="H40" s="23" t="n">
+        <v>-31.07</v>
+      </c>
+      <c r="I40" s="23" t="n">
+        <v>-58.21</v>
+      </c>
+      <c r="J40" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +508% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K40" s="24" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2067,7 +2079,7 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
@@ -2083,17 +2095,17 @@
         <v>0</v>
       </c>
       <c r="H41" s="22" t="n">
-        <v>8.15</v>
+        <v>1.85</v>
       </c>
       <c r="I41" s="22" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="J41" s="23" t="inlineStr">
+        <v>19.06</v>
+      </c>
+      <c r="J41" s="24" t="inlineStr">
         <is>
           <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
-      <c r="K41" s="23" t="inlineStr">
+      <c r="K41" s="24" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -2102,7 +2114,7 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -2110,7 +2122,7 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>티로보틱스</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
@@ -2125,27 +2137,27 @@
       <c r="G42" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="22" t="n">
-        <v>5.49</v>
+      <c r="H42" s="23" t="n">
+        <v>-1.68</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>12.03</v>
-      </c>
-      <c r="J42" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K42" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>0.36</v>
+      </c>
+      <c r="J42" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K42" s="24" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B43" s="20" t="n">
@@ -2153,253 +2165,251 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>아이로보틱스</t>
         </is>
       </c>
       <c r="D43" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E43" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H43" s="22" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I43" s="23" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="J43" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K43" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="n">
+        <v>31</v>
+      </c>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>현대무벡스</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="F43" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="24" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="I43" s="24" t="n">
-        <v>-3.04</v>
-      </c>
-      <c r="J43" s="23" t="inlineStr">
-        <is>
-          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K43" s="23" t="inlineStr">
+      <c r="E44" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="22" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I44" s="23" t="n">
+        <v>-6.16</v>
+      </c>
+      <c r="J44" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K44" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I45" s="23" t="n">
+        <v>-4.01</v>
+      </c>
+      <c r="J45" s="24" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K45" s="24" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B44" s="25" t="n">
-        <v>31</v>
-      </c>
-      <c r="C44" s="26" t="inlineStr">
-        <is>
-          <t>현대바이오랜드</t>
-        </is>
-      </c>
-      <c r="D44" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E44" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F44" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="27" t="n">
-        <v>25.03</v>
-      </c>
-      <c r="I44" s="27" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="J44" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +189%</t>
-        </is>
-      </c>
-      <c r="K44" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B45" s="25" t="n">
-        <v>32</v>
-      </c>
-      <c r="C45" s="26" t="inlineStr">
-        <is>
-          <t>베노티앤알</t>
-        </is>
-      </c>
-      <c r="D45" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E45" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="27" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="I45" s="27" t="n">
-        <v>40.46</v>
-      </c>
-      <c r="J45" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K45" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B46" s="25" t="n">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="n">
         <v>33</v>
       </c>
-      <c r="C46" s="26" t="inlineStr">
-        <is>
-          <t>HLB제약</t>
-        </is>
-      </c>
-      <c r="D46" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="27" t="n">
-        <v>29.94</v>
-      </c>
-      <c r="I46" s="27" t="n">
-        <v>69.61</v>
-      </c>
-      <c r="J46" s="28" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K46" s="28" t="n">
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="23" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="I46" s="23" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="J46" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K46" s="24" t="n">
         <v/>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B47" s="25" t="n">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="n">
         <v>34</v>
       </c>
-      <c r="C47" s="26" t="inlineStr">
-        <is>
-          <t>글로벌테크놀로지</t>
-        </is>
-      </c>
-      <c r="D47" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E47" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F47" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="25" t="n">
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>철강</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="20" t="n">
         <v/>
       </c>
-      <c r="I47" s="25" t="n">
+      <c r="I47" s="20" t="n">
         <v/>
       </c>
-      <c r="J47" s="28" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K47" s="28" t="n">
+      <c r="J47" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K47" s="24" t="n">
         <v/>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B48" s="25" t="n">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="n">
         <v>35</v>
       </c>
-      <c r="C48" s="26" t="inlineStr">
-        <is>
-          <t>루닛</t>
-        </is>
-      </c>
-      <c r="D48" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G48" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="27" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="I48" s="27" t="n">
-        <v>15.43</v>
-      </c>
-      <c r="J48" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K48" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>스테이블코인</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I48" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J48" s="24" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K48" s="24" t="n">
+        <v/>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -2407,7 +2417,7 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>현대바이오랜드</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
@@ -2423,24 +2433,26 @@
         <v>0</v>
       </c>
       <c r="H49" s="27" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="I49" s="27" t="n">
-        <v>28.37</v>
-      </c>
-      <c r="J49" s="28" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K49" s="28" t="n">
-        <v/>
+        <v>-4.59</v>
+      </c>
+      <c r="I49" s="28" t="n">
+        <v>38.54</v>
+      </c>
+      <c r="J49" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +840%</t>
+        </is>
+      </c>
+      <c r="K49" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2448,42 +2460,42 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>아리바이오홀딩스</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E50" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F50" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G50" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="29" t="n">
-        <v>-25.47</v>
-      </c>
-      <c r="I50" s="29" t="n">
-        <v>-24.04</v>
-      </c>
-      <c r="J50" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K50" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="H50" s="28" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="I50" s="28" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="J50" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +714%</t>
+        </is>
+      </c>
+      <c r="K50" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2491,7 +2503,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>MDS테크</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2506,25 +2518,27 @@
       <c r="G51" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="27" t="n">
-        <v>11.21</v>
-      </c>
-      <c r="I51" s="27" t="n">
-        <v>11.21</v>
-      </c>
-      <c r="J51" s="28" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K51" s="28" t="n">
-        <v/>
+      <c r="H51" s="28" t="n">
+        <v>43.62</v>
+      </c>
+      <c r="I51" s="28" t="n">
+        <v>43.62</v>
+      </c>
+      <c r="J51" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +606%</t>
+        </is>
+      </c>
+      <c r="K51" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2532,7 +2546,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>IBKS제25호스팩</t>
+          <t>한빛레이저</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2547,27 +2561,27 @@
       <c r="G52" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I52" s="27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="J52" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 5건</t>
-        </is>
-      </c>
-      <c r="K52" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="H52" s="28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I52" s="28" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="J52" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +280%</t>
+        </is>
+      </c>
+      <c r="K52" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2575,7 +2589,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>비케이홀딩스</t>
+          <t>한국비엔씨</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2590,27 +2604,27 @@
       <c r="G53" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="29" t="n">
-        <v>-27.91</v>
-      </c>
-      <c r="I53" s="29" t="n">
-        <v>-42.06</v>
-      </c>
-      <c r="J53" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 4건</t>
-        </is>
-      </c>
-      <c r="K53" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="H53" s="27" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="I53" s="28" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="J53" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +195%</t>
+        </is>
+      </c>
+      <c r="K53" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2618,7 +2632,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>모아라이프플러스</t>
+          <t>보원케미칼</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2634,26 +2648,26 @@
         <v>0</v>
       </c>
       <c r="H54" s="27" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="I54" s="27" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="J54" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K54" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>-2.05</v>
+      </c>
+      <c r="I54" s="28" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="J54" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +172%</t>
+        </is>
+      </c>
+      <c r="K54" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2661,42 +2675,42 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>부산주공</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E55" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F55" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G55" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="29" t="n">
-        <v>-1.74</v>
-      </c>
-      <c r="I55" s="29" t="n">
-        <v>-4.12</v>
-      </c>
-      <c r="J55" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K55" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="H55" s="28" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="I55" s="27" t="n">
+        <v>-90.95</v>
+      </c>
+      <c r="J55" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +153%</t>
+        </is>
+      </c>
+      <c r="K55" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2704,7 +2718,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>라메디텍</t>
+          <t>HLB생명과학</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2719,25 +2733,27 @@
       <c r="G56" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="27" t="n">
-        <v>29.53</v>
-      </c>
-      <c r="I56" s="27" t="n">
-        <v>50.28</v>
-      </c>
-      <c r="J56" s="28" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K56" s="28" t="n">
-        <v/>
+      <c r="H56" s="28" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="I56" s="28" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="J56" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +145%</t>
+        </is>
+      </c>
+      <c r="K56" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2745,40 +2761,42 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
+          <t>금강공업</t>
+        </is>
+      </c>
+      <c r="D57" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F57" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I57" s="28" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="J57" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +130%</t>
+        </is>
+      </c>
+      <c r="K57" s="29" t="inlineStr">
+        <is>
           <t>네이버</t>
         </is>
-      </c>
-      <c r="D57" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E57" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F57" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="25" t="n">
-        <v/>
-      </c>
-      <c r="I57" s="25" t="n">
-        <v/>
-      </c>
-      <c r="J57" s="28" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K57" s="28" t="n">
-        <v/>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2786,7 +2804,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>세미파이브</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2801,25 +2819,27 @@
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="29" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="I58" s="29" t="n">
-        <v>-3.65</v>
-      </c>
-      <c r="J58" s="28" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K58" s="28" t="n">
-        <v/>
+      <c r="H58" s="27" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="I58" s="28" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="J58" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +81% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K58" s="29" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2827,7 +2847,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>나인테크</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2842,27 +2862,27 @@
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="29" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="I59" s="27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="J59" s="28" t="inlineStr">
-        <is>
-          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K59" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H59" s="28" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="I59" s="28" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="J59" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +81% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K59" s="29" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2870,7 +2890,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2885,25 +2905,27 @@
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="29" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="I60" s="29" t="n">
-        <v>-1.31</v>
-      </c>
-      <c r="J60" s="28" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K60" s="28" t="n">
-        <v/>
+      <c r="H60" s="28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I60" s="27" t="n">
+        <v>-4.39</v>
+      </c>
+      <c r="J60" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K60" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2911,40 +2933,42 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>KT&amp;G</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E61" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F61" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="27" t="n">
-        <v>0.86</v>
+      <c r="H61" s="28" t="n">
+        <v>0.31</v>
       </c>
       <c r="I61" s="27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="J61" s="28" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K61" s="28" t="n">
-        <v/>
+        <v>-8.24</v>
+      </c>
+      <c r="J61" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K61" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2952,14 +2976,14 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>한국비엔씨</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F62" s="25" t="n">
         <v>0</v>
@@ -2967,27 +2991,27 @@
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="29" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="I62" s="27" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="J62" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +80%</t>
-        </is>
-      </c>
-      <c r="K62" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H62" s="28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I62" s="28" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="J62" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K62" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -2995,14 +3019,14 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>IBKS제25호스팩</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63" s="25" t="n">
         <v>0</v>
@@ -3010,18 +3034,18 @@
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="29" t="n">
-        <v>-3.27</v>
-      </c>
-      <c r="I63" s="29" t="n">
-        <v>-6.72</v>
-      </c>
-      <c r="J63" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K63" s="28" t="inlineStr">
+      <c r="H63" s="27" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="I63" s="27" t="n">
+        <v>-4.31</v>
+      </c>
+      <c r="J63" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 5건</t>
+        </is>
+      </c>
+      <c r="K63" s="29" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -3120,22 +3144,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3144,29 +3168,29 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H4" s="25" t="n"/>
@@ -3175,99 +3199,95 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H5" s="27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="I5" s="25" t="n">
-        <v>0</v>
-      </c>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H5" s="25" t="n"/>
+      <c r="I5" s="25" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>모비스</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="I6" s="27" t="n">
-        <v>8.24</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I6" s="28" t="n">
+        <v>2.64</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H7" s="25" t="n"/>
@@ -3276,161 +3296,169 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H8" s="25" t="n"/>
-      <c r="I8" s="25" t="n"/>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="I8" s="28" t="n">
+        <v>2.67</v>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H9" s="25" t="n"/>
-      <c r="I9" s="25" t="n"/>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H9" s="27" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I9" s="27" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H10" s="27" t="n">
-        <v>0.7</v>
+        <v>-7.08</v>
       </c>
       <c r="I10" s="27" t="n">
-        <v>6.4</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H11" s="27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="I11" s="29" t="n">
-        <v>-4.74</v>
+        <v>-0.27</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H12" s="25" t="n"/>
@@ -3439,165 +3467,165 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>모아데이타</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H13" s="29" t="n">
-        <v>-5.96</v>
-      </c>
-      <c r="I13" s="29" t="n">
-        <v>-22.05</v>
-      </c>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H13" s="25" t="n"/>
+      <c r="I13" s="25" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H14" s="27" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I14" s="29" t="n">
-        <v>-1.49</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H14" s="28" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I14" s="28" t="n">
+        <v>29.62</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>뷰노</t>
+          <t>한화투자증권</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H15" s="27" t="n">
-        <v>14.92</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H15" s="28" t="n">
+        <v>1.31</v>
       </c>
       <c r="I15" s="27" t="n">
-        <v>52.94</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>모아데이타</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H16" s="25" t="n"/>
-      <c r="I16" s="25" t="n"/>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="I16" s="27" t="n">
+        <v>-23.57</v>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>네이버</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H17" s="25" t="n"/>
@@ -3606,279 +3634,279 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H18" s="29" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="I18" s="27" t="n">
-        <v>6.92</v>
-      </c>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="25" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>대덕전자</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H19" s="27" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="I19" s="27" t="n">
-        <v>28.57</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H19" s="28" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="I19" s="28" t="n">
+        <v>11.51</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H20" s="25" t="n"/>
-      <c r="I20" s="25" t="n"/>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H20" s="28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I20" s="28" t="n">
+        <v>7.95</v>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>OCI홀딩스</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H21" s="29" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="I21" s="27" t="n">
-        <v>13.47</v>
-      </c>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="25" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>아리바이오홀딩스</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H22" s="25" t="n"/>
-      <c r="I22" s="25" t="n"/>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H22" s="28" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="I22" s="27" t="n">
+        <v>-13.43</v>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H23" s="29" t="n">
-        <v>-10.85</v>
-      </c>
-      <c r="I23" s="29" t="n">
-        <v>-8.130000000000001</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H23" s="28" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I23" s="27" t="n">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>에코프로비엠</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H24" s="29" t="n">
-        <v>-2.08</v>
-      </c>
-      <c r="I24" s="29" t="n">
-        <v>-3.54</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H24" s="28" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I24" s="28" t="n">
+        <v>4.91</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>앤씨앤</t>
+          <t>제일기획</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H25" s="29" t="n">
-        <v>-18.6</v>
-      </c>
-      <c r="I25" s="29" t="n">
-        <v>-12.5</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H25" s="28" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="I25" s="28" t="n">
+        <v>7.31</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
@@ -3895,91 +3923,95 @@
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H26" s="25" t="n"/>
-      <c r="I26" s="25" t="n"/>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H26" s="27" t="n">
+        <v>-6.96</v>
+      </c>
+      <c r="I26" s="28" t="n">
+        <v>57.8</v>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>미래산업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H27" s="27" t="n">
-        <v>7.68</v>
+        <v>-0.39</v>
       </c>
       <c r="I27" s="27" t="n">
-        <v>25.37</v>
+        <v>-5.11</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>태영건설</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H28" s="29" t="n">
-        <v>-4.26</v>
-      </c>
-      <c r="I28" s="29" t="n">
-        <v>-8.960000000000001</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H28" s="28" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="I28" s="28" t="n">
+        <v>0.42</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>테라뷰</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
@@ -3996,25 +4028,25 @@
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H29" s="27" t="n">
-        <v>30.98</v>
+        <v>-0.76</v>
       </c>
       <c r="I29" s="27" t="n">
-        <v>23.9</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>티로보틱스</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
@@ -4031,25 +4063,25 @@
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H30" s="27" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="I30" s="27" t="n">
-        <v>12.03</v>
+        <v>-1.68</v>
+      </c>
+      <c r="I30" s="28" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
@@ -4066,25 +4098,21 @@
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H31" s="27" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="I31" s="27" t="n">
-        <v>5.44</v>
-      </c>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H31" s="25" t="n"/>
+      <c r="I31" s="25" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>아이로보틱스</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
@@ -4101,200 +4129,196 @@
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H32" s="29" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="I32" s="29" t="n">
-        <v>-3.04</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H32" s="28" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I32" s="27" t="n">
+        <v>-3.02</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H33" s="27" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="I33" s="27" t="n">
-        <v>28.37</v>
-      </c>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H33" s="25" t="n"/>
+      <c r="I33" s="25" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>퀀텀레일</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H34" s="27" t="n">
-        <v>29.94</v>
+        <v>-31.07</v>
       </c>
       <c r="I34" s="27" t="n">
-        <v>69.61</v>
+        <v>-58.21</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>IBKS제25호스팩</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H35" s="27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I35" s="27" t="n">
-        <v>2.06</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H35" s="28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I35" s="28" t="n">
+        <v>19.06</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>현대무벡스</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H36" s="29" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="I36" s="29" t="n">
-        <v>-1.31</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H36" s="28" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I36" s="27" t="n">
+        <v>-6.16</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>KT&amp;G</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H37" s="27" t="n">
-        <v>0.86</v>
+        <v>-1</v>
       </c>
       <c r="I37" s="27" t="n">
-        <v>1.44</v>
+        <v>-4.01</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>MDS테크</t>
+          <t>HLB생명과학</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4311,25 +4335,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H38" s="27" t="n">
-        <v>11.21</v>
-      </c>
-      <c r="I38" s="27" t="n">
-        <v>11.21</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H38" s="28" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="I38" s="28" t="n">
+        <v>46.92</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>IBKS제25호스팩</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4346,21 +4370,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H39" s="25" t="n"/>
-      <c r="I39" s="25" t="n"/>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H39" s="27" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="I39" s="27" t="n">
+        <v>-4.31</v>
+      </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4377,25 +4405,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H40" s="29" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="I40" s="29" t="n">
-        <v>-3.65</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H40" s="28" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="I40" s="28" t="n">
+        <v>25.72</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>금강공업</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4412,21 +4440,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H41" s="25" t="n"/>
-      <c r="I41" s="25" t="n"/>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H41" s="28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I41" s="28" t="n">
+        <v>9.48</v>
+      </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>라메디텍</t>
+          <t>나인테크</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4443,25 +4475,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H42" s="27" t="n">
-        <v>29.53</v>
-      </c>
-      <c r="I42" s="27" t="n">
-        <v>50.28</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H42" s="28" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="I42" s="28" t="n">
+        <v>25.11</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4478,25 +4510,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H43" s="27" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="I43" s="27" t="n">
-        <v>15.43</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H43" s="28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I43" s="28" t="n">
+        <v>10.15</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>모아라이프플러스</t>
+          <t>보원케미칼</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4513,25 +4545,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H44" s="27" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="I44" s="27" t="n">
-        <v>4.26</v>
+        <v>-2.05</v>
+      </c>
+      <c r="I44" s="28" t="n">
+        <v>39.78</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>베노티앤알</t>
+          <t>부산주공</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4548,25 +4580,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H45" s="27" t="n">
-        <v>7.73</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H45" s="28" t="n">
+        <v>18.92</v>
       </c>
       <c r="I45" s="27" t="n">
-        <v>40.46</v>
+        <v>-90.95</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>비케이홀딩스</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4583,25 +4615,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H46" s="29" t="n">
-        <v>-27.91</v>
-      </c>
-      <c r="I46" s="29" t="n">
-        <v>-42.06</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H46" s="28" t="n">
+        <v>43.62</v>
+      </c>
+      <c r="I46" s="28" t="n">
+        <v>43.62</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>아리바이오홀딩스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4618,25 +4650,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H47" s="29" t="n">
-        <v>-25.47</v>
-      </c>
-      <c r="I47" s="29" t="n">
-        <v>-24.04</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H47" s="28" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I47" s="27" t="n">
+        <v>-8.24</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4653,25 +4685,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H48" s="29" t="n">
-        <v>-0.59</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H48" s="28" t="n">
+        <v>1.74</v>
       </c>
       <c r="I48" s="27" t="n">
-        <v>1.05</v>
+        <v>-4.39</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>세미파이브</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4688,25 +4720,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H49" s="29" t="n">
-        <v>-1.74</v>
-      </c>
-      <c r="I49" s="29" t="n">
-        <v>-4.12</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H49" s="27" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="I49" s="28" t="n">
+        <v>18.39</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>현대바이오랜드</t>
+          <t>한국비엔씨</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4723,89 +4755,89 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H50" s="27" t="n">
-        <v>25.03</v>
-      </c>
-      <c r="I50" s="27" t="n">
-        <v>45.2</v>
+        <v>-1.37</v>
+      </c>
+      <c r="I50" s="28" t="n">
+        <v>12.46</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>한국비엔씨</t>
+          <t>한빛레이저</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C51" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D51" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H51" s="29" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="I51" s="27" t="n">
-        <v>14.01</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H51" s="28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I51" s="28" t="n">
+        <v>27.27</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>현대바이오랜드</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C52" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D52" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H52" s="29" t="n">
-        <v>-3.27</v>
-      </c>
-      <c r="I52" s="29" t="n">
-        <v>-6.72</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H52" s="27" t="n">
+        <v>-4.59</v>
+      </c>
+      <c r="I52" s="28" t="n">
+        <v>38.54</v>
       </c>
     </row>
   </sheetData>
@@ -4889,19 +4921,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4920,19 +4952,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4951,19 +4983,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -4975,26 +5007,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5006,26 +5038,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5037,26 +5069,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5068,26 +5100,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5099,26 +5131,26 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B10" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G10" s="37" t="inlineStr">
@@ -5128,102 +5160,90 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="B11" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>11</v>
-      </c>
-      <c r="D11" s="36" t="n">
-        <v>11</v>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F11" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G11" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>이차전지</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="29" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G11" s="29" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>인공지능</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>29</v>
-      </c>
-      <c r="D12" s="36" t="n">
-        <v>29</v>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F12" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G12" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>AI반도체</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="29" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G12" s="29" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="35" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="B13" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="36" t="n">
-        <v>6</v>
-      </c>
-      <c r="D13" s="36" t="n">
-        <v>6</v>
-      </c>
-      <c r="E13" s="36" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F13" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G13" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>전기차</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="29" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G13" s="29" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>이차전지</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5240,17 +5260,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="28" t="inlineStr">
+      <c r="F14" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G14" s="28" t="inlineStr"/>
+      <c r="G14" s="29" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5267,17 +5287,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="28" t="inlineStr">
+      <c r="F15" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G15" s="28" t="inlineStr"/>
+      <c r="G15" s="29" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5294,17 +5314,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="28" t="inlineStr">
+      <c r="F16" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G16" s="28" t="inlineStr"/>
+      <c r="G16" s="29" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5321,17 +5341,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="28" t="inlineStr">
+      <c r="F17" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G17" s="28" t="inlineStr"/>
+      <c r="G17" s="29" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5348,17 +5368,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="28" t="inlineStr">
+      <c r="F18" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G18" s="28" t="inlineStr"/>
+      <c r="G18" s="29" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -5375,17 +5395,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="28" t="inlineStr">
+      <c r="F19" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G19" s="28" t="inlineStr"/>
+      <c r="G19" s="29" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -5402,17 +5422,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="28" t="inlineStr">
+      <c r="F20" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G20" s="28" t="inlineStr"/>
+      <c r="G20" s="29" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>의료기기</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -5429,17 +5449,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F21" s="28" t="inlineStr">
+      <c r="F21" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G21" s="28" t="inlineStr"/>
+      <c r="G21" s="29" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>의료기기</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
@@ -5456,17 +5476,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F22" s="28" t="inlineStr">
+      <c r="F22" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G22" s="28" t="inlineStr"/>
+      <c r="G22" s="29" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -5483,17 +5503,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F23" s="28" t="inlineStr">
+      <c r="F23" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G23" s="28" t="inlineStr"/>
+      <c r="G23" s="29" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -5510,12 +5530,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F24" s="28" t="inlineStr">
+      <c r="F24" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G24" s="28" t="inlineStr"/>
+      <c r="G24" s="29" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -258,13 +258,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-10-03 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-10-04 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-10-03) 상위: 반도체  점수 43.0점</t>
+          <t>⚡ 최신(2026-10-04) 상위: 반도체  점수 48.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-10-03) 상위: 삼성전자  점수 29.0점</t>
+          <t>⚡ 최신(2026-10-04) 상위: 삼성전자  점수 35.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-10-03) 상위: 인공지능  점수 25.0점</t>
+          <t>⚡ 최신(2026-10-04) 상위: 인공지능  점수 24.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -985,12 +985,12 @@
       <c r="H15" s="18" t="n">
         <v>0.55</v>
       </c>
-      <c r="I15" s="19" t="n">
-        <v>-3.66</v>
+      <c r="I15" s="18" t="n">
+        <v>2.22</v>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>-0.57</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>-2.8</v>
+        <v>-1.98</v>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
@@ -1129,7 +1129,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="inlineStr">
@@ -1172,7 +1172,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K20" s="17" t="inlineStr">
@@ -1215,7 +1215,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
@@ -1238,15 +1238,15 @@
       <c r="G21" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="18" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I21" s="19" t="n">
-        <v>-1.13</v>
+      <c r="H21" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v/>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
@@ -1258,7 +1258,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>한창</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1281,27 +1281,27 @@
       <c r="G22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v/>
+      <c r="H22" s="19" t="n">
+        <v>-91.06999999999999</v>
+      </c>
+      <c r="I22" s="19" t="n">
+        <v>-91.06999999999999</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>네이버 검색 당일 +143% / 중요공시 1건 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1309,42 +1309,42 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
         <v>7</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F23" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H23" s="18" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="I23" s="19" t="n">
-        <v>-3.53</v>
+        <v>0.77</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <v>4.6</v>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 7일 +100% / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K23" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1352,83 +1352,83 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>에스제이그룹</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
         <v>7</v>
       </c>
       <c r="E24" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="J24" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100% / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>철강</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="F24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="18" t="n">
-        <v>29.96</v>
-      </c>
-      <c r="I24" s="18" t="n">
-        <v>26.45</v>
-      </c>
-      <c r="J24" s="17" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>SG</t>
-        </is>
-      </c>
-      <c r="D25" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E25" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="22" t="n">
-        <v>-5.15</v>
-      </c>
-      <c r="I25" s="22" t="n">
-        <v>-8.68</v>
-      </c>
-      <c r="J25" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K25" s="23" t="n">
+      <c r="E25" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="n">
         <v/>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B26" s="20" t="n">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>티엠씨</t>
+          <t>세미파이브</t>
         </is>
       </c>
       <c r="D26" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E26" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F26" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="24" t="n">
-        <v>29.68</v>
-      </c>
-      <c r="I26" s="24" t="n">
-        <v>28.86</v>
+      <c r="H26" s="22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I26" s="22" t="n">
+        <v>28.88</v>
       </c>
       <c r="J26" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>네이버 검색 당일 +437% / 중요공시 2건 / 중요공시 3일 +100%</t>
         </is>
       </c>
       <c r="K26" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B27" s="20" t="n">
@@ -1479,42 +1479,40 @@
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>모아데이타</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D27" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E27" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F27" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H27" s="22" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="I27" s="22" t="n">
-        <v>-13.01</v>
+        <v>0</v>
+      </c>
+      <c r="H27" s="24" t="n">
+        <v>-5.15</v>
+      </c>
+      <c r="I27" s="24" t="n">
+        <v>-2.64</v>
       </c>
       <c r="J27" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 7일 +50%</t>
-        </is>
-      </c>
-      <c r="K27" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K27" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B28" s="20" t="n">
@@ -1522,30 +1520,30 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>아리바이오홀딩스</t>
+          <t>모아데이타</t>
         </is>
       </c>
       <c r="D28" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E28" s="20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G28" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="H28" s="22" t="n">
-        <v>-2.23</v>
-      </c>
-      <c r="I28" s="22" t="n">
-        <v>-22.77</v>
+      <c r="H28" s="24" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="I28" s="24" t="n">
+        <v>-1.83</v>
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
+          <t>중요공시 3건 / 중요공시 7일 +50%</t>
         </is>
       </c>
       <c r="K28" s="23" t="inlineStr">
@@ -1557,7 +1555,7 @@
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B29" s="20" t="n">
@@ -1565,42 +1563,42 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>선도전기</t>
+          <t>머큐리</t>
         </is>
       </c>
       <c r="D29" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29" s="20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F29" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G29" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H29" s="22" t="n">
-        <v>-1.82</v>
+        <v>29.8</v>
       </c>
       <c r="I29" s="22" t="n">
-        <v>-4.44</v>
+        <v>28.21</v>
       </c>
       <c r="J29" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
+          <t>네이버 검색 당일 +69% / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K29" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1608,40 +1606,42 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I30" s="20" t="n">
-        <v/>
+      <c r="H30" s="22" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="I30" s="22" t="n">
+        <v>9.84</v>
       </c>
       <c r="J30" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="n">
-        <v/>
+          <t>네이버 검색 당일 +67% / 중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1649,42 +1649,42 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>더코디</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
         <v>5</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F31" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="22" t="n">
-        <v>-1.27</v>
+      <c r="H31" s="24" t="n">
+        <v>-1.09</v>
       </c>
       <c r="I31" s="22" t="n">
-        <v>-2.96</v>
+        <v>0.37</v>
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>중요공시 6건 / 중요공시 3일 +100%</t>
+          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K31" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1692,42 +1692,42 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>에이전트AI</t>
+          <t>퀀텀레일</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G32" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="22" t="n">
-        <v>-2.34</v>
-      </c>
-      <c r="I32" s="22" t="n">
-        <v>-39.85</v>
+      <c r="H32" s="24" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="I32" s="24" t="n">
+        <v>-51.68</v>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>중요공시 5건 / 중요공시 3일 +400%</t>
+          <t>네이버 검색 당일 +1711% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1735,14 +1735,14 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>나인테크</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>0</v>
@@ -1750,27 +1750,27 @@
       <c r="G33" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="I33" s="24" t="n">
-        <v>5.06</v>
+      <c r="H33" s="22" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I33" s="22" t="n">
+        <v>28.05</v>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>네이버 검색 당일 +437% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K33" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1778,14 +1778,14 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>한국파마</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>0</v>
@@ -1793,27 +1793,27 @@
       <c r="G34" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="24" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="I34" s="24" t="n">
-        <v>11.24</v>
+      <c r="H34" s="22" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="I34" s="22" t="n">
+        <v>19.06</v>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>네이버 검색 당일 +202% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K34" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1821,14 +1821,14 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>에코프로머티</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F35" s="20" t="n">
         <v>0</v>
@@ -1836,27 +1836,27 @@
       <c r="G35" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I35" s="24" t="n">
-        <v>8.99</v>
+      <c r="H35" s="22" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="I35" s="22" t="n">
+        <v>5.4</v>
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>네이버 검색 당일 +156% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K35" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1864,14 +1864,14 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>에코프로에이치엔</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>0</v>
@@ -1879,27 +1879,27 @@
       <c r="G36" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I36" s="24" t="n">
-        <v>13.73</v>
+      <c r="H36" s="22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I36" s="22" t="n">
+        <v>19.41</v>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>네이버 검색 당일 +111% / 중요공시 2건</t>
         </is>
       </c>
       <c r="K36" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1907,14 +1907,14 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>에코프로비엠</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F37" s="20" t="n">
         <v>0</v>
@@ -1922,27 +1922,27 @@
       <c r="G37" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="24" t="n">
-        <v>1.58</v>
+      <c r="H37" s="22" t="n">
+        <v>0.91</v>
       </c>
       <c r="I37" s="24" t="n">
-        <v>9.57</v>
+        <v>-1.14</v>
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>네이버 검색 당일 +53% / 중요공시 2건 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K37" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1950,14 +1950,14 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F38" s="20" t="n">
         <v>0</v>
@@ -1965,25 +1965,27 @@
       <c r="G38" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="I38" s="24" t="n">
-        <v>2.38</v>
+      <c r="H38" s="22" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="I38" s="22" t="n">
+        <v>27.13</v>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K38" s="23" t="n">
-        <v/>
+          <t>네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1991,7 +1993,7 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>퀀텀레일</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
@@ -2007,26 +2009,26 @@
         <v>0</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>-1.63</v>
+        <v>11.65</v>
       </c>
       <c r="I39" s="22" t="n">
-        <v>-58.04</v>
+        <v>26.1</v>
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1443% / 중요공시 1건</t>
+          <t>네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K39" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2034,7 +2036,7 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>나인테크</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
@@ -2049,27 +2051,27 @@
       <c r="G40" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="24" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="I40" s="24" t="n">
-        <v>29.52</v>
+      <c r="H40" s="22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I40" s="22" t="n">
+        <v>1.19</v>
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +364% / 중요공시 1건</t>
+          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2077,42 +2079,42 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>세미파이브</t>
+          <t>에이에프더블류</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E41" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F41" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>1.72</v>
+        <v>-5.13</v>
       </c>
       <c r="I41" s="24" t="n">
-        <v>27.38</v>
+        <v>-51.32</v>
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +344% / 중요공시 2건</t>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K41" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -2120,42 +2122,42 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>아리바이오홀딩스</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E42" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F42" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>5.71</v>
+        <v>-2.23</v>
       </c>
       <c r="I42" s="24" t="n">
-        <v>22.79</v>
+        <v>-22.96</v>
       </c>
       <c r="J42" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +110% / 중요공시 1건</t>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K42" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B43" s="20" t="n">
@@ -2163,30 +2165,30 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>한화생명</t>
+          <t>선도전기</t>
         </is>
       </c>
       <c r="D43" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E43" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F43" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I43" s="22" t="n">
-        <v>-6.34</v>
+        <v>-1.82</v>
+      </c>
+      <c r="I43" s="24" t="n">
+        <v>-1.82</v>
       </c>
       <c r="J43" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K43" s="23" t="inlineStr">
@@ -2198,7 +2200,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B44" s="20" t="n">
@@ -2206,30 +2208,30 @@
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="D44" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E44" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G44" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>6.47</v>
+        <v>-5.03</v>
       </c>
       <c r="I44" s="24" t="n">
-        <v>11.41</v>
+        <v>-5.88</v>
       </c>
       <c r="J44" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K44" s="23" t="inlineStr">
@@ -2241,7 +2243,7 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B45" s="20" t="n">
@@ -2249,30 +2251,30 @@
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="D45" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E45" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F45" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H45" s="22" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="I45" s="22" t="n">
-        <v>-1.57</v>
+        <v>0.13</v>
+      </c>
+      <c r="I45" s="24" t="n">
+        <v>-2.24</v>
       </c>
       <c r="J45" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K45" s="23" t="inlineStr">
@@ -2284,7 +2286,7 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B46" s="20" t="n">
@@ -2292,30 +2294,30 @@
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>한창</t>
+          <t>광진실업</t>
         </is>
       </c>
       <c r="D46" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E46" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F46" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>-91.06999999999999</v>
-      </c>
-      <c r="I46" s="22" t="n">
-        <v>-91.06999999999999</v>
+        <v>0.49</v>
+      </c>
+      <c r="I46" s="24" t="n">
+        <v>-18.6</v>
       </c>
       <c r="J46" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K46" s="23" t="inlineStr">
@@ -2327,7 +2329,7 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B47" s="20" t="n">
@@ -2335,7 +2337,7 @@
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>미래산업</t>
         </is>
       </c>
       <c r="D47" s="20" t="n">
@@ -2350,11 +2352,11 @@
       <c r="G47" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="H47" s="24" t="n">
-        <v>0.13</v>
+      <c r="H47" s="22" t="n">
+        <v>0.6</v>
       </c>
       <c r="I47" s="22" t="n">
-        <v>-2.48</v>
+        <v>16.62</v>
       </c>
       <c r="J47" s="23" t="inlineStr">
         <is>
@@ -2370,7 +2372,7 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B48" s="20" t="n">
@@ -2378,42 +2380,42 @@
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>미래산업</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="D48" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E48" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F48" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H48" s="24" t="n">
-        <v>0.6</v>
+        <v>0</v>
+      </c>
+      <c r="H48" s="22" t="n">
+        <v>7.23</v>
       </c>
       <c r="I48" s="24" t="n">
-        <v>28.07</v>
+        <v>-4.78</v>
       </c>
       <c r="J48" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K48" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B49" s="20" t="n">
@@ -2421,7 +2423,7 @@
       </c>
       <c r="C49" s="21" t="inlineStr">
         <is>
-          <t>일진전기</t>
+          <t>에스제이그룹</t>
         </is>
       </c>
       <c r="D49" s="20" t="n">
@@ -2436,11 +2438,11 @@
       <c r="G49" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="24" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="I49" s="24" t="n">
-        <v>5.13</v>
+      <c r="H49" s="22" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="I49" s="22" t="n">
+        <v>30.39</v>
       </c>
       <c r="J49" s="23" t="inlineStr">
         <is>
@@ -2456,7 +2458,7 @@
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B50" s="20" t="n">
@@ -2464,7 +2466,7 @@
       </c>
       <c r="C50" s="21" t="inlineStr">
         <is>
-          <t>씨싸이트</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="D50" s="20" t="n">
@@ -2479,27 +2481,25 @@
       <c r="G50" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="22" t="n">
-        <v>-4.62</v>
-      </c>
-      <c r="I50" s="24" t="n">
-        <v>52.19</v>
+      <c r="H50" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I50" s="20" t="n">
+        <v/>
       </c>
       <c r="J50" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K50" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K50" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B51" s="20" t="n">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="C51" s="21" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="D51" s="20" t="n">
@@ -2522,27 +2522,25 @@
       <c r="G51" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="24" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="I51" s="22" t="n">
-        <v>-0.77</v>
+      <c r="H51" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I51" s="20" t="n">
+        <v/>
       </c>
       <c r="J51" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K51" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K51" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B52" s="20" t="n">
@@ -2550,7 +2548,7 @@
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="D52" s="20" t="n">
@@ -2565,15 +2563,15 @@
       <c r="G52" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="22" t="n">
-        <v>-2.58</v>
+      <c r="H52" s="24" t="n">
+        <v>-2.22</v>
       </c>
       <c r="I52" s="24" t="n">
-        <v>6.76</v>
+        <v>-6.9</v>
       </c>
       <c r="J52" s="23" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K52" s="23" t="n">
@@ -2581,132 +2579,138 @@
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="20" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B53" s="20" t="n">
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B53" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="C53" s="21" t="inlineStr">
-        <is>
-          <t>전기차</t>
-        </is>
-      </c>
-      <c r="D53" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E53" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F53" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I53" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J53" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K53" s="23" t="n">
-        <v/>
+      <c r="C53" s="26" t="inlineStr">
+        <is>
+          <t>브릴스</t>
+        </is>
+      </c>
+      <c r="D53" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="27" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="I53" s="27" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="J53" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +2242%</t>
+        </is>
+      </c>
+      <c r="K53" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="20" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B54" s="20" t="n">
+      <c r="A54" s="25" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B54" s="25" t="n">
         <v>41</v>
       </c>
-      <c r="C54" s="21" t="inlineStr">
-        <is>
-          <t>스테이블코인</t>
-        </is>
-      </c>
-      <c r="D54" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E54" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F54" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I54" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J54" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K54" s="23" t="n">
-        <v/>
+      <c r="C54" s="26" t="inlineStr">
+        <is>
+          <t>현대바이오랜드</t>
+        </is>
+      </c>
+      <c r="D54" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="29" t="n">
+        <v>-3.29</v>
+      </c>
+      <c r="I54" s="27" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="J54" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +1609%</t>
+        </is>
+      </c>
+      <c r="K54" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="20" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B55" s="20" t="n">
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B55" s="25" t="n">
         <v>42</v>
       </c>
-      <c r="C55" s="21" t="inlineStr">
-        <is>
-          <t>NH투자증권</t>
-        </is>
-      </c>
-      <c r="D55" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E55" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F55" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I55" s="24" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="J55" s="23" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K55" s="23" t="n">
-        <v/>
+      <c r="C55" s="26" t="inlineStr">
+        <is>
+          <t>코스모로보틱스</t>
+        </is>
+      </c>
+      <c r="D55" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="29" t="n">
+        <v>-8.460000000000001</v>
+      </c>
+      <c r="I55" s="29" t="n">
+        <v>-30.64</v>
+      </c>
+      <c r="J55" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +1375%</t>
+        </is>
+      </c>
+      <c r="K55" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2714,7 +2718,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2729,15 +2733,15 @@
       <c r="G56" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="27" t="n">
-        <v>9.81</v>
+      <c r="H56" s="29" t="n">
+        <v>-8.550000000000001</v>
       </c>
       <c r="I56" s="27" t="n">
-        <v>9.81</v>
+        <v>2.48</v>
       </c>
       <c r="J56" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1597%</t>
+          <t>네이버 검색 당일 +1355%</t>
         </is>
       </c>
       <c r="K56" s="28" t="inlineStr">
@@ -2749,7 +2753,7 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2757,7 +2761,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>현대바이오랜드</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2773,14 +2777,14 @@
         <v>0</v>
       </c>
       <c r="H57" s="29" t="n">
-        <v>-3.29</v>
-      </c>
-      <c r="I57" s="27" t="n">
-        <v>23.76</v>
+        <v>-1.75</v>
+      </c>
+      <c r="I57" s="29" t="n">
+        <v>-3.09</v>
       </c>
       <c r="J57" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1461%</t>
+          <t>네이버 검색 당일 +1294%</t>
         </is>
       </c>
       <c r="K57" s="28" t="inlineStr">
@@ -2792,7 +2796,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2800,7 +2804,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2815,15 +2819,15 @@
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="29" t="n">
-        <v>-8.550000000000001</v>
+      <c r="H58" s="27" t="n">
+        <v>2.75</v>
       </c>
       <c r="I58" s="27" t="n">
-        <v>2.48</v>
+        <v>17.38</v>
       </c>
       <c r="J58" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1238%</t>
+          <t>네이버 검색 당일 +1242%</t>
         </is>
       </c>
       <c r="K58" s="28" t="inlineStr">
@@ -2835,7 +2839,7 @@
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2843,7 +2847,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>코스모로보틱스</t>
+          <t>덕우전자</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2858,15 +2862,15 @@
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="29" t="n">
-        <v>-8.460000000000001</v>
-      </c>
-      <c r="I59" s="29" t="n">
-        <v>-30.94</v>
+      <c r="H59" s="27" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="I59" s="27" t="n">
+        <v>53.62</v>
       </c>
       <c r="J59" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1174%</t>
+          <t>네이버 검색 당일 +975%</t>
         </is>
       </c>
       <c r="K59" s="28" t="inlineStr">
@@ -2878,7 +2882,7 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2886,7 +2890,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>부산주공</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2902,14 +2906,14 @@
         <v>0</v>
       </c>
       <c r="H60" s="29" t="n">
-        <v>-1.75</v>
+        <v>-32.5</v>
       </c>
       <c r="I60" s="29" t="n">
-        <v>-3.09</v>
+        <v>-94.44</v>
       </c>
       <c r="J60" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1124%</t>
+          <t>네이버 검색 당일 +721%</t>
         </is>
       </c>
       <c r="K60" s="28" t="inlineStr">
@@ -2921,7 +2925,7 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2929,7 +2933,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>원일티엔아이</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2945,14 +2949,14 @@
         <v>0</v>
       </c>
       <c r="H61" s="27" t="n">
-        <v>2.75</v>
+        <v>18.34</v>
       </c>
       <c r="I61" s="27" t="n">
-        <v>17.38</v>
+        <v>54.33</v>
       </c>
       <c r="J61" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1117%</t>
+          <t>네이버 검색 당일 +596%</t>
         </is>
       </c>
       <c r="K61" s="28" t="inlineStr">
@@ -2964,7 +2968,7 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2972,7 +2976,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>부산주공</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2988,14 +2992,14 @@
         <v>0</v>
       </c>
       <c r="H62" s="29" t="n">
-        <v>-32.5</v>
-      </c>
-      <c r="I62" s="29" t="n">
-        <v>-94.44</v>
+        <v>-4.36</v>
+      </c>
+      <c r="I62" s="27" t="n">
+        <v>16.03</v>
       </c>
       <c r="J62" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +582%</t>
+          <t>네이버 검색 당일 +515%</t>
         </is>
       </c>
       <c r="K62" s="28" t="inlineStr">
@@ -3007,7 +3011,7 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3015,7 +3019,7 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>윈팩</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
@@ -3030,15 +3034,15 @@
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="29" t="n">
-        <v>-4.36</v>
+      <c r="H63" s="27" t="n">
+        <v>4.95</v>
       </c>
       <c r="I63" s="27" t="n">
-        <v>18.86</v>
+        <v>72.38</v>
       </c>
       <c r="J63" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +409%</t>
+          <t>네이버 검색 당일 +448%</t>
         </is>
       </c>
       <c r="K63" s="28" t="inlineStr">
@@ -3140,22 +3144,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3171,29 +3175,29 @@
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.55</v>
       </c>
-      <c r="I4" s="29" t="n">
-        <v>-3.66</v>
+      <c r="I4" s="27" t="n">
+        <v>2.22</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -3206,22 +3210,22 @@
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H5" s="25" t="n"/>
@@ -3237,29 +3241,29 @@
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H6" s="29" t="n">
         <v>-0.57</v>
       </c>
       <c r="I6" s="29" t="n">
-        <v>-2.8</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -3272,22 +3276,22 @@
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H7" s="25" t="n"/>
@@ -3296,29 +3300,29 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H8" s="25" t="n"/>
@@ -3327,29 +3331,29 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H9" s="25" t="n"/>
@@ -3358,7 +3362,7 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
@@ -3375,51 +3379,51 @@
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="H10" s="27" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I10" s="29" t="n">
-        <v>-1.13</v>
-      </c>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="H10" s="25" t="n"/>
+      <c r="I10" s="25" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="H11" s="25" t="n"/>
-      <c r="I11" s="25" t="n"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>4.6</v>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
@@ -3441,25 +3445,25 @@
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H12" s="27" t="n">
         <v>0.84</v>
       </c>
       <c r="I12" s="29" t="n">
-        <v>-3.53</v>
+        <v>-4.11</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>에스제이그룹</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -3476,60 +3480,56 @@
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="H13" s="27" t="n">
-        <v>29.96</v>
-      </c>
-      <c r="I13" s="27" t="n">
-        <v>26.45</v>
-      </c>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="H13" s="25" t="n"/>
+      <c r="I13" s="25" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>한창</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H14" s="29" t="n">
-        <v>-5.15</v>
+        <v>-91.06999999999999</v>
       </c>
       <c r="I14" s="29" t="n">
-        <v>-8.68</v>
+        <v>-91.06999999999999</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>모아데이타</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -3546,25 +3546,25 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H15" s="29" t="n">
-        <v>-3.6</v>
+        <v>-5.15</v>
       </c>
       <c r="I15" s="29" t="n">
-        <v>-13.01</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>선도전기</t>
+          <t>모아데이타</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H16" s="29" t="n">
-        <v>-1.82</v>
+        <v>-3.6</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>-4.44</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>아리바이오홀딩스</t>
+          <t>세미파이브</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -3616,91 +3616,95 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="H17" s="29" t="n">
-        <v>-2.23</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>-22.77</v>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I17" s="27" t="n">
+        <v>28.88</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="H18" s="25" t="n"/>
-      <c r="I18" s="25" t="n"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="H18" s="29" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="I18" s="27" t="n">
+        <v>0.37</v>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>티엠씨</t>
+          <t>머큐리</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H19" s="27" t="n">
-        <v>29.68</v>
+        <v>29.8</v>
       </c>
       <c r="I19" s="27" t="n">
-        <v>28.86</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -3717,270 +3721,270 @@
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H20" s="27" t="n">
-        <v>1.65</v>
+        <v>6.47</v>
       </c>
       <c r="I20" s="27" t="n">
-        <v>2.38</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>